--- a/pm_dashboards/Project Management Charts.xlsx
+++ b/pm_dashboards/Project Management Charts.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vishvambruth_Javagal\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\excel_tutorial\pm_dashboards\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4558EC85-C711-4A96-BD5F-1624106E2D84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DF229A9-E7AE-481E-9370-A14F1E0D639E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="412" xr2:uid="{6ACA091F-59E3-41E7-B925-EA720AB063CF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="412" xr2:uid="{6ACA091F-59E3-41E7-B925-EA720AB063CF}"/>
   </bookViews>
   <sheets>
     <sheet name="Gantt Chart" sheetId="1" r:id="rId1"/>
+    <sheet name="RACI" sheetId="4" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="70">
   <si>
     <t>Project Start Date:</t>
   </si>
@@ -164,6 +165,244 @@
 • The length of the bar represents the task duration
 • Colors often indicate task status (completed, in progress, blocked, not started)
 Gantt charts help project managers and teams see the entire project timeline at a glance, identify task dependencies, track progress, and ensure deadlines are met.</t>
+  </si>
+  <si>
+    <t>R</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>Deliverables</t>
+  </si>
+  <si>
+    <t>RACI - Resource Assignment Matrix</t>
+  </si>
+  <si>
+    <t>Project Manager:</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> R</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> - Responsible - who performs the task </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>A</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> - Accountable - who signs off </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> - Consulted - who provides expert judgement </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>u</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>I</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> - who is kept informed</t>
+    </r>
+  </si>
+  <si>
+    <t>Task or deliverable</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Project Role</t>
+  </si>
+  <si>
+    <t>Jones</t>
+  </si>
+  <si>
+    <t>Billy</t>
+  </si>
+  <si>
+    <t>Tommy</t>
+  </si>
+  <si>
+    <t>Anne</t>
+  </si>
+  <si>
+    <t>Project manager</t>
+  </si>
+  <si>
+    <t>Business Analyst</t>
+  </si>
+  <si>
+    <t>Executive Sponser</t>
+  </si>
+  <si>
+    <t>Developer</t>
+  </si>
+  <si>
+    <t>R - Responsible - who performs the task</t>
+  </si>
+  <si>
+    <t>A - Accountable - who signs off</t>
+  </si>
+  <si>
+    <t>C - Consulted - who provides expert judgement</t>
+  </si>
+  <si>
+    <t>I - who is kept informed</t>
+  </si>
+  <si>
+    <t>What is a RACI Matrix?</t>
+  </si>
+  <si>
+    <t>A RACI Matrix (also called a Responsibility Assignment Matrix) is a project management tool used to clarify roles and responsibilities for tasks and deliverables.</t>
+  </si>
+  <si>
+    <t>• R - Responsible: The person who performs the work to complete the task. There can be multiple people responsible.</t>
+  </si>
+  <si>
+    <t>• A - Accountable: The person who is ultimately answerable for the task's completion. There should be only ONE accountable person per task.</t>
+  </si>
+  <si>
+    <t>• C - Consulted: People who provide input and expertise before or during the task. Communication is two-way.</t>
+  </si>
+  <si>
+    <t>• I - Informed: People who need to be kept updated on progress or decisions. Communication is one-way.</t>
+  </si>
+  <si>
+    <t>Benefits: Eliminates confusion about roles, prevents tasks from falling through the cracks, ensures proper communication, and helps identify overloaded team members.</t>
   </si>
 </sst>
 </file>
@@ -175,7 +414,7 @@
     <numFmt numFmtId="165" formatCode="mmm"/>
     <numFmt numFmtId="166" formatCode="yyyy"/>
   </numFmts>
-  <fonts count="31" x14ac:knownFonts="1">
+  <fonts count="43">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -400,8 +639,91 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="20"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Wingdings"/>
+      <charset val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="5"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Wingdings"/>
+      <charset val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1" tint="0.499984740745262"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -498,8 +820,44 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF053C4F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99DC7E"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="51">
+  <borders count="78">
     <border>
       <left/>
       <right/>
@@ -1093,28 +1451,376 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="dotted">
+        <color theme="1" tint="0.34998626667073579"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="dotted">
+        <color theme="1" tint="0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color theme="1" tint="0.34998626667073579"/>
+      </left>
+      <right style="dotted">
+        <color theme="1" tint="0.34998626667073579"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="dotted">
+        <color theme="1" tint="0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="dotted">
+        <color theme="1" tint="0.34998626667073579"/>
+      </right>
+      <top style="dotted">
+        <color theme="1" tint="0.34998626667073579"/>
+      </top>
+      <bottom style="dotted">
+        <color theme="1" tint="0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color theme="1" tint="0.34998626667073579"/>
+      </left>
+      <right style="dotted">
+        <color theme="1" tint="0.34998626667073579"/>
+      </right>
+      <top style="dotted">
+        <color theme="1" tint="0.34998626667073579"/>
+      </top>
+      <bottom style="dotted">
+        <color theme="1" tint="0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color theme="1" tint="0.34998626667073579"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="dotted">
+        <color theme="1" tint="0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color theme="1" tint="0.34998626667073579"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="dotted">
+        <color theme="1" tint="0.34998626667073579"/>
+      </top>
+      <bottom style="dotted">
+        <color theme="1" tint="0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="dotted">
+        <color theme="1" tint="0.34998626667073579"/>
+      </right>
+      <top style="dotted">
+        <color theme="1" tint="0.34998626667073579"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color theme="1" tint="0.34998626667073579"/>
+      </left>
+      <right style="dotted">
+        <color theme="1" tint="0.34998626667073579"/>
+      </right>
+      <top style="dotted">
+        <color theme="1" tint="0.34998626667073579"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color theme="1" tint="0.34998626667073579"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="dotted">
+        <color theme="1" tint="0.34998626667073579"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color theme="0"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="0"/>
+      </left>
+      <right style="medium">
+        <color theme="0"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="0"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="dotted">
+        <color indexed="64"/>
+      </right>
+      <top style="dotted">
+        <color indexed="64"/>
+      </top>
+      <bottom style="dotted">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color indexed="64"/>
+      </left>
+      <right style="dotted">
+        <color indexed="64"/>
+      </right>
+      <top style="dotted">
+        <color indexed="64"/>
+      </top>
+      <bottom style="dotted">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="dotted">
+        <color indexed="64"/>
+      </top>
+      <bottom style="dotted">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="155">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
@@ -1205,13 +1911,7 @@
     <xf numFmtId="0" fontId="10" fillId="8" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1219,10 +1919,10 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1240,7 +1940,6 @@
     <xf numFmtId="16" fontId="8" fillId="6" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="23" fillId="13" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1289,7 +1988,7 @@
     <xf numFmtId="0" fontId="26" fillId="13" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="40" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="43" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="41" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1308,19 +2007,19 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="45" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="14" fillId="9" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="14" fillId="9" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="9" fontId="14" fillId="9" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="14" fillId="9" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="9" fontId="15" fillId="10" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="15" fillId="10" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="9" fontId="16" fillId="11" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="16" fillId="11" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="9" fontId="17" fillId="12" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="17" fillId="12" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="9" fontId="17" fillId="12" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1332,6 +2031,125 @@
     <xf numFmtId="0" fontId="7" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="8" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="31" fillId="19" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="19" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="19" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="32" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="16" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1344,69 +2162,161 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="46" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="19" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="19" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="19" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="19" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="19" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="8" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="19" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="62" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="64" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="74" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="75" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="77" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="12">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF89"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFD653"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF89"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFD653"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <border>
         <left style="thin">
@@ -1441,16 +2351,16 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
-      <color rgb="FF5DAEFF"/>
-      <color rgb="FF4FA7FF"/>
-      <color rgb="FF99CCFF"/>
-      <color rgb="FF00E3DE"/>
-      <color rgb="FFABFFFF"/>
-      <color rgb="FFCCFFFF"/>
-      <color rgb="FFC5F1F0"/>
-      <color rgb="FF00AAD2"/>
-      <color rgb="FF00CCFF"/>
-      <color rgb="FF00C9C4"/>
+      <color rgb="FFFFD653"/>
+      <color rgb="FFFFFF89"/>
+      <color rgb="FFFFD13F"/>
+      <color rgb="FFC5DCF3"/>
+      <color rgb="FFFFFF75"/>
+      <color rgb="FF99DC7E"/>
+      <color rgb="FFA0E8AA"/>
+      <color rgb="FF32CE48"/>
+      <color rgb="FF27A138"/>
+      <color rgb="FF053C4F"/>
     </mruColors>
   </colors>
   <extLst>
@@ -1786,2311 +2696,2231 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{573ED8A0-1950-4B36-ACCF-F2686D23D643}">
   <dimension ref="B1:AR30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" customWidth="1"/>
-    <col min="2" max="2" width="5.7109375" customWidth="1"/>
-    <col min="3" max="3" width="41.85546875" customWidth="1"/>
-    <col min="4" max="4" width="22.85546875" customWidth="1"/>
-    <col min="5" max="6" width="16.140625" customWidth="1"/>
-    <col min="7" max="7" width="8.5703125" customWidth="1"/>
-    <col min="8" max="8" width="16.140625" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="44" width="4.7109375" customWidth="1"/>
+    <col min="1" max="1" width="2.81640625" customWidth="1"/>
+    <col min="2" max="2" width="5.7265625" customWidth="1"/>
+    <col min="3" max="3" width="41.81640625" customWidth="1"/>
+    <col min="4" max="4" width="22.81640625" customWidth="1"/>
+    <col min="5" max="6" width="16.1796875" customWidth="1"/>
+    <col min="7" max="7" width="8.54296875" customWidth="1"/>
+    <col min="8" max="8" width="16.1796875" customWidth="1"/>
+    <col min="9" max="9" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="44" width="4.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:44" ht="40.5" x14ac:dyDescent="0.25">
-      <c r="B1" s="36" t="s">
+    <row r="1" spans="2:44" ht="39.5">
+      <c r="B1" s="118" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="37"/>
-      <c r="M1" s="37"/>
-      <c r="N1" s="37"/>
-      <c r="O1" s="37"/>
-      <c r="P1" s="37"/>
-      <c r="Q1" s="37"/>
-      <c r="R1" s="37"/>
-      <c r="S1" s="37"/>
-      <c r="T1" s="37"/>
-      <c r="U1" s="37"/>
-      <c r="V1" s="37"/>
-      <c r="W1" s="37"/>
-      <c r="X1" s="37"/>
-      <c r="Y1" s="37"/>
-      <c r="Z1" s="37"/>
-      <c r="AA1" s="37"/>
-      <c r="AB1" s="37"/>
-      <c r="AC1" s="37"/>
-      <c r="AD1" s="37"/>
-      <c r="AE1" s="37"/>
-      <c r="AF1" s="37"/>
-      <c r="AG1" s="37"/>
-      <c r="AH1" s="37"/>
-      <c r="AI1" s="37"/>
-      <c r="AJ1" s="37"/>
-      <c r="AK1" s="37"/>
-      <c r="AL1" s="37"/>
-      <c r="AM1" s="37"/>
-      <c r="AN1" s="37"/>
-      <c r="AO1" s="37"/>
-      <c r="AP1" s="37"/>
-      <c r="AQ1" s="37"/>
-      <c r="AR1" s="37"/>
+      <c r="C1" s="118"/>
+      <c r="D1" s="118"/>
+      <c r="E1" s="118"/>
+      <c r="F1" s="118"/>
+      <c r="G1" s="118"/>
+      <c r="H1" s="118"/>
+      <c r="I1" s="118"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
+      <c r="P1" s="31"/>
+      <c r="Q1" s="31"/>
+      <c r="R1" s="31"/>
+      <c r="S1" s="31"/>
+      <c r="T1" s="31"/>
+      <c r="U1" s="31"/>
+      <c r="V1" s="31"/>
+      <c r="W1" s="31"/>
+      <c r="X1" s="31"/>
+      <c r="Y1" s="31"/>
+      <c r="Z1" s="31"/>
+      <c r="AA1" s="31"/>
+      <c r="AB1" s="31"/>
+      <c r="AC1" s="31"/>
+      <c r="AD1" s="31"/>
+      <c r="AE1" s="31"/>
+      <c r="AF1" s="31"/>
+      <c r="AG1" s="31"/>
+      <c r="AH1" s="31"/>
+      <c r="AI1" s="31"/>
+      <c r="AJ1" s="31"/>
+      <c r="AK1" s="31"/>
+      <c r="AL1" s="31"/>
+      <c r="AM1" s="31"/>
+      <c r="AN1" s="31"/>
+      <c r="AO1" s="31"/>
+      <c r="AP1" s="31"/>
+      <c r="AQ1" s="31"/>
+      <c r="AR1" s="31"/>
     </row>
-    <row r="2" spans="2:44" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="38" t="s">
+    <row r="2" spans="2:44" ht="17" thickBot="1">
+      <c r="B2" s="119" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="39"/>
-      <c r="K2" s="39"/>
-      <c r="L2" s="39"/>
-      <c r="M2" s="39"/>
-      <c r="N2" s="39"/>
-      <c r="O2" s="39"/>
-      <c r="P2" s="39"/>
-      <c r="Q2" s="39"/>
-      <c r="R2" s="39"/>
-      <c r="S2" s="39"/>
-      <c r="T2" s="39"/>
-      <c r="U2" s="39"/>
-      <c r="V2" s="39"/>
-      <c r="W2" s="39"/>
-      <c r="X2" s="39"/>
-      <c r="Y2" s="39"/>
-      <c r="Z2" s="39"/>
-      <c r="AA2" s="39"/>
-      <c r="AB2" s="39"/>
-      <c r="AC2" s="39"/>
-      <c r="AD2" s="39"/>
-      <c r="AE2" s="39"/>
-      <c r="AF2" s="39"/>
-      <c r="AG2" s="39"/>
-      <c r="AH2" s="39"/>
-      <c r="AI2" s="39"/>
-      <c r="AJ2" s="39"/>
-      <c r="AK2" s="39"/>
-      <c r="AL2" s="39"/>
-      <c r="AM2" s="39"/>
-      <c r="AN2" s="39"/>
-      <c r="AO2" s="39"/>
-      <c r="AP2" s="39"/>
-      <c r="AQ2" s="39"/>
-      <c r="AR2" s="39"/>
+      <c r="C2" s="119"/>
+      <c r="D2" s="119"/>
+      <c r="E2" s="119"/>
+      <c r="F2" s="119"/>
+      <c r="G2" s="119"/>
+      <c r="H2" s="119"/>
+      <c r="I2" s="119"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="32"/>
+      <c r="Q2" s="32"/>
+      <c r="R2" s="32"/>
+      <c r="S2" s="32"/>
+      <c r="T2" s="32"/>
+      <c r="U2" s="32"/>
+      <c r="V2" s="32"/>
+      <c r="W2" s="32"/>
+      <c r="X2" s="32"/>
+      <c r="Y2" s="32"/>
+      <c r="Z2" s="32"/>
+      <c r="AA2" s="32"/>
+      <c r="AB2" s="32"/>
+      <c r="AC2" s="32"/>
+      <c r="AD2" s="32"/>
+      <c r="AE2" s="32"/>
+      <c r="AF2" s="32"/>
+      <c r="AG2" s="32"/>
+      <c r="AH2" s="32"/>
+      <c r="AI2" s="32"/>
+      <c r="AJ2" s="32"/>
+      <c r="AK2" s="32"/>
+      <c r="AL2" s="32"/>
+      <c r="AM2" s="32"/>
+      <c r="AN2" s="32"/>
+      <c r="AO2" s="32"/>
+      <c r="AP2" s="32"/>
+      <c r="AQ2" s="32"/>
+      <c r="AR2" s="32"/>
     </row>
-    <row r="3" spans="2:44" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B3" s="87"/>
-      <c r="C3" s="88"/>
-      <c r="D3" s="88"/>
-      <c r="E3" s="88"/>
-      <c r="F3" s="88"/>
-      <c r="G3" s="88"/>
-      <c r="H3" s="88"/>
-      <c r="I3" s="88"/>
-      <c r="J3" s="1">
+    <row r="3" spans="2:44" ht="18.5">
+      <c r="B3" s="120"/>
+      <c r="C3" s="121"/>
+      <c r="D3" s="121"/>
+      <c r="E3" s="121"/>
+      <c r="F3" s="121"/>
+      <c r="G3" s="121"/>
+      <c r="H3" s="121"/>
+      <c r="I3" s="121"/>
+      <c r="J3" s="104">
         <f ca="1">K5</f>
         <v>46153</v>
       </c>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2"/>
-      <c r="S3" s="2"/>
-      <c r="T3" s="2"/>
-      <c r="U3" s="2"/>
-      <c r="V3" s="2"/>
-      <c r="W3" s="2"/>
-      <c r="X3" s="2"/>
-      <c r="Y3" s="2"/>
-      <c r="Z3" s="2"/>
-      <c r="AA3" s="2"/>
-      <c r="AB3" s="2"/>
-      <c r="AC3" s="2"/>
-      <c r="AD3" s="2"/>
-      <c r="AE3" s="2"/>
-      <c r="AF3" s="2"/>
-      <c r="AG3" s="2"/>
-      <c r="AH3" s="2"/>
-      <c r="AI3" s="2"/>
-      <c r="AJ3" s="2"/>
-      <c r="AK3" s="2"/>
-      <c r="AL3" s="2"/>
-      <c r="AM3" s="2"/>
-      <c r="AN3" s="2"/>
-      <c r="AO3" s="2"/>
-      <c r="AP3" s="2"/>
-      <c r="AQ3" s="2"/>
-      <c r="AR3" s="2"/>
+      <c r="K3" s="104"/>
+      <c r="L3" s="104"/>
+      <c r="M3" s="104"/>
+      <c r="N3" s="105"/>
+      <c r="O3" s="105"/>
+      <c r="P3" s="105"/>
+      <c r="Q3" s="105"/>
+      <c r="R3" s="105"/>
+      <c r="S3" s="105"/>
+      <c r="T3" s="105"/>
+      <c r="U3" s="105"/>
+      <c r="V3" s="105"/>
+      <c r="W3" s="105"/>
+      <c r="X3" s="105"/>
+      <c r="Y3" s="105"/>
+      <c r="Z3" s="105"/>
+      <c r="AA3" s="105"/>
+      <c r="AB3" s="105"/>
+      <c r="AC3" s="105"/>
+      <c r="AD3" s="105"/>
+      <c r="AE3" s="105"/>
+      <c r="AF3" s="105"/>
+      <c r="AG3" s="105"/>
+      <c r="AH3" s="105"/>
+      <c r="AI3" s="105"/>
+      <c r="AJ3" s="105"/>
+      <c r="AK3" s="105"/>
+      <c r="AL3" s="105"/>
+      <c r="AM3" s="105"/>
+      <c r="AN3" s="105"/>
+      <c r="AO3" s="105"/>
+      <c r="AP3" s="105"/>
+      <c r="AQ3" s="105"/>
+      <c r="AR3" s="105"/>
     </row>
-    <row r="4" spans="2:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="89"/>
-      <c r="C4" s="86" t="s">
+    <row r="4" spans="2:44" ht="15" thickBot="1">
+      <c r="B4" s="122"/>
+      <c r="C4" s="78" t="s">
         <v>0</v>
       </c>
-      <c r="D4" s="96">
+      <c r="D4" s="82">
         <f ca="1">IF(MONTH(TODAY()-WEEKDAY(TODAY(),2)+1)&lt;MONTH(TODAY()),(TODAY()-28-DAY(TODAY())+7)-WEEKDAY((TODAY()-DAY(TODAY())+7),2)+1,(TODAY()-DAY(TODAY())+7)-WEEKDAY((TODAY()-DAY(TODAY())+7),2)+1)</f>
         <v>46146</v>
       </c>
-      <c r="E4" s="91"/>
-      <c r="F4" s="91"/>
-      <c r="G4" s="91"/>
-      <c r="H4" s="91"/>
-      <c r="I4" s="92"/>
-      <c r="J4" s="4">
+      <c r="E4" s="124"/>
+      <c r="F4" s="124"/>
+      <c r="G4" s="124"/>
+      <c r="H4" s="124"/>
+      <c r="I4" s="125"/>
+      <c r="J4" s="106">
         <f ca="1">K5</f>
         <v>46153</v>
       </c>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="3">
+      <c r="K4" s="106"/>
+      <c r="L4" s="106"/>
+      <c r="M4" s="106"/>
+      <c r="N4" s="111">
         <f ca="1">O5</f>
         <v>46181</v>
       </c>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4">
+      <c r="O4" s="106"/>
+      <c r="P4" s="106"/>
+      <c r="Q4" s="106"/>
+      <c r="R4" s="106"/>
+      <c r="S4" s="106">
         <f ca="1">T5</f>
         <v>46216</v>
       </c>
-      <c r="T4" s="4"/>
-      <c r="U4" s="4"/>
-      <c r="V4" s="4"/>
-      <c r="W4" s="4">
+      <c r="T4" s="106"/>
+      <c r="U4" s="106"/>
+      <c r="V4" s="106"/>
+      <c r="W4" s="106">
         <f ca="1">X5</f>
         <v>46244</v>
       </c>
-      <c r="X4" s="4"/>
-      <c r="Y4" s="4"/>
-      <c r="Z4" s="4"/>
-      <c r="AA4" s="4"/>
-      <c r="AB4" s="4">
+      <c r="X4" s="106"/>
+      <c r="Y4" s="106"/>
+      <c r="Z4" s="106"/>
+      <c r="AA4" s="106"/>
+      <c r="AB4" s="106">
         <f ca="1">AC5</f>
         <v>46279</v>
       </c>
-      <c r="AC4" s="4"/>
-      <c r="AD4" s="4"/>
-      <c r="AE4" s="4"/>
-      <c r="AF4" s="4">
+      <c r="AC4" s="106"/>
+      <c r="AD4" s="106"/>
+      <c r="AE4" s="106"/>
+      <c r="AF4" s="106">
         <f ca="1">AG5</f>
         <v>46307</v>
       </c>
-      <c r="AG4" s="4"/>
-      <c r="AH4" s="4"/>
-      <c r="AI4" s="4"/>
-      <c r="AJ4" s="4">
+      <c r="AG4" s="106"/>
+      <c r="AH4" s="106"/>
+      <c r="AI4" s="106"/>
+      <c r="AJ4" s="106">
         <f ca="1">AK5</f>
         <v>46335</v>
       </c>
-      <c r="AK4" s="4"/>
-      <c r="AL4" s="4"/>
-      <c r="AM4" s="4"/>
-      <c r="AN4" s="4"/>
-      <c r="AO4" s="4">
+      <c r="AK4" s="106"/>
+      <c r="AL4" s="106"/>
+      <c r="AM4" s="106"/>
+      <c r="AN4" s="106"/>
+      <c r="AO4" s="106">
         <f ca="1">AP5</f>
         <v>46370</v>
       </c>
-      <c r="AP4" s="4"/>
-      <c r="AQ4" s="4"/>
-      <c r="AR4" s="5"/>
+      <c r="AP4" s="106"/>
+      <c r="AQ4" s="106"/>
+      <c r="AR4" s="107"/>
     </row>
-    <row r="5" spans="2:44" ht="33" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="90"/>
-      <c r="C5" s="94" t="s">
+    <row r="5" spans="2:44" ht="32" thickBot="1">
+      <c r="B5" s="123"/>
+      <c r="C5" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="97" t="s">
+      <c r="D5" s="108" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="98"/>
-      <c r="F5" s="98"/>
-      <c r="G5" s="99"/>
-      <c r="H5" s="95"/>
-      <c r="I5" s="93" t="s">
+      <c r="E5" s="109"/>
+      <c r="F5" s="109"/>
+      <c r="G5" s="110"/>
+      <c r="H5" s="81"/>
+      <c r="I5" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="J5" s="48">
+      <c r="J5" s="41">
         <f ca="1">D4</f>
         <v>46146</v>
       </c>
-      <c r="K5" s="49">
+      <c r="K5" s="42">
         <f ca="1">J5+7</f>
         <v>46153</v>
       </c>
-      <c r="L5" s="49">
+      <c r="L5" s="42">
         <f t="shared" ref="L5:AR5" ca="1" si="0">K5+7</f>
         <v>46160</v>
       </c>
-      <c r="M5" s="49">
+      <c r="M5" s="42">
         <f t="shared" ca="1" si="0"/>
         <v>46167</v>
       </c>
-      <c r="N5" s="49">
+      <c r="N5" s="42">
         <f t="shared" ca="1" si="0"/>
         <v>46174</v>
       </c>
-      <c r="O5" s="49">
+      <c r="O5" s="42">
         <f t="shared" ca="1" si="0"/>
         <v>46181</v>
       </c>
-      <c r="P5" s="49">
+      <c r="P5" s="42">
         <f t="shared" ca="1" si="0"/>
         <v>46188</v>
       </c>
-      <c r="Q5" s="49">
+      <c r="Q5" s="42">
         <f t="shared" ca="1" si="0"/>
         <v>46195</v>
       </c>
-      <c r="R5" s="49">
+      <c r="R5" s="42">
         <f t="shared" ca="1" si="0"/>
         <v>46202</v>
       </c>
-      <c r="S5" s="49">
+      <c r="S5" s="42">
         <f t="shared" ca="1" si="0"/>
         <v>46209</v>
       </c>
-      <c r="T5" s="49">
+      <c r="T5" s="42">
         <f t="shared" ca="1" si="0"/>
         <v>46216</v>
       </c>
-      <c r="U5" s="49">
+      <c r="U5" s="42">
         <f t="shared" ca="1" si="0"/>
         <v>46223</v>
       </c>
-      <c r="V5" s="49">
+      <c r="V5" s="42">
         <f t="shared" ca="1" si="0"/>
         <v>46230</v>
       </c>
-      <c r="W5" s="49">
+      <c r="W5" s="42">
         <f t="shared" ca="1" si="0"/>
         <v>46237</v>
       </c>
-      <c r="X5" s="49">
+      <c r="X5" s="42">
         <f t="shared" ca="1" si="0"/>
         <v>46244</v>
       </c>
-      <c r="Y5" s="49">
+      <c r="Y5" s="42">
         <f t="shared" ca="1" si="0"/>
         <v>46251</v>
       </c>
-      <c r="Z5" s="49">
+      <c r="Z5" s="42">
         <f t="shared" ca="1" si="0"/>
         <v>46258</v>
       </c>
-      <c r="AA5" s="49">
+      <c r="AA5" s="42">
         <f t="shared" ca="1" si="0"/>
         <v>46265</v>
       </c>
-      <c r="AB5" s="49">
+      <c r="AB5" s="42">
         <f t="shared" ca="1" si="0"/>
         <v>46272</v>
       </c>
-      <c r="AC5" s="49">
+      <c r="AC5" s="42">
         <f t="shared" ca="1" si="0"/>
         <v>46279</v>
       </c>
-      <c r="AD5" s="49">
+      <c r="AD5" s="42">
         <f t="shared" ca="1" si="0"/>
         <v>46286</v>
       </c>
-      <c r="AE5" s="49">
+      <c r="AE5" s="42">
         <f t="shared" ca="1" si="0"/>
         <v>46293</v>
       </c>
-      <c r="AF5" s="49">
+      <c r="AF5" s="42">
         <f t="shared" ca="1" si="0"/>
         <v>46300</v>
       </c>
-      <c r="AG5" s="49">
+      <c r="AG5" s="42">
         <f t="shared" ca="1" si="0"/>
         <v>46307</v>
       </c>
-      <c r="AH5" s="49">
+      <c r="AH5" s="42">
         <f t="shared" ca="1" si="0"/>
         <v>46314</v>
       </c>
-      <c r="AI5" s="49">
+      <c r="AI5" s="42">
         <f t="shared" ca="1" si="0"/>
         <v>46321</v>
       </c>
-      <c r="AJ5" s="49">
+      <c r="AJ5" s="42">
         <f t="shared" ca="1" si="0"/>
         <v>46328</v>
       </c>
-      <c r="AK5" s="49">
+      <c r="AK5" s="42">
         <f t="shared" ca="1" si="0"/>
         <v>46335</v>
       </c>
-      <c r="AL5" s="49">
+      <c r="AL5" s="42">
         <f t="shared" ca="1" si="0"/>
         <v>46342</v>
       </c>
-      <c r="AM5" s="49">
+      <c r="AM5" s="42">
         <f t="shared" ca="1" si="0"/>
         <v>46349</v>
       </c>
-      <c r="AN5" s="49">
+      <c r="AN5" s="42">
         <f t="shared" ca="1" si="0"/>
         <v>46356</v>
       </c>
-      <c r="AO5" s="49">
+      <c r="AO5" s="42">
         <f t="shared" ca="1" si="0"/>
         <v>46363</v>
       </c>
-      <c r="AP5" s="49">
+      <c r="AP5" s="42">
         <f t="shared" ca="1" si="0"/>
         <v>46370</v>
       </c>
-      <c r="AQ5" s="49">
+      <c r="AQ5" s="42">
         <f t="shared" ca="1" si="0"/>
         <v>46377</v>
       </c>
-      <c r="AR5" s="50">
+      <c r="AR5" s="43">
         <f t="shared" ca="1" si="0"/>
         <v>46384</v>
       </c>
     </row>
-    <row r="6" spans="2:44" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="40" t="s">
+    <row r="6" spans="2:44" ht="17" thickBot="1">
+      <c r="B6" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="41" t="s">
+      <c r="C6" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="42" t="s">
+      <c r="D6" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="42" t="s">
+      <c r="E6" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="43" t="s">
+      <c r="F6" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="43" t="s">
+      <c r="G6" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="43" t="s">
+      <c r="H6" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="I6" s="44" t="s">
+      <c r="I6" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="J6" s="45"/>
-      <c r="K6" s="46"/>
-      <c r="L6" s="46"/>
-      <c r="M6" s="46"/>
-      <c r="N6" s="46"/>
-      <c r="O6" s="46"/>
-      <c r="P6" s="46"/>
-      <c r="Q6" s="46"/>
-      <c r="R6" s="46"/>
-      <c r="S6" s="46"/>
-      <c r="T6" s="46"/>
-      <c r="U6" s="46"/>
-      <c r="V6" s="46"/>
-      <c r="W6" s="46"/>
-      <c r="X6" s="46"/>
-      <c r="Y6" s="46"/>
-      <c r="Z6" s="46"/>
-      <c r="AA6" s="46"/>
-      <c r="AB6" s="46"/>
-      <c r="AC6" s="46"/>
-      <c r="AD6" s="46"/>
-      <c r="AE6" s="46"/>
-      <c r="AF6" s="46"/>
-      <c r="AG6" s="46"/>
-      <c r="AH6" s="46"/>
-      <c r="AI6" s="46"/>
-      <c r="AJ6" s="46"/>
-      <c r="AK6" s="46"/>
-      <c r="AL6" s="46"/>
-      <c r="AM6" s="46"/>
-      <c r="AN6" s="46"/>
-      <c r="AO6" s="46"/>
-      <c r="AP6" s="46"/>
-      <c r="AQ6" s="46"/>
-      <c r="AR6" s="47"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="39"/>
+      <c r="L6" s="39"/>
+      <c r="M6" s="39"/>
+      <c r="N6" s="39"/>
+      <c r="O6" s="39"/>
+      <c r="P6" s="39"/>
+      <c r="Q6" s="39"/>
+      <c r="R6" s="39"/>
+      <c r="S6" s="39"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="W6" s="39"/>
+      <c r="X6" s="39"/>
+      <c r="Y6" s="39"/>
+      <c r="Z6" s="39"/>
+      <c r="AA6" s="39"/>
+      <c r="AB6" s="39"/>
+      <c r="AC6" s="39"/>
+      <c r="AD6" s="39"/>
+      <c r="AE6" s="39"/>
+      <c r="AF6" s="39"/>
+      <c r="AG6" s="39"/>
+      <c r="AH6" s="39"/>
+      <c r="AI6" s="39"/>
+      <c r="AJ6" s="39"/>
+      <c r="AK6" s="39"/>
+      <c r="AL6" s="39"/>
+      <c r="AM6" s="39"/>
+      <c r="AN6" s="39"/>
+      <c r="AO6" s="39"/>
+      <c r="AP6" s="39"/>
+      <c r="AQ6" s="39"/>
+      <c r="AR6" s="40"/>
     </row>
-    <row r="7" spans="2:44" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B7" s="32">
+    <row r="7" spans="2:44" ht="20">
+      <c r="B7" s="27">
         <v>1</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="7">
         <v>46146</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="8">
         <v>46171</v>
       </c>
-      <c r="G7" s="18">
+      <c r="G7" s="13">
         <f>IF(OR(E7="",F7=""),"", NETWORKDAYS(E7, F7))</f>
         <v>20</v>
       </c>
-      <c r="H7" s="21" t="s">
+      <c r="H7" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="I7" s="79">
+      <c r="I7" s="71">
         <v>1</v>
       </c>
-      <c r="J7" s="52" t="str">
+      <c r="J7" s="44" t="str">
         <f ca="1">IF(J$5=($F7-WEEKDAY($F7,2)+1),"u","")</f>
         <v/>
       </c>
-      <c r="K7" s="53" t="str">
+      <c r="K7" s="45" t="str">
         <f t="shared" ref="K7:AR14" ca="1" si="1">IF(K$5=($F7-WEEKDAY($F7,2)+1),"u","")</f>
         <v/>
       </c>
-      <c r="L7" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="M7" s="53" t="str">
+      <c r="L7" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="M7" s="45" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>u</v>
       </c>
-      <c r="N7" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="O7" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="P7" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="Q7" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="R7" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="S7" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="T7" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="U7" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="V7" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="W7" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="X7" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="Y7" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="Z7" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AA7" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AB7" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AC7" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AD7" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AE7" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AF7" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AG7" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AH7" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AI7" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AJ7" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AK7" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AL7" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AM7" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AN7" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AO7" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AP7" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AQ7" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AR7" s="54" t="str">
+      <c r="N7" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="O7" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="P7" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="Q7" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="R7" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="S7" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="T7" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="U7" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="V7" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="W7" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="X7" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="Y7" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="Z7" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AA7" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AB7" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AC7" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AD7" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AE7" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AF7" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AG7" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AH7" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AI7" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AJ7" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AK7" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AL7" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AM7" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AN7" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AO7" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AP7" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AQ7" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AR7" s="46" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="8" spans="2:44" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B8" s="33">
+    <row r="8" spans="2:44" ht="20">
+      <c r="B8" s="28">
         <v>2</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="9">
         <v>46174</v>
       </c>
-      <c r="F8" s="15">
+      <c r="F8" s="10">
         <v>46199</v>
       </c>
-      <c r="G8" s="19">
+      <c r="G8" s="14">
         <f t="shared" ref="G8:G13" si="2">IF(OR(E8="",F8=""),"", NETWORKDAYS(E8, F8))</f>
         <v>20</v>
       </c>
-      <c r="H8" s="22" t="s">
+      <c r="H8" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="I8" s="80">
+      <c r="I8" s="72">
         <v>1</v>
       </c>
-      <c r="J8" s="52" t="str">
+      <c r="J8" s="44" t="str">
         <f t="shared" ref="J8:Y16" ca="1" si="3">IF(J$5=($F8-WEEKDAY($F8,2)+1),"u","")</f>
         <v/>
       </c>
-      <c r="K8" s="53" t="str">
+      <c r="K8" s="45" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
-      <c r="L8" s="53" t="str">
+      <c r="L8" s="45" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
-      <c r="M8" s="53" t="str">
+      <c r="M8" s="45" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
-      <c r="N8" s="53" t="str">
+      <c r="N8" s="45" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
-      <c r="O8" s="53" t="str">
+      <c r="O8" s="45" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
-      <c r="P8" s="53" t="str">
+      <c r="P8" s="45" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
-      <c r="Q8" s="53" t="str">
+      <c r="Q8" s="45" t="str">
         <f t="shared" ca="1" si="3"/>
         <v>u</v>
       </c>
-      <c r="R8" s="53" t="str">
+      <c r="R8" s="45" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
-      <c r="S8" s="53" t="str">
+      <c r="S8" s="45" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
-      <c r="T8" s="53" t="str">
+      <c r="T8" s="45" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
-      <c r="U8" s="53" t="str">
+      <c r="U8" s="45" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
-      <c r="V8" s="53" t="str">
+      <c r="V8" s="45" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
-      <c r="W8" s="53" t="str">
+      <c r="W8" s="45" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
-      <c r="X8" s="53" t="str">
+      <c r="X8" s="45" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
-      <c r="Y8" s="53" t="str">
+      <c r="Y8" s="45" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
-      <c r="Z8" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AA8" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AB8" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AC8" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AD8" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AE8" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AF8" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AG8" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AH8" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AI8" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AJ8" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AK8" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AL8" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AM8" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AN8" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AO8" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AP8" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AQ8" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AR8" s="55" t="str">
+      <c r="Z8" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AA8" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AB8" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AC8" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AD8" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AE8" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AF8" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AG8" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AH8" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AI8" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AJ8" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AK8" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AL8" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AM8" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AN8" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AO8" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AP8" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AQ8" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AR8" s="47" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:44" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B9" s="34">
+    <row r="9" spans="2:44" ht="20">
+      <c r="B9" s="29">
         <v>3</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="11">
         <v>46202</v>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="12">
         <v>46227</v>
       </c>
-      <c r="G9" s="20">
+      <c r="G9" s="15">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="H9" s="22" t="s">
+      <c r="H9" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="I9" s="80">
+      <c r="I9" s="72">
         <v>1</v>
       </c>
-      <c r="J9" s="52" t="str">
+      <c r="J9" s="44" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
-      <c r="K9" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="L9" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="M9" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="N9" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="O9" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="P9" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="Q9" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="R9" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="S9" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="T9" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="U9" s="53" t="str">
+      <c r="K9" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="L9" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="M9" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="N9" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="O9" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="P9" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="Q9" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="R9" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="S9" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="T9" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="U9" s="45" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>u</v>
       </c>
-      <c r="V9" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="W9" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="X9" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="Y9" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="Z9" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AA9" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AB9" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AC9" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AD9" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AE9" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AF9" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AG9" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AH9" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AI9" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AJ9" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AK9" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AL9" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AM9" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AN9" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AO9" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AP9" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AQ9" s="53" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AR9" s="55" t="str">
+      <c r="V9" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="W9" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="X9" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="Y9" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="Z9" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AA9" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AB9" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AC9" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AD9" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AE9" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AF9" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AG9" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AH9" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AI9" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AJ9" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AK9" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AL9" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AM9" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AN9" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AO9" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AP9" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AQ9" s="45" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AR9" s="47" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:44" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B10" s="33">
+    <row r="10" spans="2:44" ht="20">
+      <c r="B10" s="28">
         <v>4</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="9">
         <v>46230</v>
       </c>
-      <c r="F10" s="15">
+      <c r="F10" s="10">
         <v>46262</v>
       </c>
-      <c r="G10" s="19">
+      <c r="G10" s="14">
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="H10" s="23" t="s">
+      <c r="H10" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="I10" s="81">
+      <c r="I10" s="73">
         <v>0.2</v>
       </c>
-      <c r="J10" s="56" t="str">
+      <c r="J10" s="48" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
-      <c r="K10" s="57" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="L10" s="57" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="M10" s="57" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="N10" s="57" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="O10" s="57" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="P10" s="57" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="Q10" s="57" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="R10" s="57" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="S10" s="57" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="T10" s="57" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="U10" s="57" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="V10" s="57" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="W10" s="57" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="X10" s="57" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="Y10" s="57" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="Z10" s="57" t="str">
+      <c r="K10" s="49" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="L10" s="49" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="M10" s="49" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="N10" s="49" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="O10" s="49" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="P10" s="49" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="Q10" s="49" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="R10" s="49" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="S10" s="49" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="T10" s="49" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="U10" s="49" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="V10" s="49" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="W10" s="49" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="X10" s="49" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="Y10" s="49" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="Z10" s="49" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>u</v>
       </c>
-      <c r="AA10" s="57" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AB10" s="57" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AC10" s="57" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AD10" s="57" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AE10" s="57" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AF10" s="57" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AG10" s="57" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AH10" s="57" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AI10" s="57" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AJ10" s="57" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AK10" s="57" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AL10" s="57" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AM10" s="57" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AN10" s="57" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AO10" s="57" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AP10" s="57" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AQ10" s="57" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AR10" s="58" t="str">
+      <c r="AA10" s="49" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AB10" s="49" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AC10" s="49" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AD10" s="49" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AE10" s="49" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AF10" s="49" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AG10" s="49" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AH10" s="49" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AI10" s="49" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AJ10" s="49" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AK10" s="49" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AL10" s="49" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AM10" s="49" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AN10" s="49" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AO10" s="49" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AP10" s="49" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AQ10" s="49" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AR10" s="50" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:44" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B11" s="34">
+    <row r="11" spans="2:44" ht="20">
+      <c r="B11" s="29">
         <v>5</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="11">
         <v>46265</v>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="12">
         <v>46297</v>
       </c>
-      <c r="G11" s="20">
+      <c r="G11" s="15">
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="H11" s="24" t="s">
+      <c r="H11" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="82">
+      <c r="I11" s="74">
         <v>0.4</v>
       </c>
-      <c r="J11" s="59" t="str">
+      <c r="J11" s="51" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
-      <c r="K11" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="L11" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="M11" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="N11" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="O11" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="P11" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="Q11" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="R11" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="S11" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="T11" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="U11" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="V11" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="W11" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="X11" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="Y11" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="Z11" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AA11" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AB11" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AC11" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AD11" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AE11" s="60" t="str">
+      <c r="K11" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="L11" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="M11" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="N11" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="O11" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="P11" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="Q11" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="R11" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="S11" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="T11" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="U11" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="V11" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="W11" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="X11" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="Y11" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="Z11" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AA11" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AB11" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AC11" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AD11" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AE11" s="52" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>u</v>
       </c>
-      <c r="AF11" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AG11" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AH11" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AI11" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AJ11" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AK11" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AL11" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AM11" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AN11" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AO11" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AP11" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AQ11" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AR11" s="61" t="str">
+      <c r="AF11" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AG11" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AH11" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AI11" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AJ11" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AK11" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AL11" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AM11" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AN11" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AO11" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AP11" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AQ11" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AR11" s="53" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="12" spans="2:44" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="33">
+    <row r="12" spans="2:44" ht="20">
+      <c r="B12" s="28">
         <v>6</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="9">
         <v>46300</v>
       </c>
-      <c r="F12" s="15">
+      <c r="F12" s="10">
         <v>46332</v>
       </c>
-      <c r="G12" s="19">
+      <c r="G12" s="14">
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="H12" s="24" t="s">
+      <c r="H12" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="I12" s="82">
+      <c r="I12" s="74">
         <v>0.3</v>
       </c>
-      <c r="J12" s="59" t="str">
+      <c r="J12" s="51" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
-      <c r="K12" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="L12" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="M12" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="N12" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="O12" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="P12" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="Q12" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="R12" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="S12" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="T12" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="U12" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="V12" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="W12" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="X12" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="Y12" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="Z12" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AA12" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AB12" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AC12" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AD12" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AE12" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AF12" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AG12" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AH12" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AI12" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AJ12" s="60" t="str">
+      <c r="K12" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="L12" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="M12" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="N12" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="O12" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="P12" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="Q12" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="R12" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="S12" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="T12" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="U12" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="V12" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="W12" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="X12" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="Y12" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="Z12" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AA12" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AB12" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AC12" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AD12" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AE12" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AF12" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AG12" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AH12" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AI12" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AJ12" s="52" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>u</v>
       </c>
-      <c r="AK12" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AL12" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AM12" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AN12" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AO12" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AP12" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AQ12" s="60" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AR12" s="61" t="str">
+      <c r="AK12" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AL12" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AM12" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AN12" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AO12" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AP12" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AQ12" s="52" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AR12" s="53" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:44" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B13" s="34">
+    <row r="13" spans="2:44" ht="20">
+      <c r="B13" s="29">
         <v>7</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="11">
         <v>46335</v>
       </c>
-      <c r="F13" s="17">
+      <c r="F13" s="12">
         <v>46360</v>
       </c>
-      <c r="G13" s="20">
+      <c r="G13" s="15">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="H13" s="25" t="s">
+      <c r="H13" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="I13" s="83">
+      <c r="I13" s="75">
         <v>0</v>
       </c>
-      <c r="J13" s="62" t="str">
+      <c r="J13" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
-      <c r="K13" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="L13" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="M13" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="N13" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="O13" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="P13" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="Q13" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="R13" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="S13" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="T13" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="U13" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="V13" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="W13" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="X13" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="Y13" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="Z13" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AA13" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AB13" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AC13" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AD13" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AE13" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AF13" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AG13" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AH13" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AI13" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AJ13" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AK13" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AL13" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AM13" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AN13" s="63" t="str">
+      <c r="K13" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="L13" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="M13" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="N13" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="O13" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="P13" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="Q13" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="R13" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="S13" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="T13" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="U13" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="V13" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="W13" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="X13" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="Y13" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="Z13" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AA13" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AB13" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AC13" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AD13" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AE13" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AF13" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AG13" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AH13" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AI13" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AJ13" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AK13" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AL13" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AM13" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AN13" s="55" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>u</v>
       </c>
-      <c r="AO13" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AP13" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AQ13" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AR13" s="64" t="str">
+      <c r="AO13" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AP13" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AQ13" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AR13" s="56" t="str">
         <f t="shared" ca="1" si="1"/>
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:44" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B14" s="33">
+    <row r="14" spans="2:44" ht="20">
+      <c r="B14" s="28">
         <v>8</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="9">
         <v>46363</v>
       </c>
-      <c r="F14" s="15">
+      <c r="F14" s="10">
         <v>46374</v>
       </c>
-      <c r="G14" s="19">
+      <c r="G14" s="14">
         <f>IF(OR(E14="",F14=""),"",F14-E14+1)</f>
         <v>12</v>
       </c>
-      <c r="H14" s="25" t="s">
+      <c r="H14" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="I14" s="84">
+      <c r="I14" s="76">
         <v>0</v>
       </c>
-      <c r="J14" s="62" t="str">
+      <c r="J14" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
-      <c r="K14" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="L14" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="M14" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="N14" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="O14" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="P14" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="Q14" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="R14" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="S14" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="T14" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="U14" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="V14" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="W14" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="X14" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="Y14" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="Z14" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AA14" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AB14" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AC14" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AD14" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AE14" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AF14" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AG14" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AH14" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AI14" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AJ14" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AK14" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AL14" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AM14" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AN14" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AO14" s="63" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v/>
-      </c>
-      <c r="AP14" s="63" t="str">
+      <c r="K14" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="L14" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="M14" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="N14" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="O14" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="P14" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="Q14" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="R14" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="S14" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="T14" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="U14" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="V14" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="W14" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="X14" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="Y14" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="Z14" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AA14" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AB14" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AC14" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AD14" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AE14" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AF14" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AG14" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AH14" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AI14" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AJ14" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AK14" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AL14" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AM14" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AN14" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AO14" s="55" t="str">
+        <f t="shared" ca="1" si="1"/>
+        <v/>
+      </c>
+      <c r="AP14" s="55" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>u</v>
       </c>
-      <c r="AQ14" s="63" t="str">
+      <c r="AQ14" s="55" t="str">
         <f t="shared" ref="K14:AR16" ca="1" si="4">IF(AQ$5=($F14-WEEKDAY($F14,2)+1),"u","")</f>
         <v/>
       </c>
-      <c r="AR14" s="64" t="str">
+      <c r="AR14" s="56" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="15" spans="2:44" ht="19.5" x14ac:dyDescent="0.25">
-      <c r="B15" s="34">
+    <row r="15" spans="2:44" ht="20">
+      <c r="B15" s="29">
         <v>9</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E15" s="16">
+      <c r="E15" s="11">
         <v>46377</v>
       </c>
-      <c r="F15" s="17">
+      <c r="F15" s="12">
         <v>46381</v>
       </c>
-      <c r="G15" s="20">
+      <c r="G15" s="15">
         <f>IF(OR(E15="",F15=""),"",F15-E15+1)</f>
         <v>5</v>
       </c>
-      <c r="H15" s="25" t="s">
+      <c r="H15" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="I15" s="84">
+      <c r="I15" s="76">
         <v>0</v>
       </c>
-      <c r="J15" s="62" t="str">
+      <c r="J15" s="54" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
-      <c r="K15" s="63" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="L15" s="63" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="M15" s="63" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="N15" s="63" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="O15" s="63" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="P15" s="63" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="Q15" s="63" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="R15" s="63" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="S15" s="63" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="T15" s="63" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="U15" s="63" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="V15" s="63" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="W15" s="63" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="X15" s="63" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="Y15" s="63" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="Z15" s="63" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="AA15" s="63" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="AB15" s="63" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="AC15" s="63" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="AD15" s="63" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="AE15" s="63" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="AF15" s="63" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="AG15" s="63" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="AH15" s="63" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="AI15" s="63" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="AJ15" s="63" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="AK15" s="63" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="AL15" s="63" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="AM15" s="63" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="AN15" s="63" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="AO15" s="63" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="AP15" s="63" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="AQ15" s="63" t="str">
+      <c r="K15" s="55" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="L15" s="55" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="M15" s="55" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="N15" s="55" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="O15" s="55" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="P15" s="55" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="Q15" s="55" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="R15" s="55" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="S15" s="55" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="T15" s="55" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="U15" s="55" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="V15" s="55" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="W15" s="55" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="X15" s="55" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="Y15" s="55" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="Z15" s="55" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="AA15" s="55" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="AB15" s="55" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="AC15" s="55" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="AD15" s="55" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="AE15" s="55" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="AF15" s="55" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="AG15" s="55" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="AH15" s="55" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="AI15" s="55" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="AJ15" s="55" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="AK15" s="55" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="AL15" s="55" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="AM15" s="55" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="AN15" s="55" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="AO15" s="55" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="AP15" s="55" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="AQ15" s="55" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>u</v>
       </c>
-      <c r="AR15" s="64" t="str">
+      <c r="AR15" s="56" t="str">
         <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="16" spans="2:44" ht="20.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="35">
+    <row r="16" spans="2:44" ht="20.5" thickBot="1">
+      <c r="B16" s="30">
         <v>10</v>
       </c>
-      <c r="C16" s="26" t="s">
+      <c r="C16" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="D16" s="27" t="s">
+      <c r="D16" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="23">
         <v>46384</v>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="24">
         <v>46387</v>
       </c>
-      <c r="G16" s="30">
+      <c r="G16" s="25">
         <f>IF(OR(E16="",F16=""),"",F16-E16+1)</f>
         <v>4</v>
       </c>
-      <c r="H16" s="31" t="s">
+      <c r="H16" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="I16" s="85">
+      <c r="I16" s="77">
         <v>0</v>
       </c>
-      <c r="J16" s="65" t="str">
+      <c r="J16" s="57" t="str">
         <f t="shared" ca="1" si="3"/>
         <v/>
       </c>
-      <c r="K16" s="66" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="L16" s="66" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="M16" s="66" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="N16" s="66" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="O16" s="66" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="P16" s="66" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="Q16" s="66" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="R16" s="66" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="S16" s="66" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="T16" s="66" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="U16" s="66" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="V16" s="66" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="W16" s="66" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="X16" s="66" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="Y16" s="66" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="Z16" s="66" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="AA16" s="66" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="AB16" s="66" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="AC16" s="66" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="AD16" s="66" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="AE16" s="66" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="AF16" s="66" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="AG16" s="66" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="AH16" s="66" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="AI16" s="66" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="AJ16" s="66" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="AK16" s="66" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="AL16" s="66" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="AM16" s="66" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="AN16" s="66" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="AO16" s="66" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="AP16" s="66" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="AQ16" s="66" t="str">
-        <f t="shared" ca="1" si="4"/>
-        <v/>
-      </c>
-      <c r="AR16" s="67" t="str">
+      <c r="K16" s="58" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="L16" s="58" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="M16" s="58" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="N16" s="58" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="O16" s="58" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="P16" s="58" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="Q16" s="58" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="R16" s="58" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="S16" s="58" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="T16" s="58" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="U16" s="58" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="V16" s="58" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="W16" s="58" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="X16" s="58" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="Y16" s="58" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="Z16" s="58" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="AA16" s="58" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="AB16" s="58" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="AC16" s="58" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="AD16" s="58" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="AE16" s="58" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="AF16" s="58" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="AG16" s="58" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="AH16" s="58" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="AI16" s="58" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="AJ16" s="58" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="AK16" s="58" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="AL16" s="58" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="AM16" s="58" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="AN16" s="58" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="AO16" s="58" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="AP16" s="58" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="AQ16" s="58" t="str">
+        <f t="shared" ca="1" si="4"/>
+        <v/>
+      </c>
+      <c r="AR16" s="59" t="str">
         <f t="shared" ca="1" si="4"/>
         <v>u</v>
       </c>
     </row>
-    <row r="17" spans="2:44" x14ac:dyDescent="0.25">
-      <c r="B17" s="68"/>
-      <c r="C17" s="68"/>
-      <c r="D17" s="68"/>
-      <c r="E17" s="68"/>
-      <c r="F17" s="68"/>
-      <c r="G17" s="68"/>
-      <c r="H17" s="68"/>
-      <c r="I17" s="68"/>
-      <c r="J17" s="51"/>
-      <c r="K17" s="51"/>
-      <c r="L17" s="51"/>
-      <c r="M17" s="51"/>
-      <c r="N17" s="51"/>
-      <c r="O17" s="51"/>
-      <c r="P17" s="51"/>
-      <c r="Q17" s="51"/>
-      <c r="R17" s="51"/>
-      <c r="S17" s="51"/>
-      <c r="T17" s="51"/>
-      <c r="U17" s="51"/>
-      <c r="V17" s="51"/>
-      <c r="W17" s="51"/>
-      <c r="X17" s="51"/>
-      <c r="Y17" s="51"/>
-      <c r="Z17" s="51"/>
-      <c r="AA17" s="51"/>
-      <c r="AB17" s="51"/>
-      <c r="AC17" s="51"/>
-      <c r="AD17" s="51"/>
-      <c r="AE17" s="51"/>
-      <c r="AF17" s="51"/>
-      <c r="AG17" s="51"/>
-      <c r="AH17" s="51"/>
-      <c r="AI17" s="51"/>
-      <c r="AJ17" s="51"/>
-      <c r="AK17" s="51"/>
-      <c r="AL17" s="51"/>
-      <c r="AM17" s="51"/>
-      <c r="AN17" s="51"/>
-      <c r="AO17" s="51"/>
-      <c r="AP17" s="51"/>
-      <c r="AQ17" s="51"/>
-      <c r="AR17" s="51"/>
+    <row r="17" spans="2:9">
+      <c r="B17" s="60"/>
+      <c r="C17" s="60"/>
+      <c r="D17" s="60"/>
+      <c r="E17" s="60"/>
+      <c r="F17" s="60"/>
+      <c r="G17" s="60"/>
+      <c r="H17" s="60"/>
+      <c r="I17" s="60"/>
     </row>
-    <row r="18" spans="2:44" x14ac:dyDescent="0.25">
-      <c r="B18" s="51"/>
-      <c r="C18" s="51"/>
-      <c r="D18" s="51"/>
-      <c r="E18" s="51"/>
-      <c r="F18" s="51"/>
-      <c r="G18" s="51"/>
-      <c r="H18" s="51"/>
-      <c r="I18" s="51"/>
-      <c r="J18" s="51"/>
-      <c r="K18" s="51"/>
-      <c r="L18" s="51"/>
-      <c r="M18" s="51"/>
-      <c r="N18" s="51"/>
-      <c r="O18" s="51"/>
-      <c r="P18" s="51"/>
-      <c r="Q18" s="51"/>
-      <c r="R18" s="51"/>
-      <c r="S18" s="51"/>
-      <c r="T18" s="51"/>
-      <c r="U18" s="51"/>
-      <c r="V18" s="51"/>
-      <c r="W18" s="51"/>
-      <c r="X18" s="51"/>
-      <c r="Y18" s="51"/>
-      <c r="Z18" s="51"/>
-      <c r="AA18" s="51"/>
-      <c r="AB18" s="51"/>
-      <c r="AC18" s="51"/>
-      <c r="AD18" s="51"/>
-      <c r="AE18" s="51"/>
-      <c r="AF18" s="51"/>
-      <c r="AG18" s="51"/>
-      <c r="AH18" s="51"/>
-      <c r="AI18" s="51"/>
-      <c r="AJ18" s="51"/>
-      <c r="AK18" s="51"/>
-      <c r="AL18" s="51"/>
-      <c r="AM18" s="51"/>
-      <c r="AN18" s="51"/>
-      <c r="AO18" s="51"/>
-      <c r="AP18" s="51"/>
-      <c r="AQ18" s="51"/>
-      <c r="AR18" s="51"/>
+    <row r="19" spans="2:9" ht="16">
+      <c r="B19" s="61"/>
+      <c r="C19" s="83" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="62"/>
     </row>
-    <row r="19" spans="2:44" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B19" s="69"/>
-      <c r="C19" s="100" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="70"/>
+    <row r="20" spans="2:9">
+      <c r="B20" s="63"/>
+      <c r="C20" s="64" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" s="65"/>
     </row>
-    <row r="20" spans="2:44" x14ac:dyDescent="0.25">
-      <c r="B20" s="71"/>
-      <c r="C20" s="72" t="s">
-        <v>11</v>
-      </c>
-      <c r="D20" s="73"/>
+    <row r="21" spans="2:9">
+      <c r="B21" s="63"/>
+      <c r="C21" s="66" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="65"/>
     </row>
-    <row r="21" spans="2:44" x14ac:dyDescent="0.25">
-      <c r="B21" s="71"/>
-      <c r="C21" s="74" t="s">
-        <v>12</v>
-      </c>
-      <c r="D21" s="73"/>
+    <row r="22" spans="2:9">
+      <c r="B22" s="63"/>
+      <c r="C22" s="67" t="s">
+        <v>14</v>
+      </c>
+      <c r="D22" s="65"/>
     </row>
-    <row r="22" spans="2:44" x14ac:dyDescent="0.25">
-      <c r="B22" s="71"/>
-      <c r="C22" s="75" t="s">
-        <v>14</v>
-      </c>
-      <c r="D22" s="73"/>
+    <row r="23" spans="2:9">
+      <c r="B23" s="68"/>
+      <c r="C23" s="69" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" s="70"/>
     </row>
-    <row r="23" spans="2:44" x14ac:dyDescent="0.25">
-      <c r="B23" s="76"/>
-      <c r="C23" s="77" t="s">
-        <v>13</v>
-      </c>
-      <c r="D23" s="78"/>
+    <row r="24" spans="2:9" ht="15" thickBot="1"/>
+    <row r="25" spans="2:9" ht="25" customHeight="1">
+      <c r="B25" s="152" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" s="153"/>
+      <c r="D25" s="153"/>
+      <c r="E25" s="153"/>
+      <c r="F25" s="153"/>
+      <c r="G25" s="153"/>
+      <c r="H25" s="153"/>
+      <c r="I25" s="154"/>
     </row>
-    <row r="24" spans="2:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="25" spans="2:44" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="104" t="s">
-        <v>38</v>
-      </c>
-      <c r="C25" s="102"/>
-      <c r="D25" s="102"/>
-      <c r="E25" s="102"/>
-      <c r="F25" s="102"/>
-      <c r="G25" s="102"/>
-      <c r="H25" s="102"/>
-      <c r="I25" s="107"/>
+    <row r="26" spans="2:9" ht="90" customHeight="1">
+      <c r="B26" s="112" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" s="113"/>
+      <c r="D26" s="113"/>
+      <c r="E26" s="113"/>
+      <c r="F26" s="113"/>
+      <c r="G26" s="113"/>
+      <c r="H26" s="113"/>
+      <c r="I26" s="114"/>
     </row>
-    <row r="26" spans="2:44" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="105" t="s">
-        <v>39</v>
-      </c>
-      <c r="C26" s="101"/>
-      <c r="D26" s="101"/>
-      <c r="E26" s="101"/>
-      <c r="F26" s="101"/>
-      <c r="G26" s="101"/>
-      <c r="H26" s="101"/>
-      <c r="I26" s="108"/>
+    <row r="27" spans="2:9">
+      <c r="B27" s="112"/>
+      <c r="C27" s="113"/>
+      <c r="D27" s="113"/>
+      <c r="E27" s="113"/>
+      <c r="F27" s="113"/>
+      <c r="G27" s="113"/>
+      <c r="H27" s="113"/>
+      <c r="I27" s="114"/>
     </row>
-    <row r="27" spans="2:44" x14ac:dyDescent="0.25">
-      <c r="B27" s="105"/>
-      <c r="C27" s="101"/>
-      <c r="D27" s="101"/>
-      <c r="E27" s="101"/>
-      <c r="F27" s="101"/>
-      <c r="G27" s="101"/>
-      <c r="H27" s="101"/>
-      <c r="I27" s="108"/>
+    <row r="28" spans="2:9">
+      <c r="B28" s="112"/>
+      <c r="C28" s="113"/>
+      <c r="D28" s="113"/>
+      <c r="E28" s="113"/>
+      <c r="F28" s="113"/>
+      <c r="G28" s="113"/>
+      <c r="H28" s="113"/>
+      <c r="I28" s="114"/>
     </row>
-    <row r="28" spans="2:44" x14ac:dyDescent="0.25">
-      <c r="B28" s="105"/>
-      <c r="C28" s="101"/>
-      <c r="D28" s="101"/>
-      <c r="E28" s="101"/>
-      <c r="F28" s="101"/>
-      <c r="G28" s="101"/>
-      <c r="H28" s="101"/>
-      <c r="I28" s="108"/>
+    <row r="29" spans="2:9">
+      <c r="B29" s="112"/>
+      <c r="C29" s="113"/>
+      <c r="D29" s="113"/>
+      <c r="E29" s="113"/>
+      <c r="F29" s="113"/>
+      <c r="G29" s="113"/>
+      <c r="H29" s="113"/>
+      <c r="I29" s="114"/>
     </row>
-    <row r="29" spans="2:44" x14ac:dyDescent="0.25">
-      <c r="B29" s="105"/>
-      <c r="C29" s="101"/>
-      <c r="D29" s="101"/>
-      <c r="E29" s="101"/>
-      <c r="F29" s="101"/>
-      <c r="G29" s="101"/>
-      <c r="H29" s="101"/>
-      <c r="I29" s="108"/>
-    </row>
-    <row r="30" spans="2:44" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="106"/>
-      <c r="C30" s="103"/>
-      <c r="D30" s="103"/>
-      <c r="E30" s="103"/>
-      <c r="F30" s="103"/>
-      <c r="G30" s="103"/>
-      <c r="H30" s="103"/>
-      <c r="I30" s="109"/>
+    <row r="30" spans="2:9" ht="15" thickBot="1">
+      <c r="B30" s="115"/>
+      <c r="C30" s="116"/>
+      <c r="D30" s="116"/>
+      <c r="E30" s="116"/>
+      <c r="F30" s="116"/>
+      <c r="G30" s="116"/>
+      <c r="H30" s="116"/>
+      <c r="I30" s="117"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -4114,18 +4944,18 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H7:H16">
-    <cfRule type="containsText" dxfId="3" priority="9" operator="containsText" text="Blocked">
+    <cfRule type="containsText" dxfId="11" priority="9" operator="containsText" text="Blocked">
       <formula>NOT(ISERROR(SEARCH("Blocked",H7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7:AR16">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="10" priority="1">
       <formula>AND($I7&gt;0, J$5 &lt;= ($E7+($F7-$E7)*$I7)-WEEKDAY(($E7+($F7-$E7)*$I7),2)+1, J$5 &gt;= $E7 - WEEKDAY($E7, 2)+1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="7">
+    <cfRule type="expression" dxfId="9" priority="7">
       <formula>AND(J$5&gt;=$E7-(WEEKDAY($E7, 2)+1),J$5&lt;=$F7)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="8">
+    <cfRule type="expression" dxfId="8" priority="8">
       <formula>J$5=(TODAY()-WEEKDAY(TODAY(), 2) + 1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4137,4 +4967,498 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="0" scale="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" copies="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{041A2E35-3773-4B1B-BE4F-9CB3C9824D18}">
+  <dimension ref="B2:P25"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="4.54296875" style="90" customWidth="1"/>
+    <col min="2" max="2" width="5.54296875" style="90" customWidth="1"/>
+    <col min="3" max="3" width="12.81640625" style="90" customWidth="1"/>
+    <col min="4" max="4" width="18" style="90" customWidth="1"/>
+    <col min="5" max="16" width="7.6328125" style="90" customWidth="1"/>
+    <col min="17" max="16384" width="8.7265625" style="90"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:16" ht="26">
+      <c r="B2" s="141" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="141"/>
+      <c r="D2" s="141"/>
+      <c r="E2" s="141"/>
+      <c r="F2" s="141"/>
+      <c r="G2" s="141"/>
+      <c r="H2" s="141"/>
+      <c r="I2" s="141"/>
+      <c r="J2" s="141"/>
+      <c r="K2" s="141"/>
+      <c r="L2" s="141"/>
+      <c r="M2" s="141"/>
+      <c r="N2" s="141"/>
+      <c r="O2" s="141"/>
+      <c r="P2" s="141"/>
+    </row>
+    <row r="3" spans="2:16">
+      <c r="B3" s="142"/>
+      <c r="C3" s="142"/>
+      <c r="D3" s="84" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="143"/>
+      <c r="F3" s="143"/>
+      <c r="G3" s="143"/>
+      <c r="H3" s="85"/>
+      <c r="I3" s="144" t="s">
+        <v>46</v>
+      </c>
+      <c r="J3" s="144"/>
+      <c r="K3" s="145"/>
+      <c r="L3" s="145"/>
+      <c r="M3" s="145"/>
+      <c r="N3" s="86"/>
+      <c r="O3" s="86"/>
+      <c r="P3" s="86"/>
+    </row>
+    <row r="4" spans="2:16">
+      <c r="B4" s="142"/>
+      <c r="C4" s="142"/>
+      <c r="D4" s="142"/>
+      <c r="E4" s="142"/>
+      <c r="F4" s="142"/>
+      <c r="G4" s="142"/>
+      <c r="H4" s="142"/>
+      <c r="I4" s="142"/>
+      <c r="J4" s="142"/>
+      <c r="K4" s="142"/>
+      <c r="L4" s="142"/>
+      <c r="M4" s="142"/>
+      <c r="N4" s="142"/>
+      <c r="O4" s="142"/>
+      <c r="P4" s="142"/>
+    </row>
+    <row r="5" spans="2:16" ht="15" thickBot="1">
+      <c r="B5" s="133" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="134"/>
+      <c r="D5" s="134"/>
+      <c r="E5" s="134"/>
+      <c r="F5" s="134"/>
+      <c r="G5" s="134"/>
+      <c r="H5" s="134"/>
+      <c r="I5" s="134"/>
+      <c r="J5" s="134"/>
+      <c r="K5" s="134"/>
+      <c r="L5" s="134"/>
+      <c r="M5" s="134"/>
+      <c r="N5" s="134"/>
+      <c r="O5" s="134"/>
+      <c r="P5" s="134"/>
+    </row>
+    <row r="6" spans="2:16" ht="61" customHeight="1" thickBot="1">
+      <c r="B6" s="135" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="136"/>
+      <c r="D6" s="137"/>
+      <c r="E6" s="138" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="130" t="s">
+        <v>48</v>
+      </c>
+      <c r="G6" s="130" t="s">
+        <v>48</v>
+      </c>
+      <c r="H6" s="130" t="s">
+        <v>48</v>
+      </c>
+      <c r="I6" s="139" t="s">
+        <v>48</v>
+      </c>
+      <c r="J6" s="130" t="s">
+        <v>48</v>
+      </c>
+      <c r="K6" s="130" t="s">
+        <v>48</v>
+      </c>
+      <c r="L6" s="130" t="s">
+        <v>48</v>
+      </c>
+      <c r="M6" s="130" t="s">
+        <v>48</v>
+      </c>
+      <c r="N6" s="130" t="s">
+        <v>48</v>
+      </c>
+      <c r="O6" s="130" t="s">
+        <v>48</v>
+      </c>
+      <c r="P6" s="130" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="2:16" ht="35" customHeight="1">
+      <c r="B7" s="131" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="132"/>
+      <c r="D7" s="87" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" s="138"/>
+      <c r="F7" s="130"/>
+      <c r="G7" s="130"/>
+      <c r="H7" s="130"/>
+      <c r="I7" s="140"/>
+      <c r="J7" s="130"/>
+      <c r="K7" s="130"/>
+      <c r="L7" s="130"/>
+      <c r="M7" s="130"/>
+      <c r="N7" s="130"/>
+      <c r="O7" s="130"/>
+      <c r="P7" s="130"/>
+    </row>
+    <row r="8" spans="2:16" ht="35" customHeight="1">
+      <c r="B8" s="126" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="127"/>
+      <c r="D8" s="88" t="s">
+        <v>55</v>
+      </c>
+      <c r="E8" s="92"/>
+      <c r="F8" s="93"/>
+      <c r="G8" s="93"/>
+      <c r="H8" s="93"/>
+      <c r="I8" s="93"/>
+      <c r="J8" s="93"/>
+      <c r="K8" s="93"/>
+      <c r="L8" s="93"/>
+      <c r="M8" s="93"/>
+      <c r="N8" s="93"/>
+      <c r="O8" s="93"/>
+      <c r="P8" s="94"/>
+    </row>
+    <row r="9" spans="2:16" ht="35" customHeight="1">
+      <c r="B9" s="126" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="127"/>
+      <c r="D9" s="88" t="s">
+        <v>56</v>
+      </c>
+      <c r="E9" s="95"/>
+      <c r="F9" s="96"/>
+      <c r="G9" s="96"/>
+      <c r="H9" s="96"/>
+      <c r="I9" s="96"/>
+      <c r="J9" s="96"/>
+      <c r="K9" s="96"/>
+      <c r="L9" s="96"/>
+      <c r="M9" s="96"/>
+      <c r="N9" s="96"/>
+      <c r="O9" s="96"/>
+      <c r="P9" s="97"/>
+    </row>
+    <row r="10" spans="2:16" ht="35" customHeight="1">
+      <c r="B10" s="126" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="127"/>
+      <c r="D10" s="88" t="s">
+        <v>57</v>
+      </c>
+      <c r="E10" s="95"/>
+      <c r="F10" s="96"/>
+      <c r="G10" s="96"/>
+      <c r="H10" s="96"/>
+      <c r="I10" s="96"/>
+      <c r="J10" s="96"/>
+      <c r="K10" s="96"/>
+      <c r="L10" s="96"/>
+      <c r="M10" s="96"/>
+      <c r="N10" s="96"/>
+      <c r="O10" s="96"/>
+      <c r="P10" s="97"/>
+    </row>
+    <row r="11" spans="2:16" ht="35" customHeight="1">
+      <c r="B11" s="126" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="127"/>
+      <c r="D11" s="88" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" s="95"/>
+      <c r="F11" s="96"/>
+      <c r="G11" s="96"/>
+      <c r="H11" s="96"/>
+      <c r="I11" s="96"/>
+      <c r="J11" s="96"/>
+      <c r="K11" s="96"/>
+      <c r="L11" s="96"/>
+      <c r="M11" s="96"/>
+      <c r="N11" s="96"/>
+      <c r="O11" s="96"/>
+      <c r="P11" s="97"/>
+    </row>
+    <row r="12" spans="2:16" ht="35" customHeight="1" thickBot="1">
+      <c r="B12" s="128"/>
+      <c r="C12" s="129"/>
+      <c r="D12" s="89"/>
+      <c r="E12" s="98"/>
+      <c r="F12" s="99"/>
+      <c r="G12" s="99"/>
+      <c r="H12" s="99"/>
+      <c r="I12" s="99"/>
+      <c r="J12" s="99"/>
+      <c r="K12" s="99"/>
+      <c r="L12" s="99"/>
+      <c r="M12" s="99"/>
+      <c r="N12" s="99"/>
+      <c r="O12" s="99"/>
+      <c r="P12" s="100"/>
+    </row>
+    <row r="13" spans="2:16" ht="15" thickBot="1"/>
+    <row r="14" spans="2:16" ht="20" customHeight="1">
+      <c r="B14" s="101" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="91" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="2:16" ht="20" customHeight="1">
+      <c r="B15" s="102" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="91" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="16" spans="2:16" ht="20" customHeight="1">
+      <c r="B16" s="102" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="91" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17" spans="2:16" ht="20" customHeight="1" thickBot="1">
+      <c r="B17" s="103" t="s">
+        <v>43</v>
+      </c>
+      <c r="C17" s="91" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18" spans="2:16" ht="15" thickBot="1"/>
+    <row r="19" spans="2:16" ht="18.5">
+      <c r="B19" s="152" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" s="153"/>
+      <c r="D19" s="153"/>
+      <c r="E19" s="153"/>
+      <c r="F19" s="153"/>
+      <c r="G19" s="153"/>
+      <c r="H19" s="153"/>
+      <c r="I19" s="153"/>
+      <c r="J19" s="153"/>
+      <c r="K19" s="153"/>
+      <c r="L19" s="153"/>
+      <c r="M19" s="153"/>
+      <c r="N19" s="153"/>
+      <c r="O19" s="153"/>
+      <c r="P19" s="153"/>
+    </row>
+    <row r="20" spans="2:16">
+      <c r="B20" s="148" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" s="146"/>
+      <c r="D20" s="146"/>
+      <c r="E20" s="146"/>
+      <c r="F20" s="146"/>
+      <c r="G20" s="146"/>
+      <c r="H20" s="146"/>
+      <c r="I20" s="146"/>
+      <c r="J20" s="146"/>
+      <c r="K20" s="146"/>
+      <c r="L20" s="146"/>
+      <c r="M20" s="146"/>
+      <c r="N20" s="146"/>
+      <c r="O20" s="146"/>
+      <c r="P20" s="150"/>
+    </row>
+    <row r="21" spans="2:16">
+      <c r="B21" s="148" t="s">
+        <v>65</v>
+      </c>
+      <c r="C21" s="146"/>
+      <c r="D21" s="146"/>
+      <c r="E21" s="146"/>
+      <c r="F21" s="146"/>
+      <c r="G21" s="146"/>
+      <c r="H21" s="146"/>
+      <c r="I21" s="146"/>
+      <c r="J21" s="146"/>
+      <c r="K21" s="146"/>
+      <c r="L21" s="146"/>
+      <c r="M21" s="146"/>
+      <c r="N21" s="146"/>
+      <c r="O21" s="146"/>
+      <c r="P21" s="150"/>
+    </row>
+    <row r="22" spans="2:16">
+      <c r="B22" s="148" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" s="146"/>
+      <c r="D22" s="146"/>
+      <c r="E22" s="146"/>
+      <c r="F22" s="146"/>
+      <c r="G22" s="146"/>
+      <c r="H22" s="146"/>
+      <c r="I22" s="146"/>
+      <c r="J22" s="146"/>
+      <c r="K22" s="146"/>
+      <c r="L22" s="146"/>
+      <c r="M22" s="146"/>
+      <c r="N22" s="146"/>
+      <c r="O22" s="146"/>
+      <c r="P22" s="150"/>
+    </row>
+    <row r="23" spans="2:16">
+      <c r="B23" s="148" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" s="146"/>
+      <c r="D23" s="146"/>
+      <c r="E23" s="146"/>
+      <c r="F23" s="146"/>
+      <c r="G23" s="146"/>
+      <c r="H23" s="146"/>
+      <c r="I23" s="146"/>
+      <c r="J23" s="146"/>
+      <c r="K23" s="146"/>
+      <c r="L23" s="146"/>
+      <c r="M23" s="146"/>
+      <c r="N23" s="146"/>
+      <c r="O23" s="146"/>
+      <c r="P23" s="150"/>
+    </row>
+    <row r="24" spans="2:16">
+      <c r="B24" s="148" t="s">
+        <v>68</v>
+      </c>
+      <c r="C24" s="146"/>
+      <c r="D24" s="146"/>
+      <c r="E24" s="146"/>
+      <c r="F24" s="146"/>
+      <c r="G24" s="146"/>
+      <c r="H24" s="146"/>
+      <c r="I24" s="146"/>
+      <c r="J24" s="146"/>
+      <c r="K24" s="146"/>
+      <c r="L24" s="146"/>
+      <c r="M24" s="146"/>
+      <c r="N24" s="146"/>
+      <c r="O24" s="146"/>
+      <c r="P24" s="150"/>
+    </row>
+    <row r="25" spans="2:16">
+      <c r="B25" s="149" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="147"/>
+      <c r="D25" s="147"/>
+      <c r="E25" s="147"/>
+      <c r="F25" s="147"/>
+      <c r="G25" s="147"/>
+      <c r="H25" s="147"/>
+      <c r="I25" s="147"/>
+      <c r="J25" s="147"/>
+      <c r="K25" s="147"/>
+      <c r="L25" s="147"/>
+      <c r="M25" s="147"/>
+      <c r="N25" s="147"/>
+      <c r="O25" s="147"/>
+      <c r="P25" s="151"/>
+    </row>
+  </sheetData>
+  <mergeCells count="33">
+    <mergeCell ref="B23:P23"/>
+    <mergeCell ref="B24:P24"/>
+    <mergeCell ref="B25:P25"/>
+    <mergeCell ref="B4:P4"/>
+    <mergeCell ref="B19:P19"/>
+    <mergeCell ref="B20:P20"/>
+    <mergeCell ref="B21:P21"/>
+    <mergeCell ref="B22:P22"/>
+    <mergeCell ref="B2:P2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="B5:P5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="N6:N7"/>
+    <mergeCell ref="O6:O7"/>
+    <mergeCell ref="P6:P7"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="M6:M7"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B14:B17">
+    <cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",B14)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="6" priority="2" operator="containsText" text="C">
+      <formula>NOT(ISERROR(SEARCH("C",B14)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="A">
+      <formula>NOT(ISERROR(SEARCH("A",B14)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="4" priority="4" operator="containsText" text="R">
+      <formula>NOT(ISERROR(SEARCH("R",B14)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E8:P12">
+    <cfRule type="containsText" dxfId="3" priority="17" operator="containsText" text="I">
+      <formula>NOT(ISERROR(SEARCH("I",E8)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="18" operator="containsText" text="C">
+      <formula>NOT(ISERROR(SEARCH("C",E8)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="19" operator="containsText" text="A">
+      <formula>NOT(ISERROR(SEARCH("A",E8)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="20" operator="containsText" text="R">
+      <formula>NOT(ISERROR(SEARCH("R",E8)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E8:P12" xr:uid="{15FD789B-D55F-4F5D-BB73-334610605AE6}">
+      <formula1>$B$14:$B$17</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/pm_dashboards/Project Management Charts.xlsx
+++ b/pm_dashboards/Project Management Charts.xlsx
@@ -8,17 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\excel_tutorial\pm_dashboards\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{622988BD-25D4-46BC-BCF8-A9031A15B49E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABA8D240-7D97-4908-8E58-D90597AA851F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="412" firstSheet="1" activeTab="5" xr2:uid="{6ACA091F-59E3-41E7-B925-EA720AB063CF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="513" activeTab="2" xr2:uid="{6ACA091F-59E3-41E7-B925-EA720AB063CF}"/>
   </bookViews>
   <sheets>
-    <sheet name="Project Charter" sheetId="7" r:id="rId1"/>
-    <sheet name="Gantt Chart" sheetId="1" r:id="rId2"/>
-    <sheet name="RACI" sheetId="4" r:id="rId3"/>
-    <sheet name="Risk Assessment" sheetId="8" r:id="rId4"/>
-    <sheet name="Requirement Traceability" sheetId="9" r:id="rId5"/>
-    <sheet name="Pareto Principle" sheetId="10" r:id="rId6"/>
+    <sheet name="PMP" sheetId="11" r:id="rId1"/>
+    <sheet name="Project Charter" sheetId="7" r:id="rId2"/>
+    <sheet name="Impact over Influence Chart" sheetId="13" r:id="rId3"/>
+    <sheet name="Gantt Chart" sheetId="1" r:id="rId4"/>
+    <sheet name="RACI" sheetId="4" r:id="rId5"/>
+    <sheet name="Risk Assessment" sheetId="8" r:id="rId6"/>
+    <sheet name="Requirement Traceability" sheetId="9" r:id="rId7"/>
+    <sheet name="Pareto Principle" sheetId="10" r:id="rId8"/>
+    <sheet name="Heatmap" sheetId="12" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -161,7 +164,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="386">
   <si>
     <t>Project Start Date:</t>
   </si>
@@ -1080,6 +1083,330 @@
   <si>
     <t>Search Functionality Bugs</t>
   </si>
+  <si>
+    <t>Knowledge Area</t>
+  </si>
+  <si>
+    <t>Initiating - 2</t>
+  </si>
+  <si>
+    <t>Planning - 24</t>
+  </si>
+  <si>
+    <t>Executing - 10</t>
+  </si>
+  <si>
+    <t>Monitoring and Controlling - 12</t>
+  </si>
+  <si>
+    <t>Closing - 1</t>
+  </si>
+  <si>
+    <t>Project Integration Management</t>
+  </si>
+  <si>
+    <t>Develop project charter</t>
+  </si>
+  <si>
+    <t>Develop project management plan</t>
+  </si>
+  <si>
+    <t>• Direct and manage the project work
+• Manage project knowledge</t>
+  </si>
+  <si>
+    <t>• Monitor and Control Project Work
+• Perform Integrated Change Control</t>
+  </si>
+  <si>
+    <t>Close project or phase</t>
+  </si>
+  <si>
+    <t>Project Scope Management</t>
+  </si>
+  <si>
+    <t>• Plan scope management
+• Collect requirements
+• Create WBS</t>
+  </si>
+  <si>
+    <t>• Validate scope
+• Control scope</t>
+  </si>
+  <si>
+    <t>Project Schedule Management</t>
+  </si>
+  <si>
+    <t>• Plan schedule management
+• Define activities
+• Sequence activities
+• Estimate activity durations
+• Develop schedule</t>
+  </si>
+  <si>
+    <t>Control schedule</t>
+  </si>
+  <si>
+    <t>Project Cost Management</t>
+  </si>
+  <si>
+    <t>• Plan cost management
+• Estimate costs
+• Determine budget</t>
+  </si>
+  <si>
+    <t>Control costs</t>
+  </si>
+  <si>
+    <t>Project Quality Management</t>
+  </si>
+  <si>
+    <t>Plan quality management</t>
+  </si>
+  <si>
+    <t>Manage quality</t>
+  </si>
+  <si>
+    <t>Control quality</t>
+  </si>
+  <si>
+    <t>Project Resource Management</t>
+  </si>
+  <si>
+    <t>• Plan resource management
+• Estimate activity resources</t>
+  </si>
+  <si>
+    <t>• Acquire resources
+• Develop team
+• Manage team</t>
+  </si>
+  <si>
+    <t>Project Communications Management</t>
+  </si>
+  <si>
+    <t>Plan communications management</t>
+  </si>
+  <si>
+    <t>Manage communications</t>
+  </si>
+  <si>
+    <t>Monitor communications</t>
+  </si>
+  <si>
+    <t>Project Risk Management</t>
+  </si>
+  <si>
+    <t>• Plan risk management
+• Perform qualitative risk analysis
+• Perform quantitative risk analysis
+• Plan risk responses</t>
+  </si>
+  <si>
+    <t>Implement risk responses</t>
+  </si>
+  <si>
+    <t>Monitor risks</t>
+  </si>
+  <si>
+    <t>Project Procurement Management</t>
+  </si>
+  <si>
+    <t>Plan procurement management</t>
+  </si>
+  <si>
+    <t>Conduct procurements</t>
+  </si>
+  <si>
+    <t>Control procurements</t>
+  </si>
+  <si>
+    <t>Project Stakeholder Management</t>
+  </si>
+  <si>
+    <t>Identify stakeholders</t>
+  </si>
+  <si>
+    <t>Plan stakeholder engagement</t>
+  </si>
+  <si>
+    <t>Manage stakeholder engagement</t>
+  </si>
+  <si>
+    <t>Monitor stakeholder engagement</t>
+  </si>
+  <si>
+    <t>10 Knowledge Areas</t>
+  </si>
+  <si>
+    <t>5 Process Groups</t>
+  </si>
+  <si>
+    <t>Project Management Heatmap - Enterprise CRM System Implementation</t>
+  </si>
+  <si>
+    <t>Activity Status Overview by Key Metrics</t>
+  </si>
+  <si>
+    <t>% Complete</t>
+  </si>
+  <si>
+    <t>Schedule</t>
+  </si>
+  <si>
+    <t>Risk Level</t>
+  </si>
+  <si>
+    <t>Resource Load</t>
+  </si>
+  <si>
+    <t>Quality</t>
+  </si>
+  <si>
+    <t>Budget</t>
+  </si>
+  <si>
+    <t>Overall Health</t>
+  </si>
+  <si>
+    <t>Legend (1-5 Scale)</t>
+  </si>
+  <si>
+    <t>5 - Excellent</t>
+  </si>
+  <si>
+    <t>Green</t>
+  </si>
+  <si>
+    <t>On track / No issues</t>
+  </si>
+  <si>
+    <t>4 - Good</t>
+  </si>
+  <si>
+    <t>Light Green</t>
+  </si>
+  <si>
+    <t>Minor concerns</t>
+  </si>
+  <si>
+    <t>3 - Fair</t>
+  </si>
+  <si>
+    <t>Yellow</t>
+  </si>
+  <si>
+    <t>Needs attention</t>
+  </si>
+  <si>
+    <t>2 - Poor</t>
+  </si>
+  <si>
+    <t>Orange</t>
+  </si>
+  <si>
+    <t>At risk</t>
+  </si>
+  <si>
+    <t>1 - Critical</t>
+  </si>
+  <si>
+    <t>Red</t>
+  </si>
+  <si>
+    <t>Immediate action required</t>
+  </si>
+  <si>
+    <t>Project Health Summary</t>
+  </si>
+  <si>
+    <t>Total Activities:</t>
+  </si>
+  <si>
+    <t>Completed (100%):</t>
+  </si>
+  <si>
+    <t>In Progress:</t>
+  </si>
+  <si>
+    <t>Not Started:</t>
+  </si>
+  <si>
+    <t>Avg Completion:</t>
+  </si>
+  <si>
+    <t>Avg Overall Health:</t>
+  </si>
+  <si>
+    <t>Critical Items (1-2):</t>
+  </si>
+  <si>
+    <t>Fair Items (3):</t>
+  </si>
+  <si>
+    <t>Good/Excellent (4-5):</t>
+  </si>
+  <si>
+    <t>What is a Project Heatmap?</t>
+  </si>
+  <si>
+    <t>A Project Heatmap is a visual management tool that uses color-coding to quickly communicate the health status of project activities across multiple dimensions.
+• Schedule: How well is the activity tracking against planned timeline?
+• Risk Level: Current risk exposure for the activity (linked to Risk Assessment)
+• Resource Load: Are resources adequately allocated and available?
+• Quality: Are deliverables meeting quality standards?
+• Budget: Is spending within planned budget?
+• Overall Health: Aggregate score indicating overall activity status
+Benefits: Enables quick identification of problem areas, facilitates stakeholder communication, supports proactive decision-making, and provides at-a-glance project status.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Project Name: </t>
+  </si>
+  <si>
+    <t>Stakeholder Map</t>
+  </si>
+  <si>
+    <t>Stakeholder Name</t>
+  </si>
+  <si>
+    <t>Impact of Change</t>
+  </si>
+  <si>
+    <t>Level of Influence</t>
+  </si>
+  <si>
+    <t>Chart Axis</t>
+  </si>
+  <si>
+    <t>Role</t>
+  </si>
+  <si>
+    <t>Impact over Influence Chart - Tutorial</t>
+  </si>
+  <si>
+    <t>What is an Impact over Influence Chart?</t>
+  </si>
+  <si>
+    <t>A stakeholder mapping tool that plots stakeholders based on how much they are IMPACTED by the project vs. how much INFLUENCE they have over decisions.</t>
+  </si>
+  <si>
+    <t>How to Read the Quadrants:</t>
+  </si>
+  <si>
+    <t>• High Impact, High Influence (Top-Right): Key players - Manage closely (e.g., PM, Product Owner)</t>
+  </si>
+  <si>
+    <t>• High Impact, Low Influence (Top-Left): Keep satisfied - Address concerns (e.g., Developers)</t>
+  </si>
+  <si>
+    <t>• Low Impact, High Influence (Bottom-Right): Keep informed - They influence but aren't impacted</t>
+  </si>
+  <si>
+    <t>• Low Impact, Low Influence (Bottom-Left): Monitor - Minimal engagement needed</t>
+  </si>
+  <si>
+    <t>💡 Tip: Update scores as the project evolves. Use this to prioritize communication strategies.</t>
+  </si>
 </sst>
 </file>
 
@@ -1091,7 +1418,7 @@
     <numFmt numFmtId="166" formatCode="yyyy"/>
     <numFmt numFmtId="167" formatCode="dd\ mmm\ yy"/>
   </numFmts>
-  <fonts count="60">
+  <fonts count="74">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1515,8 +1842,107 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="26"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Serif"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFD700"/>
+      <name val="Aptos Serif"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Serif"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Serif"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Serif"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Aptos Serif"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF2E75B6"/>
+      <name val="Aptos Serif"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="51">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1721,8 +2147,104 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEEBF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F8FC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF548235"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC55A11"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7030A0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF806000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6BCB77"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF98D8AA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFD93D"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFB347"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF6B6B"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6DCE4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="132">
+  <borders count="149">
     <border>
       <left/>
       <right/>
@@ -3399,12 +3921,253 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF1F4E79"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9DC3E6"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF1F4E79"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9DC3E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9DC3E6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9DC3E6"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF1F4E79"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9DC3E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9DC3E6"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF1F4E79"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF1F4E79"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9DC3E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF1F4E79"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9DC3E6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF9DC3E6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9DC3E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9DC3E6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9DC3E6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF9DC3E6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9DC3E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9DC3E6"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF1F4E79"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF9DC3E6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9DC3E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF1F4E79"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9DC3E6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF9DC3E6"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF1F4E79"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9DC3E6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9DC3E6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF9DC3E6"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF1F4E79"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9DC3E6"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF1F4E79"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF9DC3E6"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF1F4E79"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF1F4E79"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9DC3E6"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF9DC3E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9DC3E6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9DC3E6"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF9DC3E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9DC3E6"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF1F4E79"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF9DC3E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FFFFD700"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="319">
+  <cellXfs count="423">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
@@ -3860,6 +4623,227 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="55" fillId="21" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="56" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="55" fillId="21" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="56" fillId="27" borderId="114" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="27" borderId="104" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="118" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="119" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="121" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="122" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="119" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="120" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="123" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="115" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="116" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="117" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="118" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="119" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="120" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="121" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="122" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="123" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="34" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="125" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="27" borderId="127" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="27" borderId="128" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="27" borderId="129" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="60" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="131" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="33" borderId="125" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="130" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="62" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="32" fillId="18" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="125" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="18" borderId="119" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="50" fillId="18" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="126" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="124" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="118" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="67" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="71" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="118" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="118" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="119" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="119" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="119" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="119" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="42" borderId="119" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="43" borderId="119" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="44" borderId="119" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="119" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="120" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="124" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="125" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="126" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="121" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="122" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="122" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="123" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="121" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="45" borderId="122" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="122" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="122" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="123" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="67" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="71" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="118" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="121" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="64" fillId="18" borderId="132" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="64" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="136" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="37" borderId="136" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="38" borderId="136" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="39" borderId="136" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="40" borderId="137" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="6" borderId="136" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="6" borderId="139" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="35" borderId="136" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="35" borderId="137" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="36" borderId="136" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="36" borderId="137" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="36" borderId="139" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="36" borderId="140" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="135" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="138" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="2" borderId="133" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="2" borderId="134" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="40" fillId="26" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -4131,82 +5115,14 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="54" fillId="21" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="54" fillId="21" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="21" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="21" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="56" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="55" fillId="21" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="56" fillId="27" borderId="114" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="27" borderId="104" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="118" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="119" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="121" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="122" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="119" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="120" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="123" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="115" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="116" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="117" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="118" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="119" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="120" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="121" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="122" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="123" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="34" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="18" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="18" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="55" fillId="21" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -4217,19 +5133,10 @@
     <xf numFmtId="0" fontId="55" fillId="21" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="22" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="22" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="22" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="57" fillId="24" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="57" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="57" fillId="24" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4244,50 +5151,20 @@
     <xf numFmtId="0" fontId="57" fillId="24" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" indent="1"/>
+    <xf numFmtId="0" fontId="52" fillId="22" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="125" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="52" fillId="22" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="22" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="18" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="27" borderId="127" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="27" borderId="128" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="27" borderId="129" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="60" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="131" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="33" borderId="125" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="130" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="62" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="32" fillId="18" borderId="63" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="125" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="18" borderId="119" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="50" fillId="18" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="126" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="55" fillId="18" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="52" fillId="22" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -4301,7 +5178,7 @@
     <xf numFmtId="0" fontId="59" fillId="24" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="59" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="24" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4316,11 +5193,139 @@
     <xf numFmtId="0" fontId="59" fillId="24" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="124" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="58" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="2" borderId="131" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="142" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="143" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="144" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="124" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="125" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="126" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="124" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="125" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="126" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="63" fillId="3" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="131" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="141" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="106" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="113" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="55" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="55" fillId="2" borderId="148" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="2" borderId="148" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="69" fillId="2" borderId="145" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="2" borderId="146" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="2" borderId="147" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="46" borderId="135" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="47" borderId="136" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="118" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="55" fillId="48" borderId="136" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="49" borderId="136" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="50" borderId="137" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="46" borderId="138" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="47" borderId="139" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="48" borderId="139" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="49" borderId="139" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="50" borderId="140" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="18" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="18" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="18" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="55" fillId="18" borderId="131" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="71" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="71" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="71" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="72" fillId="18" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="72" fillId="18" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="72" fillId="18" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="55" fillId="18" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="18" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="18" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="18" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="18" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4328,148 +5333,6 @@
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="25">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="medium">
-          <color indexed="64"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right/>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="medium">
-          <color indexed="64"/>
-        </top>
-        <bottom style="medium">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFE9A159"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="dotted">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dotted">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="dotted">
-          <color indexed="64"/>
-        </top>
-        <bottom style="dotted">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -4585,6 +5448,148 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="medium">
+          <color indexed="64"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFE9A159"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="dotted">
+          <color indexed="64"/>
+        </top>
+        <bottom style="dotted">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right/>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="dotted">
+          <color indexed="64"/>
+        </top>
+        <bottom style="dotted">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="medium">
+          <color indexed="64"/>
+        </top>
+        <bottom style="medium">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -4668,16 +5673,16 @@
   </tableStyles>
   <colors>
     <mruColors>
+      <color rgb="FFFFFF9F"/>
+      <color rgb="FF163D64"/>
+      <color rgb="FFA0E8AA"/>
+      <color rgb="FF0D3514"/>
+      <color rgb="FF061809"/>
+      <color rgb="FF218B30"/>
       <color rgb="FFE9A159"/>
-      <color rgb="FFA0E8AA"/>
-      <color rgb="FF163D64"/>
-      <color rgb="FFFFFF9F"/>
       <color rgb="FFFF3737"/>
       <color rgb="FFE1801F"/>
       <color rgb="FFFF5757"/>
-      <color rgb="FFFFFF8F"/>
-      <color rgb="FF90A9B6"/>
-      <color rgb="FF64889A"/>
     </mruColors>
   </colors>
   <extLst>
@@ -4692,6 +5697,1175 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:strRef>
+          <c:f>'Impact over Influence Chart'!$A$2</c:f>
+          <c:strCache>
+            <c:ptCount val="1"/>
+            <c:pt idx="0">
+              <c:v>Stakeholder Map</c:v>
+            </c:pt>
+          </c:strCache>
+        </c:strRef>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="6.6469816272965873E-2"/>
+          <c:y val="0.18097222222222226"/>
+          <c:w val="0.89030796150481195"/>
+          <c:h val="0.72125801983085447"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Impact over Influence Chart'!$F$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Level of Influence</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{53032ED7-4EB4-41A7-AC46-FE2657719D13}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-IN"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="b"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-205A-458A-BCD4-4806845F94F5}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="1"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{4ECB827D-8B78-485C-A75C-FBE563675091}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-IN"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="b"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-205A-458A-BCD4-4806845F94F5}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="2"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{1795C169-1019-45AB-9E38-5AFEFEFDAE62}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-IN"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="b"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000004-205A-458A-BCD4-4806845F94F5}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="3"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{D5B6BB3E-3FF3-47B3-B342-E1BA4A5E4EB4}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-IN"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="b"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000005-205A-458A-BCD4-4806845F94F5}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="4"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{0E1300CA-5C83-420F-9704-D8903A08BD3C}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-IN"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="b"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000006-205A-458A-BCD4-4806845F94F5}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="5"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{8DDC48C5-9729-4356-A492-E6662C3D6FF0}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-IN"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="b"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000007-205A-458A-BCD4-4806845F94F5}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="6"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{C18172B9-A854-45BE-884C-A067CC1D6485}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-IN"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="b"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000008-205A-458A-BCD4-4806845F94F5}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="7"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{5BA259FD-6A5D-44A9-B50E-B2AA7B6DAF4C}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-IN"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="b"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000009-205A-458A-BCD4-4806845F94F5}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="8"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{49EDD687-D1F3-4A0F-8C53-929B39C1887B}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-IN"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="b"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000A-205A-458A-BCD4-4806845F94F5}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="9"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{1D526259-6245-40A0-A01A-1EC888EABBC2}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-IN"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="b"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000B-205A-458A-BCD4-4806845F94F5}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="10"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{AC1C8268-BC5E-4F15-8DC9-B42F424792EA}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-IN"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="b"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000C-205A-458A-BCD4-4806845F94F5}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="11"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{0EEE9CC6-7BCE-4D34-A3C0-593144196EC4}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-IN"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="b"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000D-205A-458A-BCD4-4806845F94F5}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="12"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{2A2EAE76-B8B8-40AE-A567-76E93ECDC457}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-IN"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="b"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000E-205A-458A-BCD4-4806845F94F5}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
+              <c:idx val="13"/>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:fld id="{F6267437-9B51-4F2F-9F87-9441BAA3461B}" type="CELLRANGE">
+                      <a:rPr lang="en-US"/>
+                      <a:pPr/>
+                      <a:t>[CELLRANGE]</a:t>
+                    </a:fld>
+                    <a:endParaRPr lang="en-IN"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:dLblPos val="b"/>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="0"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:dlblFieldTable/>
+                  <c15:xForSave val="1"/>
+                  <c15:showDataLabelsRange val="1"/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000F-205A-458A-BCD4-4806845F94F5}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="b"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showDataLabelsRange val="1"/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Impact over Influence Chart'!$E$7:$E$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Impact over Influence Chart'!$F$7:$F$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="14"/>
+                <c:pt idx="0">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+              <c15:datalabelsRange>
+                <c15:f>'Impact over Influence Chart'!$C$7:$C$20</c15:f>
+                <c15:dlblRangeCache>
+                  <c:ptCount val="14"/>
+                  <c:pt idx="0">
+                    <c:v>Sarah Johnson</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>Tom Williams</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>Michael Chen</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>David Kumar</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>Emma Wilson</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>James Rodriguez</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>Lisa Park</c:v>
+                  </c:pt>
+                  <c:pt idx="7">
+                    <c:v>Robert Taylor</c:v>
+                  </c:pt>
+                  <c:pt idx="8">
+                    <c:v>Anna Martinez</c:v>
+                  </c:pt>
+                  <c:pt idx="9">
+                    <c:v>Chris Brown</c:v>
+                  </c:pt>
+                  <c:pt idx="10">
+                    <c:v>Jennifer Lee</c:v>
+                  </c:pt>
+                  <c:pt idx="11">
+                    <c:v>Kevin Zhang</c:v>
+                  </c:pt>
+                  <c:pt idx="12">
+                    <c:v>Rachel Green</c:v>
+                  </c:pt>
+                  <c:pt idx="13">
+                    <c:v>Maria Santos</c:v>
+                  </c:pt>
+                </c15:dlblRangeCache>
+              </c15:datalabelsRange>
+            </c:ext>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-205A-458A-BCD4-4806845F94F5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Impact over Influence Chart'!$B$23:$C$23</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Chart Axis</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln w="9525">
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:errBars>
+            <c:errDir val="x"/>
+            <c:errBarType val="both"/>
+            <c:errValType val="percentage"/>
+            <c:noEndCap val="0"/>
+            <c:val val="100"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:srgbClr val="FFC000"/>
+                </a:solidFill>
+                <a:round/>
+                <a:tailEnd type="none"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:errBars>
+          <c:errBars>
+            <c:errDir val="y"/>
+            <c:errBarType val="both"/>
+            <c:errValType val="percentage"/>
+            <c:noEndCap val="1"/>
+            <c:val val="100"/>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:srgbClr val="FFC000"/>
+                </a:solidFill>
+                <a:round/>
+                <a:tailEnd type="none"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:errBars>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Impact over Influence Chart'!$D$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Impact over Influence Chart'!$E$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-205A-458A-BCD4-4806845F94F5}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="570423279"/>
+        <c:axId val="570424719"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="570423279"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="10"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Impact over Influence Chart'!$E$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Impact of Change</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="570424719"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="570424719"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="10"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Impact over Influence Chart'!$F$6</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Level of Influence</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="570423279"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="28575" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:userShapes r:id="rId3"/>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -5250,6 +7424,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="261711855"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
@@ -5310,7 +7485,1317 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>190499</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>42862</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2BFF0E6D-90D6-D30A-DB8E-12390528D9B6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.06832</cdr:x>
+      <cdr:y>0.8386</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.15155</cdr:x>
+      <cdr:y>0.89708</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F1AE427C-0C9C-8973-41FC-ACEF1D5FF677}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="523876" y="3414713"/>
+          <a:ext cx="638175" cy="238125"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="square" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:endParaRPr lang="en-IN" sz="1100" kern="1200"/>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.00663</cdr:x>
+      <cdr:y>0.01248</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.08986</cdr:x>
+      <cdr:y>0.07096</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="3" name="TextBox 1">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58B17026-8100-72B1-2E6E-1ED005FDA690}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="50800" y="50800"/>
+          <a:ext cx="638175" cy="238125"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:endParaRPr lang="en-IN" sz="1100" kern="1200"/>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.06998</cdr:x>
+      <cdr:y>0.84288</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.15321</cdr:x>
+      <cdr:y>0.90136</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="4" name="TextBox 1">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58B17026-8100-72B1-2E6E-1ED005FDA690}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="536575" y="3432175"/>
+          <a:ext cx="638175" cy="238125"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:endParaRPr lang="en-IN" sz="1100" kern="1200"/>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.07915</cdr:x>
+      <cdr:y>0.90486</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.13695</cdr:x>
+      <cdr:y>0.9432</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="5" name="TextBox 4">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3C9315E9-CA8A-5B3F-F7C8-7D311A036C64}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="875316" y="5856494"/>
+          <a:ext cx="639159" cy="248103"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" b="1" kern="1200"/>
+            <a:t>Monitor</a:t>
+          </a:r>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.00663</cdr:x>
+      <cdr:y>0.01248</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.08986</cdr:x>
+      <cdr:y>0.07096</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="6" name="TextBox 1">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58B17026-8100-72B1-2E6E-1ED005FDA690}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="50800" y="50800"/>
+          <a:ext cx="638175" cy="238125"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:endParaRPr lang="en-IN" sz="1100" kern="1200"/>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.05836</cdr:x>
+      <cdr:y>0.14202</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.18777</cdr:x>
+      <cdr:y>0.16422</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="8" name="TextBox 1">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{510A3A6A-BD96-07F8-988F-D22B6EE03F65}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="645373" y="919163"/>
+          <a:ext cx="1431077" cy="143732"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" b="1" kern="1200"/>
+            <a:t>Maintain Confidence</a:t>
+          </a:r>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.84496</cdr:x>
+      <cdr:y>0.13861</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.95852</cdr:x>
+      <cdr:y>0.16409</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="9" name="TextBox 1">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{69EEB57F-990F-4250-45A8-B202ED4EC93B}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="9344025" y="897099"/>
+          <a:ext cx="1255823" cy="164939"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" b="1" kern="1200"/>
+            <a:t>Collaborate With</a:t>
+          </a:r>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.88923</cdr:x>
+      <cdr:y>0.91346</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.94128</cdr:x>
+      <cdr:y>0.93751</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="10" name="TextBox 1">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{59F8EF42-B815-ECC2-2307-A3BBD1F8038B}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="11163299" y="6434138"/>
+          <a:ext cx="653485" cy="169438"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-IN" sz="1100" b="1" kern="1200"/>
+            <a:t>Inform</a:t>
+          </a:r>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+</c:userShapes>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -5364,11 +8849,11 @@
     <sortCondition descending="1" ref="C5:C24"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{943459A8-0FE9-4160-A47E-FA2D69FBEA80}" name="Options" totalsRowLabel="TOTAL" dataDxfId="21" totalsRowDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{8211ECFE-775B-4AAB-9AC0-3ADF3A0F719A}" name="Data" totalsRowFunction="custom" dataDxfId="4" totalsRowDxfId="1">
+    <tableColumn id="1" xr3:uid="{943459A8-0FE9-4160-A47E-FA2D69FBEA80}" name="Options" totalsRowLabel="TOTAL" dataDxfId="21" totalsRowDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{8211ECFE-775B-4AAB-9AC0-3ADF3A0F719A}" name="Data" totalsRowFunction="custom" dataDxfId="19" totalsRowDxfId="18">
       <totalsRowFormula>SUM(Table4[Data])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{7F1106EA-ECA2-4B33-896F-6D8F9CF0D4C8}" name="%" totalsRowFunction="sum" dataDxfId="3" totalsRowDxfId="0" dataCellStyle="Percent" totalsRowCellStyle="Percent">
+    <tableColumn id="3" xr3:uid="{7F1106EA-ECA2-4B33-896F-6D8F9CF0D4C8}" name="%" totalsRowFunction="sum" dataDxfId="17" totalsRowDxfId="16" dataCellStyle="Percent" totalsRowCellStyle="Percent">
       <calculatedColumnFormula>(Table4[[#This Row],[Data]]/C$25)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5733,6 +9218,233 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FCCB04F-8289-4A2D-AD3B-CFF9C4071F1C}">
+  <dimension ref="A1:G12"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="5.7109375" style="234" customWidth="1"/>
+    <col min="2" max="2" width="31.85546875" style="234" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.42578125" style="234" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.5703125" style="234" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="34.42578125" style="234" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33.85546875" style="234" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.7109375" style="234" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="234"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="30" customHeight="1">
+      <c r="A1" s="233"/>
+      <c r="B1" s="250" t="s">
+        <v>332</v>
+      </c>
+      <c r="C1" s="250"/>
+      <c r="D1" s="250"/>
+      <c r="E1" s="250"/>
+      <c r="F1" s="250"/>
+      <c r="G1" s="251"/>
+    </row>
+    <row r="2" spans="1:7" ht="30" customHeight="1">
+      <c r="A2" s="248" t="s">
+        <v>331</v>
+      </c>
+      <c r="B2" s="235" t="s">
+        <v>286</v>
+      </c>
+      <c r="C2" s="236" t="s">
+        <v>287</v>
+      </c>
+      <c r="D2" s="235" t="s">
+        <v>288</v>
+      </c>
+      <c r="E2" s="237" t="s">
+        <v>289</v>
+      </c>
+      <c r="F2" s="238" t="s">
+        <v>290</v>
+      </c>
+      <c r="G2" s="239" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="28.5">
+      <c r="A3" s="248"/>
+      <c r="B3" s="240" t="s">
+        <v>292</v>
+      </c>
+      <c r="C3" s="242" t="s">
+        <v>293</v>
+      </c>
+      <c r="D3" s="242" t="s">
+        <v>294</v>
+      </c>
+      <c r="E3" s="242" t="s">
+        <v>295</v>
+      </c>
+      <c r="F3" s="242" t="s">
+        <v>296</v>
+      </c>
+      <c r="G3" s="243" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="42.75">
+      <c r="A4" s="248"/>
+      <c r="B4" s="240" t="s">
+        <v>298</v>
+      </c>
+      <c r="C4" s="244"/>
+      <c r="D4" s="244" t="s">
+        <v>299</v>
+      </c>
+      <c r="E4" s="244"/>
+      <c r="F4" s="244" t="s">
+        <v>300</v>
+      </c>
+      <c r="G4" s="245"/>
+    </row>
+    <row r="5" spans="1:7" ht="71.25">
+      <c r="A5" s="248"/>
+      <c r="B5" s="240" t="s">
+        <v>301</v>
+      </c>
+      <c r="C5" s="242"/>
+      <c r="D5" s="242" t="s">
+        <v>302</v>
+      </c>
+      <c r="E5" s="242"/>
+      <c r="F5" s="242" t="s">
+        <v>303</v>
+      </c>
+      <c r="G5" s="243"/>
+    </row>
+    <row r="6" spans="1:7" ht="42.75">
+      <c r="A6" s="248"/>
+      <c r="B6" s="240" t="s">
+        <v>304</v>
+      </c>
+      <c r="C6" s="244"/>
+      <c r="D6" s="244" t="s">
+        <v>305</v>
+      </c>
+      <c r="E6" s="244"/>
+      <c r="F6" s="244" t="s">
+        <v>306</v>
+      </c>
+      <c r="G6" s="245"/>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="248"/>
+      <c r="B7" s="240" t="s">
+        <v>307</v>
+      </c>
+      <c r="C7" s="242"/>
+      <c r="D7" s="242" t="s">
+        <v>308</v>
+      </c>
+      <c r="E7" s="242" t="s">
+        <v>309</v>
+      </c>
+      <c r="F7" s="242" t="s">
+        <v>310</v>
+      </c>
+      <c r="G7" s="243"/>
+    </row>
+    <row r="8" spans="1:7" ht="42.75">
+      <c r="A8" s="248"/>
+      <c r="B8" s="240" t="s">
+        <v>311</v>
+      </c>
+      <c r="C8" s="244"/>
+      <c r="D8" s="244" t="s">
+        <v>312</v>
+      </c>
+      <c r="E8" s="244" t="s">
+        <v>313</v>
+      </c>
+      <c r="F8" s="244"/>
+      <c r="G8" s="245"/>
+    </row>
+    <row r="9" spans="1:7" ht="28.5">
+      <c r="A9" s="248"/>
+      <c r="B9" s="240" t="s">
+        <v>314</v>
+      </c>
+      <c r="C9" s="242"/>
+      <c r="D9" s="242" t="s">
+        <v>315</v>
+      </c>
+      <c r="E9" s="242" t="s">
+        <v>316</v>
+      </c>
+      <c r="F9" s="242" t="s">
+        <v>317</v>
+      </c>
+      <c r="G9" s="243"/>
+    </row>
+    <row r="10" spans="1:7" ht="85.5">
+      <c r="A10" s="248"/>
+      <c r="B10" s="240" t="s">
+        <v>318</v>
+      </c>
+      <c r="C10" s="244"/>
+      <c r="D10" s="244" t="s">
+        <v>319</v>
+      </c>
+      <c r="E10" s="244" t="s">
+        <v>320</v>
+      </c>
+      <c r="F10" s="244" t="s">
+        <v>321</v>
+      </c>
+      <c r="G10" s="245"/>
+    </row>
+    <row r="11" spans="1:7" ht="28.5">
+      <c r="A11" s="248"/>
+      <c r="B11" s="240" t="s">
+        <v>322</v>
+      </c>
+      <c r="C11" s="242"/>
+      <c r="D11" s="242" t="s">
+        <v>323</v>
+      </c>
+      <c r="E11" s="242" t="s">
+        <v>324</v>
+      </c>
+      <c r="F11" s="242" t="s">
+        <v>325</v>
+      </c>
+      <c r="G11" s="243"/>
+    </row>
+    <row r="12" spans="1:7" ht="17.25" thickBot="1">
+      <c r="A12" s="249"/>
+      <c r="B12" s="241" t="s">
+        <v>326</v>
+      </c>
+      <c r="C12" s="246" t="s">
+        <v>327</v>
+      </c>
+      <c r="D12" s="246" t="s">
+        <v>328</v>
+      </c>
+      <c r="E12" s="246" t="s">
+        <v>329</v>
+      </c>
+      <c r="F12" s="246" t="s">
+        <v>330</v>
+      </c>
+      <c r="G12" s="247"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:A12"/>
+    <mergeCell ref="B1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1DEED6C-4F0E-4895-BD77-03C3FD341752}">
   <dimension ref="B1:C19"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -5745,10 +9457,10 @@
   <sheetData>
     <row r="1" spans="2:3" ht="15.75" thickBot="1"/>
     <row r="2" spans="2:3" ht="36.75" customHeight="1" thickBot="1">
-      <c r="B2" s="162" t="s">
+      <c r="B2" s="254" t="s">
         <v>80</v>
       </c>
-      <c r="C2" s="163"/>
+      <c r="C2" s="255"/>
     </row>
     <row r="3" spans="2:3" ht="17.25" thickBot="1">
       <c r="B3" s="104" t="s">
@@ -5803,10 +9515,10 @@
       <c r="C9" s="102"/>
     </row>
     <row r="10" spans="2:3" ht="30.75" customHeight="1">
-      <c r="B10" s="160" t="s">
+      <c r="B10" s="252" t="s">
         <v>89</v>
       </c>
-      <c r="C10" s="161"/>
+      <c r="C10" s="253"/>
     </row>
     <row r="11" spans="2:3" ht="30.75" customHeight="1">
       <c r="B11" s="107" t="s">
@@ -5889,7 +9601,526 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C09200B-DE07-433A-B20C-531E1AA60A65}">
+  <dimension ref="A1:R34"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="17.7109375" style="390" customWidth="1"/>
+    <col min="2" max="2" width="3.28515625" style="390" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" style="390" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="55.140625" style="390" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19" style="390" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.42578125" style="390" bestFit="1" customWidth="1"/>
+    <col min="7" max="16" width="16" style="390" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="390"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" ht="20.100000000000001" customHeight="1">
+      <c r="A1" s="389"/>
+      <c r="B1" s="389"/>
+      <c r="C1" s="389"/>
+      <c r="D1" s="389"/>
+      <c r="E1" s="389"/>
+      <c r="F1" s="389"/>
+      <c r="G1" s="389"/>
+      <c r="H1" s="389"/>
+      <c r="I1" s="389"/>
+      <c r="J1" s="389"/>
+      <c r="K1" s="389"/>
+      <c r="L1" s="389"/>
+      <c r="M1" s="389"/>
+      <c r="N1" s="389"/>
+      <c r="O1" s="389"/>
+      <c r="P1" s="389"/>
+      <c r="Q1" s="389"/>
+      <c r="R1" s="389"/>
+    </row>
+    <row r="2" spans="1:18" ht="36.75" customHeight="1">
+      <c r="A2" s="386" t="s">
+        <v>371</v>
+      </c>
+      <c r="B2" s="386"/>
+      <c r="C2" s="386"/>
+      <c r="D2" s="389"/>
+      <c r="E2" s="389"/>
+      <c r="F2" s="389"/>
+      <c r="G2" s="389"/>
+      <c r="H2" s="389"/>
+      <c r="I2" s="389"/>
+      <c r="J2" s="389"/>
+      <c r="K2" s="389"/>
+      <c r="L2" s="389"/>
+      <c r="M2" s="389"/>
+      <c r="N2" s="389"/>
+      <c r="O2" s="389"/>
+      <c r="P2" s="389"/>
+      <c r="Q2" s="389"/>
+      <c r="R2" s="389"/>
+    </row>
+    <row r="3" spans="1:18" ht="20.100000000000001" customHeight="1">
+      <c r="A3" s="391"/>
+      <c r="B3" s="391"/>
+      <c r="C3" s="391"/>
+      <c r="D3" s="389"/>
+      <c r="E3" s="389"/>
+      <c r="F3" s="389"/>
+      <c r="G3" s="389"/>
+      <c r="H3" s="389"/>
+      <c r="I3" s="389"/>
+      <c r="J3" s="389"/>
+      <c r="K3" s="389"/>
+      <c r="L3" s="389"/>
+      <c r="M3" s="389"/>
+      <c r="N3" s="389"/>
+      <c r="O3" s="389"/>
+      <c r="P3" s="389"/>
+      <c r="Q3" s="389"/>
+      <c r="R3" s="389"/>
+    </row>
+    <row r="4" spans="1:18" ht="20.100000000000001" customHeight="1">
+      <c r="A4" s="389"/>
+      <c r="B4" s="389"/>
+      <c r="C4" s="388" t="s">
+        <v>370</v>
+      </c>
+      <c r="D4" s="387" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="389"/>
+      <c r="F4" s="389"/>
+      <c r="G4" s="389"/>
+      <c r="H4" s="389"/>
+      <c r="I4" s="389"/>
+      <c r="J4" s="389"/>
+      <c r="K4" s="389"/>
+      <c r="L4" s="389"/>
+      <c r="M4" s="389"/>
+      <c r="N4" s="389"/>
+      <c r="O4" s="389"/>
+      <c r="P4" s="389"/>
+      <c r="Q4" s="389"/>
+      <c r="R4" s="389"/>
+    </row>
+    <row r="5" spans="1:18" ht="20.100000000000001" customHeight="1" thickBot="1">
+      <c r="A5" s="392"/>
+      <c r="B5" s="392"/>
+      <c r="C5" s="393"/>
+      <c r="D5" s="393"/>
+      <c r="E5" s="392"/>
+      <c r="F5" s="392"/>
+      <c r="G5" s="392"/>
+      <c r="H5" s="392"/>
+      <c r="I5" s="392"/>
+      <c r="J5" s="392"/>
+      <c r="K5" s="392"/>
+      <c r="L5" s="392"/>
+      <c r="M5" s="392"/>
+      <c r="N5" s="392"/>
+      <c r="O5" s="392"/>
+      <c r="P5" s="392"/>
+      <c r="Q5" s="392"/>
+      <c r="R5" s="392"/>
+    </row>
+    <row r="6" spans="1:18" ht="24.95" customHeight="1">
+      <c r="B6" s="394" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="395" t="s">
+        <v>372</v>
+      </c>
+      <c r="D6" s="395" t="s">
+        <v>376</v>
+      </c>
+      <c r="E6" s="395" t="s">
+        <v>373</v>
+      </c>
+      <c r="F6" s="396" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
+      <c r="B7" s="397">
+        <f>ROW()-6</f>
+        <v>1</v>
+      </c>
+      <c r="C7" s="398" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="399" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="400">
+        <v>7</v>
+      </c>
+      <c r="F7" s="401">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
+      <c r="B8" s="397">
+        <f>ROW()-6</f>
+        <v>2</v>
+      </c>
+      <c r="C8" s="398" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8" s="399" t="s">
+        <v>77</v>
+      </c>
+      <c r="E8" s="400">
+        <v>6</v>
+      </c>
+      <c r="F8" s="401">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
+      <c r="B9" s="397">
+        <f>ROW()-6</f>
+        <v>3</v>
+      </c>
+      <c r="C9" s="398" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="399" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" s="400">
+        <v>8</v>
+      </c>
+      <c r="F9" s="401">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
+      <c r="B10" s="397">
+        <f>ROW()-6</f>
+        <v>4</v>
+      </c>
+      <c r="C10" s="398" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="399" t="s">
+        <v>63</v>
+      </c>
+      <c r="E10" s="400">
+        <v>6</v>
+      </c>
+      <c r="F10" s="401">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
+      <c r="B11" s="397">
+        <f>ROW()-6</f>
+        <v>5</v>
+      </c>
+      <c r="C11" s="398" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="399" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" s="400">
+        <v>9</v>
+      </c>
+      <c r="F11" s="401">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
+      <c r="B12" s="397">
+        <f>ROW()-6</f>
+        <v>6</v>
+      </c>
+      <c r="C12" s="398" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="399" t="s">
+        <v>65</v>
+      </c>
+      <c r="E12" s="400">
+        <v>8</v>
+      </c>
+      <c r="F12" s="401">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
+      <c r="B13" s="397">
+        <f>ROW()-6</f>
+        <v>7</v>
+      </c>
+      <c r="C13" s="398" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="399" t="s">
+        <v>66</v>
+      </c>
+      <c r="E13" s="400">
+        <v>8</v>
+      </c>
+      <c r="F13" s="401">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
+      <c r="B14" s="397">
+        <f>ROW()-6</f>
+        <v>8</v>
+      </c>
+      <c r="C14" s="398" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="399" t="s">
+        <v>67</v>
+      </c>
+      <c r="E14" s="400">
+        <v>7</v>
+      </c>
+      <c r="F14" s="401">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
+      <c r="B15" s="397">
+        <f>ROW()-6</f>
+        <v>9</v>
+      </c>
+      <c r="C15" s="398" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" s="399" t="s">
+        <v>68</v>
+      </c>
+      <c r="E15" s="400">
+        <v>6</v>
+      </c>
+      <c r="F15" s="401">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
+      <c r="B16" s="397">
+        <f>ROW()-6</f>
+        <v>10</v>
+      </c>
+      <c r="C16" s="398" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="399" t="s">
+        <v>69</v>
+      </c>
+      <c r="E16" s="400">
+        <v>7</v>
+      </c>
+      <c r="F16" s="401">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="B17" s="397">
+        <f>ROW()-6</f>
+        <v>11</v>
+      </c>
+      <c r="C17" s="398" t="s">
+        <v>35</v>
+      </c>
+      <c r="D17" s="399" t="s">
+        <v>70</v>
+      </c>
+      <c r="E17" s="400">
+        <v>5</v>
+      </c>
+      <c r="F17" s="401">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="B18" s="397">
+        <f>ROW()-6</f>
+        <v>12</v>
+      </c>
+      <c r="C18" s="398" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18" s="399" t="s">
+        <v>72</v>
+      </c>
+      <c r="E18" s="400">
+        <v>4</v>
+      </c>
+      <c r="F18" s="401">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="B19" s="397">
+        <f>ROW()-6</f>
+        <v>13</v>
+      </c>
+      <c r="C19" s="398" t="s">
+        <v>75</v>
+      </c>
+      <c r="D19" s="399" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19" s="400">
+        <v>3</v>
+      </c>
+      <c r="F19" s="401">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15.75" thickBot="1">
+      <c r="B20" s="402">
+        <f>ROW()-6</f>
+        <v>14</v>
+      </c>
+      <c r="C20" s="403" t="s">
+        <v>73</v>
+      </c>
+      <c r="D20" s="404" t="s">
+        <v>76</v>
+      </c>
+      <c r="E20" s="405">
+        <v>2</v>
+      </c>
+      <c r="F20" s="406">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="15.75" thickBot="1"/>
+    <row r="23" spans="1:6" ht="15.75" thickBot="1">
+      <c r="B23" s="407" t="s">
+        <v>375</v>
+      </c>
+      <c r="C23" s="408"/>
+      <c r="D23" s="409">
+        <v>5</v>
+      </c>
+      <c r="E23" s="410">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15.75" thickBot="1"/>
+    <row r="26" spans="1:6" ht="17.100000000000001" customHeight="1" thickBot="1">
+      <c r="A26" s="411" t="s">
+        <v>377</v>
+      </c>
+      <c r="B26" s="412"/>
+      <c r="C26" s="412"/>
+      <c r="D26" s="412"/>
+      <c r="E26" s="412"/>
+      <c r="F26" s="413"/>
+    </row>
+    <row r="27" spans="1:6" ht="14.25" customHeight="1" thickBot="1">
+      <c r="A27" s="414" t="s">
+        <v>378</v>
+      </c>
+      <c r="B27" s="415"/>
+      <c r="C27" s="415"/>
+      <c r="D27" s="415"/>
+      <c r="E27" s="415"/>
+      <c r="F27" s="416"/>
+    </row>
+    <row r="28" spans="1:6" ht="30" customHeight="1" thickBot="1">
+      <c r="A28" s="417" t="s">
+        <v>379</v>
+      </c>
+      <c r="B28" s="418"/>
+      <c r="C28" s="418"/>
+      <c r="D28" s="418"/>
+      <c r="E28" s="418"/>
+      <c r="F28" s="419"/>
+    </row>
+    <row r="29" spans="1:6" ht="14.25" customHeight="1" thickBot="1">
+      <c r="A29" s="414" t="s">
+        <v>380</v>
+      </c>
+      <c r="B29" s="415"/>
+      <c r="C29" s="415"/>
+      <c r="D29" s="415"/>
+      <c r="E29" s="415"/>
+      <c r="F29" s="416"/>
+    </row>
+    <row r="30" spans="1:6" ht="14.25" customHeight="1">
+      <c r="A30" s="417" t="s">
+        <v>381</v>
+      </c>
+      <c r="B30" s="418"/>
+      <c r="C30" s="418"/>
+      <c r="D30" s="418"/>
+      <c r="E30" s="418"/>
+      <c r="F30" s="419"/>
+    </row>
+    <row r="31" spans="1:6" ht="14.25" customHeight="1">
+      <c r="A31" s="417" t="s">
+        <v>382</v>
+      </c>
+      <c r="B31" s="418"/>
+      <c r="C31" s="418"/>
+      <c r="D31" s="418"/>
+      <c r="E31" s="418"/>
+      <c r="F31" s="419"/>
+    </row>
+    <row r="32" spans="1:6" ht="14.25" customHeight="1">
+      <c r="A32" s="417" t="s">
+        <v>383</v>
+      </c>
+      <c r="B32" s="418"/>
+      <c r="C32" s="418"/>
+      <c r="D32" s="418"/>
+      <c r="E32" s="418"/>
+      <c r="F32" s="419"/>
+    </row>
+    <row r="33" spans="1:6" ht="14.25" customHeight="1">
+      <c r="A33" s="417" t="s">
+        <v>384</v>
+      </c>
+      <c r="B33" s="418"/>
+      <c r="C33" s="418"/>
+      <c r="D33" s="418"/>
+      <c r="E33" s="418"/>
+      <c r="F33" s="419"/>
+    </row>
+    <row r="34" spans="1:6" ht="14.25" customHeight="1" thickBot="1">
+      <c r="A34" s="420" t="s">
+        <v>385</v>
+      </c>
+      <c r="B34" s="421"/>
+      <c r="C34" s="421"/>
+      <c r="D34" s="421"/>
+      <c r="E34" s="421"/>
+      <c r="F34" s="422"/>
+    </row>
+  </sheetData>
+  <mergeCells count="16">
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="D2:R2"/>
+    <mergeCell ref="D3:R3"/>
+    <mergeCell ref="A4:B5"/>
+    <mergeCell ref="E4:R5"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A29:F29"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{573ED8A0-1950-4B36-ACCF-F2686D23D643}">
   <dimension ref="B1:AR30"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -5906,16 +10137,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:44" ht="40.5">
-      <c r="B1" s="173" t="s">
+      <c r="B1" s="265" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="173"/>
-      <c r="D1" s="173"/>
-      <c r="E1" s="173"/>
-      <c r="F1" s="173"/>
-      <c r="G1" s="173"/>
-      <c r="H1" s="173"/>
-      <c r="I1" s="173"/>
+      <c r="C1" s="265"/>
+      <c r="D1" s="265"/>
+      <c r="E1" s="265"/>
+      <c r="F1" s="265"/>
+      <c r="G1" s="265"/>
+      <c r="H1" s="265"/>
+      <c r="I1" s="265"/>
       <c r="J1" s="31"/>
       <c r="K1" s="31"/>
       <c r="L1" s="31"/>
@@ -5953,16 +10184,16 @@
       <c r="AR1" s="31"/>
     </row>
     <row r="2" spans="2:44" ht="17.25" thickBot="1">
-      <c r="B2" s="174" t="s">
+      <c r="B2" s="266" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="174"/>
-      <c r="D2" s="174"/>
-      <c r="E2" s="174"/>
-      <c r="F2" s="174"/>
-      <c r="G2" s="174"/>
-      <c r="H2" s="174"/>
-      <c r="I2" s="174"/>
+      <c r="C2" s="266"/>
+      <c r="D2" s="266"/>
+      <c r="E2" s="266"/>
+      <c r="F2" s="266"/>
+      <c r="G2" s="266"/>
+      <c r="H2" s="266"/>
+      <c r="I2" s="266"/>
       <c r="J2" s="32"/>
       <c r="K2" s="32"/>
       <c r="L2" s="32"/>
@@ -6000,281 +10231,281 @@
       <c r="AR2" s="32"/>
     </row>
     <row r="3" spans="2:44" ht="18.75">
-      <c r="B3" s="175"/>
-      <c r="C3" s="176"/>
-      <c r="D3" s="176"/>
-      <c r="E3" s="176"/>
-      <c r="F3" s="176"/>
-      <c r="G3" s="176"/>
-      <c r="H3" s="176"/>
-      <c r="I3" s="176"/>
-      <c r="J3" s="181">
+      <c r="B3" s="267"/>
+      <c r="C3" s="268"/>
+      <c r="D3" s="268"/>
+      <c r="E3" s="268"/>
+      <c r="F3" s="268"/>
+      <c r="G3" s="268"/>
+      <c r="H3" s="268"/>
+      <c r="I3" s="268"/>
+      <c r="J3" s="273">
         <f ca="1">K5</f>
-        <v>46153</v>
-      </c>
-      <c r="K3" s="181"/>
-      <c r="L3" s="181"/>
-      <c r="M3" s="181"/>
-      <c r="N3" s="182"/>
-      <c r="O3" s="182"/>
-      <c r="P3" s="182"/>
-      <c r="Q3" s="182"/>
-      <c r="R3" s="182"/>
-      <c r="S3" s="182"/>
-      <c r="T3" s="182"/>
-      <c r="U3" s="182"/>
-      <c r="V3" s="182"/>
-      <c r="W3" s="182"/>
-      <c r="X3" s="182"/>
-      <c r="Y3" s="182"/>
-      <c r="Z3" s="182"/>
-      <c r="AA3" s="182"/>
-      <c r="AB3" s="182"/>
-      <c r="AC3" s="182"/>
-      <c r="AD3" s="182"/>
-      <c r="AE3" s="182"/>
-      <c r="AF3" s="182"/>
-      <c r="AG3" s="182"/>
-      <c r="AH3" s="182"/>
-      <c r="AI3" s="182"/>
-      <c r="AJ3" s="182"/>
-      <c r="AK3" s="182"/>
-      <c r="AL3" s="182"/>
-      <c r="AM3" s="182"/>
-      <c r="AN3" s="182"/>
-      <c r="AO3" s="182"/>
-      <c r="AP3" s="182"/>
-      <c r="AQ3" s="182"/>
-      <c r="AR3" s="182"/>
+        <v>46181</v>
+      </c>
+      <c r="K3" s="273"/>
+      <c r="L3" s="273"/>
+      <c r="M3" s="273"/>
+      <c r="N3" s="274"/>
+      <c r="O3" s="274"/>
+      <c r="P3" s="274"/>
+      <c r="Q3" s="274"/>
+      <c r="R3" s="274"/>
+      <c r="S3" s="274"/>
+      <c r="T3" s="274"/>
+      <c r="U3" s="274"/>
+      <c r="V3" s="274"/>
+      <c r="W3" s="274"/>
+      <c r="X3" s="274"/>
+      <c r="Y3" s="274"/>
+      <c r="Z3" s="274"/>
+      <c r="AA3" s="274"/>
+      <c r="AB3" s="274"/>
+      <c r="AC3" s="274"/>
+      <c r="AD3" s="274"/>
+      <c r="AE3" s="274"/>
+      <c r="AF3" s="274"/>
+      <c r="AG3" s="274"/>
+      <c r="AH3" s="274"/>
+      <c r="AI3" s="274"/>
+      <c r="AJ3" s="274"/>
+      <c r="AK3" s="274"/>
+      <c r="AL3" s="274"/>
+      <c r="AM3" s="274"/>
+      <c r="AN3" s="274"/>
+      <c r="AO3" s="274"/>
+      <c r="AP3" s="274"/>
+      <c r="AQ3" s="274"/>
+      <c r="AR3" s="274"/>
     </row>
     <row r="4" spans="2:44" ht="15.75" thickBot="1">
-      <c r="B4" s="177"/>
+      <c r="B4" s="269"/>
       <c r="C4" s="78" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="82">
         <f ca="1">IF(MONTH(TODAY()-WEEKDAY(TODAY(),2)+1)&lt;MONTH(TODAY()),(TODAY()-28-DAY(TODAY())+7)-WEEKDAY((TODAY()-DAY(TODAY())+7),2)+1,(TODAY()-DAY(TODAY())+7)-WEEKDAY((TODAY()-DAY(TODAY())+7),2)+1)</f>
-        <v>46146</v>
-      </c>
-      <c r="E4" s="179"/>
-      <c r="F4" s="179"/>
-      <c r="G4" s="179"/>
-      <c r="H4" s="179"/>
-      <c r="I4" s="180"/>
-      <c r="J4" s="183">
+        <v>46174</v>
+      </c>
+      <c r="E4" s="271"/>
+      <c r="F4" s="271"/>
+      <c r="G4" s="271"/>
+      <c r="H4" s="271"/>
+      <c r="I4" s="272"/>
+      <c r="J4" s="275">
         <f ca="1">K5</f>
-        <v>46153</v>
-      </c>
-      <c r="K4" s="183"/>
-      <c r="L4" s="183"/>
-      <c r="M4" s="183"/>
-      <c r="N4" s="188">
+        <v>46181</v>
+      </c>
+      <c r="K4" s="275"/>
+      <c r="L4" s="275"/>
+      <c r="M4" s="275"/>
+      <c r="N4" s="280">
         <f ca="1">O5</f>
-        <v>46181</v>
-      </c>
-      <c r="O4" s="183"/>
-      <c r="P4" s="183"/>
-      <c r="Q4" s="183"/>
-      <c r="R4" s="183"/>
-      <c r="S4" s="183">
+        <v>46209</v>
+      </c>
+      <c r="O4" s="275"/>
+      <c r="P4" s="275"/>
+      <c r="Q4" s="275"/>
+      <c r="R4" s="275"/>
+      <c r="S4" s="275">
         <f ca="1">T5</f>
-        <v>46216</v>
-      </c>
-      <c r="T4" s="183"/>
-      <c r="U4" s="183"/>
-      <c r="V4" s="183"/>
-      <c r="W4" s="183">
+        <v>46244</v>
+      </c>
+      <c r="T4" s="275"/>
+      <c r="U4" s="275"/>
+      <c r="V4" s="275"/>
+      <c r="W4" s="275">
         <f ca="1">X5</f>
-        <v>46244</v>
-      </c>
-      <c r="X4" s="183"/>
-      <c r="Y4" s="183"/>
-      <c r="Z4" s="183"/>
-      <c r="AA4" s="183"/>
-      <c r="AB4" s="183">
+        <v>46272</v>
+      </c>
+      <c r="X4" s="275"/>
+      <c r="Y4" s="275"/>
+      <c r="Z4" s="275"/>
+      <c r="AA4" s="275"/>
+      <c r="AB4" s="275">
         <f ca="1">AC5</f>
-        <v>46279</v>
-      </c>
-      <c r="AC4" s="183"/>
-      <c r="AD4" s="183"/>
-      <c r="AE4" s="183"/>
-      <c r="AF4" s="183">
+        <v>46307</v>
+      </c>
+      <c r="AC4" s="275"/>
+      <c r="AD4" s="275"/>
+      <c r="AE4" s="275"/>
+      <c r="AF4" s="275">
         <f ca="1">AG5</f>
-        <v>46307</v>
-      </c>
-      <c r="AG4" s="183"/>
-      <c r="AH4" s="183"/>
-      <c r="AI4" s="183"/>
-      <c r="AJ4" s="183">
+        <v>46335</v>
+      </c>
+      <c r="AG4" s="275"/>
+      <c r="AH4" s="275"/>
+      <c r="AI4" s="275"/>
+      <c r="AJ4" s="275">
         <f ca="1">AK5</f>
-        <v>46335</v>
-      </c>
-      <c r="AK4" s="183"/>
-      <c r="AL4" s="183"/>
-      <c r="AM4" s="183"/>
-      <c r="AN4" s="183"/>
-      <c r="AO4" s="183">
+        <v>46363</v>
+      </c>
+      <c r="AK4" s="275"/>
+      <c r="AL4" s="275"/>
+      <c r="AM4" s="275"/>
+      <c r="AN4" s="275"/>
+      <c r="AO4" s="275">
         <f ca="1">AP5</f>
-        <v>46370</v>
-      </c>
-      <c r="AP4" s="183"/>
-      <c r="AQ4" s="183"/>
-      <c r="AR4" s="184"/>
+        <v>46398</v>
+      </c>
+      <c r="AP4" s="275"/>
+      <c r="AQ4" s="275"/>
+      <c r="AR4" s="276"/>
     </row>
     <row r="5" spans="2:44" ht="33" thickBot="1">
-      <c r="B5" s="178"/>
+      <c r="B5" s="270"/>
       <c r="C5" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="185" t="s">
+      <c r="D5" s="277" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="186"/>
-      <c r="F5" s="186"/>
-      <c r="G5" s="187"/>
+      <c r="E5" s="278"/>
+      <c r="F5" s="278"/>
+      <c r="G5" s="279"/>
       <c r="H5" s="81"/>
       <c r="I5" s="79" t="s">
         <v>2</v>
       </c>
       <c r="J5" s="41">
         <f ca="1">D4</f>
-        <v>46146</v>
+        <v>46174</v>
       </c>
       <c r="K5" s="42">
         <f ca="1">J5+7</f>
-        <v>46153</v>
+        <v>46181</v>
       </c>
       <c r="L5" s="42">
         <f t="shared" ref="L5:AR5" ca="1" si="0">K5+7</f>
-        <v>46160</v>
+        <v>46188</v>
       </c>
       <c r="M5" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>46167</v>
+        <v>46195</v>
       </c>
       <c r="N5" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>46174</v>
+        <v>46202</v>
       </c>
       <c r="O5" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>46181</v>
+        <v>46209</v>
       </c>
       <c r="P5" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>46188</v>
+        <v>46216</v>
       </c>
       <c r="Q5" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>46195</v>
+        <v>46223</v>
       </c>
       <c r="R5" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>46202</v>
+        <v>46230</v>
       </c>
       <c r="S5" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>46209</v>
+        <v>46237</v>
       </c>
       <c r="T5" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>46216</v>
+        <v>46244</v>
       </c>
       <c r="U5" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>46223</v>
+        <v>46251</v>
       </c>
       <c r="V5" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>46230</v>
+        <v>46258</v>
       </c>
       <c r="W5" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>46237</v>
+        <v>46265</v>
       </c>
       <c r="X5" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>46244</v>
+        <v>46272</v>
       </c>
       <c r="Y5" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>46251</v>
+        <v>46279</v>
       </c>
       <c r="Z5" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>46258</v>
+        <v>46286</v>
       </c>
       <c r="AA5" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>46265</v>
+        <v>46293</v>
       </c>
       <c r="AB5" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>46272</v>
+        <v>46300</v>
       </c>
       <c r="AC5" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>46279</v>
+        <v>46307</v>
       </c>
       <c r="AD5" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>46286</v>
+        <v>46314</v>
       </c>
       <c r="AE5" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>46293</v>
+        <v>46321</v>
       </c>
       <c r="AF5" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>46300</v>
+        <v>46328</v>
       </c>
       <c r="AG5" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>46307</v>
+        <v>46335</v>
       </c>
       <c r="AH5" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>46314</v>
+        <v>46342</v>
       </c>
       <c r="AI5" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>46321</v>
+        <v>46349</v>
       </c>
       <c r="AJ5" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>46328</v>
+        <v>46356</v>
       </c>
       <c r="AK5" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>46335</v>
+        <v>46363</v>
       </c>
       <c r="AL5" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>46342</v>
+        <v>46370</v>
       </c>
       <c r="AM5" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>46349</v>
+        <v>46377</v>
       </c>
       <c r="AN5" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>46356</v>
+        <v>46384</v>
       </c>
       <c r="AO5" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>46363</v>
+        <v>46391</v>
       </c>
       <c r="AP5" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>46370</v>
+        <v>46398</v>
       </c>
       <c r="AQ5" s="42">
         <f t="shared" ca="1" si="0"/>
-        <v>46377</v>
+        <v>46405</v>
       </c>
       <c r="AR5" s="43">
         <f t="shared" ca="1" si="0"/>
-        <v>46384</v>
+        <v>46412</v>
       </c>
     </row>
     <row r="6" spans="2:44" ht="17.25" thickBot="1">
@@ -6378,7 +10609,7 @@
       </c>
       <c r="M7" s="45" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>u</v>
+        <v/>
       </c>
       <c r="N7" s="45" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -6545,7 +10776,7 @@
       </c>
       <c r="M8" s="45" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v/>
+        <v>u</v>
       </c>
       <c r="N8" s="45" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -6561,7 +10792,7 @@
       </c>
       <c r="Q8" s="45" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>u</v>
+        <v/>
       </c>
       <c r="R8" s="45" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -6728,7 +10959,7 @@
       </c>
       <c r="Q9" s="45" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>u</v>
       </c>
       <c r="R9" s="45" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -6744,7 +10975,7 @@
       </c>
       <c r="U9" s="45" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>u</v>
+        <v/>
       </c>
       <c r="V9" s="45" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -6915,7 +11146,7 @@
       </c>
       <c r="V10" s="49" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>u</v>
       </c>
       <c r="W10" s="49" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -6931,7 +11162,7 @@
       </c>
       <c r="Z10" s="49" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>u</v>
+        <v/>
       </c>
       <c r="AA10" s="49" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -7102,7 +11333,7 @@
       </c>
       <c r="AA11" s="52" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>u</v>
       </c>
       <c r="AB11" s="52" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -7118,7 +11349,7 @@
       </c>
       <c r="AE11" s="52" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>u</v>
+        <v/>
       </c>
       <c r="AF11" s="52" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -7289,7 +11520,7 @@
       </c>
       <c r="AF12" s="52" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>u</v>
       </c>
       <c r="AG12" s="52" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -7305,7 +11536,7 @@
       </c>
       <c r="AJ12" s="52" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>u</v>
+        <v/>
       </c>
       <c r="AK12" s="52" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -7472,7 +11703,7 @@
       </c>
       <c r="AJ13" s="55" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>u</v>
       </c>
       <c r="AK13" s="55" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -7488,7 +11719,7 @@
       </c>
       <c r="AN13" s="55" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>u</v>
+        <v/>
       </c>
       <c r="AO13" s="55" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -7647,7 +11878,7 @@
       </c>
       <c r="AL14" s="55" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v/>
+        <v>u</v>
       </c>
       <c r="AM14" s="55" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -7663,7 +11894,7 @@
       </c>
       <c r="AP14" s="55" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>u</v>
+        <v/>
       </c>
       <c r="AQ14" s="55" t="str">
         <f t="shared" ref="K14:AR16" ca="1" si="4">IF(AQ$5=($F14-WEEKDAY($F14,2)+1),"u","")</f>
@@ -7818,7 +12049,7 @@
       </c>
       <c r="AM15" s="55" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v/>
+        <v>u</v>
       </c>
       <c r="AN15" s="55" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -7834,7 +12065,7 @@
       </c>
       <c r="AQ15" s="55" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>u</v>
+        <v/>
       </c>
       <c r="AR15" s="56" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -7989,7 +12220,7 @@
       </c>
       <c r="AN16" s="58" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v/>
+        <v>u</v>
       </c>
       <c r="AO16" s="58" t="str">
         <f t="shared" ca="1" si="4"/>
@@ -8005,7 +12236,7 @@
       </c>
       <c r="AR16" s="59" t="str">
         <f t="shared" ca="1" si="4"/>
-        <v>u</v>
+        <v/>
       </c>
     </row>
     <row r="17" spans="2:9">
@@ -8055,68 +12286,68 @@
     </row>
     <row r="24" spans="2:9" ht="15.75" thickBot="1"/>
     <row r="25" spans="2:9" ht="24.95" customHeight="1">
-      <c r="B25" s="164" t="s">
+      <c r="B25" s="256" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="165"/>
-      <c r="D25" s="165"/>
-      <c r="E25" s="165"/>
-      <c r="F25" s="165"/>
-      <c r="G25" s="165"/>
-      <c r="H25" s="165"/>
-      <c r="I25" s="166"/>
+      <c r="C25" s="257"/>
+      <c r="D25" s="257"/>
+      <c r="E25" s="257"/>
+      <c r="F25" s="257"/>
+      <c r="G25" s="257"/>
+      <c r="H25" s="257"/>
+      <c r="I25" s="258"/>
     </row>
     <row r="26" spans="2:9" ht="90" customHeight="1">
-      <c r="B26" s="167" t="s">
+      <c r="B26" s="259" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="168"/>
-      <c r="D26" s="168"/>
-      <c r="E26" s="168"/>
-      <c r="F26" s="168"/>
-      <c r="G26" s="168"/>
-      <c r="H26" s="168"/>
-      <c r="I26" s="169"/>
+      <c r="C26" s="260"/>
+      <c r="D26" s="260"/>
+      <c r="E26" s="260"/>
+      <c r="F26" s="260"/>
+      <c r="G26" s="260"/>
+      <c r="H26" s="260"/>
+      <c r="I26" s="261"/>
     </row>
     <row r="27" spans="2:9">
-      <c r="B27" s="167"/>
-      <c r="C27" s="168"/>
-      <c r="D27" s="168"/>
-      <c r="E27" s="168"/>
-      <c r="F27" s="168"/>
-      <c r="G27" s="168"/>
-      <c r="H27" s="168"/>
-      <c r="I27" s="169"/>
+      <c r="B27" s="259"/>
+      <c r="C27" s="260"/>
+      <c r="D27" s="260"/>
+      <c r="E27" s="260"/>
+      <c r="F27" s="260"/>
+      <c r="G27" s="260"/>
+      <c r="H27" s="260"/>
+      <c r="I27" s="261"/>
     </row>
     <row r="28" spans="2:9">
-      <c r="B28" s="167"/>
-      <c r="C28" s="168"/>
-      <c r="D28" s="168"/>
-      <c r="E28" s="168"/>
-      <c r="F28" s="168"/>
-      <c r="G28" s="168"/>
-      <c r="H28" s="168"/>
-      <c r="I28" s="169"/>
+      <c r="B28" s="259"/>
+      <c r="C28" s="260"/>
+      <c r="D28" s="260"/>
+      <c r="E28" s="260"/>
+      <c r="F28" s="260"/>
+      <c r="G28" s="260"/>
+      <c r="H28" s="260"/>
+      <c r="I28" s="261"/>
     </row>
     <row r="29" spans="2:9">
-      <c r="B29" s="167"/>
-      <c r="C29" s="168"/>
-      <c r="D29" s="168"/>
-      <c r="E29" s="168"/>
-      <c r="F29" s="168"/>
-      <c r="G29" s="168"/>
-      <c r="H29" s="168"/>
-      <c r="I29" s="169"/>
+      <c r="B29" s="259"/>
+      <c r="C29" s="260"/>
+      <c r="D29" s="260"/>
+      <c r="E29" s="260"/>
+      <c r="F29" s="260"/>
+      <c r="G29" s="260"/>
+      <c r="H29" s="260"/>
+      <c r="I29" s="261"/>
     </row>
     <row r="30" spans="2:9" ht="15.75" thickBot="1">
-      <c r="B30" s="170"/>
-      <c r="C30" s="171"/>
-      <c r="D30" s="171"/>
-      <c r="E30" s="171"/>
-      <c r="F30" s="171"/>
-      <c r="G30" s="171"/>
-      <c r="H30" s="171"/>
-      <c r="I30" s="172"/>
+      <c r="B30" s="262"/>
+      <c r="C30" s="263"/>
+      <c r="D30" s="263"/>
+      <c r="E30" s="263"/>
+      <c r="F30" s="263"/>
+      <c r="G30" s="263"/>
+      <c r="H30" s="263"/>
+      <c r="I30" s="264"/>
     </row>
   </sheetData>
   <mergeCells count="17">
@@ -8140,18 +12371,18 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H7:H16">
-    <cfRule type="containsText" dxfId="20" priority="9" operator="containsText" text="Blocked">
+    <cfRule type="containsText" dxfId="15" priority="9" operator="containsText" text="Blocked">
       <formula>NOT(ISERROR(SEARCH("Blocked",H7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7:AR16">
-    <cfRule type="expression" dxfId="19" priority="1">
+    <cfRule type="expression" dxfId="14" priority="1">
       <formula>AND($I7&gt;0, J$5 &lt;= ($E7+($F7-$E7)*$I7)-WEEKDAY(($E7+($F7-$E7)*$I7),2)+1, J$5 &gt;= $E7 - WEEKDAY($E7, 2)+1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="7">
+    <cfRule type="expression" dxfId="13" priority="7">
       <formula>AND(J$5&gt;=$E7-(WEEKDAY($E7, 2)+1),J$5&lt;=$F7)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="17" priority="8">
+    <cfRule type="expression" dxfId="12" priority="8">
       <formula>J$5=(TODAY()-WEEKDAY(TODAY(), 2) + 1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8165,7 +12396,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{041A2E35-3773-4B1B-BE4F-9CB3C9824D18}">
   <dimension ref="A2:P48"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15"/>
@@ -8179,150 +12410,150 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" ht="29.25" thickBot="1">
-      <c r="B2" s="190" t="s">
+      <c r="B2" s="282" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="191"/>
-      <c r="D2" s="191"/>
-      <c r="E2" s="191"/>
-      <c r="F2" s="191"/>
-      <c r="G2" s="191"/>
-      <c r="H2" s="191"/>
-      <c r="I2" s="191"/>
-      <c r="J2" s="191"/>
-      <c r="K2" s="191"/>
-      <c r="L2" s="191"/>
-      <c r="M2" s="191"/>
-      <c r="N2" s="191"/>
-      <c r="O2" s="191"/>
-      <c r="P2" s="192"/>
+      <c r="C2" s="283"/>
+      <c r="D2" s="283"/>
+      <c r="E2" s="283"/>
+      <c r="F2" s="283"/>
+      <c r="G2" s="283"/>
+      <c r="H2" s="283"/>
+      <c r="I2" s="283"/>
+      <c r="J2" s="283"/>
+      <c r="K2" s="283"/>
+      <c r="L2" s="283"/>
+      <c r="M2" s="283"/>
+      <c r="N2" s="283"/>
+      <c r="O2" s="283"/>
+      <c r="P2" s="284"/>
     </row>
     <row r="3" spans="2:16">
-      <c r="B3" s="193"/>
-      <c r="C3" s="194"/>
+      <c r="B3" s="285"/>
+      <c r="C3" s="286"/>
       <c r="D3" s="99" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="212" t="s">
+      <c r="E3" s="304" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="212"/>
-      <c r="G3" s="212"/>
-      <c r="H3" s="212"/>
-      <c r="I3" s="195" t="s">
+      <c r="F3" s="304"/>
+      <c r="G3" s="304"/>
+      <c r="H3" s="304"/>
+      <c r="I3" s="287" t="s">
         <v>46</v>
       </c>
-      <c r="J3" s="195"/>
-      <c r="K3" s="196" t="s">
+      <c r="J3" s="287"/>
+      <c r="K3" s="288" t="s">
         <v>17</v>
       </c>
-      <c r="L3" s="196"/>
-      <c r="M3" s="196"/>
-      <c r="N3" s="194"/>
-      <c r="O3" s="194"/>
-      <c r="P3" s="197"/>
+      <c r="L3" s="288"/>
+      <c r="M3" s="288"/>
+      <c r="N3" s="286"/>
+      <c r="O3" s="286"/>
+      <c r="P3" s="289"/>
     </row>
     <row r="4" spans="2:16" ht="15.75" thickBot="1">
-      <c r="B4" s="198"/>
-      <c r="C4" s="199"/>
-      <c r="D4" s="199"/>
-      <c r="E4" s="199"/>
-      <c r="F4" s="199"/>
-      <c r="G4" s="199"/>
-      <c r="H4" s="199"/>
-      <c r="I4" s="199"/>
-      <c r="J4" s="199"/>
-      <c r="K4" s="199"/>
-      <c r="L4" s="199"/>
-      <c r="M4" s="199"/>
-      <c r="N4" s="199"/>
-      <c r="O4" s="199"/>
-      <c r="P4" s="200"/>
+      <c r="B4" s="290"/>
+      <c r="C4" s="291"/>
+      <c r="D4" s="291"/>
+      <c r="E4" s="291"/>
+      <c r="F4" s="291"/>
+      <c r="G4" s="291"/>
+      <c r="H4" s="291"/>
+      <c r="I4" s="291"/>
+      <c r="J4" s="291"/>
+      <c r="K4" s="291"/>
+      <c r="L4" s="291"/>
+      <c r="M4" s="291"/>
+      <c r="N4" s="291"/>
+      <c r="O4" s="291"/>
+      <c r="P4" s="292"/>
     </row>
     <row r="5" spans="2:16" ht="15.75" thickBot="1">
-      <c r="B5" s="201" t="s">
+      <c r="B5" s="293" t="s">
         <v>79</v>
       </c>
-      <c r="C5" s="202"/>
-      <c r="D5" s="202"/>
-      <c r="E5" s="202"/>
-      <c r="F5" s="202"/>
-      <c r="G5" s="202"/>
-      <c r="H5" s="202"/>
-      <c r="I5" s="202"/>
-      <c r="J5" s="202"/>
-      <c r="K5" s="202"/>
-      <c r="L5" s="202"/>
-      <c r="M5" s="202"/>
-      <c r="N5" s="202"/>
-      <c r="O5" s="202"/>
-      <c r="P5" s="203"/>
+      <c r="C5" s="294"/>
+      <c r="D5" s="294"/>
+      <c r="E5" s="294"/>
+      <c r="F5" s="294"/>
+      <c r="G5" s="294"/>
+      <c r="H5" s="294"/>
+      <c r="I5" s="294"/>
+      <c r="J5" s="294"/>
+      <c r="K5" s="294"/>
+      <c r="L5" s="294"/>
+      <c r="M5" s="294"/>
+      <c r="N5" s="294"/>
+      <c r="O5" s="294"/>
+      <c r="P5" s="295"/>
     </row>
     <row r="6" spans="2:16" ht="129.75" customHeight="1" thickBot="1">
-      <c r="B6" s="204" t="s">
+      <c r="B6" s="296" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="205"/>
-      <c r="D6" s="206"/>
-      <c r="E6" s="207" t="s">
+      <c r="C6" s="297"/>
+      <c r="D6" s="298"/>
+      <c r="E6" s="299" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="207" t="s">
+      <c r="F6" s="299" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="207" t="s">
+      <c r="G6" s="299" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="207" t="s">
+      <c r="H6" s="299" t="s">
         <v>22</v>
       </c>
-      <c r="I6" s="207" t="s">
+      <c r="I6" s="299" t="s">
         <v>24</v>
       </c>
-      <c r="J6" s="207" t="s">
+      <c r="J6" s="299" t="s">
         <v>26</v>
       </c>
-      <c r="K6" s="207" t="s">
+      <c r="K6" s="299" t="s">
         <v>28</v>
       </c>
-      <c r="L6" s="207" t="s">
+      <c r="L6" s="299" t="s">
         <v>30</v>
       </c>
-      <c r="M6" s="207" t="s">
+      <c r="M6" s="299" t="s">
         <v>32</v>
       </c>
-      <c r="N6" s="189" t="s">
+      <c r="N6" s="281" t="s">
         <v>34</v>
       </c>
-      <c r="O6" s="189"/>
-      <c r="P6" s="189"/>
+      <c r="O6" s="281"/>
+      <c r="P6" s="281"/>
     </row>
     <row r="7" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B7" s="210" t="s">
+      <c r="B7" s="302" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="211"/>
+      <c r="C7" s="303"/>
       <c r="D7" s="114" t="s">
         <v>48</v>
       </c>
-      <c r="E7" s="207"/>
-      <c r="F7" s="207"/>
-      <c r="G7" s="207"/>
-      <c r="H7" s="207"/>
-      <c r="I7" s="207"/>
-      <c r="J7" s="207"/>
-      <c r="K7" s="207"/>
-      <c r="L7" s="207"/>
-      <c r="M7" s="207"/>
-      <c r="N7" s="189"/>
-      <c r="O7" s="189"/>
-      <c r="P7" s="189"/>
+      <c r="E7" s="299"/>
+      <c r="F7" s="299"/>
+      <c r="G7" s="299"/>
+      <c r="H7" s="299"/>
+      <c r="I7" s="299"/>
+      <c r="J7" s="299"/>
+      <c r="K7" s="299"/>
+      <c r="L7" s="299"/>
+      <c r="M7" s="299"/>
+      <c r="N7" s="281"/>
+      <c r="O7" s="281"/>
+      <c r="P7" s="281"/>
     </row>
     <row r="8" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B8" s="208" t="s">
+      <c r="B8" s="300" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="209"/>
+      <c r="C8" s="301"/>
       <c r="D8" s="100" t="s">
         <v>62</v>
       </c>
@@ -8360,10 +12591,10 @@
       <c r="P8" s="90"/>
     </row>
     <row r="9" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B9" s="208" t="s">
+      <c r="B9" s="300" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="209"/>
+      <c r="C9" s="301"/>
       <c r="D9" s="100" t="s">
         <v>50</v>
       </c>
@@ -8401,10 +12632,10 @@
       <c r="P9" s="94"/>
     </row>
     <row r="10" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B10" s="208" t="s">
+      <c r="B10" s="300" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="209"/>
+      <c r="C10" s="301"/>
       <c r="D10" s="100" t="s">
         <v>63</v>
       </c>
@@ -8442,10 +12673,10 @@
       <c r="P10" s="94"/>
     </row>
     <row r="11" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B11" s="208" t="s">
+      <c r="B11" s="300" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="209"/>
+      <c r="C11" s="301"/>
       <c r="D11" s="100" t="s">
         <v>64</v>
       </c>
@@ -8483,10 +12714,10 @@
       <c r="P11" s="94"/>
     </row>
     <row r="12" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B12" s="208" t="s">
+      <c r="B12" s="300" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="209"/>
+      <c r="C12" s="301"/>
       <c r="D12" s="100" t="s">
         <v>65</v>
       </c>
@@ -8524,10 +12755,10 @@
       <c r="P12" s="94"/>
     </row>
     <row r="13" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B13" s="208" t="s">
+      <c r="B13" s="300" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="209"/>
+      <c r="C13" s="301"/>
       <c r="D13" s="100" t="s">
         <v>66</v>
       </c>
@@ -8565,10 +12796,10 @@
       <c r="P13" s="94"/>
     </row>
     <row r="14" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B14" s="208" t="s">
+      <c r="B14" s="300" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="209"/>
+      <c r="C14" s="301"/>
       <c r="D14" s="100" t="s">
         <v>67</v>
       </c>
@@ -8606,10 +12837,10 @@
       <c r="P14" s="94"/>
     </row>
     <row r="15" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B15" s="208" t="s">
+      <c r="B15" s="300" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="209"/>
+      <c r="C15" s="301"/>
       <c r="D15" s="100" t="s">
         <v>68</v>
       </c>
@@ -8647,10 +12878,10 @@
       <c r="P15" s="94"/>
     </row>
     <row r="16" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B16" s="208" t="s">
+      <c r="B16" s="300" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="209"/>
+      <c r="C16" s="301"/>
       <c r="D16" s="100" t="s">
         <v>69</v>
       </c>
@@ -8688,10 +12919,10 @@
       <c r="P16" s="94"/>
     </row>
     <row r="17" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B17" s="208" t="s">
+      <c r="B17" s="300" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="209"/>
+      <c r="C17" s="301"/>
       <c r="D17" s="100" t="s">
         <v>70</v>
       </c>
@@ -8729,10 +12960,10 @@
       <c r="P17" s="94"/>
     </row>
     <row r="18" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B18" s="208" t="s">
+      <c r="B18" s="300" t="s">
         <v>71</v>
       </c>
-      <c r="C18" s="209"/>
+      <c r="C18" s="301"/>
       <c r="D18" s="100" t="s">
         <v>72</v>
       </c>
@@ -8770,10 +13001,10 @@
       <c r="P18" s="94"/>
     </row>
     <row r="19" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B19" s="208" t="s">
+      <c r="B19" s="300" t="s">
         <v>74</v>
       </c>
-      <c r="C19" s="209"/>
+      <c r="C19" s="301"/>
       <c r="D19" s="100" t="s">
         <v>77</v>
       </c>
@@ -8811,10 +13042,10 @@
       <c r="P19" s="94"/>
     </row>
     <row r="20" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B20" s="208" t="s">
+      <c r="B20" s="300" t="s">
         <v>75</v>
       </c>
-      <c r="C20" s="209"/>
+      <c r="C20" s="301"/>
       <c r="D20" s="100" t="s">
         <v>78</v>
       </c>
@@ -8852,10 +13083,10 @@
       <c r="P20" s="94"/>
     </row>
     <row r="21" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B21" s="208" t="s">
+      <c r="B21" s="300" t="s">
         <v>73</v>
       </c>
-      <c r="C21" s="209"/>
+      <c r="C21" s="301"/>
       <c r="D21" s="101" t="s">
         <v>76</v>
       </c>
@@ -8926,137 +13157,137 @@
       </c>
     </row>
     <row r="28" spans="2:16">
-      <c r="B28" s="221" t="s">
+      <c r="B28" s="313" t="s">
         <v>55</v>
       </c>
-      <c r="C28" s="222"/>
-      <c r="D28" s="222"/>
-      <c r="E28" s="222"/>
-      <c r="F28" s="222"/>
-      <c r="G28" s="222"/>
-      <c r="H28" s="222"/>
-      <c r="I28" s="222"/>
-      <c r="J28" s="222"/>
-      <c r="K28" s="222"/>
-      <c r="L28" s="222"/>
-      <c r="M28" s="222"/>
-      <c r="N28" s="222"/>
-      <c r="O28" s="222"/>
-      <c r="P28" s="223"/>
+      <c r="C28" s="314"/>
+      <c r="D28" s="314"/>
+      <c r="E28" s="314"/>
+      <c r="F28" s="314"/>
+      <c r="G28" s="314"/>
+      <c r="H28" s="314"/>
+      <c r="I28" s="314"/>
+      <c r="J28" s="314"/>
+      <c r="K28" s="314"/>
+      <c r="L28" s="314"/>
+      <c r="M28" s="314"/>
+      <c r="N28" s="314"/>
+      <c r="O28" s="314"/>
+      <c r="P28" s="315"/>
     </row>
     <row r="29" spans="2:16" ht="15" customHeight="1">
-      <c r="B29" s="213" t="s">
+      <c r="B29" s="305" t="s">
         <v>56</v>
       </c>
-      <c r="C29" s="214"/>
-      <c r="D29" s="214"/>
-      <c r="E29" s="214"/>
-      <c r="F29" s="214"/>
-      <c r="G29" s="214"/>
-      <c r="H29" s="214"/>
-      <c r="I29" s="214"/>
-      <c r="J29" s="214"/>
-      <c r="K29" s="214"/>
-      <c r="L29" s="214"/>
-      <c r="M29" s="214"/>
-      <c r="N29" s="214"/>
-      <c r="O29" s="214"/>
-      <c r="P29" s="215"/>
+      <c r="C29" s="306"/>
+      <c r="D29" s="306"/>
+      <c r="E29" s="306"/>
+      <c r="F29" s="306"/>
+      <c r="G29" s="306"/>
+      <c r="H29" s="306"/>
+      <c r="I29" s="306"/>
+      <c r="J29" s="306"/>
+      <c r="K29" s="306"/>
+      <c r="L29" s="306"/>
+      <c r="M29" s="306"/>
+      <c r="N29" s="306"/>
+      <c r="O29" s="306"/>
+      <c r="P29" s="307"/>
     </row>
     <row r="30" spans="2:16" ht="15" customHeight="1">
-      <c r="B30" s="213" t="s">
+      <c r="B30" s="305" t="s">
         <v>57</v>
       </c>
-      <c r="C30" s="214"/>
-      <c r="D30" s="214"/>
-      <c r="E30" s="214"/>
-      <c r="F30" s="214"/>
-      <c r="G30" s="214"/>
-      <c r="H30" s="214"/>
-      <c r="I30" s="214"/>
-      <c r="J30" s="214"/>
-      <c r="K30" s="214"/>
-      <c r="L30" s="214"/>
-      <c r="M30" s="214"/>
-      <c r="N30" s="214"/>
-      <c r="O30" s="214"/>
-      <c r="P30" s="215"/>
+      <c r="C30" s="306"/>
+      <c r="D30" s="306"/>
+      <c r="E30" s="306"/>
+      <c r="F30" s="306"/>
+      <c r="G30" s="306"/>
+      <c r="H30" s="306"/>
+      <c r="I30" s="306"/>
+      <c r="J30" s="306"/>
+      <c r="K30" s="306"/>
+      <c r="L30" s="306"/>
+      <c r="M30" s="306"/>
+      <c r="N30" s="306"/>
+      <c r="O30" s="306"/>
+      <c r="P30" s="307"/>
     </row>
     <row r="31" spans="2:16" ht="15" customHeight="1">
-      <c r="B31" s="213" t="s">
+      <c r="B31" s="305" t="s">
         <v>58</v>
       </c>
-      <c r="C31" s="214"/>
-      <c r="D31" s="214"/>
-      <c r="E31" s="214"/>
-      <c r="F31" s="214"/>
-      <c r="G31" s="214"/>
-      <c r="H31" s="214"/>
-      <c r="I31" s="214"/>
-      <c r="J31" s="214"/>
-      <c r="K31" s="214"/>
-      <c r="L31" s="214"/>
-      <c r="M31" s="214"/>
-      <c r="N31" s="214"/>
-      <c r="O31" s="214"/>
-      <c r="P31" s="215"/>
+      <c r="C31" s="306"/>
+      <c r="D31" s="306"/>
+      <c r="E31" s="306"/>
+      <c r="F31" s="306"/>
+      <c r="G31" s="306"/>
+      <c r="H31" s="306"/>
+      <c r="I31" s="306"/>
+      <c r="J31" s="306"/>
+      <c r="K31" s="306"/>
+      <c r="L31" s="306"/>
+      <c r="M31" s="306"/>
+      <c r="N31" s="306"/>
+      <c r="O31" s="306"/>
+      <c r="P31" s="307"/>
     </row>
     <row r="32" spans="2:16" ht="20.100000000000001" customHeight="1">
-      <c r="B32" s="213" t="s">
+      <c r="B32" s="305" t="s">
         <v>59</v>
       </c>
-      <c r="C32" s="216"/>
-      <c r="D32" s="216"/>
-      <c r="E32" s="216"/>
-      <c r="F32" s="216"/>
-      <c r="G32" s="216"/>
-      <c r="H32" s="216"/>
-      <c r="I32" s="216"/>
-      <c r="J32" s="216"/>
-      <c r="K32" s="216"/>
-      <c r="L32" s="216"/>
-      <c r="M32" s="216"/>
-      <c r="N32" s="216"/>
-      <c r="O32" s="216"/>
-      <c r="P32" s="217"/>
+      <c r="C32" s="308"/>
+      <c r="D32" s="308"/>
+      <c r="E32" s="308"/>
+      <c r="F32" s="308"/>
+      <c r="G32" s="308"/>
+      <c r="H32" s="308"/>
+      <c r="I32" s="308"/>
+      <c r="J32" s="308"/>
+      <c r="K32" s="308"/>
+      <c r="L32" s="308"/>
+      <c r="M32" s="308"/>
+      <c r="N32" s="308"/>
+      <c r="O32" s="308"/>
+      <c r="P32" s="309"/>
     </row>
     <row r="33" spans="1:16" ht="20.100000000000001" customHeight="1">
-      <c r="B33" s="213" t="s">
+      <c r="B33" s="305" t="s">
         <v>60</v>
       </c>
-      <c r="C33" s="216"/>
-      <c r="D33" s="216"/>
-      <c r="E33" s="216"/>
-      <c r="F33" s="216"/>
-      <c r="G33" s="216"/>
-      <c r="H33" s="216"/>
-      <c r="I33" s="216"/>
-      <c r="J33" s="216"/>
-      <c r="K33" s="216"/>
-      <c r="L33" s="216"/>
-      <c r="M33" s="216"/>
-      <c r="N33" s="216"/>
-      <c r="O33" s="216"/>
-      <c r="P33" s="217"/>
+      <c r="C33" s="308"/>
+      <c r="D33" s="308"/>
+      <c r="E33" s="308"/>
+      <c r="F33" s="308"/>
+      <c r="G33" s="308"/>
+      <c r="H33" s="308"/>
+      <c r="I33" s="308"/>
+      <c r="J33" s="308"/>
+      <c r="K33" s="308"/>
+      <c r="L33" s="308"/>
+      <c r="M33" s="308"/>
+      <c r="N33" s="308"/>
+      <c r="O33" s="308"/>
+      <c r="P33" s="309"/>
     </row>
     <row r="34" spans="1:16" ht="20.100000000000001" customHeight="1">
-      <c r="B34" s="218" t="s">
+      <c r="B34" s="310" t="s">
         <v>61</v>
       </c>
-      <c r="C34" s="219"/>
-      <c r="D34" s="219"/>
-      <c r="E34" s="219"/>
-      <c r="F34" s="219"/>
-      <c r="G34" s="219"/>
-      <c r="H34" s="219"/>
-      <c r="I34" s="219"/>
-      <c r="J34" s="219"/>
-      <c r="K34" s="219"/>
-      <c r="L34" s="219"/>
-      <c r="M34" s="219"/>
-      <c r="N34" s="219"/>
-      <c r="O34" s="219"/>
-      <c r="P34" s="220"/>
+      <c r="C34" s="311"/>
+      <c r="D34" s="311"/>
+      <c r="E34" s="311"/>
+      <c r="F34" s="311"/>
+      <c r="G34" s="311"/>
+      <c r="H34" s="311"/>
+      <c r="I34" s="311"/>
+      <c r="J34" s="311"/>
+      <c r="K34" s="311"/>
+      <c r="L34" s="311"/>
+      <c r="M34" s="311"/>
+      <c r="N34" s="311"/>
+      <c r="O34" s="311"/>
+      <c r="P34" s="312"/>
     </row>
     <row r="35" spans="1:16" ht="20.100000000000001" customHeight="1"/>
     <row r="39" spans="1:16" ht="15" customHeight="1"/>
@@ -9115,16 +13346,16 @@
     <mergeCell ref="I6:I7"/>
   </mergeCells>
   <conditionalFormatting sqref="E8:N21 B23:B26">
-    <cfRule type="containsText" dxfId="16" priority="1" operator="containsText" text="I">
+    <cfRule type="containsText" dxfId="11" priority="1" operator="containsText" text="I">
       <formula>NOT(ISERROR(SEARCH("I",B8)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="15" priority="2" operator="containsText" text="C">
+    <cfRule type="containsText" dxfId="10" priority="2" operator="containsText" text="C">
       <formula>NOT(ISERROR(SEARCH("C",B8)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="3" operator="containsText" text="A">
+    <cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="A">
       <formula>NOT(ISERROR(SEARCH("A",B8)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="13" priority="4" operator="containsText" text="R">
+    <cfRule type="containsText" dxfId="8" priority="4" operator="containsText" text="R">
       <formula>NOT(ISERROR(SEARCH("R",B8)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9138,7 +13369,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72973369-D106-4CF9-BD30-5E71A4B4AA76}">
   <dimension ref="A1:Y1000"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9164,20 +13395,20 @@
   <sheetData>
     <row r="1" spans="1:25" ht="33" customHeight="1" thickBot="1">
       <c r="A1" s="115"/>
-      <c r="B1" s="241" t="s">
+      <c r="B1" s="333" t="s">
         <v>111</v>
       </c>
-      <c r="C1" s="242"/>
-      <c r="D1" s="242"/>
-      <c r="E1" s="242"/>
-      <c r="F1" s="242"/>
-      <c r="G1" s="242"/>
-      <c r="H1" s="242"/>
-      <c r="I1" s="242"/>
-      <c r="J1" s="242"/>
-      <c r="K1" s="242"/>
-      <c r="L1" s="242"/>
-      <c r="M1" s="243"/>
+      <c r="C1" s="334"/>
+      <c r="D1" s="334"/>
+      <c r="E1" s="334"/>
+      <c r="F1" s="334"/>
+      <c r="G1" s="334"/>
+      <c r="H1" s="334"/>
+      <c r="I1" s="334"/>
+      <c r="J1" s="334"/>
+      <c r="K1" s="334"/>
+      <c r="L1" s="334"/>
+      <c r="M1" s="335"/>
       <c r="N1" s="115"/>
       <c r="O1" s="115"/>
       <c r="P1" s="115"/>
@@ -9201,16 +13432,16 @@
       <c r="E2" s="130" t="s">
         <v>112</v>
       </c>
-      <c r="F2" s="244"/>
-      <c r="G2" s="244"/>
-      <c r="H2" s="244"/>
+      <c r="F2" s="336"/>
+      <c r="G2" s="336"/>
+      <c r="H2" s="336"/>
       <c r="I2" s="132" t="s">
         <v>113</v>
       </c>
-      <c r="J2" s="245">
+      <c r="J2" s="337">
         <v>46173</v>
       </c>
-      <c r="K2" s="245"/>
+      <c r="K2" s="337"/>
       <c r="L2" s="133"/>
       <c r="M2" s="117"/>
       <c r="N2" s="115"/>
@@ -9271,18 +13502,18 @@
       <c r="C4" s="133"/>
       <c r="D4" s="133"/>
       <c r="E4" s="133"/>
-      <c r="F4" s="246" t="s">
+      <c r="F4" s="338" t="s">
         <v>118</v>
       </c>
-      <c r="G4" s="246"/>
-      <c r="H4" s="246"/>
+      <c r="G4" s="338"/>
+      <c r="H4" s="338"/>
       <c r="I4" s="133"/>
       <c r="J4" s="133"/>
-      <c r="K4" s="247" t="s">
+      <c r="K4" s="339" t="s">
         <v>137</v>
       </c>
-      <c r="L4" s="247"/>
-      <c r="M4" s="248"/>
+      <c r="L4" s="339"/>
+      <c r="M4" s="340"/>
       <c r="N4" s="115"/>
       <c r="O4" s="115"/>
       <c r="P4" s="115"/>
@@ -9339,10 +13570,10 @@
         <v>126</v>
       </c>
       <c r="N5" s="115"/>
-      <c r="O5" s="224" t="s">
+      <c r="O5" s="316" t="s">
         <v>131</v>
       </c>
-      <c r="P5" s="225"/>
+      <c r="P5" s="317"/>
       <c r="Q5" s="139" t="str">
         <f>Y$7</f>
         <v>Very Low</v>
@@ -9413,7 +13644,7 @@
         <v>Severe</v>
       </c>
       <c r="N6" s="115"/>
-      <c r="O6" s="226" t="s">
+      <c r="O6" s="318" t="s">
         <v>121</v>
       </c>
       <c r="P6" s="140" t="str">
@@ -9485,7 +13716,7 @@
         <v>Moderate</v>
       </c>
       <c r="N7" s="115"/>
-      <c r="O7" s="227"/>
+      <c r="O7" s="319"/>
       <c r="P7" s="140" t="str">
         <f>X$4</f>
         <v>High</v>
@@ -9555,7 +13786,7 @@
         <v>Moderate</v>
       </c>
       <c r="N8" s="115"/>
-      <c r="O8" s="227"/>
+      <c r="O8" s="319"/>
       <c r="P8" s="140" t="str">
         <f>X$5</f>
         <v>Medium</v>
@@ -9621,7 +13852,7 @@
         <v>Moderate</v>
       </c>
       <c r="N9" s="115"/>
-      <c r="O9" s="227"/>
+      <c r="O9" s="319"/>
       <c r="P9" s="140" t="str">
         <f>X$6</f>
         <v>Low</v>
@@ -9687,7 +13918,7 @@
         <v>Moderate</v>
       </c>
       <c r="N10" s="115"/>
-      <c r="O10" s="228"/>
+      <c r="O10" s="320"/>
       <c r="P10" s="151" t="str">
         <f>X$7</f>
         <v>Very Low</v>
@@ -9808,10 +14039,10 @@
         <v>Moderate</v>
       </c>
       <c r="N12" s="115"/>
-      <c r="O12" s="224" t="s">
+      <c r="O12" s="316" t="s">
         <v>131</v>
       </c>
-      <c r="P12" s="225"/>
+      <c r="P12" s="317"/>
       <c r="Q12" s="139" t="str">
         <f>Y$7</f>
         <v>Very Low</v>
@@ -9878,7 +14109,7 @@
         <v>Sustainable</v>
       </c>
       <c r="N13" s="115"/>
-      <c r="O13" s="226" t="s">
+      <c r="O13" s="318" t="s">
         <v>121</v>
       </c>
       <c r="P13" s="140" t="str">
@@ -9951,7 +14182,7 @@
         <v>Moderate</v>
       </c>
       <c r="N14" s="115"/>
-      <c r="O14" s="227"/>
+      <c r="O14" s="319"/>
       <c r="P14" s="140" t="str">
         <f>X$4</f>
         <v>High</v>
@@ -10022,7 +14253,7 @@
         <v>Severe</v>
       </c>
       <c r="N15" s="115"/>
-      <c r="O15" s="227"/>
+      <c r="O15" s="319"/>
       <c r="P15" s="140" t="str">
         <f>X$5</f>
         <v>Medium</v>
@@ -10065,7 +14296,7 @@
       <c r="K16" s="115"/>
       <c r="L16" s="115"/>
       <c r="N16" s="115"/>
-      <c r="O16" s="227"/>
+      <c r="O16" s="319"/>
       <c r="P16" s="140" t="str">
         <f>X$6</f>
         <v>Low</v>
@@ -10097,22 +14328,22 @@
     </row>
     <row r="17" spans="1:25" ht="42" customHeight="1" thickBot="1">
       <c r="A17" s="115"/>
-      <c r="B17" s="229" t="s">
+      <c r="B17" s="321" t="s">
         <v>141</v>
       </c>
-      <c r="C17" s="230"/>
-      <c r="D17" s="230"/>
-      <c r="E17" s="230"/>
-      <c r="F17" s="230"/>
-      <c r="G17" s="230"/>
-      <c r="H17" s="231"/>
-      <c r="I17" s="230"/>
-      <c r="J17" s="230"/>
-      <c r="K17" s="230"/>
-      <c r="L17" s="230"/>
-      <c r="M17" s="232"/>
+      <c r="C17" s="322"/>
+      <c r="D17" s="322"/>
+      <c r="E17" s="322"/>
+      <c r="F17" s="322"/>
+      <c r="G17" s="322"/>
+      <c r="H17" s="323"/>
+      <c r="I17" s="322"/>
+      <c r="J17" s="322"/>
+      <c r="K17" s="322"/>
+      <c r="L17" s="322"/>
+      <c r="M17" s="324"/>
       <c r="N17" s="115"/>
-      <c r="O17" s="228"/>
+      <c r="O17" s="320"/>
       <c r="P17" s="151" t="str">
         <f>X$7</f>
         <v>Very Low</v>
@@ -10144,20 +14375,20 @@
     </row>
     <row r="18" spans="1:25">
       <c r="A18" s="115"/>
-      <c r="B18" s="233" t="s">
+      <c r="B18" s="325" t="s">
         <v>142</v>
       </c>
-      <c r="C18" s="234"/>
-      <c r="D18" s="234"/>
-      <c r="E18" s="234"/>
-      <c r="F18" s="234"/>
-      <c r="G18" s="234"/>
-      <c r="H18" s="235"/>
-      <c r="I18" s="234"/>
-      <c r="J18" s="234"/>
-      <c r="K18" s="234"/>
-      <c r="L18" s="234"/>
-      <c r="M18" s="236"/>
+      <c r="C18" s="326"/>
+      <c r="D18" s="326"/>
+      <c r="E18" s="326"/>
+      <c r="F18" s="326"/>
+      <c r="G18" s="326"/>
+      <c r="H18" s="327"/>
+      <c r="I18" s="326"/>
+      <c r="J18" s="326"/>
+      <c r="K18" s="326"/>
+      <c r="L18" s="326"/>
+      <c r="M18" s="328"/>
       <c r="N18" s="115"/>
       <c r="O18" s="115"/>
       <c r="P18" s="115"/>
@@ -10173,20 +14404,20 @@
     </row>
     <row r="19" spans="1:25" ht="19.5" thickBot="1">
       <c r="A19" s="115"/>
-      <c r="B19" s="233" t="s">
+      <c r="B19" s="325" t="s">
         <v>143</v>
       </c>
-      <c r="C19" s="234"/>
-      <c r="D19" s="234"/>
-      <c r="E19" s="234"/>
-      <c r="F19" s="234"/>
-      <c r="G19" s="234"/>
-      <c r="H19" s="235"/>
-      <c r="I19" s="234"/>
-      <c r="J19" s="234"/>
-      <c r="K19" s="234"/>
-      <c r="L19" s="234"/>
-      <c r="M19" s="236"/>
+      <c r="C19" s="326"/>
+      <c r="D19" s="326"/>
+      <c r="E19" s="326"/>
+      <c r="F19" s="326"/>
+      <c r="G19" s="326"/>
+      <c r="H19" s="327"/>
+      <c r="I19" s="326"/>
+      <c r="J19" s="326"/>
+      <c r="K19" s="326"/>
+      <c r="L19" s="326"/>
+      <c r="M19" s="328"/>
       <c r="N19" s="115"/>
       <c r="O19" s="138" t="s">
         <v>139</v>
@@ -10204,25 +14435,25 @@
     </row>
     <row r="20" spans="1:25" ht="42" customHeight="1" thickBot="1">
       <c r="A20" s="115"/>
-      <c r="B20" s="233" t="s">
+      <c r="B20" s="325" t="s">
         <v>144</v>
       </c>
-      <c r="C20" s="234"/>
-      <c r="D20" s="234"/>
-      <c r="E20" s="234"/>
-      <c r="F20" s="234"/>
-      <c r="G20" s="234"/>
-      <c r="H20" s="235"/>
-      <c r="I20" s="234"/>
-      <c r="J20" s="234"/>
-      <c r="K20" s="234"/>
-      <c r="L20" s="234"/>
-      <c r="M20" s="236"/>
+      <c r="C20" s="326"/>
+      <c r="D20" s="326"/>
+      <c r="E20" s="326"/>
+      <c r="F20" s="326"/>
+      <c r="G20" s="326"/>
+      <c r="H20" s="327"/>
+      <c r="I20" s="326"/>
+      <c r="J20" s="326"/>
+      <c r="K20" s="326"/>
+      <c r="L20" s="326"/>
+      <c r="M20" s="328"/>
       <c r="N20" s="115"/>
-      <c r="O20" s="224" t="s">
+      <c r="O20" s="316" t="s">
         <v>131</v>
       </c>
-      <c r="P20" s="225"/>
+      <c r="P20" s="317"/>
       <c r="Q20" s="139" t="str">
         <f>Y$7</f>
         <v>Very Low</v>
@@ -10250,22 +14481,22 @@
     </row>
     <row r="21" spans="1:25" ht="42" customHeight="1" thickBot="1">
       <c r="A21" s="115"/>
-      <c r="B21" s="233" t="s">
+      <c r="B21" s="325" t="s">
         <v>145</v>
       </c>
-      <c r="C21" s="234"/>
-      <c r="D21" s="234"/>
-      <c r="E21" s="234"/>
-      <c r="F21" s="234"/>
-      <c r="G21" s="234"/>
-      <c r="H21" s="235"/>
-      <c r="I21" s="234"/>
-      <c r="J21" s="234"/>
-      <c r="K21" s="234"/>
-      <c r="L21" s="234"/>
-      <c r="M21" s="236"/>
+      <c r="C21" s="326"/>
+      <c r="D21" s="326"/>
+      <c r="E21" s="326"/>
+      <c r="F21" s="326"/>
+      <c r="G21" s="326"/>
+      <c r="H21" s="327"/>
+      <c r="I21" s="326"/>
+      <c r="J21" s="326"/>
+      <c r="K21" s="326"/>
+      <c r="L21" s="326"/>
+      <c r="M21" s="328"/>
       <c r="N21" s="115"/>
-      <c r="O21" s="226" t="s">
+      <c r="O21" s="318" t="s">
         <v>121</v>
       </c>
       <c r="P21" s="140" t="str">
@@ -10299,22 +14530,22 @@
     </row>
     <row r="22" spans="1:25" ht="42" customHeight="1" thickBot="1">
       <c r="A22" s="115"/>
-      <c r="B22" s="237" t="s">
+      <c r="B22" s="329" t="s">
         <v>146</v>
       </c>
-      <c r="C22" s="238"/>
-      <c r="D22" s="238"/>
-      <c r="E22" s="238"/>
-      <c r="F22" s="238"/>
-      <c r="G22" s="238"/>
-      <c r="H22" s="239"/>
-      <c r="I22" s="238"/>
-      <c r="J22" s="238"/>
-      <c r="K22" s="238"/>
-      <c r="L22" s="238"/>
-      <c r="M22" s="240"/>
+      <c r="C22" s="330"/>
+      <c r="D22" s="330"/>
+      <c r="E22" s="330"/>
+      <c r="F22" s="330"/>
+      <c r="G22" s="330"/>
+      <c r="H22" s="331"/>
+      <c r="I22" s="330"/>
+      <c r="J22" s="330"/>
+      <c r="K22" s="330"/>
+      <c r="L22" s="330"/>
+      <c r="M22" s="332"/>
       <c r="N22" s="115"/>
-      <c r="O22" s="227"/>
+      <c r="O22" s="319"/>
       <c r="P22" s="140" t="str">
         <f>X$4</f>
         <v>High</v>
@@ -10357,7 +14588,7 @@
       <c r="K23" s="115"/>
       <c r="L23" s="115"/>
       <c r="N23" s="115"/>
-      <c r="O23" s="227"/>
+      <c r="O23" s="319"/>
       <c r="P23" s="140" t="str">
         <f>X$5</f>
         <v>Medium</v>
@@ -10400,7 +14631,7 @@
       <c r="K24" s="115"/>
       <c r="L24" s="115"/>
       <c r="N24" s="115"/>
-      <c r="O24" s="227"/>
+      <c r="O24" s="319"/>
       <c r="P24" s="140" t="str">
         <f>X$6</f>
         <v>Low</v>
@@ -10443,7 +14674,7 @@
       <c r="K25" s="115"/>
       <c r="L25" s="115"/>
       <c r="N25" s="115"/>
-      <c r="O25" s="228"/>
+      <c r="O25" s="320"/>
       <c r="P25" s="151" t="str">
         <f>X$7</f>
         <v>Very Low</v>
@@ -34869,30 +39100,30 @@
     <mergeCell ref="B22:M22"/>
   </mergeCells>
   <conditionalFormatting sqref="H6:H15">
-    <cfRule type="containsText" dxfId="12" priority="13" operator="containsText" text="Sustainable">
+    <cfRule type="containsText" dxfId="7" priority="13" operator="containsText" text="Sustainable">
       <formula>NOT(ISERROR(SEARCH("Sustainable",H6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="11" priority="14" operator="containsText" text="Moderate">
+    <cfRule type="containsText" dxfId="6" priority="14" operator="containsText" text="Moderate">
       <formula>NOT(ISERROR(SEARCH("Moderate",H6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="15" operator="containsText" text="Critical">
+    <cfRule type="containsText" dxfId="5" priority="15" operator="containsText" text="Critical">
       <formula>NOT(ISERROR(SEARCH("Critical",H6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="9" priority="16" operator="containsText" text="Severe">
+    <cfRule type="containsText" dxfId="4" priority="16" operator="containsText" text="Severe">
       <formula>NOT(ISERROR(SEARCH("Severe",H6)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M6:M15">
-    <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="Sustainable">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="Sustainable">
       <formula>NOT(ISERROR(SEARCH("Sustainable",M6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="Moderate">
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="Moderate">
       <formula>NOT(ISERROR(SEARCH("Moderate",M6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="Critical">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="Critical">
       <formula>NOT(ISERROR(SEARCH("Critical",M6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="4" operator="containsText" text="Severe">
+    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="Severe">
       <formula>NOT(ISERROR(SEARCH("Severe",M6)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -34908,7 +39139,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F843D7-B818-4CF8-9731-186E42EDF19F}">
   <dimension ref="B1:M29"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -34924,521 +39155,521 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13" ht="24" customHeight="1">
-      <c r="B1" s="251" t="s">
+      <c r="B1" s="341" t="s">
         <v>185</v>
       </c>
-      <c r="C1" s="251"/>
-      <c r="D1" s="251"/>
-      <c r="E1" s="251"/>
-      <c r="F1" s="251"/>
-      <c r="G1" s="251"/>
-      <c r="H1" s="251"/>
-      <c r="I1" s="251"/>
-      <c r="J1" s="251"/>
+      <c r="C1" s="341"/>
+      <c r="D1" s="341"/>
+      <c r="E1" s="341"/>
+      <c r="F1" s="341"/>
+      <c r="G1" s="341"/>
+      <c r="H1" s="341"/>
+      <c r="I1" s="341"/>
+      <c r="J1" s="341"/>
     </row>
     <row r="2" spans="2:13" ht="24" customHeight="1">
-      <c r="B2" s="251"/>
-      <c r="C2" s="251"/>
-      <c r="D2" s="251"/>
-      <c r="E2" s="251"/>
-      <c r="F2" s="251"/>
-      <c r="G2" s="251"/>
-      <c r="H2" s="251"/>
-      <c r="I2" s="251"/>
-      <c r="J2" s="251"/>
+      <c r="B2" s="341"/>
+      <c r="C2" s="341"/>
+      <c r="D2" s="341"/>
+      <c r="E2" s="341"/>
+      <c r="F2" s="341"/>
+      <c r="G2" s="341"/>
+      <c r="H2" s="341"/>
+      <c r="I2" s="341"/>
+      <c r="J2" s="341"/>
     </row>
     <row r="3" spans="2:13" ht="24" customHeight="1" thickBot="1">
-      <c r="B3" s="250"/>
-      <c r="C3" s="251"/>
-      <c r="D3" s="251"/>
-      <c r="E3" s="251"/>
-      <c r="F3" s="251"/>
-      <c r="G3" s="251"/>
-      <c r="H3" s="251"/>
-      <c r="I3" s="251"/>
-      <c r="J3" s="252"/>
+      <c r="B3" s="342"/>
+      <c r="C3" s="341"/>
+      <c r="D3" s="341"/>
+      <c r="E3" s="341"/>
+      <c r="F3" s="341"/>
+      <c r="G3" s="341"/>
+      <c r="H3" s="341"/>
+      <c r="I3" s="341"/>
+      <c r="J3" s="343"/>
     </row>
     <row r="4" spans="2:13" ht="24" customHeight="1" thickBot="1">
-      <c r="B4" s="253"/>
-      <c r="C4" s="254" t="s">
+      <c r="B4" s="161"/>
+      <c r="C4" s="162" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="278" t="s">
+      <c r="D4" s="356" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="279"/>
-      <c r="F4" s="255"/>
-      <c r="G4" s="254" t="s">
+      <c r="E4" s="357"/>
+      <c r="F4" s="163"/>
+      <c r="G4" s="162" t="s">
         <v>186</v>
       </c>
-      <c r="H4" s="278" t="s">
+      <c r="H4" s="356" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="279"/>
-      <c r="J4" s="256"/>
+      <c r="I4" s="357"/>
+      <c r="J4" s="164"/>
     </row>
     <row r="5" spans="2:13" ht="24" customHeight="1" thickBot="1">
-      <c r="B5" s="280"/>
-      <c r="C5" s="281"/>
-      <c r="D5" s="281"/>
-      <c r="E5" s="281"/>
-      <c r="F5" s="281"/>
-      <c r="G5" s="281"/>
-      <c r="H5" s="281"/>
-      <c r="I5" s="281"/>
-      <c r="J5" s="282"/>
+      <c r="B5" s="344"/>
+      <c r="C5" s="345"/>
+      <c r="D5" s="345"/>
+      <c r="E5" s="345"/>
+      <c r="F5" s="345"/>
+      <c r="G5" s="345"/>
+      <c r="H5" s="345"/>
+      <c r="I5" s="345"/>
+      <c r="J5" s="346"/>
     </row>
     <row r="6" spans="2:13" ht="45.75" customHeight="1">
-      <c r="B6" s="258" t="s">
+      <c r="B6" s="165" t="s">
         <v>187</v>
       </c>
-      <c r="C6" s="258" t="s">
+      <c r="C6" s="165" t="s">
         <v>188</v>
       </c>
-      <c r="D6" s="258" t="s">
+      <c r="D6" s="165" t="s">
         <v>189</v>
       </c>
-      <c r="E6" s="258" t="s">
+      <c r="E6" s="165" t="s">
         <v>190</v>
       </c>
-      <c r="F6" s="258" t="s">
+      <c r="F6" s="165" t="s">
         <v>191</v>
       </c>
-      <c r="G6" s="258" t="s">
+      <c r="G6" s="165" t="s">
         <v>192</v>
       </c>
-      <c r="H6" s="258" t="s">
+      <c r="H6" s="165" t="s">
         <v>5</v>
       </c>
-      <c r="I6" s="258" t="s">
+      <c r="I6" s="165" t="s">
         <v>193</v>
       </c>
-      <c r="J6" s="259" t="s">
+      <c r="J6" s="166" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="7" spans="2:13" ht="45" customHeight="1">
-      <c r="B7" s="267" t="s">
+      <c r="B7" s="174" t="s">
         <v>202</v>
       </c>
-      <c r="C7" s="268" t="s">
+      <c r="C7" s="175" t="s">
         <v>203</v>
       </c>
-      <c r="D7" s="268" t="s">
+      <c r="D7" s="175" t="s">
         <v>204</v>
       </c>
-      <c r="E7" s="268" t="s">
+      <c r="E7" s="175" t="s">
         <v>205</v>
       </c>
-      <c r="F7" s="268" t="s">
+      <c r="F7" s="175" t="s">
         <v>206</v>
       </c>
-      <c r="G7" s="268" t="s">
+      <c r="G7" s="175" t="s">
         <v>207</v>
       </c>
-      <c r="H7" s="268" t="s">
+      <c r="H7" s="175" t="s">
         <v>71</v>
       </c>
-      <c r="I7" s="268" t="s">
+      <c r="I7" s="175" t="s">
         <v>208</v>
       </c>
-      <c r="J7" s="269" t="s">
+      <c r="J7" s="176" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="8" spans="2:13" ht="45" customHeight="1">
-      <c r="B8" s="270" t="s">
+      <c r="B8" s="177" t="s">
         <v>209</v>
       </c>
-      <c r="C8" s="271" t="s">
+      <c r="C8" s="178" t="s">
         <v>210</v>
       </c>
-      <c r="D8" s="271" t="s">
+      <c r="D8" s="178" t="s">
         <v>204</v>
       </c>
-      <c r="E8" s="271" t="s">
+      <c r="E8" s="178" t="s">
         <v>211</v>
       </c>
-      <c r="F8" s="271" t="s">
+      <c r="F8" s="178" t="s">
         <v>212</v>
       </c>
-      <c r="G8" s="271" t="s">
+      <c r="G8" s="178" t="s">
         <v>213</v>
       </c>
-      <c r="H8" s="271" t="s">
+      <c r="H8" s="178" t="s">
         <v>27</v>
       </c>
-      <c r="I8" s="271" t="s">
+      <c r="I8" s="178" t="s">
         <v>214</v>
       </c>
-      <c r="J8" s="272" t="s">
+      <c r="J8" s="179" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="9" spans="2:13" ht="45" customHeight="1">
-      <c r="B9" s="270" t="s">
+      <c r="B9" s="177" t="s">
         <v>215</v>
       </c>
-      <c r="C9" s="271" t="s">
+      <c r="C9" s="178" t="s">
         <v>216</v>
       </c>
-      <c r="D9" s="271" t="s">
+      <c r="D9" s="178" t="s">
         <v>217</v>
       </c>
-      <c r="E9" s="271" t="s">
+      <c r="E9" s="178" t="s">
         <v>218</v>
       </c>
-      <c r="F9" s="271" t="s">
+      <c r="F9" s="178" t="s">
         <v>219</v>
       </c>
-      <c r="G9" s="271" t="s">
+      <c r="G9" s="178" t="s">
         <v>220</v>
       </c>
-      <c r="H9" s="271" t="s">
+      <c r="H9" s="178" t="s">
         <v>25</v>
       </c>
-      <c r="I9" s="271" t="s">
+      <c r="I9" s="178" t="s">
         <v>221</v>
       </c>
-      <c r="J9" s="272" t="s">
+      <c r="J9" s="179" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="10" spans="2:13" ht="45" customHeight="1">
-      <c r="B10" s="270" t="s">
+      <c r="B10" s="177" t="s">
         <v>222</v>
       </c>
-      <c r="C10" s="271" t="s">
+      <c r="C10" s="178" t="s">
         <v>223</v>
       </c>
-      <c r="D10" s="271" t="s">
+      <c r="D10" s="178" t="s">
         <v>204</v>
       </c>
-      <c r="E10" s="271" t="s">
+      <c r="E10" s="178" t="s">
         <v>218</v>
       </c>
-      <c r="F10" s="271" t="s">
+      <c r="F10" s="178" t="s">
         <v>219</v>
       </c>
-      <c r="G10" s="271" t="s">
+      <c r="G10" s="178" t="s">
         <v>224</v>
       </c>
-      <c r="H10" s="271" t="s">
+      <c r="H10" s="178" t="s">
         <v>25</v>
       </c>
-      <c r="I10" s="271" t="s">
+      <c r="I10" s="178" t="s">
         <v>225</v>
       </c>
-      <c r="J10" s="272" t="s">
+      <c r="J10" s="179" t="s">
         <v>197</v>
       </c>
-      <c r="M10" s="276" t="s">
+      <c r="M10" s="183" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="11" spans="2:13" ht="45" customHeight="1">
-      <c r="B11" s="270" t="s">
+      <c r="B11" s="177" t="s">
         <v>226</v>
       </c>
-      <c r="C11" s="271" t="s">
+      <c r="C11" s="178" t="s">
         <v>227</v>
       </c>
-      <c r="D11" s="271" t="s">
+      <c r="D11" s="178" t="s">
         <v>228</v>
       </c>
-      <c r="E11" s="271" t="s">
+      <c r="E11" s="178" t="s">
         <v>229</v>
       </c>
-      <c r="F11" s="271" t="s">
+      <c r="F11" s="178" t="s">
         <v>230</v>
       </c>
-      <c r="G11" s="271" t="s">
+      <c r="G11" s="178" t="s">
         <v>231</v>
       </c>
-      <c r="H11" s="271" t="s">
+      <c r="H11" s="178" t="s">
         <v>21</v>
       </c>
-      <c r="I11" s="271" t="s">
+      <c r="I11" s="178" t="s">
         <v>232</v>
       </c>
-      <c r="J11" s="272" t="s">
+      <c r="J11" s="179" t="s">
         <v>196</v>
       </c>
-      <c r="M11" s="277" t="s">
+      <c r="M11" s="184" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="12" spans="2:13" ht="45" customHeight="1">
-      <c r="B12" s="270" t="s">
+      <c r="B12" s="177" t="s">
         <v>233</v>
       </c>
-      <c r="C12" s="271" t="s">
+      <c r="C12" s="178" t="s">
         <v>234</v>
       </c>
-      <c r="D12" s="271" t="s">
+      <c r="D12" s="178" t="s">
         <v>217</v>
       </c>
-      <c r="E12" s="271" t="s">
+      <c r="E12" s="178" t="s">
         <v>235</v>
       </c>
-      <c r="F12" s="271" t="s">
+      <c r="F12" s="178" t="s">
         <v>236</v>
       </c>
-      <c r="G12" s="271" t="s">
+      <c r="G12" s="178" t="s">
         <v>237</v>
       </c>
-      <c r="H12" s="271" t="s">
+      <c r="H12" s="178" t="s">
         <v>27</v>
       </c>
-      <c r="I12" s="271" t="s">
+      <c r="I12" s="178" t="s">
         <v>238</v>
       </c>
-      <c r="J12" s="272" t="s">
+      <c r="J12" s="179" t="s">
         <v>196</v>
       </c>
-      <c r="M12" s="277" t="s">
+      <c r="M12" s="184" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="13" spans="2:13" ht="45" customHeight="1">
-      <c r="B13" s="270" t="s">
+      <c r="B13" s="177" t="s">
         <v>239</v>
       </c>
-      <c r="C13" s="271" t="s">
+      <c r="C13" s="178" t="s">
         <v>240</v>
       </c>
-      <c r="D13" s="271" t="s">
+      <c r="D13" s="178" t="s">
         <v>204</v>
       </c>
-      <c r="E13" s="271" t="s">
+      <c r="E13" s="178" t="s">
         <v>241</v>
       </c>
-      <c r="F13" s="271" t="s">
+      <c r="F13" s="178" t="s">
         <v>242</v>
       </c>
-      <c r="G13" s="271" t="s">
+      <c r="G13" s="178" t="s">
         <v>243</v>
       </c>
-      <c r="H13" s="271" t="s">
+      <c r="H13" s="178" t="s">
         <v>27</v>
       </c>
-      <c r="I13" s="271" t="s">
+      <c r="I13" s="178" t="s">
         <v>244</v>
       </c>
-      <c r="J13" s="272" t="s">
+      <c r="J13" s="179" t="s">
         <v>195</v>
       </c>
-      <c r="M13" s="277" t="s">
+      <c r="M13" s="184" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="14" spans="2:13" ht="45" customHeight="1">
-      <c r="B14" s="270" t="s">
+      <c r="B14" s="177" t="s">
         <v>245</v>
       </c>
-      <c r="C14" s="271" t="s">
+      <c r="C14" s="178" t="s">
         <v>246</v>
       </c>
-      <c r="D14" s="271" t="s">
+      <c r="D14" s="178" t="s">
         <v>217</v>
       </c>
-      <c r="E14" s="271" t="s">
+      <c r="E14" s="178" t="s">
         <v>247</v>
       </c>
-      <c r="F14" s="271" t="s">
+      <c r="F14" s="178" t="s">
         <v>248</v>
       </c>
-      <c r="G14" s="271" t="s">
+      <c r="G14" s="178" t="s">
         <v>249</v>
       </c>
-      <c r="H14" s="271" t="s">
+      <c r="H14" s="178" t="s">
         <v>23</v>
       </c>
-      <c r="I14" s="271" t="s">
+      <c r="I14" s="178" t="s">
         <v>250</v>
       </c>
-      <c r="J14" s="272" t="s">
+      <c r="J14" s="179" t="s">
         <v>197</v>
       </c>
-      <c r="M14" s="277" t="s">
+      <c r="M14" s="184" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="15" spans="2:13" ht="45" customHeight="1">
-      <c r="B15" s="270" t="s">
+      <c r="B15" s="177" t="s">
         <v>251</v>
       </c>
-      <c r="C15" s="271" t="s">
+      <c r="C15" s="178" t="s">
         <v>252</v>
       </c>
-      <c r="D15" s="271" t="s">
+      <c r="D15" s="178" t="s">
         <v>253</v>
       </c>
-      <c r="E15" s="271" t="s">
+      <c r="E15" s="178" t="s">
         <v>254</v>
       </c>
-      <c r="F15" s="271" t="s">
+      <c r="F15" s="178" t="s">
         <v>255</v>
       </c>
-      <c r="G15" s="271" t="s">
+      <c r="G15" s="178" t="s">
         <v>256</v>
       </c>
-      <c r="H15" s="271" t="s">
+      <c r="H15" s="178" t="s">
         <v>71</v>
       </c>
-      <c r="I15" s="271" t="s">
+      <c r="I15" s="178" t="s">
         <v>257</v>
       </c>
-      <c r="J15" s="272" t="s">
+      <c r="J15" s="179" t="s">
         <v>198</v>
       </c>
-      <c r="M15" s="277" t="s">
+      <c r="M15" s="184" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="16" spans="2:13" ht="45" customHeight="1">
-      <c r="B16" s="270" t="s">
+      <c r="B16" s="177" t="s">
         <v>258</v>
       </c>
-      <c r="C16" s="271" t="s">
+      <c r="C16" s="178" t="s">
         <v>259</v>
       </c>
-      <c r="D16" s="271" t="s">
+      <c r="D16" s="178" t="s">
         <v>228</v>
       </c>
-      <c r="E16" s="271" t="s">
+      <c r="E16" s="178" t="s">
         <v>260</v>
       </c>
-      <c r="F16" s="271" t="s">
+      <c r="F16" s="178" t="s">
         <v>261</v>
       </c>
-      <c r="G16" s="271" t="s">
+      <c r="G16" s="178" t="s">
         <v>262</v>
       </c>
-      <c r="H16" s="271" t="s">
+      <c r="H16" s="178" t="s">
         <v>25</v>
       </c>
-      <c r="I16" s="271" t="s">
+      <c r="I16" s="178" t="s">
         <v>263</v>
       </c>
-      <c r="J16" s="272" t="s">
+      <c r="J16" s="179" t="s">
         <v>195</v>
       </c>
-      <c r="M16" s="277" t="s">
+      <c r="M16" s="184" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="17" spans="2:10" ht="30" customHeight="1">
-      <c r="B17" s="270"/>
-      <c r="C17" s="271"/>
-      <c r="D17" s="271"/>
-      <c r="E17" s="271"/>
-      <c r="F17" s="271"/>
-      <c r="G17" s="271"/>
-      <c r="H17" s="271"/>
-      <c r="I17" s="271"/>
-      <c r="J17" s="272"/>
+      <c r="B17" s="177"/>
+      <c r="C17" s="178"/>
+      <c r="D17" s="178"/>
+      <c r="E17" s="178"/>
+      <c r="F17" s="178"/>
+      <c r="G17" s="178"/>
+      <c r="H17" s="178"/>
+      <c r="I17" s="178"/>
+      <c r="J17" s="179"/>
     </row>
     <row r="18" spans="2:10" ht="30" customHeight="1">
-      <c r="B18" s="270"/>
-      <c r="C18" s="271"/>
-      <c r="D18" s="271"/>
-      <c r="E18" s="271"/>
-      <c r="F18" s="271"/>
-      <c r="G18" s="271"/>
-      <c r="H18" s="271"/>
-      <c r="I18" s="271"/>
-      <c r="J18" s="272"/>
+      <c r="B18" s="177"/>
+      <c r="C18" s="178"/>
+      <c r="D18" s="178"/>
+      <c r="E18" s="178"/>
+      <c r="F18" s="178"/>
+      <c r="G18" s="178"/>
+      <c r="H18" s="178"/>
+      <c r="I18" s="178"/>
+      <c r="J18" s="179"/>
     </row>
     <row r="19" spans="2:10" ht="30" customHeight="1">
-      <c r="B19" s="270"/>
-      <c r="C19" s="271"/>
-      <c r="D19" s="271"/>
-      <c r="E19" s="271"/>
-      <c r="F19" s="271"/>
-      <c r="G19" s="271"/>
-      <c r="H19" s="271"/>
-      <c r="I19" s="271"/>
-      <c r="J19" s="272"/>
+      <c r="B19" s="177"/>
+      <c r="C19" s="178"/>
+      <c r="D19" s="178"/>
+      <c r="E19" s="178"/>
+      <c r="F19" s="178"/>
+      <c r="G19" s="178"/>
+      <c r="H19" s="178"/>
+      <c r="I19" s="178"/>
+      <c r="J19" s="179"/>
     </row>
     <row r="20" spans="2:10" ht="30" customHeight="1">
-      <c r="B20" s="270"/>
-      <c r="C20" s="271"/>
-      <c r="D20" s="271"/>
-      <c r="E20" s="271"/>
-      <c r="F20" s="271"/>
-      <c r="G20" s="271"/>
-      <c r="H20" s="271"/>
-      <c r="I20" s="271"/>
-      <c r="J20" s="272"/>
+      <c r="B20" s="177"/>
+      <c r="C20" s="178"/>
+      <c r="D20" s="178"/>
+      <c r="E20" s="178"/>
+      <c r="F20" s="178"/>
+      <c r="G20" s="178"/>
+      <c r="H20" s="178"/>
+      <c r="I20" s="178"/>
+      <c r="J20" s="179"/>
     </row>
     <row r="21" spans="2:10" ht="30" customHeight="1" thickBot="1">
-      <c r="B21" s="273"/>
-      <c r="C21" s="274"/>
-      <c r="D21" s="274"/>
-      <c r="E21" s="274"/>
-      <c r="F21" s="274"/>
-      <c r="G21" s="274"/>
-      <c r="H21" s="274"/>
-      <c r="I21" s="274"/>
-      <c r="J21" s="275"/>
+      <c r="B21" s="180"/>
+      <c r="C21" s="181"/>
+      <c r="D21" s="181"/>
+      <c r="E21" s="181"/>
+      <c r="F21" s="181"/>
+      <c r="G21" s="181"/>
+      <c r="H21" s="181"/>
+      <c r="I21" s="181"/>
+      <c r="J21" s="182"/>
     </row>
     <row r="23" spans="2:10" ht="15.75" thickBot="1"/>
     <row r="24" spans="2:10" ht="16.5" thickBot="1">
-      <c r="B24" s="283" t="s">
+      <c r="B24" s="353" t="s">
         <v>264</v>
       </c>
-      <c r="C24" s="284"/>
-      <c r="D24" s="284"/>
-      <c r="E24" s="284"/>
-      <c r="F24" s="285"/>
+      <c r="C24" s="354"/>
+      <c r="D24" s="354"/>
+      <c r="E24" s="354"/>
+      <c r="F24" s="355"/>
     </row>
     <row r="25" spans="2:10" ht="30" customHeight="1">
-      <c r="B25" s="286" t="s">
+      <c r="B25" s="347" t="s">
         <v>265</v>
       </c>
-      <c r="C25" s="287"/>
-      <c r="D25" s="287"/>
-      <c r="E25" s="287"/>
-      <c r="F25" s="288"/>
+      <c r="C25" s="348"/>
+      <c r="D25" s="348"/>
+      <c r="E25" s="348"/>
+      <c r="F25" s="349"/>
     </row>
     <row r="26" spans="2:10" ht="30" customHeight="1">
-      <c r="B26" s="286"/>
-      <c r="C26" s="287"/>
-      <c r="D26" s="287"/>
-      <c r="E26" s="287"/>
-      <c r="F26" s="288"/>
+      <c r="B26" s="347"/>
+      <c r="C26" s="348"/>
+      <c r="D26" s="348"/>
+      <c r="E26" s="348"/>
+      <c r="F26" s="349"/>
     </row>
     <row r="27" spans="2:10" ht="30" customHeight="1">
-      <c r="B27" s="286"/>
-      <c r="C27" s="287"/>
-      <c r="D27" s="287"/>
-      <c r="E27" s="287"/>
-      <c r="F27" s="288"/>
+      <c r="B27" s="347"/>
+      <c r="C27" s="348"/>
+      <c r="D27" s="348"/>
+      <c r="E27" s="348"/>
+      <c r="F27" s="349"/>
     </row>
     <row r="28" spans="2:10" ht="30" customHeight="1">
-      <c r="B28" s="286"/>
-      <c r="C28" s="287"/>
-      <c r="D28" s="287"/>
-      <c r="E28" s="287"/>
-      <c r="F28" s="288"/>
+      <c r="B28" s="347"/>
+      <c r="C28" s="348"/>
+      <c r="D28" s="348"/>
+      <c r="E28" s="348"/>
+      <c r="F28" s="349"/>
     </row>
     <row r="29" spans="2:10" ht="30" customHeight="1" thickBot="1">
-      <c r="B29" s="289"/>
-      <c r="C29" s="290"/>
-      <c r="D29" s="290"/>
-      <c r="E29" s="290"/>
-      <c r="F29" s="291"/>
+      <c r="B29" s="350"/>
+      <c r="C29" s="351"/>
+      <c r="D29" s="351"/>
+      <c r="E29" s="351"/>
+      <c r="F29" s="352"/>
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="B1:J2"/>
     <mergeCell ref="B3:J3"/>
     <mergeCell ref="B5:J5"/>
     <mergeCell ref="B25:F29"/>
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="H4:I4"/>
-    <mergeCell ref="B1:J2"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J7:J21" xr:uid="{0F1818C4-76BA-4990-A120-0FFD781F5786}">
@@ -35449,7 +39680,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FF4BFDB-04D3-4D71-B461-94763CCB5FD7}">
   <dimension ref="A1:O33"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -35467,542 +39698,533 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="23.25" customHeight="1">
-      <c r="A1" s="251" t="s">
+      <c r="A1" s="341" t="s">
         <v>266</v>
       </c>
-      <c r="B1" s="251"/>
-      <c r="C1" s="251"/>
-      <c r="D1" s="251"/>
-      <c r="E1" s="251"/>
-      <c r="F1" s="251"/>
-      <c r="G1" s="251"/>
-      <c r="H1" s="251"/>
-      <c r="I1" s="251"/>
-      <c r="J1" s="251"/>
-      <c r="K1" s="251"/>
-      <c r="L1" s="251"/>
-      <c r="M1" s="251"/>
-      <c r="N1" s="251"/>
-      <c r="O1" s="251"/>
+      <c r="B1" s="341"/>
+      <c r="C1" s="341"/>
+      <c r="D1" s="341"/>
+      <c r="E1" s="341"/>
+      <c r="F1" s="341"/>
+      <c r="G1" s="341"/>
+      <c r="H1" s="341"/>
+      <c r="I1" s="341"/>
+      <c r="J1" s="341"/>
+      <c r="K1" s="341"/>
+      <c r="L1" s="341"/>
+      <c r="M1" s="341"/>
+      <c r="N1" s="341"/>
+      <c r="O1" s="341"/>
     </row>
     <row r="2" spans="1:15">
-      <c r="A2" s="249"/>
-      <c r="B2" s="249"/>
-      <c r="C2" s="249"/>
-      <c r="D2" s="249"/>
-      <c r="E2" s="249"/>
-      <c r="F2" s="249"/>
-      <c r="G2" s="249"/>
-      <c r="H2" s="249"/>
-      <c r="I2" s="249"/>
-      <c r="J2" s="249"/>
-      <c r="K2" s="249"/>
-      <c r="L2" s="249"/>
-      <c r="M2" s="249"/>
-      <c r="N2" s="249"/>
-      <c r="O2" s="249"/>
+      <c r="A2" s="160"/>
+      <c r="B2" s="160"/>
+      <c r="C2" s="160"/>
+      <c r="D2" s="160"/>
+      <c r="E2" s="160"/>
+      <c r="F2" s="160"/>
+      <c r="G2" s="160"/>
+      <c r="H2" s="160"/>
+      <c r="I2" s="160"/>
+      <c r="J2" s="160"/>
+      <c r="K2" s="160"/>
+      <c r="L2" s="160"/>
+      <c r="M2" s="160"/>
+      <c r="N2" s="160"/>
+      <c r="O2" s="160"/>
     </row>
     <row r="3" spans="1:15" ht="21">
-      <c r="A3" s="249"/>
-      <c r="B3" s="249"/>
-      <c r="C3" s="249"/>
-      <c r="D3" s="292" t="s">
+      <c r="A3" s="160"/>
+      <c r="B3" s="160"/>
+      <c r="C3" s="160"/>
+      <c r="D3" s="185" t="s">
         <v>267</v>
       </c>
-      <c r="E3" s="305">
+      <c r="E3" s="198">
         <v>0.7</v>
       </c>
-      <c r="F3" s="249"/>
-      <c r="G3" s="249"/>
-      <c r="H3" s="249"/>
-      <c r="I3" s="249"/>
-      <c r="J3" s="292" t="s">
+      <c r="F3" s="160"/>
+      <c r="G3" s="160"/>
+      <c r="H3" s="160"/>
+      <c r="I3" s="160"/>
+      <c r="J3" s="185" t="s">
         <v>268</v>
       </c>
-      <c r="K3" s="307" t="s">
+      <c r="K3" s="367" t="s">
         <v>15</v>
       </c>
-      <c r="L3" s="307"/>
-      <c r="M3" s="249"/>
-      <c r="N3" s="249"/>
-      <c r="O3" s="249"/>
+      <c r="L3" s="367"/>
+      <c r="M3" s="160"/>
+      <c r="N3" s="160"/>
+      <c r="O3" s="160"/>
     </row>
     <row r="4" spans="1:15" ht="15.75" thickBot="1">
-      <c r="A4" s="249"/>
-      <c r="B4" s="249"/>
-      <c r="C4" s="249"/>
-      <c r="D4" s="249"/>
-      <c r="E4" s="249"/>
-      <c r="F4" s="249"/>
-      <c r="G4" s="249"/>
-      <c r="H4" s="249"/>
-      <c r="I4" s="249"/>
-      <c r="J4" s="249"/>
-      <c r="K4" s="249"/>
-      <c r="L4" s="249"/>
-      <c r="M4" s="249"/>
-      <c r="N4" s="249"/>
-      <c r="O4" s="249"/>
+      <c r="A4" s="160"/>
+      <c r="B4" s="160"/>
+      <c r="C4" s="160"/>
+      <c r="D4" s="160"/>
+      <c r="E4" s="160"/>
+      <c r="F4" s="160"/>
+      <c r="G4" s="160"/>
+      <c r="H4" s="160"/>
+      <c r="I4" s="160"/>
+      <c r="J4" s="160"/>
+      <c r="K4" s="160"/>
+      <c r="L4" s="160"/>
+      <c r="M4" s="160"/>
+      <c r="N4" s="160"/>
+      <c r="O4" s="160"/>
     </row>
     <row r="5" spans="1:15" ht="15.75" thickBot="1">
-      <c r="B5" s="294" t="s">
+      <c r="B5" s="187" t="s">
         <v>269</v>
       </c>
-      <c r="C5" s="295" t="s">
+      <c r="C5" s="188" t="s">
         <v>270</v>
       </c>
-      <c r="D5" s="295" t="s">
+      <c r="D5" s="188" t="s">
         <v>271</v>
       </c>
-      <c r="E5" s="295" t="s">
+      <c r="E5" s="188" t="s">
         <v>272</v>
       </c>
-      <c r="F5" s="296" t="s">
+      <c r="F5" s="189" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="15.75" thickBot="1">
-      <c r="B6" s="317" t="s">
+      <c r="B6" s="200" t="s">
         <v>277</v>
       </c>
-      <c r="C6" s="293">
+      <c r="C6" s="186">
         <v>45</v>
       </c>
-      <c r="D6" s="299">
+      <c r="D6" s="192">
         <f>(Table4[[#This Row],[Data]]/C$25)</f>
         <v>0.33088235294117646</v>
       </c>
-      <c r="E6" s="303">
+      <c r="E6" s="196">
         <f>Table4[[#This Row],[%]]</f>
         <v>0.33088235294117646</v>
       </c>
-      <c r="F6" s="306">
+      <c r="F6" s="199">
         <f>IF(ISBLANK(E6),"",E$3)</f>
         <v>0.7</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="15.75" thickBot="1">
-      <c r="B7" s="318" t="s">
+      <c r="B7" s="201" t="s">
         <v>278</v>
       </c>
-      <c r="C7" s="264">
+      <c r="C7" s="171">
         <v>30</v>
       </c>
-      <c r="D7" s="299">
+      <c r="D7" s="192">
         <f>(Table4[[#This Row],[Data]]/C$25)</f>
         <v>0.22058823529411764</v>
       </c>
-      <c r="E7" s="304">
+      <c r="E7" s="197">
         <f>E6+Table4[[#This Row],[%]]</f>
         <v>0.55147058823529416</v>
       </c>
-      <c r="F7" s="265">
+      <c r="F7" s="172">
         <f t="shared" ref="F7:F24" si="0">IF(ISBLANK(E7),"",E$3)</f>
         <v>0.7</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="15.75" thickBot="1">
-      <c r="B8" s="318" t="s">
+      <c r="B8" s="201" t="s">
         <v>279</v>
       </c>
-      <c r="C8" s="264">
+      <c r="C8" s="171">
         <v>20</v>
       </c>
-      <c r="D8" s="299">
+      <c r="D8" s="192">
         <f>(Table4[[#This Row],[Data]]/C$25)</f>
         <v>0.14705882352941177</v>
       </c>
-      <c r="E8" s="304">
+      <c r="E8" s="197">
         <f>E7+Table4[[#This Row],[%]]</f>
         <v>0.69852941176470595</v>
       </c>
-      <c r="F8" s="265">
+      <c r="F8" s="172">
         <f t="shared" si="0"/>
         <v>0.7</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="15.75" thickBot="1">
-      <c r="B9" s="318" t="s">
+      <c r="B9" s="201" t="s">
         <v>280</v>
       </c>
-      <c r="C9" s="264">
+      <c r="C9" s="171">
         <v>15</v>
       </c>
-      <c r="D9" s="299">
+      <c r="D9" s="192">
         <f>(Table4[[#This Row],[Data]]/C$25)</f>
         <v>0.11029411764705882</v>
       </c>
-      <c r="E9" s="304">
+      <c r="E9" s="197">
         <f>E8+Table4[[#This Row],[%]]</f>
         <v>0.80882352941176472</v>
       </c>
-      <c r="F9" s="265">
+      <c r="F9" s="172">
         <f t="shared" si="0"/>
         <v>0.7</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="15.75" thickBot="1">
-      <c r="B10" s="318" t="s">
+      <c r="B10" s="201" t="s">
         <v>161</v>
       </c>
-      <c r="C10" s="264">
+      <c r="C10" s="171">
         <v>10</v>
       </c>
-      <c r="D10" s="299">
+      <c r="D10" s="192">
         <f>(Table4[[#This Row],[Data]]/C$25)</f>
         <v>7.3529411764705885E-2</v>
       </c>
-      <c r="E10" s="304">
+      <c r="E10" s="197">
         <f>E9+Table4[[#This Row],[%]]</f>
         <v>0.88235294117647056</v>
       </c>
-      <c r="F10" s="265">
+      <c r="F10" s="172">
         <f t="shared" si="0"/>
         <v>0.7</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="15.75" thickBot="1">
-      <c r="B11" s="318" t="s">
+      <c r="B11" s="201" t="s">
         <v>281</v>
       </c>
-      <c r="C11" s="264">
+      <c r="C11" s="171">
         <v>5</v>
       </c>
-      <c r="D11" s="299">
+      <c r="D11" s="192">
         <f>(Table4[[#This Row],[Data]]/C$25)</f>
         <v>3.6764705882352942E-2</v>
       </c>
-      <c r="E11" s="304">
+      <c r="E11" s="197">
         <f>E10+Table4[[#This Row],[%]]</f>
         <v>0.91911764705882348</v>
       </c>
-      <c r="F11" s="265">
+      <c r="F11" s="172">
         <f t="shared" si="0"/>
         <v>0.7</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="15.75" thickBot="1">
-      <c r="B12" s="318" t="s">
+      <c r="B12" s="201" t="s">
         <v>282</v>
       </c>
-      <c r="C12" s="264">
+      <c r="C12" s="171">
         <v>4</v>
       </c>
-      <c r="D12" s="299">
+      <c r="D12" s="192">
         <f>(Table4[[#This Row],[Data]]/C$25)</f>
         <v>2.9411764705882353E-2</v>
       </c>
-      <c r="E12" s="304">
+      <c r="E12" s="197">
         <f>E11+Table4[[#This Row],[%]]</f>
         <v>0.94852941176470584</v>
       </c>
-      <c r="F12" s="265">
+      <c r="F12" s="172">
         <f t="shared" si="0"/>
         <v>0.7</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="15.75" thickBot="1">
-      <c r="B13" s="318" t="s">
+      <c r="B13" s="201" t="s">
         <v>283</v>
       </c>
-      <c r="C13" s="264">
+      <c r="C13" s="171">
         <v>3</v>
       </c>
-      <c r="D13" s="299">
+      <c r="D13" s="192">
         <f>(Table4[[#This Row],[Data]]/C$25)</f>
         <v>2.2058823529411766E-2</v>
       </c>
-      <c r="E13" s="304">
+      <c r="E13" s="197">
         <f>E12+Table4[[#This Row],[%]]</f>
         <v>0.97058823529411764</v>
       </c>
-      <c r="F13" s="265">
+      <c r="F13" s="172">
         <f t="shared" si="0"/>
         <v>0.7</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="15.75" thickBot="1">
-      <c r="B14" s="318" t="s">
+      <c r="B14" s="201" t="s">
         <v>284</v>
       </c>
-      <c r="C14" s="264">
+      <c r="C14" s="171">
         <v>2</v>
       </c>
-      <c r="D14" s="299">
+      <c r="D14" s="192">
         <f>(Table4[[#This Row],[Data]]/C$25)</f>
         <v>1.4705882352941176E-2</v>
       </c>
-      <c r="E14" s="304">
+      <c r="E14" s="197">
         <f>E13+Table4[[#This Row],[%]]</f>
         <v>0.98529411764705876</v>
       </c>
-      <c r="F14" s="265">
+      <c r="F14" s="172">
         <f t="shared" si="0"/>
         <v>0.7</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="15.75" thickBot="1">
-      <c r="B15" s="318" t="s">
+      <c r="B15" s="201" t="s">
         <v>285</v>
       </c>
-      <c r="C15" s="264">
+      <c r="C15" s="171">
         <v>2</v>
       </c>
-      <c r="D15" s="299">
+      <c r="D15" s="192">
         <f>(Table4[[#This Row],[Data]]/C$25)</f>
         <v>1.4705882352941176E-2</v>
       </c>
-      <c r="E15" s="304">
+      <c r="E15" s="197">
         <f>E14+Table4[[#This Row],[%]]</f>
         <v>0.99999999999999989</v>
       </c>
-      <c r="F15" s="265">
+      <c r="F15" s="172">
         <f t="shared" si="0"/>
         <v>0.7</v>
       </c>
     </row>
     <row r="16" spans="1:15" ht="15.75" thickBot="1">
-      <c r="B16" s="260"/>
-      <c r="C16" s="261"/>
-      <c r="D16" s="299">
+      <c r="B16" s="167"/>
+      <c r="C16" s="168"/>
+      <c r="D16" s="192">
         <f>(Table4[[#This Row],[Data]]/C$25)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="304">
+      <c r="E16" s="197">
         <f>E15+Table4[[#This Row],[%]]</f>
         <v>0.99999999999999989</v>
       </c>
-      <c r="F16" s="265">
+      <c r="F16" s="172">
         <f t="shared" si="0"/>
         <v>0.7</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15.75" thickBot="1">
-      <c r="B17" s="260"/>
-      <c r="C17" s="261"/>
-      <c r="D17" s="299">
+    <row r="17" spans="2:9" ht="15.75" thickBot="1">
+      <c r="B17" s="167"/>
+      <c r="C17" s="168"/>
+      <c r="D17" s="192">
         <f>(Table4[[#This Row],[Data]]/C$25)</f>
         <v>0</v>
       </c>
-      <c r="E17" s="304">
+      <c r="E17" s="197">
         <f>E16+Table4[[#This Row],[%]]</f>
         <v>0.99999999999999989</v>
       </c>
-      <c r="F17" s="265">
+      <c r="F17" s="172">
         <f t="shared" si="0"/>
         <v>0.7</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15.75" thickBot="1">
-      <c r="B18" s="260"/>
-      <c r="C18" s="261"/>
-      <c r="D18" s="299">
+    <row r="18" spans="2:9" ht="15.75" thickBot="1">
+      <c r="B18" s="167"/>
+      <c r="C18" s="168"/>
+      <c r="D18" s="192">
         <f>(Table4[[#This Row],[Data]]/C$25)</f>
         <v>0</v>
       </c>
-      <c r="E18" s="304">
+      <c r="E18" s="197">
         <f>E17+Table4[[#This Row],[%]]</f>
         <v>0.99999999999999989</v>
       </c>
-      <c r="F18" s="265">
+      <c r="F18" s="172">
         <f t="shared" si="0"/>
         <v>0.7</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15.75" thickBot="1">
-      <c r="B19" s="260"/>
-      <c r="C19" s="261"/>
-      <c r="D19" s="299">
+    <row r="19" spans="2:9" ht="15.75" thickBot="1">
+      <c r="B19" s="167"/>
+      <c r="C19" s="168"/>
+      <c r="D19" s="192">
         <f>(Table4[[#This Row],[Data]]/C$25)</f>
         <v>0</v>
       </c>
-      <c r="E19" s="304">
+      <c r="E19" s="197">
         <f>E18+Table4[[#This Row],[%]]</f>
         <v>0.99999999999999989</v>
       </c>
-      <c r="F19" s="265">
+      <c r="F19" s="172">
         <f t="shared" si="0"/>
         <v>0.7</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="15.75" thickBot="1">
-      <c r="B20" s="260"/>
-      <c r="C20" s="261"/>
-      <c r="D20" s="299">
+    <row r="20" spans="2:9" ht="15.75" thickBot="1">
+      <c r="B20" s="167"/>
+      <c r="C20" s="168"/>
+      <c r="D20" s="192">
         <f>(Table4[[#This Row],[Data]]/C$25)</f>
         <v>0</v>
       </c>
-      <c r="E20" s="304">
+      <c r="E20" s="197">
         <f>E19+Table4[[#This Row],[%]]</f>
         <v>0.99999999999999989</v>
       </c>
-      <c r="F20" s="265">
+      <c r="F20" s="172">
         <f t="shared" si="0"/>
         <v>0.7</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="15.75" thickBot="1">
-      <c r="B21" s="260"/>
-      <c r="C21" s="261"/>
-      <c r="D21" s="299">
+    <row r="21" spans="2:9" ht="15.75" thickBot="1">
+      <c r="B21" s="167"/>
+      <c r="C21" s="168"/>
+      <c r="D21" s="192">
         <f>(Table4[[#This Row],[Data]]/C$25)</f>
         <v>0</v>
       </c>
-      <c r="E21" s="304">
+      <c r="E21" s="197">
         <f>E20+Table4[[#This Row],[%]]</f>
         <v>0.99999999999999989</v>
       </c>
-      <c r="F21" s="265">
+      <c r="F21" s="172">
         <f t="shared" si="0"/>
         <v>0.7</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="15.75" thickBot="1">
-      <c r="B22" s="260"/>
-      <c r="C22" s="261"/>
-      <c r="D22" s="299">
+    <row r="22" spans="2:9" ht="15.75" thickBot="1">
+      <c r="B22" s="167"/>
+      <c r="C22" s="168"/>
+      <c r="D22" s="192">
         <f>(Table4[[#This Row],[Data]]/C$25)</f>
         <v>0</v>
       </c>
-      <c r="E22" s="304">
+      <c r="E22" s="197">
         <f>E21+Table4[[#This Row],[%]]</f>
         <v>0.99999999999999989</v>
       </c>
-      <c r="F22" s="265">
+      <c r="F22" s="172">
         <f t="shared" si="0"/>
         <v>0.7</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15.75" thickBot="1">
-      <c r="B23" s="260"/>
-      <c r="C23" s="261"/>
-      <c r="D23" s="299">
+    <row r="23" spans="2:9" ht="15.75" thickBot="1">
+      <c r="B23" s="167"/>
+      <c r="C23" s="168"/>
+      <c r="D23" s="192">
         <f>(Table4[[#This Row],[Data]]/C$25)</f>
         <v>0</v>
       </c>
-      <c r="E23" s="304">
+      <c r="E23" s="197">
         <f>E22+Table4[[#This Row],[%]]</f>
         <v>0.99999999999999989</v>
       </c>
-      <c r="F23" s="265">
+      <c r="F23" s="172">
         <f t="shared" si="0"/>
         <v>0.7</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="15.75" thickBot="1">
-      <c r="B24" s="262"/>
-      <c r="C24" s="263"/>
-      <c r="D24" s="299">
+    <row r="24" spans="2:9" ht="15.75" thickBot="1">
+      <c r="B24" s="169"/>
+      <c r="C24" s="170"/>
+      <c r="D24" s="192">
         <f>(Table4[[#This Row],[Data]]/C$25)</f>
         <v>0</v>
       </c>
-      <c r="E24" s="304">
+      <c r="E24" s="197">
         <f>E23+Table4[[#This Row],[%]]</f>
         <v>0.99999999999999989</v>
       </c>
-      <c r="F24" s="266">
+      <c r="F24" s="173">
         <f t="shared" si="0"/>
         <v>0.7</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A25" s="257"/>
-      <c r="B25" s="302" t="s">
+    <row r="25" spans="2:9" ht="15.75" thickBot="1">
+      <c r="B25" s="195" t="s">
         <v>274</v>
       </c>
-      <c r="C25" s="300">
+      <c r="C25" s="193">
         <f>SUM(Table4[Data])</f>
         <v>136</v>
       </c>
-      <c r="D25" s="301">
+      <c r="D25" s="194">
         <f>SUBTOTAL(109,Table4[%])</f>
         <v>0.99999999999999989</v>
       </c>
-      <c r="E25" s="297"/>
-      <c r="F25" s="298"/>
-    </row>
-    <row r="26" spans="1:9" ht="15.75" thickBot="1">
-      <c r="A26" s="257"/>
-      <c r="B26" s="257"/>
-      <c r="C26" s="257"/>
-      <c r="D26" s="257"/>
-      <c r="E26" s="257"/>
-      <c r="F26" s="257"/>
-    </row>
-    <row r="27" spans="1:9" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A27" s="257"/>
-      <c r="B27" s="308" t="s">
+      <c r="E25" s="190"/>
+      <c r="F25" s="191"/>
+    </row>
+    <row r="26" spans="2:9" ht="15.75" thickBot="1"/>
+    <row r="27" spans="2:9" ht="20.25" customHeight="1" thickBot="1">
+      <c r="B27" s="358" t="s">
         <v>275</v>
       </c>
-      <c r="C27" s="309"/>
-      <c r="D27" s="309"/>
-      <c r="E27" s="309"/>
-      <c r="F27" s="309"/>
-      <c r="G27" s="309"/>
-      <c r="H27" s="309"/>
-      <c r="I27" s="310"/>
-    </row>
-    <row r="28" spans="1:9" ht="20.25" customHeight="1">
-      <c r="B28" s="311" t="s">
+      <c r="C27" s="359"/>
+      <c r="D27" s="359"/>
+      <c r="E27" s="359"/>
+      <c r="F27" s="359"/>
+      <c r="G27" s="359"/>
+      <c r="H27" s="359"/>
+      <c r="I27" s="360"/>
+    </row>
+    <row r="28" spans="2:9" ht="20.25" customHeight="1">
+      <c r="B28" s="361" t="s">
         <v>276</v>
       </c>
-      <c r="C28" s="312"/>
-      <c r="D28" s="312"/>
-      <c r="E28" s="312"/>
-      <c r="F28" s="312"/>
-      <c r="G28" s="312"/>
-      <c r="H28" s="312"/>
-      <c r="I28" s="313"/>
-    </row>
-    <row r="29" spans="1:9" ht="20.25" customHeight="1">
-      <c r="B29" s="311"/>
-      <c r="C29" s="312"/>
-      <c r="D29" s="312"/>
-      <c r="E29" s="312"/>
-      <c r="F29" s="312"/>
-      <c r="G29" s="312"/>
-      <c r="H29" s="312"/>
-      <c r="I29" s="313"/>
-    </row>
-    <row r="30" spans="1:9" ht="20.25" customHeight="1">
-      <c r="B30" s="311"/>
-      <c r="C30" s="312"/>
-      <c r="D30" s="312"/>
-      <c r="E30" s="312"/>
-      <c r="F30" s="312"/>
-      <c r="G30" s="312"/>
-      <c r="H30" s="312"/>
-      <c r="I30" s="313"/>
-    </row>
-    <row r="31" spans="1:9" ht="20.25" customHeight="1">
-      <c r="B31" s="311"/>
-      <c r="C31" s="312"/>
-      <c r="D31" s="312"/>
-      <c r="E31" s="312"/>
-      <c r="F31" s="312"/>
-      <c r="G31" s="312"/>
-      <c r="H31" s="312"/>
-      <c r="I31" s="313"/>
-    </row>
-    <row r="32" spans="1:9" ht="20.25" customHeight="1">
-      <c r="B32" s="311"/>
-      <c r="C32" s="312"/>
-      <c r="D32" s="312"/>
-      <c r="E32" s="312"/>
-      <c r="F32" s="312"/>
-      <c r="G32" s="312"/>
-      <c r="H32" s="312"/>
-      <c r="I32" s="313"/>
+      <c r="C28" s="362"/>
+      <c r="D28" s="362"/>
+      <c r="E28" s="362"/>
+      <c r="F28" s="362"/>
+      <c r="G28" s="362"/>
+      <c r="H28" s="362"/>
+      <c r="I28" s="363"/>
+    </row>
+    <row r="29" spans="2:9" ht="20.25" customHeight="1">
+      <c r="B29" s="361"/>
+      <c r="C29" s="362"/>
+      <c r="D29" s="362"/>
+      <c r="E29" s="362"/>
+      <c r="F29" s="362"/>
+      <c r="G29" s="362"/>
+      <c r="H29" s="362"/>
+      <c r="I29" s="363"/>
+    </row>
+    <row r="30" spans="2:9" ht="20.25" customHeight="1">
+      <c r="B30" s="361"/>
+      <c r="C30" s="362"/>
+      <c r="D30" s="362"/>
+      <c r="E30" s="362"/>
+      <c r="F30" s="362"/>
+      <c r="G30" s="362"/>
+      <c r="H30" s="362"/>
+      <c r="I30" s="363"/>
+    </row>
+    <row r="31" spans="2:9" ht="20.25" customHeight="1">
+      <c r="B31" s="361"/>
+      <c r="C31" s="362"/>
+      <c r="D31" s="362"/>
+      <c r="E31" s="362"/>
+      <c r="F31" s="362"/>
+      <c r="G31" s="362"/>
+      <c r="H31" s="362"/>
+      <c r="I31" s="363"/>
+    </row>
+    <row r="32" spans="2:9" ht="20.25" customHeight="1">
+      <c r="B32" s="361"/>
+      <c r="C32" s="362"/>
+      <c r="D32" s="362"/>
+      <c r="E32" s="362"/>
+      <c r="F32" s="362"/>
+      <c r="G32" s="362"/>
+      <c r="H32" s="362"/>
+      <c r="I32" s="363"/>
     </row>
     <row r="33" spans="2:9" ht="66" customHeight="1" thickBot="1">
-      <c r="B33" s="314"/>
-      <c r="C33" s="315"/>
-      <c r="D33" s="315"/>
-      <c r="E33" s="315"/>
-      <c r="F33" s="315"/>
-      <c r="G33" s="315"/>
-      <c r="H33" s="315"/>
-      <c r="I33" s="316"/>
+      <c r="B33" s="364"/>
+      <c r="C33" s="365"/>
+      <c r="D33" s="365"/>
+      <c r="E33" s="365"/>
+      <c r="F33" s="365"/>
+      <c r="G33" s="365"/>
+      <c r="H33" s="365"/>
+      <c r="I33" s="366"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -36018,4 +40240,556 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D8A1204-435E-499D-B4E0-6FE9897E6BA9}">
+  <dimension ref="B1:I26"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="84"/>
+    <col min="2" max="2" width="38.140625" style="84" customWidth="1"/>
+    <col min="3" max="3" width="17.140625" style="84" customWidth="1"/>
+    <col min="4" max="4" width="24.7109375" style="84" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.140625" style="84" customWidth="1"/>
+    <col min="6" max="6" width="18.42578125" style="84" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.140625" style="84" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" style="84" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.140625" style="84" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="84"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:9" ht="15.75" thickBot="1">
+      <c r="B1"/>
+      <c r="C1"/>
+      <c r="D1"/>
+      <c r="E1"/>
+      <c r="F1"/>
+      <c r="G1"/>
+      <c r="H1"/>
+      <c r="I1"/>
+    </row>
+    <row r="2" spans="2:9" ht="30" customHeight="1" thickBot="1">
+      <c r="B2" s="368" t="s">
+        <v>333</v>
+      </c>
+      <c r="C2" s="369"/>
+      <c r="D2" s="369"/>
+      <c r="E2" s="369"/>
+      <c r="F2" s="369"/>
+      <c r="G2" s="369"/>
+      <c r="H2" s="369"/>
+      <c r="I2" s="370"/>
+    </row>
+    <row r="3" spans="2:9">
+      <c r="B3" s="371" t="s">
+        <v>334</v>
+      </c>
+      <c r="C3" s="372"/>
+      <c r="D3" s="372"/>
+      <c r="E3" s="372"/>
+      <c r="F3" s="372"/>
+      <c r="G3" s="372"/>
+      <c r="H3" s="372"/>
+      <c r="I3" s="373"/>
+    </row>
+    <row r="4" spans="2:9" ht="15.75" thickBot="1">
+      <c r="B4" s="229"/>
+      <c r="I4" s="230"/>
+    </row>
+    <row r="5" spans="2:9" ht="24.95" customHeight="1">
+      <c r="B5" s="217" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="218" t="s">
+        <v>335</v>
+      </c>
+      <c r="D5" s="218" t="s">
+        <v>336</v>
+      </c>
+      <c r="E5" s="218" t="s">
+        <v>337</v>
+      </c>
+      <c r="F5" s="218" t="s">
+        <v>338</v>
+      </c>
+      <c r="G5" s="218" t="s">
+        <v>339</v>
+      </c>
+      <c r="H5" s="218" t="s">
+        <v>340</v>
+      </c>
+      <c r="I5" s="219" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="6" spans="2:9">
+      <c r="B6" s="206" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="207">
+        <v>1</v>
+      </c>
+      <c r="D6" s="208">
+        <v>5</v>
+      </c>
+      <c r="E6" s="208">
+        <v>5</v>
+      </c>
+      <c r="F6" s="208">
+        <v>4</v>
+      </c>
+      <c r="G6" s="208">
+        <v>5</v>
+      </c>
+      <c r="H6" s="208">
+        <v>5</v>
+      </c>
+      <c r="I6" s="209">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9">
+      <c r="B7" s="206" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="207">
+        <v>1</v>
+      </c>
+      <c r="D7" s="208">
+        <v>5</v>
+      </c>
+      <c r="E7" s="208">
+        <v>4</v>
+      </c>
+      <c r="F7" s="208">
+        <v>4</v>
+      </c>
+      <c r="G7" s="208">
+        <v>5</v>
+      </c>
+      <c r="H7" s="208">
+        <v>5</v>
+      </c>
+      <c r="I7" s="209">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9">
+      <c r="B8" s="206" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="207">
+        <v>1</v>
+      </c>
+      <c r="D8" s="208">
+        <v>5</v>
+      </c>
+      <c r="E8" s="208">
+        <v>4</v>
+      </c>
+      <c r="F8" s="208">
+        <v>4</v>
+      </c>
+      <c r="G8" s="208">
+        <v>4</v>
+      </c>
+      <c r="H8" s="208">
+        <v>5</v>
+      </c>
+      <c r="I8" s="209">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9">
+      <c r="B9" s="206" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="207">
+        <v>0.2</v>
+      </c>
+      <c r="D9" s="208">
+        <v>1</v>
+      </c>
+      <c r="E9" s="208">
+        <v>2</v>
+      </c>
+      <c r="F9" s="208">
+        <v>3</v>
+      </c>
+      <c r="G9" s="208">
+        <v>2</v>
+      </c>
+      <c r="H9" s="208">
+        <v>3</v>
+      </c>
+      <c r="I9" s="209">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9">
+      <c r="B10" s="206" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="207">
+        <v>0.4</v>
+      </c>
+      <c r="D10" s="208">
+        <v>3</v>
+      </c>
+      <c r="E10" s="208">
+        <v>3</v>
+      </c>
+      <c r="F10" s="208">
+        <v>4</v>
+      </c>
+      <c r="G10" s="208">
+        <v>3</v>
+      </c>
+      <c r="H10" s="208">
+        <v>4</v>
+      </c>
+      <c r="I10" s="209">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="2:9">
+      <c r="B11" s="206" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="207">
+        <v>0.3</v>
+      </c>
+      <c r="D11" s="208">
+        <v>3</v>
+      </c>
+      <c r="E11" s="208">
+        <v>3</v>
+      </c>
+      <c r="F11" s="208">
+        <v>4</v>
+      </c>
+      <c r="G11" s="208">
+        <v>3</v>
+      </c>
+      <c r="H11" s="208">
+        <v>3</v>
+      </c>
+      <c r="I11" s="209">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="2:9">
+      <c r="B12" s="206" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="207">
+        <v>0</v>
+      </c>
+      <c r="D12" s="208">
+        <v>4</v>
+      </c>
+      <c r="E12" s="208">
+        <v>3</v>
+      </c>
+      <c r="F12" s="208">
+        <v>3</v>
+      </c>
+      <c r="G12" s="208">
+        <v>3</v>
+      </c>
+      <c r="H12" s="208">
+        <v>4</v>
+      </c>
+      <c r="I12" s="209">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="2:9">
+      <c r="B13" s="206" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="207">
+        <v>0</v>
+      </c>
+      <c r="D13" s="208">
+        <v>4</v>
+      </c>
+      <c r="E13" s="208">
+        <v>3</v>
+      </c>
+      <c r="F13" s="208">
+        <v>3</v>
+      </c>
+      <c r="G13" s="208">
+        <v>3</v>
+      </c>
+      <c r="H13" s="208">
+        <v>4</v>
+      </c>
+      <c r="I13" s="209">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="2:9">
+      <c r="B14" s="206" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="207">
+        <v>0</v>
+      </c>
+      <c r="D14" s="208">
+        <v>4</v>
+      </c>
+      <c r="E14" s="208">
+        <v>2</v>
+      </c>
+      <c r="F14" s="208">
+        <v>3</v>
+      </c>
+      <c r="G14" s="208">
+        <v>3</v>
+      </c>
+      <c r="H14" s="208">
+        <v>4</v>
+      </c>
+      <c r="I14" s="209">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="2:9" ht="15.75" thickBot="1">
+      <c r="B15" s="220" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="221">
+        <v>0</v>
+      </c>
+      <c r="D15" s="222">
+        <v>4</v>
+      </c>
+      <c r="E15" s="222">
+        <v>3</v>
+      </c>
+      <c r="F15" s="222">
+        <v>3</v>
+      </c>
+      <c r="G15" s="222">
+        <v>3</v>
+      </c>
+      <c r="H15" s="222">
+        <v>4</v>
+      </c>
+      <c r="I15" s="223">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" ht="15.75" thickBot="1">
+      <c r="B16" s="202"/>
+      <c r="C16"/>
+      <c r="D16"/>
+      <c r="F16"/>
+      <c r="G16"/>
+      <c r="H16"/>
+      <c r="I16" s="203"/>
+    </row>
+    <row r="17" spans="2:9">
+      <c r="B17" s="374" t="s">
+        <v>342</v>
+      </c>
+      <c r="C17" s="375"/>
+      <c r="D17" s="376"/>
+      <c r="F17" s="377" t="s">
+        <v>358</v>
+      </c>
+      <c r="G17" s="378"/>
+      <c r="H17" s="378"/>
+      <c r="I17" s="379"/>
+    </row>
+    <row r="18" spans="2:9">
+      <c r="B18" s="204" t="s">
+        <v>343</v>
+      </c>
+      <c r="C18" s="210" t="s">
+        <v>344</v>
+      </c>
+      <c r="D18" s="205" t="s">
+        <v>345</v>
+      </c>
+      <c r="F18" s="231" t="s">
+        <v>359</v>
+      </c>
+      <c r="G18" s="215">
+        <f>COUNTA(B6:B15)</f>
+        <v>10</v>
+      </c>
+      <c r="H18" s="211" t="s">
+        <v>364</v>
+      </c>
+      <c r="I18" s="216">
+        <f>ROUND(AVERAGE(I6:I15),1)</f>
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9">
+      <c r="B19" s="204" t="s">
+        <v>346</v>
+      </c>
+      <c r="C19" s="212" t="s">
+        <v>347</v>
+      </c>
+      <c r="D19" s="205" t="s">
+        <v>348</v>
+      </c>
+      <c r="F19" s="231" t="s">
+        <v>360</v>
+      </c>
+      <c r="G19" s="215">
+        <f>COUNTIF(C6:C15,1)</f>
+        <v>3</v>
+      </c>
+      <c r="H19" s="211" t="s">
+        <v>365</v>
+      </c>
+      <c r="I19" s="216">
+        <f>COUNTIF(D6:I15,1)+COUNTIF(D6:I15,2)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9">
+      <c r="B20" s="204" t="s">
+        <v>349</v>
+      </c>
+      <c r="C20" s="213" t="s">
+        <v>350</v>
+      </c>
+      <c r="D20" s="205" t="s">
+        <v>351</v>
+      </c>
+      <c r="F20" s="231" t="s">
+        <v>361</v>
+      </c>
+      <c r="G20" s="215">
+        <f>COUNTIFS(C6:C15,"&gt;0",C6:C15,"&lt;1")</f>
+        <v>3</v>
+      </c>
+      <c r="H20" s="211" t="s">
+        <v>366</v>
+      </c>
+      <c r="I20" s="216">
+        <f>COUNTIF(D6:I15,3)</f>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9">
+      <c r="B21" s="204" t="s">
+        <v>352</v>
+      </c>
+      <c r="C21" s="214" t="s">
+        <v>353</v>
+      </c>
+      <c r="D21" s="205" t="s">
+        <v>354</v>
+      </c>
+      <c r="F21" s="231" t="s">
+        <v>362</v>
+      </c>
+      <c r="G21" s="215">
+        <f>COUNTIF(C6:C15,0)</f>
+        <v>4</v>
+      </c>
+      <c r="H21" s="211" t="s">
+        <v>367</v>
+      </c>
+      <c r="I21" s="216">
+        <f>COUNTIF(D6:I15,4)+COUNTIF(D6:I15,5)</f>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" ht="15.75" thickBot="1">
+      <c r="B22" s="224" t="s">
+        <v>355</v>
+      </c>
+      <c r="C22" s="225" t="s">
+        <v>356</v>
+      </c>
+      <c r="D22" s="228" t="s">
+        <v>357</v>
+      </c>
+      <c r="F22" s="232" t="s">
+        <v>363</v>
+      </c>
+      <c r="G22" s="227" t="str">
+        <f>TEXT(AVERAGE(C6:C15),"0%")</f>
+        <v>39%</v>
+      </c>
+      <c r="H22" s="226"/>
+      <c r="I22" s="228"/>
+    </row>
+    <row r="23" spans="2:9">
+      <c r="B23" s="229"/>
+      <c r="I23" s="230"/>
+    </row>
+    <row r="24" spans="2:9" ht="15.75" thickBot="1">
+      <c r="B24" s="229"/>
+      <c r="I24" s="230"/>
+    </row>
+    <row r="25" spans="2:9" ht="16.5" thickBot="1">
+      <c r="B25" s="380" t="s">
+        <v>368</v>
+      </c>
+      <c r="C25" s="381"/>
+      <c r="D25" s="381"/>
+      <c r="E25" s="381"/>
+      <c r="F25" s="381"/>
+      <c r="G25" s="381"/>
+      <c r="H25" s="381"/>
+      <c r="I25" s="382"/>
+    </row>
+    <row r="26" spans="2:9" ht="151.5" customHeight="1" thickBot="1">
+      <c r="B26" s="383" t="s">
+        <v>369</v>
+      </c>
+      <c r="C26" s="384"/>
+      <c r="D26" s="384"/>
+      <c r="E26" s="384"/>
+      <c r="F26" s="384"/>
+      <c r="G26" s="384"/>
+      <c r="H26" s="384"/>
+      <c r="I26" s="385"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="B26:I26"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="F17:I17"/>
+    <mergeCell ref="B25:I25"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C6:C15">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF6B6B"/>
+        <color rgb="FFFFD93D"/>
+        <color rgb="FF6BCB77"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D6:I15">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF6B6B"/>
+        <color rgb="FFFFD93D"/>
+        <color rgb="FF6BCB77"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/pm_dashboards/Project Management Charts.xlsx
+++ b/pm_dashboards/Project Management Charts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\excel_tutorial\pm_dashboards\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABA8D240-7D97-4908-8E58-D90597AA851F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77CCFD15-676D-410B-9A6B-E874C4309FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="513" activeTab="2" xr2:uid="{6ACA091F-59E3-41E7-B925-EA720AB063CF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="513" firstSheet="6" activeTab="9" xr2:uid="{6ACA091F-59E3-41E7-B925-EA720AB063CF}"/>
   </bookViews>
   <sheets>
     <sheet name="PMP" sheetId="11" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="Requirement Traceability" sheetId="9" r:id="rId7"/>
     <sheet name="Pareto Principle" sheetId="10" r:id="rId8"/>
     <sheet name="Heatmap" sheetId="12" r:id="rId9"/>
+    <sheet name="Nominal Group Technique" sheetId="15" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -164,7 +165,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="407">
   <si>
     <t>Project Start Date:</t>
   </si>
@@ -1407,6 +1408,81 @@
   <si>
     <t>💡 Tip: Update scores as the project evolves. Use this to prioritize communication strategies.</t>
   </si>
+  <si>
+    <t>Each Team member has:</t>
+  </si>
+  <si>
+    <t>Facilitator:</t>
+  </si>
+  <si>
+    <t>Date:</t>
+  </si>
+  <si>
+    <t>Points to distribute on ideas.</t>
+  </si>
+  <si>
+    <t>Allocated Points</t>
+  </si>
+  <si>
+    <t>Brainstormed Ideas List</t>
+  </si>
+  <si>
+    <t>Team Member 1</t>
+  </si>
+  <si>
+    <t>Team Member 2</t>
+  </si>
+  <si>
+    <t>Team Member 3</t>
+  </si>
+  <si>
+    <t>Team Member 4</t>
+  </si>
+  <si>
+    <t>Team Member 5</t>
+  </si>
+  <si>
+    <t>Team Member 6</t>
+  </si>
+  <si>
+    <t>Team Member 7</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Feature 1</t>
+  </si>
+  <si>
+    <t>Feature 2</t>
+  </si>
+  <si>
+    <t>Feature 3</t>
+  </si>
+  <si>
+    <t>Feature 4</t>
+  </si>
+  <si>
+    <t>Feature 5</t>
+  </si>
+  <si>
+    <t>Rank</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Nominal Group Technique - </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="20"/>
+        <color theme="0"/>
+        <rFont val="Aptos Serif"/>
+        <family val="1"/>
+      </rPr>
+      <t>Multi Voting</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -1418,7 +1494,7 @@
     <numFmt numFmtId="166" formatCode="yyyy"/>
     <numFmt numFmtId="167" formatCode="dd\ mmm\ yy"/>
   </numFmts>
-  <fonts count="74">
+  <fonts count="78">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1941,8 +2017,35 @@
       <name val="Aptos Serif"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="20"/>
+      <color theme="0"/>
+      <name val="Aptos Serif"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="20"/>
+      <color theme="0"/>
+      <name val="Aptos Serif"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1" tint="4.9989318521683403E-2"/>
+      <name val="Aptos Serif"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Aptos Serif"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="51">
+  <fills count="54">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2243,8 +2346,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF163D64"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="149">
+  <borders count="152">
     <border>
       <left/>
       <right/>
@@ -4162,12 +4283,55 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="dotted">
+        <color indexed="64"/>
+      </top>
+      <bottom style="dotted">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="dotted">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="dotted">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="423">
+  <cellXfs count="450">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
@@ -4832,6 +4996,95 @@
     <xf numFmtId="0" fontId="60" fillId="36" borderId="140" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="68" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="55" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="55" fillId="2" borderId="148" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="69" fillId="2" borderId="145" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="2" borderId="146" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="2" borderId="147" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="46" borderId="135" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="47" borderId="136" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="48" borderId="136" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="49" borderId="136" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="50" borderId="137" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="46" borderId="138" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="47" borderId="139" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="48" borderId="139" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="49" borderId="139" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="50" borderId="140" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="18" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="55" fillId="18" borderId="131" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="67" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="2" borderId="148" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="18" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="18" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="18" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="18" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="18" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="18" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="18" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="71" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="71" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="72" fillId="18" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="72" fillId="18" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="72" fillId="18" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="135" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -4855,6 +5108,30 @@
     </xf>
     <xf numFmtId="0" fontId="38" fillId="21" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -4907,29 +5184,46 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="57" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="18" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="28" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
@@ -4985,53 +5279,6 @@
     <xf numFmtId="0" fontId="5" fillId="28" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="28" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="28" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="28" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="28" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="18" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="57" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="45" fillId="18" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="18" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="45" fillId="18" borderId="104" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -5040,6 +5287,44 @@
     </xf>
     <xf numFmtId="0" fontId="45" fillId="18" borderId="93" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="29" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="29" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="29" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="36" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="27" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="27" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="18" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="18" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="52" fillId="22" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
@@ -5082,38 +5367,6 @@
     </xf>
     <xf numFmtId="0" fontId="53" fillId="24" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="29" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="29" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="29" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="36" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="27" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="27" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5196,6 +5449,15 @@
     <xf numFmtId="0" fontId="58" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="141" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="106" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="113" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="2" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5229,110 +5491,102 @@
     <xf numFmtId="0" fontId="63" fillId="3" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="131" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="141" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="106" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="113" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="67" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="74" fillId="51" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="68" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="55" fillId="53" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="55" fillId="51" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="51" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="56" fillId="51" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="7"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="18" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="69" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="56" fillId="51" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="51" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="18" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="55" fillId="18" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="51" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="55" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="55" fillId="2" borderId="148" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="55" fillId="51" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="2" borderId="148" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="69" fillId="2" borderId="145" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="56" fillId="51" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="51" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="69" fillId="2" borderId="146" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="55" fillId="51" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="69" fillId="2" borderId="147" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="76" fillId="25" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="46" borderId="135" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="76" fillId="25" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="47" borderId="136" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="48" borderId="136" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="49" borderId="136" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="76" fillId="25" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="50" borderId="137" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="76" fillId="25" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="46" borderId="138" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="77" fillId="52" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="52" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="47" borderId="139" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="48" borderId="139" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="70" fillId="49" borderId="139" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="55" fillId="18" borderId="151" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="50" borderId="140" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="55" fillId="18" borderId="149" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="18" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="55" fillId="18" borderId="150" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="18" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="70" fillId="18" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="16"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="18" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="55" fillId="18" borderId="131" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="71" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="71" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="71" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="72" fillId="18" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="72" fillId="18" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="72" fillId="18" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="55" fillId="18" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="18" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="18" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="18" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="73" fillId="18" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="55" fillId="18" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="25">
+  <dxfs count="28">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF5D5D"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -5673,16 +5927,16 @@
   </tableStyles>
   <colors>
     <mruColors>
+      <color rgb="FFFF5D5D"/>
+      <color rgb="FFA0E8AA"/>
+      <color rgb="FF5E9DDC"/>
+      <color rgb="FF3B88D5"/>
+      <color rgb="FF205A94"/>
+      <color rgb="FF9FBFFF"/>
+      <color rgb="FF85DFFF"/>
+      <color rgb="FF163D64"/>
       <color rgb="FFFFFF9F"/>
-      <color rgb="FF163D64"/>
-      <color rgb="FFA0E8AA"/>
       <color rgb="FF0D3514"/>
-      <color rgb="FF061809"/>
-      <color rgb="FF218B30"/>
-      <color rgb="FFE9A159"/>
-      <color rgb="FFFF3737"/>
-      <color rgb="FFE1801F"/>
-      <color rgb="FFFF5757"/>
     </mruColors>
   </colors>
   <extLst>
@@ -5811,7 +6065,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{53032ED7-4EB4-41A7-AC46-FE2657719D13}" type="CELLRANGE">
+                    <a:fld id="{DA0660E6-EC0C-49CE-99A6-F6BE3B21BEDF}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -5830,7 +6084,6 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:dlblFieldTable/>
-                  <c15:xForSave val="1"/>
                   <c15:showDataLabelsRange val="1"/>
                 </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -5845,8 +6098,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{4ECB827D-8B78-485C-A75C-FBE563675091}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{63A9569A-564A-4B44-9A8E-96F448807024}" type="CELLRANGE">
+                      <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -5879,8 +6132,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{1795C169-1019-45AB-9E38-5AFEFEFDAE62}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{E4F1BB72-A833-4920-BB6F-CFC27D7838C4}" type="CELLRANGE">
+                      <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -5913,8 +6166,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D5B6BB3E-3FF3-47B3-B342-E1BA4A5E4EB4}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{C59BDC6A-710E-4FC6-9332-1C030920EBD2}" type="CELLRANGE">
+                      <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -5947,8 +6200,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0E1300CA-5C83-420F-9704-D8903A08BD3C}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{7BAF19CE-9B91-494B-BC61-4EFEC1A269E3}" type="CELLRANGE">
+                      <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -5981,8 +6234,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{8DDC48C5-9729-4356-A492-E6662C3D6FF0}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{0C340198-E7AE-481C-9042-F91BEC5D4BF4}" type="CELLRANGE">
+                      <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -6015,8 +6268,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C18172B9-A854-45BE-884C-A067CC1D6485}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{147FEB83-D47C-42D2-ABB9-B4847CABD015}" type="CELLRANGE">
+                      <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -6049,8 +6302,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{5BA259FD-6A5D-44A9-B50E-B2AA7B6DAF4C}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{ADB3E8EC-F276-4F3C-A95E-1AD68CBD02CF}" type="CELLRANGE">
+                      <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -6083,8 +6336,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{49EDD687-D1F3-4A0F-8C53-929B39C1887B}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{85DD4A33-2AF0-4066-B8E1-E474FCD5BF9D}" type="CELLRANGE">
+                      <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -6117,8 +6370,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{1D526259-6245-40A0-A01A-1EC888EABBC2}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{2157F310-6946-4776-9FAD-148F5489557B}" type="CELLRANGE">
+                      <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -6151,8 +6404,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{AC1C8268-BC5E-4F15-8DC9-B42F424792EA}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{55ADDAF0-8732-40B9-8112-85CD13F65E76}" type="CELLRANGE">
+                      <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -6185,8 +6438,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0EEE9CC6-7BCE-4D34-A3C0-593144196EC4}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{17961558-11C8-4550-ADF1-123025DAAFA9}" type="CELLRANGE">
+                      <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -6219,8 +6472,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2A2EAE76-B8B8-40AE-A567-76E93ECDC457}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{A6F4F703-541A-49CB-ABE8-55E747BCF9B3}" type="CELLRANGE">
+                      <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -6253,8 +6506,8 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{F6267437-9B51-4F2F-9F87-9441BAA3461B}" type="CELLRANGE">
-                      <a:rPr lang="en-US"/>
+                    <a:fld id="{236656AF-A6DE-405B-BC73-7370C561BD76}" type="CELLRANGE">
+                      <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
                     </a:fld>
@@ -8843,17 +9096,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{94A622BC-7ED1-488B-9C49-1BDAC25B3D53}" name="Table4" displayName="Table4" ref="B5:D25" totalsRowCount="1" headerRowDxfId="24" dataDxfId="23" totalsRowBorderDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{94A622BC-7ED1-488B-9C49-1BDAC25B3D53}" name="Table4" displayName="Table4" ref="B5:D25" totalsRowCount="1" headerRowDxfId="27" dataDxfId="26" totalsRowBorderDxfId="25">
   <autoFilter ref="B5:D24" xr:uid="{94A622BC-7ED1-488B-9C49-1BDAC25B3D53}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B6:D24">
     <sortCondition descending="1" ref="C5:C24"/>
   </sortState>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{943459A8-0FE9-4160-A47E-FA2D69FBEA80}" name="Options" totalsRowLabel="TOTAL" dataDxfId="21" totalsRowDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{8211ECFE-775B-4AAB-9AC0-3ADF3A0F719A}" name="Data" totalsRowFunction="custom" dataDxfId="19" totalsRowDxfId="18">
+    <tableColumn id="1" xr3:uid="{943459A8-0FE9-4160-A47E-FA2D69FBEA80}" name="Options" totalsRowLabel="TOTAL" dataDxfId="24" totalsRowDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{8211ECFE-775B-4AAB-9AC0-3ADF3A0F719A}" name="Data" totalsRowFunction="custom" dataDxfId="22" totalsRowDxfId="21">
       <totalsRowFormula>SUM(Table4[Data])</totalsRowFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{7F1106EA-ECA2-4B33-896F-6D8F9CF0D4C8}" name="%" totalsRowFunction="sum" dataDxfId="17" totalsRowDxfId="16" dataCellStyle="Percent" totalsRowCellStyle="Percent">
+    <tableColumn id="3" xr3:uid="{7F1106EA-ECA2-4B33-896F-6D8F9CF0D4C8}" name="%" totalsRowFunction="sum" dataDxfId="20" totalsRowDxfId="19" dataCellStyle="Percent" totalsRowCellStyle="Percent">
       <calculatedColumnFormula>(Table4[[#This Row],[Data]]/C$25)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -9234,17 +9487,17 @@
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1">
       <c r="A1" s="233"/>
-      <c r="B1" s="250" t="s">
+      <c r="B1" s="287" t="s">
         <v>332</v>
       </c>
-      <c r="C1" s="250"/>
-      <c r="D1" s="250"/>
-      <c r="E1" s="250"/>
-      <c r="F1" s="250"/>
-      <c r="G1" s="251"/>
+      <c r="C1" s="287"/>
+      <c r="D1" s="287"/>
+      <c r="E1" s="287"/>
+      <c r="F1" s="287"/>
+      <c r="G1" s="288"/>
     </row>
     <row r="2" spans="1:7" ht="30" customHeight="1">
-      <c r="A2" s="248" t="s">
+      <c r="A2" s="285" t="s">
         <v>331</v>
       </c>
       <c r="B2" s="235" t="s">
@@ -9267,7 +9520,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="28.5">
-      <c r="A3" s="248"/>
+      <c r="A3" s="285"/>
       <c r="B3" s="240" t="s">
         <v>292</v>
       </c>
@@ -9288,7 +9541,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="42.75">
-      <c r="A4" s="248"/>
+      <c r="A4" s="285"/>
       <c r="B4" s="240" t="s">
         <v>298</v>
       </c>
@@ -9303,7 +9556,7 @@
       <c r="G4" s="245"/>
     </row>
     <row r="5" spans="1:7" ht="71.25">
-      <c r="A5" s="248"/>
+      <c r="A5" s="285"/>
       <c r="B5" s="240" t="s">
         <v>301</v>
       </c>
@@ -9318,7 +9571,7 @@
       <c r="G5" s="243"/>
     </row>
     <row r="6" spans="1:7" ht="42.75">
-      <c r="A6" s="248"/>
+      <c r="A6" s="285"/>
       <c r="B6" s="240" t="s">
         <v>304</v>
       </c>
@@ -9333,7 +9586,7 @@
       <c r="G6" s="245"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="248"/>
+      <c r="A7" s="285"/>
       <c r="B7" s="240" t="s">
         <v>307</v>
       </c>
@@ -9350,7 +9603,7 @@
       <c r="G7" s="243"/>
     </row>
     <row r="8" spans="1:7" ht="42.75">
-      <c r="A8" s="248"/>
+      <c r="A8" s="285"/>
       <c r="B8" s="240" t="s">
         <v>311</v>
       </c>
@@ -9365,7 +9618,7 @@
       <c r="G8" s="245"/>
     </row>
     <row r="9" spans="1:7" ht="28.5">
-      <c r="A9" s="248"/>
+      <c r="A9" s="285"/>
       <c r="B9" s="240" t="s">
         <v>314</v>
       </c>
@@ -9382,7 +9635,7 @@
       <c r="G9" s="243"/>
     </row>
     <row r="10" spans="1:7" ht="85.5">
-      <c r="A10" s="248"/>
+      <c r="A10" s="285"/>
       <c r="B10" s="240" t="s">
         <v>318</v>
       </c>
@@ -9399,7 +9652,7 @@
       <c r="G10" s="245"/>
     </row>
     <row r="11" spans="1:7" ht="28.5">
-      <c r="A11" s="248"/>
+      <c r="A11" s="285"/>
       <c r="B11" s="240" t="s">
         <v>322</v>
       </c>
@@ -9416,7 +9669,7 @@
       <c r="G11" s="243"/>
     </row>
     <row r="12" spans="1:7" ht="17.25" thickBot="1">
-      <c r="A12" s="249"/>
+      <c r="A12" s="286"/>
       <c r="B12" s="241" t="s">
         <v>326</v>
       </c>
@@ -9441,6 +9694,550 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A1336A8-0BDF-47A9-8475-C5035F8DF71A}">
+  <dimension ref="A1:L24"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="2.7109375" style="423" customWidth="1"/>
+    <col min="2" max="2" width="35.85546875" style="423" bestFit="1" customWidth="1"/>
+    <col min="3" max="10" width="10.7109375" style="423" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="423"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="26.25">
+      <c r="A1" s="424" t="s">
+        <v>406</v>
+      </c>
+      <c r="B1" s="424"/>
+      <c r="C1" s="424"/>
+      <c r="D1" s="424"/>
+      <c r="E1" s="424"/>
+      <c r="F1" s="424"/>
+      <c r="G1" s="424"/>
+      <c r="H1" s="424"/>
+      <c r="I1" s="424"/>
+      <c r="J1" s="424"/>
+      <c r="K1" s="424"/>
+      <c r="L1" s="425"/>
+    </row>
+    <row r="2" spans="1:12" ht="15.75" thickBot="1">
+      <c r="A2" s="426"/>
+      <c r="B2" s="426"/>
+      <c r="C2" s="426"/>
+      <c r="D2" s="426"/>
+      <c r="E2" s="426"/>
+      <c r="F2" s="426"/>
+      <c r="G2" s="426"/>
+      <c r="H2" s="426"/>
+      <c r="I2" s="426"/>
+      <c r="J2" s="426"/>
+      <c r="K2" s="426"/>
+      <c r="L2" s="425"/>
+    </row>
+    <row r="3" spans="1:12" ht="15.75" thickBot="1">
+      <c r="A3" s="427"/>
+      <c r="B3" s="428" t="s">
+        <v>386</v>
+      </c>
+      <c r="C3" s="429">
+        <v>10</v>
+      </c>
+      <c r="D3" s="430" t="s">
+        <v>389</v>
+      </c>
+      <c r="E3" s="427"/>
+      <c r="F3" s="427"/>
+      <c r="G3" s="426"/>
+      <c r="H3" s="426"/>
+      <c r="I3" s="426"/>
+      <c r="J3" s="426"/>
+      <c r="K3" s="426"/>
+      <c r="L3" s="425"/>
+    </row>
+    <row r="4" spans="1:12" ht="15.75" thickBot="1">
+      <c r="A4" s="426"/>
+      <c r="B4" s="426"/>
+      <c r="C4" s="426"/>
+      <c r="D4" s="426"/>
+      <c r="E4" s="426"/>
+      <c r="F4" s="426"/>
+      <c r="G4" s="426"/>
+      <c r="H4" s="426"/>
+      <c r="I4" s="426"/>
+      <c r="J4" s="426"/>
+      <c r="K4" s="426"/>
+      <c r="L4" s="425"/>
+    </row>
+    <row r="5" spans="1:12" ht="15.75" thickBot="1">
+      <c r="A5" s="427"/>
+      <c r="B5" s="431" t="s">
+        <v>387</v>
+      </c>
+      <c r="C5" s="432"/>
+      <c r="D5" s="433"/>
+      <c r="E5" s="434"/>
+      <c r="F5" s="435"/>
+      <c r="G5" s="435"/>
+      <c r="H5" s="435"/>
+      <c r="I5" s="435"/>
+      <c r="J5" s="435"/>
+      <c r="K5" s="435"/>
+      <c r="L5" s="425"/>
+    </row>
+    <row r="6" spans="1:12" ht="15.75" thickBot="1">
+      <c r="A6" s="426"/>
+      <c r="B6" s="426"/>
+      <c r="C6" s="426"/>
+      <c r="D6" s="426"/>
+      <c r="E6" s="426"/>
+      <c r="F6" s="426"/>
+      <c r="G6" s="426"/>
+      <c r="H6" s="426"/>
+      <c r="I6" s="426"/>
+      <c r="J6" s="426"/>
+      <c r="K6" s="426"/>
+      <c r="L6" s="425"/>
+    </row>
+    <row r="7" spans="1:12" ht="15.75" thickBot="1">
+      <c r="A7" s="427"/>
+      <c r="B7" s="436" t="s">
+        <v>388</v>
+      </c>
+      <c r="C7" s="429"/>
+      <c r="D7" s="437"/>
+      <c r="E7" s="438"/>
+      <c r="F7" s="438"/>
+      <c r="G7" s="438"/>
+      <c r="H7" s="438"/>
+      <c r="I7" s="438"/>
+      <c r="J7" s="438"/>
+      <c r="K7" s="438"/>
+      <c r="L7" s="425"/>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="426"/>
+      <c r="B8" s="426"/>
+      <c r="C8" s="426"/>
+      <c r="D8" s="426"/>
+      <c r="E8" s="426"/>
+      <c r="F8" s="426"/>
+      <c r="G8" s="426"/>
+      <c r="H8" s="426"/>
+      <c r="I8" s="426"/>
+      <c r="J8" s="426"/>
+      <c r="K8" s="426"/>
+      <c r="L8" s="425"/>
+    </row>
+    <row r="9" spans="1:12" ht="15.75" thickBot="1">
+      <c r="A9" s="425"/>
+      <c r="B9" s="425"/>
+      <c r="C9" s="425"/>
+      <c r="D9" s="425"/>
+      <c r="E9" s="425"/>
+      <c r="F9" s="425"/>
+      <c r="G9" s="425"/>
+      <c r="H9" s="425"/>
+      <c r="I9" s="425"/>
+      <c r="J9" s="425"/>
+      <c r="K9" s="425"/>
+      <c r="L9" s="425"/>
+    </row>
+    <row r="10" spans="1:12" ht="15.75" thickBot="1">
+      <c r="A10" s="425"/>
+      <c r="B10" s="425"/>
+      <c r="C10" s="439" t="s">
+        <v>390</v>
+      </c>
+      <c r="D10" s="440"/>
+      <c r="E10" s="440"/>
+      <c r="F10" s="440"/>
+      <c r="G10" s="440"/>
+      <c r="H10" s="440"/>
+      <c r="I10" s="441"/>
+      <c r="J10" s="425"/>
+      <c r="K10" s="425"/>
+      <c r="L10" s="425"/>
+    </row>
+    <row r="11" spans="1:12" ht="28.5" customHeight="1" thickBot="1">
+      <c r="A11" s="425"/>
+      <c r="B11" s="442" t="s">
+        <v>391</v>
+      </c>
+      <c r="C11" s="443" t="s">
+        <v>392</v>
+      </c>
+      <c r="D11" s="443" t="s">
+        <v>393</v>
+      </c>
+      <c r="E11" s="443" t="s">
+        <v>394</v>
+      </c>
+      <c r="F11" s="443" t="s">
+        <v>395</v>
+      </c>
+      <c r="G11" s="443" t="s">
+        <v>396</v>
+      </c>
+      <c r="H11" s="443" t="s">
+        <v>397</v>
+      </c>
+      <c r="I11" s="443" t="s">
+        <v>398</v>
+      </c>
+      <c r="J11" s="444" t="s">
+        <v>399</v>
+      </c>
+      <c r="K11" s="444" t="s">
+        <v>405</v>
+      </c>
+      <c r="L11" s="425"/>
+    </row>
+    <row r="12" spans="1:12" ht="20.100000000000001" customHeight="1">
+      <c r="A12" s="425"/>
+      <c r="B12" s="445" t="s">
+        <v>400</v>
+      </c>
+      <c r="C12" s="445">
+        <v>2</v>
+      </c>
+      <c r="D12" s="445">
+        <v>3</v>
+      </c>
+      <c r="E12" s="445">
+        <v>1</v>
+      </c>
+      <c r="F12" s="445"/>
+      <c r="G12" s="445"/>
+      <c r="H12" s="445"/>
+      <c r="I12" s="445"/>
+      <c r="J12" s="445">
+        <f>SUM(C12:I12)</f>
+        <v>6</v>
+      </c>
+      <c r="K12" s="445">
+        <f>IF(OR(J12=0,J12=""),"",RANK(J12,J$12:J$20,0))</f>
+        <v>5</v>
+      </c>
+      <c r="L12" s="425"/>
+    </row>
+    <row r="13" spans="1:12" ht="20.100000000000001" customHeight="1">
+      <c r="A13" s="425"/>
+      <c r="B13" s="446" t="s">
+        <v>401</v>
+      </c>
+      <c r="C13" s="446">
+        <v>3</v>
+      </c>
+      <c r="D13" s="446">
+        <v>4</v>
+      </c>
+      <c r="E13" s="446">
+        <v>3</v>
+      </c>
+      <c r="F13" s="446"/>
+      <c r="G13" s="446"/>
+      <c r="H13" s="446"/>
+      <c r="I13" s="446"/>
+      <c r="J13" s="446">
+        <f t="shared" ref="J13:J20" si="0">SUM(C13:I13)</f>
+        <v>10</v>
+      </c>
+      <c r="K13" s="446">
+        <f t="shared" ref="K13:K20" si="1">IF(OR(J13=0,J13=""),"",RANK(J13,J$12:J$20,0))</f>
+        <v>4</v>
+      </c>
+      <c r="L13" s="425"/>
+    </row>
+    <row r="14" spans="1:12" ht="20.100000000000001" customHeight="1">
+      <c r="A14" s="425"/>
+      <c r="B14" s="446" t="s">
+        <v>402</v>
+      </c>
+      <c r="C14" s="446">
+        <v>4</v>
+      </c>
+      <c r="D14" s="446">
+        <v>5</v>
+      </c>
+      <c r="E14" s="446">
+        <v>3</v>
+      </c>
+      <c r="F14" s="446"/>
+      <c r="G14" s="446"/>
+      <c r="H14" s="446"/>
+      <c r="I14" s="446"/>
+      <c r="J14" s="446">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="K14" s="446">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L14" s="425"/>
+    </row>
+    <row r="15" spans="1:12" ht="20.100000000000001" customHeight="1">
+      <c r="A15" s="425"/>
+      <c r="B15" s="446" t="s">
+        <v>403</v>
+      </c>
+      <c r="C15" s="446">
+        <v>5</v>
+      </c>
+      <c r="D15" s="446">
+        <v>6</v>
+      </c>
+      <c r="E15" s="446">
+        <v>1</v>
+      </c>
+      <c r="F15" s="446"/>
+      <c r="G15" s="446"/>
+      <c r="H15" s="446"/>
+      <c r="I15" s="446"/>
+      <c r="J15" s="446">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="K15" s="446">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L15" s="425"/>
+    </row>
+    <row r="16" spans="1:12" ht="20.100000000000001" customHeight="1">
+      <c r="A16" s="425"/>
+      <c r="B16" s="446" t="s">
+        <v>404</v>
+      </c>
+      <c r="C16" s="446">
+        <v>6</v>
+      </c>
+      <c r="D16" s="446">
+        <v>7</v>
+      </c>
+      <c r="E16" s="446">
+        <v>2</v>
+      </c>
+      <c r="F16" s="446"/>
+      <c r="G16" s="446"/>
+      <c r="H16" s="446"/>
+      <c r="I16" s="446"/>
+      <c r="J16" s="446">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="K16" s="446">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="L16" s="425"/>
+    </row>
+    <row r="17" spans="1:12" ht="20.100000000000001" customHeight="1">
+      <c r="A17" s="425"/>
+      <c r="B17" s="446"/>
+      <c r="C17" s="446"/>
+      <c r="D17" s="446"/>
+      <c r="E17" s="446"/>
+      <c r="F17" s="446"/>
+      <c r="G17" s="446"/>
+      <c r="H17" s="446"/>
+      <c r="I17" s="446"/>
+      <c r="J17" s="446">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K17" s="446" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L17" s="425"/>
+    </row>
+    <row r="18" spans="1:12" ht="20.100000000000001" customHeight="1">
+      <c r="A18" s="425"/>
+      <c r="B18" s="446"/>
+      <c r="C18" s="446"/>
+      <c r="D18" s="446"/>
+      <c r="E18" s="446"/>
+      <c r="F18" s="446"/>
+      <c r="G18" s="446"/>
+      <c r="H18" s="446"/>
+      <c r="I18" s="446"/>
+      <c r="J18" s="446">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K18" s="446" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L18" s="425"/>
+    </row>
+    <row r="19" spans="1:12" ht="20.100000000000001" customHeight="1">
+      <c r="A19" s="425"/>
+      <c r="B19" s="446"/>
+      <c r="C19" s="446"/>
+      <c r="D19" s="446"/>
+      <c r="E19" s="446"/>
+      <c r="F19" s="446"/>
+      <c r="G19" s="446"/>
+      <c r="H19" s="446"/>
+      <c r="I19" s="446"/>
+      <c r="J19" s="446">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K19" s="446" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L19" s="425"/>
+    </row>
+    <row r="20" spans="1:12" ht="20.100000000000001" customHeight="1" thickBot="1">
+      <c r="A20" s="425"/>
+      <c r="B20" s="447"/>
+      <c r="C20" s="447"/>
+      <c r="D20" s="447"/>
+      <c r="E20" s="447"/>
+      <c r="F20" s="447"/>
+      <c r="G20" s="447"/>
+      <c r="H20" s="447"/>
+      <c r="I20" s="447"/>
+      <c r="J20" s="447">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K20" s="447" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="L20" s="425"/>
+    </row>
+    <row r="21" spans="1:12" ht="20.100000000000001" customHeight="1" thickBot="1">
+      <c r="A21" s="425"/>
+      <c r="B21" s="448" t="s">
+        <v>399</v>
+      </c>
+      <c r="C21" s="429">
+        <f>SUM(C12:C20)</f>
+        <v>20</v>
+      </c>
+      <c r="D21" s="429">
+        <f t="shared" ref="D21:J21" si="2">SUM(D12:D20)</f>
+        <v>25</v>
+      </c>
+      <c r="E21" s="429">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="F21" s="429">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G21" s="429">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H21" s="429">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="I21" s="429">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="429">
+        <f t="shared" si="2"/>
+        <v>55</v>
+      </c>
+      <c r="K21" s="449"/>
+      <c r="L21" s="425"/>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="425"/>
+      <c r="B22" s="425"/>
+      <c r="C22" s="425"/>
+      <c r="D22" s="425"/>
+      <c r="E22" s="425"/>
+      <c r="F22" s="425"/>
+      <c r="G22" s="425"/>
+      <c r="H22" s="425"/>
+      <c r="I22" s="425"/>
+      <c r="J22" s="425"/>
+      <c r="K22" s="425"/>
+      <c r="L22" s="425"/>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" s="425"/>
+      <c r="B23" s="425"/>
+      <c r="C23" s="425"/>
+      <c r="D23" s="425"/>
+      <c r="E23" s="425"/>
+      <c r="F23" s="425"/>
+      <c r="G23" s="425"/>
+      <c r="H23" s="425"/>
+      <c r="I23" s="425"/>
+      <c r="J23" s="425"/>
+      <c r="K23" s="425"/>
+      <c r="L23" s="425"/>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" s="425"/>
+      <c r="B24" s="425"/>
+      <c r="C24" s="425"/>
+      <c r="D24" s="425"/>
+      <c r="E24" s="425"/>
+      <c r="F24" s="425"/>
+      <c r="G24" s="425"/>
+      <c r="H24" s="425"/>
+      <c r="I24" s="425"/>
+      <c r="J24" s="425"/>
+      <c r="K24" s="425"/>
+      <c r="L24" s="425"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A8:K8"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="G3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="E5:K5"/>
+    <mergeCell ref="A6:K6"/>
+    <mergeCell ref="D7:K7"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C10:I10"/>
+    <mergeCell ref="A2:K2"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <conditionalFormatting sqref="C21:J21">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="greaterThan">
+      <formula>$C$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C21:J21">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J12:J20">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K12:K20">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color theme="7" tint="-0.499984740745262"/>
+        <color theme="0"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -9457,10 +10254,10 @@
   <sheetData>
     <row r="1" spans="2:3" ht="15.75" thickBot="1"/>
     <row r="2" spans="2:3" ht="36.75" customHeight="1" thickBot="1">
-      <c r="B2" s="254" t="s">
+      <c r="B2" s="291" t="s">
         <v>80</v>
       </c>
-      <c r="C2" s="255"/>
+      <c r="C2" s="292"/>
     </row>
     <row r="3" spans="2:3" ht="17.25" thickBot="1">
       <c r="B3" s="104" t="s">
@@ -9515,10 +10312,10 @@
       <c r="C9" s="102"/>
     </row>
     <row r="10" spans="2:3" ht="30.75" customHeight="1">
-      <c r="B10" s="252" t="s">
+      <c r="B10" s="289" t="s">
         <v>89</v>
       </c>
-      <c r="C10" s="253"/>
+      <c r="C10" s="290"/>
     </row>
     <row r="11" spans="2:3" ht="30.75" customHeight="1">
       <c r="B11" s="107" t="s">
@@ -9606,513 +10403,513 @@
   <dimension ref="A1:R34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17.7109375" style="390" customWidth="1"/>
-    <col min="2" max="2" width="3.28515625" style="390" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.140625" style="390" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="55.140625" style="390" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19" style="390" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.42578125" style="390" bestFit="1" customWidth="1"/>
-    <col min="7" max="16" width="16" style="390" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="390"/>
+    <col min="1" max="1" width="17.7109375" style="250" customWidth="1"/>
+    <col min="2" max="2" width="3.28515625" style="250" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" style="250" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="55.140625" style="250" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19" style="250" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.42578125" style="250" bestFit="1" customWidth="1"/>
+    <col min="7" max="16" width="16" style="250" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="250"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="20.100000000000001" customHeight="1">
-      <c r="A1" s="389"/>
-      <c r="B1" s="389"/>
-      <c r="C1" s="389"/>
-      <c r="D1" s="389"/>
-      <c r="E1" s="389"/>
-      <c r="F1" s="389"/>
-      <c r="G1" s="389"/>
-      <c r="H1" s="389"/>
-      <c r="I1" s="389"/>
-      <c r="J1" s="389"/>
-      <c r="K1" s="389"/>
-      <c r="L1" s="389"/>
-      <c r="M1" s="389"/>
-      <c r="N1" s="389"/>
-      <c r="O1" s="389"/>
-      <c r="P1" s="389"/>
-      <c r="Q1" s="389"/>
-      <c r="R1" s="389"/>
+      <c r="A1" s="269"/>
+      <c r="B1" s="269"/>
+      <c r="C1" s="269"/>
+      <c r="D1" s="269"/>
+      <c r="E1" s="269"/>
+      <c r="F1" s="269"/>
+      <c r="G1" s="269"/>
+      <c r="H1" s="269"/>
+      <c r="I1" s="269"/>
+      <c r="J1" s="269"/>
+      <c r="K1" s="269"/>
+      <c r="L1" s="269"/>
+      <c r="M1" s="269"/>
+      <c r="N1" s="269"/>
+      <c r="O1" s="269"/>
+      <c r="P1" s="269"/>
+      <c r="Q1" s="269"/>
+      <c r="R1" s="269"/>
     </row>
     <row r="2" spans="1:18" ht="36.75" customHeight="1">
-      <c r="A2" s="386" t="s">
+      <c r="A2" s="268" t="s">
         <v>371</v>
       </c>
-      <c r="B2" s="386"/>
-      <c r="C2" s="386"/>
-      <c r="D2" s="389"/>
-      <c r="E2" s="389"/>
-      <c r="F2" s="389"/>
-      <c r="G2" s="389"/>
-      <c r="H2" s="389"/>
-      <c r="I2" s="389"/>
-      <c r="J2" s="389"/>
-      <c r="K2" s="389"/>
-      <c r="L2" s="389"/>
-      <c r="M2" s="389"/>
-      <c r="N2" s="389"/>
-      <c r="O2" s="389"/>
-      <c r="P2" s="389"/>
-      <c r="Q2" s="389"/>
-      <c r="R2" s="389"/>
+      <c r="B2" s="268"/>
+      <c r="C2" s="268"/>
+      <c r="D2" s="269"/>
+      <c r="E2" s="269"/>
+      <c r="F2" s="269"/>
+      <c r="G2" s="269"/>
+      <c r="H2" s="269"/>
+      <c r="I2" s="269"/>
+      <c r="J2" s="269"/>
+      <c r="K2" s="269"/>
+      <c r="L2" s="269"/>
+      <c r="M2" s="269"/>
+      <c r="N2" s="269"/>
+      <c r="O2" s="269"/>
+      <c r="P2" s="269"/>
+      <c r="Q2" s="269"/>
+      <c r="R2" s="269"/>
     </row>
     <row r="3" spans="1:18" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="391"/>
-      <c r="B3" s="391"/>
-      <c r="C3" s="391"/>
-      <c r="D3" s="389"/>
-      <c r="E3" s="389"/>
-      <c r="F3" s="389"/>
-      <c r="G3" s="389"/>
-      <c r="H3" s="389"/>
-      <c r="I3" s="389"/>
-      <c r="J3" s="389"/>
-      <c r="K3" s="389"/>
-      <c r="L3" s="389"/>
-      <c r="M3" s="389"/>
-      <c r="N3" s="389"/>
-      <c r="O3" s="389"/>
-      <c r="P3" s="389"/>
-      <c r="Q3" s="389"/>
-      <c r="R3" s="389"/>
+      <c r="A3" s="251"/>
+      <c r="B3" s="251"/>
+      <c r="C3" s="251"/>
+      <c r="D3" s="269"/>
+      <c r="E3" s="269"/>
+      <c r="F3" s="269"/>
+      <c r="G3" s="269"/>
+      <c r="H3" s="269"/>
+      <c r="I3" s="269"/>
+      <c r="J3" s="269"/>
+      <c r="K3" s="269"/>
+      <c r="L3" s="269"/>
+      <c r="M3" s="269"/>
+      <c r="N3" s="269"/>
+      <c r="O3" s="269"/>
+      <c r="P3" s="269"/>
+      <c r="Q3" s="269"/>
+      <c r="R3" s="269"/>
     </row>
     <row r="4" spans="1:18" ht="20.100000000000001" customHeight="1">
-      <c r="A4" s="389"/>
-      <c r="B4" s="389"/>
-      <c r="C4" s="388" t="s">
+      <c r="A4" s="269"/>
+      <c r="B4" s="269"/>
+      <c r="C4" s="249" t="s">
         <v>370</v>
       </c>
-      <c r="D4" s="387" t="s">
+      <c r="D4" s="248" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="389"/>
-      <c r="F4" s="389"/>
-      <c r="G4" s="389"/>
-      <c r="H4" s="389"/>
-      <c r="I4" s="389"/>
-      <c r="J4" s="389"/>
-      <c r="K4" s="389"/>
-      <c r="L4" s="389"/>
-      <c r="M4" s="389"/>
-      <c r="N4" s="389"/>
-      <c r="O4" s="389"/>
-      <c r="P4" s="389"/>
-      <c r="Q4" s="389"/>
-      <c r="R4" s="389"/>
+      <c r="E4" s="269"/>
+      <c r="F4" s="269"/>
+      <c r="G4" s="269"/>
+      <c r="H4" s="269"/>
+      <c r="I4" s="269"/>
+      <c r="J4" s="269"/>
+      <c r="K4" s="269"/>
+      <c r="L4" s="269"/>
+      <c r="M4" s="269"/>
+      <c r="N4" s="269"/>
+      <c r="O4" s="269"/>
+      <c r="P4" s="269"/>
+      <c r="Q4" s="269"/>
+      <c r="R4" s="269"/>
     </row>
     <row r="5" spans="1:18" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A5" s="392"/>
-      <c r="B5" s="392"/>
-      <c r="C5" s="393"/>
-      <c r="D5" s="393"/>
-      <c r="E5" s="392"/>
-      <c r="F5" s="392"/>
-      <c r="G5" s="392"/>
-      <c r="H5" s="392"/>
-      <c r="I5" s="392"/>
-      <c r="J5" s="392"/>
-      <c r="K5" s="392"/>
-      <c r="L5" s="392"/>
-      <c r="M5" s="392"/>
-      <c r="N5" s="392"/>
-      <c r="O5" s="392"/>
-      <c r="P5" s="392"/>
-      <c r="Q5" s="392"/>
-      <c r="R5" s="392"/>
+      <c r="A5" s="270"/>
+      <c r="B5" s="270"/>
+      <c r="C5" s="252"/>
+      <c r="D5" s="252"/>
+      <c r="E5" s="270"/>
+      <c r="F5" s="270"/>
+      <c r="G5" s="270"/>
+      <c r="H5" s="270"/>
+      <c r="I5" s="270"/>
+      <c r="J5" s="270"/>
+      <c r="K5" s="270"/>
+      <c r="L5" s="270"/>
+      <c r="M5" s="270"/>
+      <c r="N5" s="270"/>
+      <c r="O5" s="270"/>
+      <c r="P5" s="270"/>
+      <c r="Q5" s="270"/>
+      <c r="R5" s="270"/>
     </row>
     <row r="6" spans="1:18" ht="24.95" customHeight="1">
-      <c r="B6" s="394" t="s">
+      <c r="B6" s="253" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="395" t="s">
+      <c r="C6" s="254" t="s">
         <v>372</v>
       </c>
-      <c r="D6" s="395" t="s">
+      <c r="D6" s="254" t="s">
         <v>376</v>
       </c>
-      <c r="E6" s="395" t="s">
+      <c r="E6" s="254" t="s">
         <v>373</v>
       </c>
-      <c r="F6" s="396" t="s">
+      <c r="F6" s="255" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="7" spans="1:18">
-      <c r="B7" s="397">
-        <f>ROW()-6</f>
+      <c r="B7" s="256">
+        <f t="shared" ref="B7:B20" si="0">ROW()-6</f>
         <v>1</v>
       </c>
-      <c r="C7" s="398" t="s">
+      <c r="C7" s="257" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="399" t="s">
+      <c r="D7" s="258" t="s">
         <v>62</v>
       </c>
-      <c r="E7" s="400">
+      <c r="E7" s="259">
         <v>7</v>
       </c>
-      <c r="F7" s="401">
+      <c r="F7" s="260">
         <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:18">
-      <c r="B8" s="397">
-        <f>ROW()-6</f>
+      <c r="B8" s="256">
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="C8" s="398" t="s">
+      <c r="C8" s="257" t="s">
         <v>74</v>
       </c>
-      <c r="D8" s="399" t="s">
+      <c r="D8" s="258" t="s">
         <v>77</v>
       </c>
-      <c r="E8" s="400">
+      <c r="E8" s="259">
         <v>6</v>
       </c>
-      <c r="F8" s="401">
+      <c r="F8" s="260">
         <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:18">
-      <c r="B9" s="397">
-        <f>ROW()-6</f>
+      <c r="B9" s="256">
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="C9" s="398" t="s">
+      <c r="C9" s="257" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="399" t="s">
+      <c r="D9" s="258" t="s">
         <v>50</v>
       </c>
-      <c r="E9" s="400">
+      <c r="E9" s="259">
         <v>8</v>
       </c>
-      <c r="F9" s="401">
+      <c r="F9" s="260">
         <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:18">
-      <c r="B10" s="397">
-        <f>ROW()-6</f>
+      <c r="B10" s="256">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C10" s="398" t="s">
+      <c r="C10" s="257" t="s">
         <v>21</v>
       </c>
-      <c r="D10" s="399" t="s">
+      <c r="D10" s="258" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="400">
+      <c r="E10" s="259">
         <v>6</v>
       </c>
-      <c r="F10" s="401">
+      <c r="F10" s="260">
         <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:18">
-      <c r="B11" s="397">
-        <f>ROW()-6</f>
+      <c r="B11" s="256">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="C11" s="398" t="s">
+      <c r="C11" s="257" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="399" t="s">
+      <c r="D11" s="258" t="s">
         <v>64</v>
       </c>
-      <c r="E11" s="400">
+      <c r="E11" s="259">
         <v>9</v>
       </c>
-      <c r="F11" s="401">
+      <c r="F11" s="260">
         <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:18">
-      <c r="B12" s="397">
-        <f>ROW()-6</f>
+      <c r="B12" s="256">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C12" s="398" t="s">
+      <c r="C12" s="257" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="399" t="s">
+      <c r="D12" s="258" t="s">
         <v>65</v>
       </c>
-      <c r="E12" s="400">
+      <c r="E12" s="259">
         <v>8</v>
       </c>
-      <c r="F12" s="401">
+      <c r="F12" s="260">
         <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:18">
-      <c r="B13" s="397">
-        <f>ROW()-6</f>
+      <c r="B13" s="256">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="C13" s="398" t="s">
+      <c r="C13" s="257" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="399" t="s">
+      <c r="D13" s="258" t="s">
         <v>66</v>
       </c>
-      <c r="E13" s="400">
+      <c r="E13" s="259">
         <v>8</v>
       </c>
-      <c r="F13" s="401">
+      <c r="F13" s="260">
         <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:18">
-      <c r="B14" s="397">
-        <f>ROW()-6</f>
+      <c r="B14" s="256">
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="C14" s="398" t="s">
+      <c r="C14" s="257" t="s">
         <v>29</v>
       </c>
-      <c r="D14" s="399" t="s">
+      <c r="D14" s="258" t="s">
         <v>67</v>
       </c>
-      <c r="E14" s="400">
+      <c r="E14" s="259">
         <v>7</v>
       </c>
-      <c r="F14" s="401">
+      <c r="F14" s="260">
         <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:18">
-      <c r="B15" s="397">
-        <f>ROW()-6</f>
+      <c r="B15" s="256">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="C15" s="398" t="s">
+      <c r="C15" s="257" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="399" t="s">
+      <c r="D15" s="258" t="s">
         <v>68</v>
       </c>
-      <c r="E15" s="400">
+      <c r="E15" s="259">
         <v>6</v>
       </c>
-      <c r="F15" s="401">
+      <c r="F15" s="260">
         <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:18">
-      <c r="B16" s="397">
-        <f>ROW()-6</f>
+      <c r="B16" s="256">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="C16" s="398" t="s">
+      <c r="C16" s="257" t="s">
         <v>33</v>
       </c>
-      <c r="D16" s="399" t="s">
+      <c r="D16" s="258" t="s">
         <v>69</v>
       </c>
-      <c r="E16" s="400">
+      <c r="E16" s="259">
         <v>7</v>
       </c>
-      <c r="F16" s="401">
+      <c r="F16" s="260">
         <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:6">
-      <c r="B17" s="397">
-        <f>ROW()-6</f>
+      <c r="B17" s="256">
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="C17" s="398" t="s">
+      <c r="C17" s="257" t="s">
         <v>35</v>
       </c>
-      <c r="D17" s="399" t="s">
+      <c r="D17" s="258" t="s">
         <v>70</v>
       </c>
-      <c r="E17" s="400">
+      <c r="E17" s="259">
         <v>5</v>
       </c>
-      <c r="F17" s="401">
+      <c r="F17" s="260">
         <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:6">
-      <c r="B18" s="397">
-        <f>ROW()-6</f>
+      <c r="B18" s="256">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="C18" s="398" t="s">
+      <c r="C18" s="257" t="s">
         <v>71</v>
       </c>
-      <c r="D18" s="399" t="s">
+      <c r="D18" s="258" t="s">
         <v>72</v>
       </c>
-      <c r="E18" s="400">
+      <c r="E18" s="259">
         <v>4</v>
       </c>
-      <c r="F18" s="401">
+      <c r="F18" s="260">
         <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:6">
-      <c r="B19" s="397">
-        <f>ROW()-6</f>
+      <c r="B19" s="256">
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="C19" s="398" t="s">
+      <c r="C19" s="257" t="s">
         <v>75</v>
       </c>
-      <c r="D19" s="399" t="s">
+      <c r="D19" s="258" t="s">
         <v>78</v>
       </c>
-      <c r="E19" s="400">
+      <c r="E19" s="259">
         <v>3</v>
       </c>
-      <c r="F19" s="401">
+      <c r="F19" s="260">
         <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15.75" thickBot="1">
-      <c r="B20" s="402">
-        <f>ROW()-6</f>
+      <c r="B20" s="261">
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="C20" s="403" t="s">
+      <c r="C20" s="262" t="s">
         <v>73</v>
       </c>
-      <c r="D20" s="404" t="s">
+      <c r="D20" s="263" t="s">
         <v>76</v>
       </c>
-      <c r="E20" s="405">
+      <c r="E20" s="264">
         <v>2</v>
       </c>
-      <c r="F20" s="406">
+      <c r="F20" s="265">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15.75" thickBot="1"/>
     <row r="23" spans="1:6" ht="15.75" thickBot="1">
-      <c r="B23" s="407" t="s">
+      <c r="B23" s="277" t="s">
         <v>375</v>
       </c>
-      <c r="C23" s="408"/>
-      <c r="D23" s="409">
+      <c r="C23" s="278"/>
+      <c r="D23" s="266">
         <v>5</v>
       </c>
-      <c r="E23" s="410">
+      <c r="E23" s="267">
         <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.75" thickBot="1"/>
     <row r="26" spans="1:6" ht="17.100000000000001" customHeight="1" thickBot="1">
-      <c r="A26" s="411" t="s">
+      <c r="A26" s="279" t="s">
         <v>377</v>
       </c>
-      <c r="B26" s="412"/>
-      <c r="C26" s="412"/>
-      <c r="D26" s="412"/>
-      <c r="E26" s="412"/>
-      <c r="F26" s="413"/>
+      <c r="B26" s="280"/>
+      <c r="C26" s="280"/>
+      <c r="D26" s="280"/>
+      <c r="E26" s="280"/>
+      <c r="F26" s="281"/>
     </row>
     <row r="27" spans="1:6" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A27" s="414" t="s">
+      <c r="A27" s="282" t="s">
         <v>378</v>
       </c>
-      <c r="B27" s="415"/>
-      <c r="C27" s="415"/>
-      <c r="D27" s="415"/>
-      <c r="E27" s="415"/>
-      <c r="F27" s="416"/>
+      <c r="B27" s="283"/>
+      <c r="C27" s="283"/>
+      <c r="D27" s="283"/>
+      <c r="E27" s="283"/>
+      <c r="F27" s="284"/>
     </row>
     <row r="28" spans="1:6" ht="30" customHeight="1" thickBot="1">
-      <c r="A28" s="417" t="s">
+      <c r="A28" s="271" t="s">
         <v>379</v>
       </c>
-      <c r="B28" s="418"/>
-      <c r="C28" s="418"/>
-      <c r="D28" s="418"/>
-      <c r="E28" s="418"/>
-      <c r="F28" s="419"/>
+      <c r="B28" s="272"/>
+      <c r="C28" s="272"/>
+      <c r="D28" s="272"/>
+      <c r="E28" s="272"/>
+      <c r="F28" s="273"/>
     </row>
     <row r="29" spans="1:6" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A29" s="414" t="s">
+      <c r="A29" s="282" t="s">
         <v>380</v>
       </c>
-      <c r="B29" s="415"/>
-      <c r="C29" s="415"/>
-      <c r="D29" s="415"/>
-      <c r="E29" s="415"/>
-      <c r="F29" s="416"/>
+      <c r="B29" s="283"/>
+      <c r="C29" s="283"/>
+      <c r="D29" s="283"/>
+      <c r="E29" s="283"/>
+      <c r="F29" s="284"/>
     </row>
     <row r="30" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A30" s="417" t="s">
+      <c r="A30" s="271" t="s">
         <v>381</v>
       </c>
-      <c r="B30" s="418"/>
-      <c r="C30" s="418"/>
-      <c r="D30" s="418"/>
-      <c r="E30" s="418"/>
-      <c r="F30" s="419"/>
+      <c r="B30" s="272"/>
+      <c r="C30" s="272"/>
+      <c r="D30" s="272"/>
+      <c r="E30" s="272"/>
+      <c r="F30" s="273"/>
     </row>
     <row r="31" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A31" s="417" t="s">
+      <c r="A31" s="271" t="s">
         <v>382</v>
       </c>
-      <c r="B31" s="418"/>
-      <c r="C31" s="418"/>
-      <c r="D31" s="418"/>
-      <c r="E31" s="418"/>
-      <c r="F31" s="419"/>
+      <c r="B31" s="272"/>
+      <c r="C31" s="272"/>
+      <c r="D31" s="272"/>
+      <c r="E31" s="272"/>
+      <c r="F31" s="273"/>
     </row>
     <row r="32" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A32" s="417" t="s">
+      <c r="A32" s="271" t="s">
         <v>383</v>
       </c>
-      <c r="B32" s="418"/>
-      <c r="C32" s="418"/>
-      <c r="D32" s="418"/>
-      <c r="E32" s="418"/>
-      <c r="F32" s="419"/>
+      <c r="B32" s="272"/>
+      <c r="C32" s="272"/>
+      <c r="D32" s="272"/>
+      <c r="E32" s="272"/>
+      <c r="F32" s="273"/>
     </row>
     <row r="33" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A33" s="417" t="s">
+      <c r="A33" s="271" t="s">
         <v>384</v>
       </c>
-      <c r="B33" s="418"/>
-      <c r="C33" s="418"/>
-      <c r="D33" s="418"/>
-      <c r="E33" s="418"/>
-      <c r="F33" s="419"/>
+      <c r="B33" s="272"/>
+      <c r="C33" s="272"/>
+      <c r="D33" s="272"/>
+      <c r="E33" s="272"/>
+      <c r="F33" s="273"/>
     </row>
     <row r="34" spans="1:6" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A34" s="420" t="s">
+      <c r="A34" s="274" t="s">
         <v>385</v>
       </c>
-      <c r="B34" s="421"/>
-      <c r="C34" s="421"/>
-      <c r="D34" s="421"/>
-      <c r="E34" s="421"/>
-      <c r="F34" s="422"/>
+      <c r="B34" s="275"/>
+      <c r="C34" s="275"/>
+      <c r="D34" s="275"/>
+      <c r="E34" s="275"/>
+      <c r="F34" s="276"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A34:F34"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="D2:R2"/>
     <mergeCell ref="D3:R3"/>
     <mergeCell ref="A4:B5"/>
     <mergeCell ref="E4:R5"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A29:F29"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10137,16 +10934,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:44" ht="40.5">
-      <c r="B1" s="265" t="s">
+      <c r="B1" s="310" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="265"/>
-      <c r="D1" s="265"/>
-      <c r="E1" s="265"/>
-      <c r="F1" s="265"/>
-      <c r="G1" s="265"/>
-      <c r="H1" s="265"/>
-      <c r="I1" s="265"/>
+      <c r="C1" s="310"/>
+      <c r="D1" s="310"/>
+      <c r="E1" s="310"/>
+      <c r="F1" s="310"/>
+      <c r="G1" s="310"/>
+      <c r="H1" s="310"/>
+      <c r="I1" s="310"/>
       <c r="J1" s="31"/>
       <c r="K1" s="31"/>
       <c r="L1" s="31"/>
@@ -10184,16 +10981,16 @@
       <c r="AR1" s="31"/>
     </row>
     <row r="2" spans="2:44" ht="17.25" thickBot="1">
-      <c r="B2" s="266" t="s">
+      <c r="B2" s="311" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="266"/>
-      <c r="D2" s="266"/>
-      <c r="E2" s="266"/>
-      <c r="F2" s="266"/>
-      <c r="G2" s="266"/>
-      <c r="H2" s="266"/>
-      <c r="I2" s="266"/>
+      <c r="C2" s="311"/>
+      <c r="D2" s="311"/>
+      <c r="E2" s="311"/>
+      <c r="F2" s="311"/>
+      <c r="G2" s="311"/>
+      <c r="H2" s="311"/>
+      <c r="I2" s="311"/>
       <c r="J2" s="32"/>
       <c r="K2" s="32"/>
       <c r="L2" s="32"/>
@@ -10231,55 +11028,55 @@
       <c r="AR2" s="32"/>
     </row>
     <row r="3" spans="2:44" ht="18.75">
-      <c r="B3" s="267"/>
-      <c r="C3" s="268"/>
-      <c r="D3" s="268"/>
-      <c r="E3" s="268"/>
-      <c r="F3" s="268"/>
-      <c r="G3" s="268"/>
-      <c r="H3" s="268"/>
-      <c r="I3" s="268"/>
-      <c r="J3" s="273">
+      <c r="B3" s="312"/>
+      <c r="C3" s="313"/>
+      <c r="D3" s="313"/>
+      <c r="E3" s="313"/>
+      <c r="F3" s="313"/>
+      <c r="G3" s="313"/>
+      <c r="H3" s="313"/>
+      <c r="I3" s="313"/>
+      <c r="J3" s="293">
         <f ca="1">K5</f>
         <v>46181</v>
       </c>
-      <c r="K3" s="273"/>
-      <c r="L3" s="273"/>
-      <c r="M3" s="273"/>
-      <c r="N3" s="274"/>
-      <c r="O3" s="274"/>
-      <c r="P3" s="274"/>
-      <c r="Q3" s="274"/>
-      <c r="R3" s="274"/>
-      <c r="S3" s="274"/>
-      <c r="T3" s="274"/>
-      <c r="U3" s="274"/>
-      <c r="V3" s="274"/>
-      <c r="W3" s="274"/>
-      <c r="X3" s="274"/>
-      <c r="Y3" s="274"/>
-      <c r="Z3" s="274"/>
-      <c r="AA3" s="274"/>
-      <c r="AB3" s="274"/>
-      <c r="AC3" s="274"/>
-      <c r="AD3" s="274"/>
-      <c r="AE3" s="274"/>
-      <c r="AF3" s="274"/>
-      <c r="AG3" s="274"/>
-      <c r="AH3" s="274"/>
-      <c r="AI3" s="274"/>
-      <c r="AJ3" s="274"/>
-      <c r="AK3" s="274"/>
-      <c r="AL3" s="274"/>
-      <c r="AM3" s="274"/>
-      <c r="AN3" s="274"/>
-      <c r="AO3" s="274"/>
-      <c r="AP3" s="274"/>
-      <c r="AQ3" s="274"/>
-      <c r="AR3" s="274"/>
+      <c r="K3" s="293"/>
+      <c r="L3" s="293"/>
+      <c r="M3" s="293"/>
+      <c r="N3" s="294"/>
+      <c r="O3" s="294"/>
+      <c r="P3" s="294"/>
+      <c r="Q3" s="294"/>
+      <c r="R3" s="294"/>
+      <c r="S3" s="294"/>
+      <c r="T3" s="294"/>
+      <c r="U3" s="294"/>
+      <c r="V3" s="294"/>
+      <c r="W3" s="294"/>
+      <c r="X3" s="294"/>
+      <c r="Y3" s="294"/>
+      <c r="Z3" s="294"/>
+      <c r="AA3" s="294"/>
+      <c r="AB3" s="294"/>
+      <c r="AC3" s="294"/>
+      <c r="AD3" s="294"/>
+      <c r="AE3" s="294"/>
+      <c r="AF3" s="294"/>
+      <c r="AG3" s="294"/>
+      <c r="AH3" s="294"/>
+      <c r="AI3" s="294"/>
+      <c r="AJ3" s="294"/>
+      <c r="AK3" s="294"/>
+      <c r="AL3" s="294"/>
+      <c r="AM3" s="294"/>
+      <c r="AN3" s="294"/>
+      <c r="AO3" s="294"/>
+      <c r="AP3" s="294"/>
+      <c r="AQ3" s="294"/>
+      <c r="AR3" s="294"/>
     </row>
     <row r="4" spans="2:44" ht="15.75" thickBot="1">
-      <c r="B4" s="269"/>
+      <c r="B4" s="314"/>
       <c r="C4" s="78" t="s">
         <v>0</v>
       </c>
@@ -10287,82 +11084,82 @@
         <f ca="1">IF(MONTH(TODAY()-WEEKDAY(TODAY(),2)+1)&lt;MONTH(TODAY()),(TODAY()-28-DAY(TODAY())+7)-WEEKDAY((TODAY()-DAY(TODAY())+7),2)+1,(TODAY()-DAY(TODAY())+7)-WEEKDAY((TODAY()-DAY(TODAY())+7),2)+1)</f>
         <v>46174</v>
       </c>
-      <c r="E4" s="271"/>
-      <c r="F4" s="271"/>
-      <c r="G4" s="271"/>
-      <c r="H4" s="271"/>
-      <c r="I4" s="272"/>
-      <c r="J4" s="275">
+      <c r="E4" s="316"/>
+      <c r="F4" s="316"/>
+      <c r="G4" s="316"/>
+      <c r="H4" s="316"/>
+      <c r="I4" s="317"/>
+      <c r="J4" s="295">
         <f ca="1">K5</f>
         <v>46181</v>
       </c>
-      <c r="K4" s="275"/>
-      <c r="L4" s="275"/>
-      <c r="M4" s="275"/>
-      <c r="N4" s="280">
+      <c r="K4" s="295"/>
+      <c r="L4" s="295"/>
+      <c r="M4" s="295"/>
+      <c r="N4" s="300">
         <f ca="1">O5</f>
         <v>46209</v>
       </c>
-      <c r="O4" s="275"/>
-      <c r="P4" s="275"/>
-      <c r="Q4" s="275"/>
-      <c r="R4" s="275"/>
-      <c r="S4" s="275">
+      <c r="O4" s="295"/>
+      <c r="P4" s="295"/>
+      <c r="Q4" s="295"/>
+      <c r="R4" s="295"/>
+      <c r="S4" s="295">
         <f ca="1">T5</f>
         <v>46244</v>
       </c>
-      <c r="T4" s="275"/>
-      <c r="U4" s="275"/>
-      <c r="V4" s="275"/>
-      <c r="W4" s="275">
+      <c r="T4" s="295"/>
+      <c r="U4" s="295"/>
+      <c r="V4" s="295"/>
+      <c r="W4" s="295">
         <f ca="1">X5</f>
         <v>46272</v>
       </c>
-      <c r="X4" s="275"/>
-      <c r="Y4" s="275"/>
-      <c r="Z4" s="275"/>
-      <c r="AA4" s="275"/>
-      <c r="AB4" s="275">
+      <c r="X4" s="295"/>
+      <c r="Y4" s="295"/>
+      <c r="Z4" s="295"/>
+      <c r="AA4" s="295"/>
+      <c r="AB4" s="295">
         <f ca="1">AC5</f>
         <v>46307</v>
       </c>
-      <c r="AC4" s="275"/>
-      <c r="AD4" s="275"/>
-      <c r="AE4" s="275"/>
-      <c r="AF4" s="275">
+      <c r="AC4" s="295"/>
+      <c r="AD4" s="295"/>
+      <c r="AE4" s="295"/>
+      <c r="AF4" s="295">
         <f ca="1">AG5</f>
         <v>46335</v>
       </c>
-      <c r="AG4" s="275"/>
-      <c r="AH4" s="275"/>
-      <c r="AI4" s="275"/>
-      <c r="AJ4" s="275">
+      <c r="AG4" s="295"/>
+      <c r="AH4" s="295"/>
+      <c r="AI4" s="295"/>
+      <c r="AJ4" s="295">
         <f ca="1">AK5</f>
         <v>46363</v>
       </c>
-      <c r="AK4" s="275"/>
-      <c r="AL4" s="275"/>
-      <c r="AM4" s="275"/>
-      <c r="AN4" s="275"/>
-      <c r="AO4" s="275">
+      <c r="AK4" s="295"/>
+      <c r="AL4" s="295"/>
+      <c r="AM4" s="295"/>
+      <c r="AN4" s="295"/>
+      <c r="AO4" s="295">
         <f ca="1">AP5</f>
         <v>46398</v>
       </c>
-      <c r="AP4" s="275"/>
-      <c r="AQ4" s="275"/>
-      <c r="AR4" s="276"/>
+      <c r="AP4" s="295"/>
+      <c r="AQ4" s="295"/>
+      <c r="AR4" s="296"/>
     </row>
     <row r="5" spans="2:44" ht="33" thickBot="1">
-      <c r="B5" s="270"/>
+      <c r="B5" s="315"/>
       <c r="C5" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="277" t="s">
+      <c r="D5" s="297" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="278"/>
-      <c r="F5" s="278"/>
-      <c r="G5" s="279"/>
+      <c r="E5" s="298"/>
+      <c r="F5" s="298"/>
+      <c r="G5" s="299"/>
       <c r="H5" s="81"/>
       <c r="I5" s="79" t="s">
         <v>2</v>
@@ -12286,71 +13083,78 @@
     </row>
     <row r="24" spans="2:9" ht="15.75" thickBot="1"/>
     <row r="25" spans="2:9" ht="24.95" customHeight="1">
-      <c r="B25" s="256" t="s">
+      <c r="B25" s="301" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="257"/>
-      <c r="D25" s="257"/>
-      <c r="E25" s="257"/>
-      <c r="F25" s="257"/>
-      <c r="G25" s="257"/>
-      <c r="H25" s="257"/>
-      <c r="I25" s="258"/>
+      <c r="C25" s="302"/>
+      <c r="D25" s="302"/>
+      <c r="E25" s="302"/>
+      <c r="F25" s="302"/>
+      <c r="G25" s="302"/>
+      <c r="H25" s="302"/>
+      <c r="I25" s="303"/>
     </row>
     <row r="26" spans="2:9" ht="90" customHeight="1">
-      <c r="B26" s="259" t="s">
+      <c r="B26" s="304" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="260"/>
-      <c r="D26" s="260"/>
-      <c r="E26" s="260"/>
-      <c r="F26" s="260"/>
-      <c r="G26" s="260"/>
-      <c r="H26" s="260"/>
-      <c r="I26" s="261"/>
+      <c r="C26" s="305"/>
+      <c r="D26" s="305"/>
+      <c r="E26" s="305"/>
+      <c r="F26" s="305"/>
+      <c r="G26" s="305"/>
+      <c r="H26" s="305"/>
+      <c r="I26" s="306"/>
     </row>
     <row r="27" spans="2:9">
-      <c r="B27" s="259"/>
-      <c r="C27" s="260"/>
-      <c r="D27" s="260"/>
-      <c r="E27" s="260"/>
-      <c r="F27" s="260"/>
-      <c r="G27" s="260"/>
-      <c r="H27" s="260"/>
-      <c r="I27" s="261"/>
+      <c r="B27" s="304"/>
+      <c r="C27" s="305"/>
+      <c r="D27" s="305"/>
+      <c r="E27" s="305"/>
+      <c r="F27" s="305"/>
+      <c r="G27" s="305"/>
+      <c r="H27" s="305"/>
+      <c r="I27" s="306"/>
     </row>
     <row r="28" spans="2:9">
-      <c r="B28" s="259"/>
-      <c r="C28" s="260"/>
-      <c r="D28" s="260"/>
-      <c r="E28" s="260"/>
-      <c r="F28" s="260"/>
-      <c r="G28" s="260"/>
-      <c r="H28" s="260"/>
-      <c r="I28" s="261"/>
+      <c r="B28" s="304"/>
+      <c r="C28" s="305"/>
+      <c r="D28" s="305"/>
+      <c r="E28" s="305"/>
+      <c r="F28" s="305"/>
+      <c r="G28" s="305"/>
+      <c r="H28" s="305"/>
+      <c r="I28" s="306"/>
     </row>
     <row r="29" spans="2:9">
-      <c r="B29" s="259"/>
-      <c r="C29" s="260"/>
-      <c r="D29" s="260"/>
-      <c r="E29" s="260"/>
-      <c r="F29" s="260"/>
-      <c r="G29" s="260"/>
-      <c r="H29" s="260"/>
-      <c r="I29" s="261"/>
+      <c r="B29" s="304"/>
+      <c r="C29" s="305"/>
+      <c r="D29" s="305"/>
+      <c r="E29" s="305"/>
+      <c r="F29" s="305"/>
+      <c r="G29" s="305"/>
+      <c r="H29" s="305"/>
+      <c r="I29" s="306"/>
     </row>
     <row r="30" spans="2:9" ht="15.75" thickBot="1">
-      <c r="B30" s="262"/>
-      <c r="C30" s="263"/>
-      <c r="D30" s="263"/>
-      <c r="E30" s="263"/>
-      <c r="F30" s="263"/>
-      <c r="G30" s="263"/>
-      <c r="H30" s="263"/>
-      <c r="I30" s="264"/>
+      <c r="B30" s="307"/>
+      <c r="C30" s="308"/>
+      <c r="D30" s="308"/>
+      <c r="E30" s="308"/>
+      <c r="F30" s="308"/>
+      <c r="G30" s="308"/>
+      <c r="H30" s="308"/>
+      <c r="I30" s="309"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B25:I25"/>
+    <mergeCell ref="B26:I30"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="E4:I4"/>
     <mergeCell ref="J3:AR3"/>
     <mergeCell ref="AF4:AI4"/>
     <mergeCell ref="AJ4:AN4"/>
@@ -12361,28 +13165,21 @@
     <mergeCell ref="S4:V4"/>
     <mergeCell ref="W4:AA4"/>
     <mergeCell ref="AB4:AE4"/>
-    <mergeCell ref="B25:I25"/>
-    <mergeCell ref="B26:I30"/>
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="E4:I4"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H7:H16">
-    <cfRule type="containsText" dxfId="15" priority="9" operator="containsText" text="Blocked">
+    <cfRule type="containsText" dxfId="18" priority="9" operator="containsText" text="Blocked">
       <formula>NOT(ISERROR(SEARCH("Blocked",H7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7:AR16">
-    <cfRule type="expression" dxfId="14" priority="1">
+    <cfRule type="expression" dxfId="17" priority="1">
       <formula>AND($I7&gt;0, J$5 &lt;= ($E7+($F7-$E7)*$I7)-WEEKDAY(($E7+($F7-$E7)*$I7),2)+1, J$5 &gt;= $E7 - WEEKDAY($E7, 2)+1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="7">
+    <cfRule type="expression" dxfId="16" priority="7">
       <formula>AND(J$5&gt;=$E7-(WEEKDAY($E7, 2)+1),J$5&lt;=$F7)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="8">
+    <cfRule type="expression" dxfId="15" priority="8">
       <formula>J$5=(TODAY()-WEEKDAY(TODAY(), 2) + 1)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12410,150 +13207,150 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" ht="29.25" thickBot="1">
-      <c r="B2" s="282" t="s">
+      <c r="B2" s="336" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="283"/>
-      <c r="D2" s="283"/>
-      <c r="E2" s="283"/>
-      <c r="F2" s="283"/>
-      <c r="G2" s="283"/>
-      <c r="H2" s="283"/>
-      <c r="I2" s="283"/>
-      <c r="J2" s="283"/>
-      <c r="K2" s="283"/>
-      <c r="L2" s="283"/>
-      <c r="M2" s="283"/>
-      <c r="N2" s="283"/>
-      <c r="O2" s="283"/>
-      <c r="P2" s="284"/>
+      <c r="C2" s="337"/>
+      <c r="D2" s="337"/>
+      <c r="E2" s="337"/>
+      <c r="F2" s="337"/>
+      <c r="G2" s="337"/>
+      <c r="H2" s="337"/>
+      <c r="I2" s="337"/>
+      <c r="J2" s="337"/>
+      <c r="K2" s="337"/>
+      <c r="L2" s="337"/>
+      <c r="M2" s="337"/>
+      <c r="N2" s="337"/>
+      <c r="O2" s="337"/>
+      <c r="P2" s="338"/>
     </row>
     <row r="3" spans="2:16">
-      <c r="B3" s="285"/>
-      <c r="C3" s="286"/>
+      <c r="B3" s="339"/>
+      <c r="C3" s="340"/>
       <c r="D3" s="99" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="304" t="s">
+      <c r="E3" s="332" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="304"/>
-      <c r="G3" s="304"/>
-      <c r="H3" s="304"/>
-      <c r="I3" s="287" t="s">
+      <c r="F3" s="332"/>
+      <c r="G3" s="332"/>
+      <c r="H3" s="332"/>
+      <c r="I3" s="341" t="s">
         <v>46</v>
       </c>
-      <c r="J3" s="287"/>
-      <c r="K3" s="288" t="s">
+      <c r="J3" s="341"/>
+      <c r="K3" s="342" t="s">
         <v>17</v>
       </c>
-      <c r="L3" s="288"/>
-      <c r="M3" s="288"/>
-      <c r="N3" s="286"/>
-      <c r="O3" s="286"/>
-      <c r="P3" s="289"/>
+      <c r="L3" s="342"/>
+      <c r="M3" s="342"/>
+      <c r="N3" s="340"/>
+      <c r="O3" s="340"/>
+      <c r="P3" s="343"/>
     </row>
     <row r="4" spans="2:16" ht="15.75" thickBot="1">
-      <c r="B4" s="290"/>
-      <c r="C4" s="291"/>
-      <c r="D4" s="291"/>
-      <c r="E4" s="291"/>
-      <c r="F4" s="291"/>
-      <c r="G4" s="291"/>
-      <c r="H4" s="291"/>
-      <c r="I4" s="291"/>
-      <c r="J4" s="291"/>
-      <c r="K4" s="291"/>
-      <c r="L4" s="291"/>
-      <c r="M4" s="291"/>
-      <c r="N4" s="291"/>
-      <c r="O4" s="291"/>
-      <c r="P4" s="292"/>
+      <c r="B4" s="344"/>
+      <c r="C4" s="345"/>
+      <c r="D4" s="345"/>
+      <c r="E4" s="345"/>
+      <c r="F4" s="345"/>
+      <c r="G4" s="345"/>
+      <c r="H4" s="345"/>
+      <c r="I4" s="345"/>
+      <c r="J4" s="345"/>
+      <c r="K4" s="345"/>
+      <c r="L4" s="345"/>
+      <c r="M4" s="345"/>
+      <c r="N4" s="345"/>
+      <c r="O4" s="345"/>
+      <c r="P4" s="346"/>
     </row>
     <row r="5" spans="2:16" ht="15.75" thickBot="1">
-      <c r="B5" s="293" t="s">
+      <c r="B5" s="347" t="s">
         <v>79</v>
       </c>
-      <c r="C5" s="294"/>
-      <c r="D5" s="294"/>
-      <c r="E5" s="294"/>
-      <c r="F5" s="294"/>
-      <c r="G5" s="294"/>
-      <c r="H5" s="294"/>
-      <c r="I5" s="294"/>
-      <c r="J5" s="294"/>
-      <c r="K5" s="294"/>
-      <c r="L5" s="294"/>
-      <c r="M5" s="294"/>
-      <c r="N5" s="294"/>
-      <c r="O5" s="294"/>
-      <c r="P5" s="295"/>
+      <c r="C5" s="348"/>
+      <c r="D5" s="348"/>
+      <c r="E5" s="348"/>
+      <c r="F5" s="348"/>
+      <c r="G5" s="348"/>
+      <c r="H5" s="348"/>
+      <c r="I5" s="348"/>
+      <c r="J5" s="348"/>
+      <c r="K5" s="348"/>
+      <c r="L5" s="348"/>
+      <c r="M5" s="348"/>
+      <c r="N5" s="348"/>
+      <c r="O5" s="348"/>
+      <c r="P5" s="349"/>
     </row>
     <row r="6" spans="2:16" ht="129.75" customHeight="1" thickBot="1">
-      <c r="B6" s="296" t="s">
+      <c r="B6" s="350" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="297"/>
-      <c r="D6" s="298"/>
-      <c r="E6" s="299" t="s">
+      <c r="C6" s="351"/>
+      <c r="D6" s="352"/>
+      <c r="E6" s="331" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="299" t="s">
+      <c r="F6" s="331" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="299" t="s">
+      <c r="G6" s="331" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="299" t="s">
+      <c r="H6" s="331" t="s">
         <v>22</v>
       </c>
-      <c r="I6" s="299" t="s">
+      <c r="I6" s="331" t="s">
         <v>24</v>
       </c>
-      <c r="J6" s="299" t="s">
+      <c r="J6" s="331" t="s">
         <v>26</v>
       </c>
-      <c r="K6" s="299" t="s">
+      <c r="K6" s="331" t="s">
         <v>28</v>
       </c>
-      <c r="L6" s="299" t="s">
+      <c r="L6" s="331" t="s">
         <v>30</v>
       </c>
-      <c r="M6" s="299" t="s">
+      <c r="M6" s="331" t="s">
         <v>32</v>
       </c>
-      <c r="N6" s="281" t="s">
+      <c r="N6" s="335" t="s">
         <v>34</v>
       </c>
-      <c r="O6" s="281"/>
-      <c r="P6" s="281"/>
+      <c r="O6" s="335"/>
+      <c r="P6" s="335"/>
     </row>
     <row r="7" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B7" s="302" t="s">
+      <c r="B7" s="333" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="303"/>
+      <c r="C7" s="334"/>
       <c r="D7" s="114" t="s">
         <v>48</v>
       </c>
-      <c r="E7" s="299"/>
-      <c r="F7" s="299"/>
-      <c r="G7" s="299"/>
-      <c r="H7" s="299"/>
-      <c r="I7" s="299"/>
-      <c r="J7" s="299"/>
-      <c r="K7" s="299"/>
-      <c r="L7" s="299"/>
-      <c r="M7" s="299"/>
-      <c r="N7" s="281"/>
-      <c r="O7" s="281"/>
-      <c r="P7" s="281"/>
+      <c r="E7" s="331"/>
+      <c r="F7" s="331"/>
+      <c r="G7" s="331"/>
+      <c r="H7" s="331"/>
+      <c r="I7" s="331"/>
+      <c r="J7" s="331"/>
+      <c r="K7" s="331"/>
+      <c r="L7" s="331"/>
+      <c r="M7" s="331"/>
+      <c r="N7" s="335"/>
+      <c r="O7" s="335"/>
+      <c r="P7" s="335"/>
     </row>
     <row r="8" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B8" s="300" t="s">
+      <c r="B8" s="318" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="301"/>
+      <c r="C8" s="319"/>
       <c r="D8" s="100" t="s">
         <v>62</v>
       </c>
@@ -12591,10 +13388,10 @@
       <c r="P8" s="90"/>
     </row>
     <row r="9" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B9" s="300" t="s">
+      <c r="B9" s="318" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="301"/>
+      <c r="C9" s="319"/>
       <c r="D9" s="100" t="s">
         <v>50</v>
       </c>
@@ -12632,10 +13429,10 @@
       <c r="P9" s="94"/>
     </row>
     <row r="10" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B10" s="300" t="s">
+      <c r="B10" s="318" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="301"/>
+      <c r="C10" s="319"/>
       <c r="D10" s="100" t="s">
         <v>63</v>
       </c>
@@ -12673,10 +13470,10 @@
       <c r="P10" s="94"/>
     </row>
     <row r="11" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B11" s="300" t="s">
+      <c r="B11" s="318" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="301"/>
+      <c r="C11" s="319"/>
       <c r="D11" s="100" t="s">
         <v>64</v>
       </c>
@@ -12714,10 +13511,10 @@
       <c r="P11" s="94"/>
     </row>
     <row r="12" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B12" s="300" t="s">
+      <c r="B12" s="318" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="301"/>
+      <c r="C12" s="319"/>
       <c r="D12" s="100" t="s">
         <v>65</v>
       </c>
@@ -12755,10 +13552,10 @@
       <c r="P12" s="94"/>
     </row>
     <row r="13" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B13" s="300" t="s">
+      <c r="B13" s="318" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="301"/>
+      <c r="C13" s="319"/>
       <c r="D13" s="100" t="s">
         <v>66</v>
       </c>
@@ -12796,10 +13593,10 @@
       <c r="P13" s="94"/>
     </row>
     <row r="14" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B14" s="300" t="s">
+      <c r="B14" s="318" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="301"/>
+      <c r="C14" s="319"/>
       <c r="D14" s="100" t="s">
         <v>67</v>
       </c>
@@ -12837,10 +13634,10 @@
       <c r="P14" s="94"/>
     </row>
     <row r="15" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B15" s="300" t="s">
+      <c r="B15" s="318" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="301"/>
+      <c r="C15" s="319"/>
       <c r="D15" s="100" t="s">
         <v>68</v>
       </c>
@@ -12878,10 +13675,10 @@
       <c r="P15" s="94"/>
     </row>
     <row r="16" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B16" s="300" t="s">
+      <c r="B16" s="318" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="301"/>
+      <c r="C16" s="319"/>
       <c r="D16" s="100" t="s">
         <v>69</v>
       </c>
@@ -12919,10 +13716,10 @@
       <c r="P16" s="94"/>
     </row>
     <row r="17" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B17" s="300" t="s">
+      <c r="B17" s="318" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="301"/>
+      <c r="C17" s="319"/>
       <c r="D17" s="100" t="s">
         <v>70</v>
       </c>
@@ -12960,10 +13757,10 @@
       <c r="P17" s="94"/>
     </row>
     <row r="18" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B18" s="300" t="s">
+      <c r="B18" s="318" t="s">
         <v>71</v>
       </c>
-      <c r="C18" s="301"/>
+      <c r="C18" s="319"/>
       <c r="D18" s="100" t="s">
         <v>72</v>
       </c>
@@ -13001,10 +13798,10 @@
       <c r="P18" s="94"/>
     </row>
     <row r="19" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B19" s="300" t="s">
+      <c r="B19" s="318" t="s">
         <v>74</v>
       </c>
-      <c r="C19" s="301"/>
+      <c r="C19" s="319"/>
       <c r="D19" s="100" t="s">
         <v>77</v>
       </c>
@@ -13042,10 +13839,10 @@
       <c r="P19" s="94"/>
     </row>
     <row r="20" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B20" s="300" t="s">
+      <c r="B20" s="318" t="s">
         <v>75</v>
       </c>
-      <c r="C20" s="301"/>
+      <c r="C20" s="319"/>
       <c r="D20" s="100" t="s">
         <v>78</v>
       </c>
@@ -13083,10 +13880,10 @@
       <c r="P20" s="94"/>
     </row>
     <row r="21" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B21" s="300" t="s">
+      <c r="B21" s="318" t="s">
         <v>73</v>
       </c>
-      <c r="C21" s="301"/>
+      <c r="C21" s="319"/>
       <c r="D21" s="101" t="s">
         <v>76</v>
       </c>
@@ -13157,137 +13954,137 @@
       </c>
     </row>
     <row r="28" spans="2:16">
-      <c r="B28" s="313" t="s">
+      <c r="B28" s="323" t="s">
         <v>55</v>
       </c>
-      <c r="C28" s="314"/>
-      <c r="D28" s="314"/>
-      <c r="E28" s="314"/>
-      <c r="F28" s="314"/>
-      <c r="G28" s="314"/>
-      <c r="H28" s="314"/>
-      <c r="I28" s="314"/>
-      <c r="J28" s="314"/>
-      <c r="K28" s="314"/>
-      <c r="L28" s="314"/>
-      <c r="M28" s="314"/>
-      <c r="N28" s="314"/>
-      <c r="O28" s="314"/>
-      <c r="P28" s="315"/>
+      <c r="C28" s="324"/>
+      <c r="D28" s="324"/>
+      <c r="E28" s="324"/>
+      <c r="F28" s="324"/>
+      <c r="G28" s="324"/>
+      <c r="H28" s="324"/>
+      <c r="I28" s="324"/>
+      <c r="J28" s="324"/>
+      <c r="K28" s="324"/>
+      <c r="L28" s="324"/>
+      <c r="M28" s="324"/>
+      <c r="N28" s="324"/>
+      <c r="O28" s="324"/>
+      <c r="P28" s="325"/>
     </row>
     <row r="29" spans="2:16" ht="15" customHeight="1">
-      <c r="B29" s="305" t="s">
+      <c r="B29" s="320" t="s">
         <v>56</v>
       </c>
-      <c r="C29" s="306"/>
-      <c r="D29" s="306"/>
-      <c r="E29" s="306"/>
-      <c r="F29" s="306"/>
-      <c r="G29" s="306"/>
-      <c r="H29" s="306"/>
-      <c r="I29" s="306"/>
-      <c r="J29" s="306"/>
-      <c r="K29" s="306"/>
-      <c r="L29" s="306"/>
-      <c r="M29" s="306"/>
-      <c r="N29" s="306"/>
-      <c r="O29" s="306"/>
-      <c r="P29" s="307"/>
+      <c r="C29" s="321"/>
+      <c r="D29" s="321"/>
+      <c r="E29" s="321"/>
+      <c r="F29" s="321"/>
+      <c r="G29" s="321"/>
+      <c r="H29" s="321"/>
+      <c r="I29" s="321"/>
+      <c r="J29" s="321"/>
+      <c r="K29" s="321"/>
+      <c r="L29" s="321"/>
+      <c r="M29" s="321"/>
+      <c r="N29" s="321"/>
+      <c r="O29" s="321"/>
+      <c r="P29" s="322"/>
     </row>
     <row r="30" spans="2:16" ht="15" customHeight="1">
-      <c r="B30" s="305" t="s">
+      <c r="B30" s="320" t="s">
         <v>57</v>
       </c>
-      <c r="C30" s="306"/>
-      <c r="D30" s="306"/>
-      <c r="E30" s="306"/>
-      <c r="F30" s="306"/>
-      <c r="G30" s="306"/>
-      <c r="H30" s="306"/>
-      <c r="I30" s="306"/>
-      <c r="J30" s="306"/>
-      <c r="K30" s="306"/>
-      <c r="L30" s="306"/>
-      <c r="M30" s="306"/>
-      <c r="N30" s="306"/>
-      <c r="O30" s="306"/>
-      <c r="P30" s="307"/>
+      <c r="C30" s="321"/>
+      <c r="D30" s="321"/>
+      <c r="E30" s="321"/>
+      <c r="F30" s="321"/>
+      <c r="G30" s="321"/>
+      <c r="H30" s="321"/>
+      <c r="I30" s="321"/>
+      <c r="J30" s="321"/>
+      <c r="K30" s="321"/>
+      <c r="L30" s="321"/>
+      <c r="M30" s="321"/>
+      <c r="N30" s="321"/>
+      <c r="O30" s="321"/>
+      <c r="P30" s="322"/>
     </row>
     <row r="31" spans="2:16" ht="15" customHeight="1">
-      <c r="B31" s="305" t="s">
+      <c r="B31" s="320" t="s">
         <v>58</v>
       </c>
-      <c r="C31" s="306"/>
-      <c r="D31" s="306"/>
-      <c r="E31" s="306"/>
-      <c r="F31" s="306"/>
-      <c r="G31" s="306"/>
-      <c r="H31" s="306"/>
-      <c r="I31" s="306"/>
-      <c r="J31" s="306"/>
-      <c r="K31" s="306"/>
-      <c r="L31" s="306"/>
-      <c r="M31" s="306"/>
-      <c r="N31" s="306"/>
-      <c r="O31" s="306"/>
-      <c r="P31" s="307"/>
+      <c r="C31" s="321"/>
+      <c r="D31" s="321"/>
+      <c r="E31" s="321"/>
+      <c r="F31" s="321"/>
+      <c r="G31" s="321"/>
+      <c r="H31" s="321"/>
+      <c r="I31" s="321"/>
+      <c r="J31" s="321"/>
+      <c r="K31" s="321"/>
+      <c r="L31" s="321"/>
+      <c r="M31" s="321"/>
+      <c r="N31" s="321"/>
+      <c r="O31" s="321"/>
+      <c r="P31" s="322"/>
     </row>
     <row r="32" spans="2:16" ht="20.100000000000001" customHeight="1">
-      <c r="B32" s="305" t="s">
+      <c r="B32" s="320" t="s">
         <v>59</v>
       </c>
-      <c r="C32" s="308"/>
-      <c r="D32" s="308"/>
-      <c r="E32" s="308"/>
-      <c r="F32" s="308"/>
-      <c r="G32" s="308"/>
-      <c r="H32" s="308"/>
-      <c r="I32" s="308"/>
-      <c r="J32" s="308"/>
-      <c r="K32" s="308"/>
-      <c r="L32" s="308"/>
-      <c r="M32" s="308"/>
-      <c r="N32" s="308"/>
-      <c r="O32" s="308"/>
-      <c r="P32" s="309"/>
+      <c r="C32" s="326"/>
+      <c r="D32" s="326"/>
+      <c r="E32" s="326"/>
+      <c r="F32" s="326"/>
+      <c r="G32" s="326"/>
+      <c r="H32" s="326"/>
+      <c r="I32" s="326"/>
+      <c r="J32" s="326"/>
+      <c r="K32" s="326"/>
+      <c r="L32" s="326"/>
+      <c r="M32" s="326"/>
+      <c r="N32" s="326"/>
+      <c r="O32" s="326"/>
+      <c r="P32" s="327"/>
     </row>
     <row r="33" spans="1:16" ht="20.100000000000001" customHeight="1">
-      <c r="B33" s="305" t="s">
+      <c r="B33" s="320" t="s">
         <v>60</v>
       </c>
-      <c r="C33" s="308"/>
-      <c r="D33" s="308"/>
-      <c r="E33" s="308"/>
-      <c r="F33" s="308"/>
-      <c r="G33" s="308"/>
-      <c r="H33" s="308"/>
-      <c r="I33" s="308"/>
-      <c r="J33" s="308"/>
-      <c r="K33" s="308"/>
-      <c r="L33" s="308"/>
-      <c r="M33" s="308"/>
-      <c r="N33" s="308"/>
-      <c r="O33" s="308"/>
-      <c r="P33" s="309"/>
+      <c r="C33" s="326"/>
+      <c r="D33" s="326"/>
+      <c r="E33" s="326"/>
+      <c r="F33" s="326"/>
+      <c r="G33" s="326"/>
+      <c r="H33" s="326"/>
+      <c r="I33" s="326"/>
+      <c r="J33" s="326"/>
+      <c r="K33" s="326"/>
+      <c r="L33" s="326"/>
+      <c r="M33" s="326"/>
+      <c r="N33" s="326"/>
+      <c r="O33" s="326"/>
+      <c r="P33" s="327"/>
     </row>
     <row r="34" spans="1:16" ht="20.100000000000001" customHeight="1">
-      <c r="B34" s="310" t="s">
+      <c r="B34" s="328" t="s">
         <v>61</v>
       </c>
-      <c r="C34" s="311"/>
-      <c r="D34" s="311"/>
-      <c r="E34" s="311"/>
-      <c r="F34" s="311"/>
-      <c r="G34" s="311"/>
-      <c r="H34" s="311"/>
-      <c r="I34" s="311"/>
-      <c r="J34" s="311"/>
-      <c r="K34" s="311"/>
-      <c r="L34" s="311"/>
-      <c r="M34" s="311"/>
-      <c r="N34" s="311"/>
-      <c r="O34" s="311"/>
-      <c r="P34" s="312"/>
+      <c r="C34" s="329"/>
+      <c r="D34" s="329"/>
+      <c r="E34" s="329"/>
+      <c r="F34" s="329"/>
+      <c r="G34" s="329"/>
+      <c r="H34" s="329"/>
+      <c r="I34" s="329"/>
+      <c r="J34" s="329"/>
+      <c r="K34" s="329"/>
+      <c r="L34" s="329"/>
+      <c r="M34" s="329"/>
+      <c r="N34" s="329"/>
+      <c r="O34" s="329"/>
+      <c r="P34" s="330"/>
     </row>
     <row r="35" spans="1:16" ht="20.100000000000001" customHeight="1"/>
     <row r="39" spans="1:16" ht="15" customHeight="1"/>
@@ -13301,33 +14098,6 @@
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B29:P29"/>
-    <mergeCell ref="B28:P28"/>
-    <mergeCell ref="B30:P30"/>
-    <mergeCell ref="B31:P31"/>
-    <mergeCell ref="B32:P32"/>
-    <mergeCell ref="B33:P33"/>
-    <mergeCell ref="B34:P34"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="M6:M7"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="E3:H3"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="L6:L7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
     <mergeCell ref="N6:N7"/>
     <mergeCell ref="O6:O7"/>
     <mergeCell ref="P6:P7"/>
@@ -13344,18 +14114,45 @@
     <mergeCell ref="G6:G7"/>
     <mergeCell ref="H6:H7"/>
     <mergeCell ref="I6:I7"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="M6:M7"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="B31:P31"/>
+    <mergeCell ref="B32:P32"/>
+    <mergeCell ref="B33:P33"/>
+    <mergeCell ref="B34:P34"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B29:P29"/>
+    <mergeCell ref="B28:P28"/>
+    <mergeCell ref="B30:P30"/>
   </mergeCells>
   <conditionalFormatting sqref="E8:N21 B23:B26">
-    <cfRule type="containsText" dxfId="11" priority="1" operator="containsText" text="I">
+    <cfRule type="containsText" dxfId="14" priority="1" operator="containsText" text="I">
       <formula>NOT(ISERROR(SEARCH("I",B8)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="10" priority="2" operator="containsText" text="C">
+    <cfRule type="containsText" dxfId="13" priority="2" operator="containsText" text="C">
       <formula>NOT(ISERROR(SEARCH("C",B8)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="A">
+    <cfRule type="containsText" dxfId="12" priority="3" operator="containsText" text="A">
       <formula>NOT(ISERROR(SEARCH("A",B8)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="8" priority="4" operator="containsText" text="R">
+    <cfRule type="containsText" dxfId="11" priority="4" operator="containsText" text="R">
       <formula>NOT(ISERROR(SEARCH("R",B8)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13395,20 +14192,20 @@
   <sheetData>
     <row r="1" spans="1:25" ht="33" customHeight="1" thickBot="1">
       <c r="A1" s="115"/>
-      <c r="B1" s="333" t="s">
+      <c r="B1" s="356" t="s">
         <v>111</v>
       </c>
-      <c r="C1" s="334"/>
-      <c r="D1" s="334"/>
-      <c r="E1" s="334"/>
-      <c r="F1" s="334"/>
-      <c r="G1" s="334"/>
-      <c r="H1" s="334"/>
-      <c r="I1" s="334"/>
-      <c r="J1" s="334"/>
-      <c r="K1" s="334"/>
-      <c r="L1" s="334"/>
-      <c r="M1" s="335"/>
+      <c r="C1" s="357"/>
+      <c r="D1" s="357"/>
+      <c r="E1" s="357"/>
+      <c r="F1" s="357"/>
+      <c r="G1" s="357"/>
+      <c r="H1" s="357"/>
+      <c r="I1" s="357"/>
+      <c r="J1" s="357"/>
+      <c r="K1" s="357"/>
+      <c r="L1" s="357"/>
+      <c r="M1" s="358"/>
       <c r="N1" s="115"/>
       <c r="O1" s="115"/>
       <c r="P1" s="115"/>
@@ -13432,16 +14229,16 @@
       <c r="E2" s="130" t="s">
         <v>112</v>
       </c>
-      <c r="F2" s="336"/>
-      <c r="G2" s="336"/>
-      <c r="H2" s="336"/>
+      <c r="F2" s="359"/>
+      <c r="G2" s="359"/>
+      <c r="H2" s="359"/>
       <c r="I2" s="132" t="s">
         <v>113</v>
       </c>
-      <c r="J2" s="337">
+      <c r="J2" s="360">
         <v>46173</v>
       </c>
-      <c r="K2" s="337"/>
+      <c r="K2" s="360"/>
       <c r="L2" s="133"/>
       <c r="M2" s="117"/>
       <c r="N2" s="115"/>
@@ -13502,18 +14299,18 @@
       <c r="C4" s="133"/>
       <c r="D4" s="133"/>
       <c r="E4" s="133"/>
-      <c r="F4" s="338" t="s">
+      <c r="F4" s="361" t="s">
         <v>118</v>
       </c>
-      <c r="G4" s="338"/>
-      <c r="H4" s="338"/>
+      <c r="G4" s="361"/>
+      <c r="H4" s="361"/>
       <c r="I4" s="133"/>
       <c r="J4" s="133"/>
-      <c r="K4" s="339" t="s">
+      <c r="K4" s="362" t="s">
         <v>137</v>
       </c>
-      <c r="L4" s="339"/>
-      <c r="M4" s="340"/>
+      <c r="L4" s="362"/>
+      <c r="M4" s="363"/>
       <c r="N4" s="115"/>
       <c r="O4" s="115"/>
       <c r="P4" s="115"/>
@@ -13570,10 +14367,10 @@
         <v>126</v>
       </c>
       <c r="N5" s="115"/>
-      <c r="O5" s="316" t="s">
+      <c r="O5" s="364" t="s">
         <v>131</v>
       </c>
-      <c r="P5" s="317"/>
+      <c r="P5" s="365"/>
       <c r="Q5" s="139" t="str">
         <f>Y$7</f>
         <v>Very Low</v>
@@ -13644,7 +14441,7 @@
         <v>Severe</v>
       </c>
       <c r="N6" s="115"/>
-      <c r="O6" s="318" t="s">
+      <c r="O6" s="353" t="s">
         <v>121</v>
       </c>
       <c r="P6" s="140" t="str">
@@ -13716,7 +14513,7 @@
         <v>Moderate</v>
       </c>
       <c r="N7" s="115"/>
-      <c r="O7" s="319"/>
+      <c r="O7" s="354"/>
       <c r="P7" s="140" t="str">
         <f>X$4</f>
         <v>High</v>
@@ -13786,7 +14583,7 @@
         <v>Moderate</v>
       </c>
       <c r="N8" s="115"/>
-      <c r="O8" s="319"/>
+      <c r="O8" s="354"/>
       <c r="P8" s="140" t="str">
         <f>X$5</f>
         <v>Medium</v>
@@ -13852,7 +14649,7 @@
         <v>Moderate</v>
       </c>
       <c r="N9" s="115"/>
-      <c r="O9" s="319"/>
+      <c r="O9" s="354"/>
       <c r="P9" s="140" t="str">
         <f>X$6</f>
         <v>Low</v>
@@ -13918,7 +14715,7 @@
         <v>Moderate</v>
       </c>
       <c r="N10" s="115"/>
-      <c r="O10" s="320"/>
+      <c r="O10" s="355"/>
       <c r="P10" s="151" t="str">
         <f>X$7</f>
         <v>Very Low</v>
@@ -14039,10 +14836,10 @@
         <v>Moderate</v>
       </c>
       <c r="N12" s="115"/>
-      <c r="O12" s="316" t="s">
+      <c r="O12" s="364" t="s">
         <v>131</v>
       </c>
-      <c r="P12" s="317"/>
+      <c r="P12" s="365"/>
       <c r="Q12" s="139" t="str">
         <f>Y$7</f>
         <v>Very Low</v>
@@ -14109,7 +14906,7 @@
         <v>Sustainable</v>
       </c>
       <c r="N13" s="115"/>
-      <c r="O13" s="318" t="s">
+      <c r="O13" s="353" t="s">
         <v>121</v>
       </c>
       <c r="P13" s="140" t="str">
@@ -14182,7 +14979,7 @@
         <v>Moderate</v>
       </c>
       <c r="N14" s="115"/>
-      <c r="O14" s="319"/>
+      <c r="O14" s="354"/>
       <c r="P14" s="140" t="str">
         <f>X$4</f>
         <v>High</v>
@@ -14253,7 +15050,7 @@
         <v>Severe</v>
       </c>
       <c r="N15" s="115"/>
-      <c r="O15" s="319"/>
+      <c r="O15" s="354"/>
       <c r="P15" s="140" t="str">
         <f>X$5</f>
         <v>Medium</v>
@@ -14296,7 +15093,7 @@
       <c r="K16" s="115"/>
       <c r="L16" s="115"/>
       <c r="N16" s="115"/>
-      <c r="O16" s="319"/>
+      <c r="O16" s="354"/>
       <c r="P16" s="140" t="str">
         <f>X$6</f>
         <v>Low</v>
@@ -14328,22 +15125,22 @@
     </row>
     <row r="17" spans="1:25" ht="42" customHeight="1" thickBot="1">
       <c r="A17" s="115"/>
-      <c r="B17" s="321" t="s">
+      <c r="B17" s="366" t="s">
         <v>141</v>
       </c>
-      <c r="C17" s="322"/>
-      <c r="D17" s="322"/>
-      <c r="E17" s="322"/>
-      <c r="F17" s="322"/>
-      <c r="G17" s="322"/>
-      <c r="H17" s="323"/>
-      <c r="I17" s="322"/>
-      <c r="J17" s="322"/>
-      <c r="K17" s="322"/>
-      <c r="L17" s="322"/>
-      <c r="M17" s="324"/>
+      <c r="C17" s="367"/>
+      <c r="D17" s="367"/>
+      <c r="E17" s="367"/>
+      <c r="F17" s="367"/>
+      <c r="G17" s="367"/>
+      <c r="H17" s="368"/>
+      <c r="I17" s="367"/>
+      <c r="J17" s="367"/>
+      <c r="K17" s="367"/>
+      <c r="L17" s="367"/>
+      <c r="M17" s="369"/>
       <c r="N17" s="115"/>
-      <c r="O17" s="320"/>
+      <c r="O17" s="355"/>
       <c r="P17" s="151" t="str">
         <f>X$7</f>
         <v>Very Low</v>
@@ -14375,20 +15172,20 @@
     </row>
     <row r="18" spans="1:25">
       <c r="A18" s="115"/>
-      <c r="B18" s="325" t="s">
+      <c r="B18" s="370" t="s">
         <v>142</v>
       </c>
-      <c r="C18" s="326"/>
-      <c r="D18" s="326"/>
-      <c r="E18" s="326"/>
-      <c r="F18" s="326"/>
-      <c r="G18" s="326"/>
-      <c r="H18" s="327"/>
-      <c r="I18" s="326"/>
-      <c r="J18" s="326"/>
-      <c r="K18" s="326"/>
-      <c r="L18" s="326"/>
-      <c r="M18" s="328"/>
+      <c r="C18" s="371"/>
+      <c r="D18" s="371"/>
+      <c r="E18" s="371"/>
+      <c r="F18" s="371"/>
+      <c r="G18" s="371"/>
+      <c r="H18" s="372"/>
+      <c r="I18" s="371"/>
+      <c r="J18" s="371"/>
+      <c r="K18" s="371"/>
+      <c r="L18" s="371"/>
+      <c r="M18" s="373"/>
       <c r="N18" s="115"/>
       <c r="O18" s="115"/>
       <c r="P18" s="115"/>
@@ -14404,20 +15201,20 @@
     </row>
     <row r="19" spans="1:25" ht="19.5" thickBot="1">
       <c r="A19" s="115"/>
-      <c r="B19" s="325" t="s">
+      <c r="B19" s="370" t="s">
         <v>143</v>
       </c>
-      <c r="C19" s="326"/>
-      <c r="D19" s="326"/>
-      <c r="E19" s="326"/>
-      <c r="F19" s="326"/>
-      <c r="G19" s="326"/>
-      <c r="H19" s="327"/>
-      <c r="I19" s="326"/>
-      <c r="J19" s="326"/>
-      <c r="K19" s="326"/>
-      <c r="L19" s="326"/>
-      <c r="M19" s="328"/>
+      <c r="C19" s="371"/>
+      <c r="D19" s="371"/>
+      <c r="E19" s="371"/>
+      <c r="F19" s="371"/>
+      <c r="G19" s="371"/>
+      <c r="H19" s="372"/>
+      <c r="I19" s="371"/>
+      <c r="J19" s="371"/>
+      <c r="K19" s="371"/>
+      <c r="L19" s="371"/>
+      <c r="M19" s="373"/>
       <c r="N19" s="115"/>
       <c r="O19" s="138" t="s">
         <v>139</v>
@@ -14435,25 +15232,25 @@
     </row>
     <row r="20" spans="1:25" ht="42" customHeight="1" thickBot="1">
       <c r="A20" s="115"/>
-      <c r="B20" s="325" t="s">
+      <c r="B20" s="370" t="s">
         <v>144</v>
       </c>
-      <c r="C20" s="326"/>
-      <c r="D20" s="326"/>
-      <c r="E20" s="326"/>
-      <c r="F20" s="326"/>
-      <c r="G20" s="326"/>
-      <c r="H20" s="327"/>
-      <c r="I20" s="326"/>
-      <c r="J20" s="326"/>
-      <c r="K20" s="326"/>
-      <c r="L20" s="326"/>
-      <c r="M20" s="328"/>
+      <c r="C20" s="371"/>
+      <c r="D20" s="371"/>
+      <c r="E20" s="371"/>
+      <c r="F20" s="371"/>
+      <c r="G20" s="371"/>
+      <c r="H20" s="372"/>
+      <c r="I20" s="371"/>
+      <c r="J20" s="371"/>
+      <c r="K20" s="371"/>
+      <c r="L20" s="371"/>
+      <c r="M20" s="373"/>
       <c r="N20" s="115"/>
-      <c r="O20" s="316" t="s">
+      <c r="O20" s="364" t="s">
         <v>131</v>
       </c>
-      <c r="P20" s="317"/>
+      <c r="P20" s="365"/>
       <c r="Q20" s="139" t="str">
         <f>Y$7</f>
         <v>Very Low</v>
@@ -14481,22 +15278,22 @@
     </row>
     <row r="21" spans="1:25" ht="42" customHeight="1" thickBot="1">
       <c r="A21" s="115"/>
-      <c r="B21" s="325" t="s">
+      <c r="B21" s="370" t="s">
         <v>145</v>
       </c>
-      <c r="C21" s="326"/>
-      <c r="D21" s="326"/>
-      <c r="E21" s="326"/>
-      <c r="F21" s="326"/>
-      <c r="G21" s="326"/>
-      <c r="H21" s="327"/>
-      <c r="I21" s="326"/>
-      <c r="J21" s="326"/>
-      <c r="K21" s="326"/>
-      <c r="L21" s="326"/>
-      <c r="M21" s="328"/>
+      <c r="C21" s="371"/>
+      <c r="D21" s="371"/>
+      <c r="E21" s="371"/>
+      <c r="F21" s="371"/>
+      <c r="G21" s="371"/>
+      <c r="H21" s="372"/>
+      <c r="I21" s="371"/>
+      <c r="J21" s="371"/>
+      <c r="K21" s="371"/>
+      <c r="L21" s="371"/>
+      <c r="M21" s="373"/>
       <c r="N21" s="115"/>
-      <c r="O21" s="318" t="s">
+      <c r="O21" s="353" t="s">
         <v>121</v>
       </c>
       <c r="P21" s="140" t="str">
@@ -14530,22 +15327,22 @@
     </row>
     <row r="22" spans="1:25" ht="42" customHeight="1" thickBot="1">
       <c r="A22" s="115"/>
-      <c r="B22" s="329" t="s">
+      <c r="B22" s="374" t="s">
         <v>146</v>
       </c>
-      <c r="C22" s="330"/>
-      <c r="D22" s="330"/>
-      <c r="E22" s="330"/>
-      <c r="F22" s="330"/>
-      <c r="G22" s="330"/>
-      <c r="H22" s="331"/>
-      <c r="I22" s="330"/>
-      <c r="J22" s="330"/>
-      <c r="K22" s="330"/>
-      <c r="L22" s="330"/>
-      <c r="M22" s="332"/>
+      <c r="C22" s="375"/>
+      <c r="D22" s="375"/>
+      <c r="E22" s="375"/>
+      <c r="F22" s="375"/>
+      <c r="G22" s="375"/>
+      <c r="H22" s="376"/>
+      <c r="I22" s="375"/>
+      <c r="J22" s="375"/>
+      <c r="K22" s="375"/>
+      <c r="L22" s="375"/>
+      <c r="M22" s="377"/>
       <c r="N22" s="115"/>
-      <c r="O22" s="319"/>
+      <c r="O22" s="354"/>
       <c r="P22" s="140" t="str">
         <f>X$4</f>
         <v>High</v>
@@ -14588,7 +15385,7 @@
       <c r="K23" s="115"/>
       <c r="L23" s="115"/>
       <c r="N23" s="115"/>
-      <c r="O23" s="319"/>
+      <c r="O23" s="354"/>
       <c r="P23" s="140" t="str">
         <f>X$5</f>
         <v>Medium</v>
@@ -14631,7 +15428,7 @@
       <c r="K24" s="115"/>
       <c r="L24" s="115"/>
       <c r="N24" s="115"/>
-      <c r="O24" s="319"/>
+      <c r="O24" s="354"/>
       <c r="P24" s="140" t="str">
         <f>X$6</f>
         <v>Low</v>
@@ -14674,7 +15471,7 @@
       <c r="K25" s="115"/>
       <c r="L25" s="115"/>
       <c r="N25" s="115"/>
-      <c r="O25" s="320"/>
+      <c r="O25" s="355"/>
       <c r="P25" s="151" t="str">
         <f>X$7</f>
         <v>Very Low</v>
@@ -39081,13 +39878,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="O6:O10"/>
-    <mergeCell ref="B1:M1"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="O5:P5"/>
     <mergeCell ref="O12:P12"/>
     <mergeCell ref="O13:O17"/>
     <mergeCell ref="O20:P20"/>
@@ -39098,32 +39888,39 @@
     <mergeCell ref="B20:M20"/>
     <mergeCell ref="B21:M21"/>
     <mergeCell ref="B22:M22"/>
+    <mergeCell ref="O6:O10"/>
+    <mergeCell ref="B1:M1"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="O5:P5"/>
   </mergeCells>
   <conditionalFormatting sqref="H6:H15">
-    <cfRule type="containsText" dxfId="7" priority="13" operator="containsText" text="Sustainable">
+    <cfRule type="containsText" dxfId="10" priority="13" operator="containsText" text="Sustainable">
       <formula>NOT(ISERROR(SEARCH("Sustainable",H6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="14" operator="containsText" text="Moderate">
+    <cfRule type="containsText" dxfId="9" priority="14" operator="containsText" text="Moderate">
       <formula>NOT(ISERROR(SEARCH("Moderate",H6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="15" operator="containsText" text="Critical">
+    <cfRule type="containsText" dxfId="8" priority="15" operator="containsText" text="Critical">
       <formula>NOT(ISERROR(SEARCH("Critical",H6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="16" operator="containsText" text="Severe">
+    <cfRule type="containsText" dxfId="7" priority="16" operator="containsText" text="Severe">
       <formula>NOT(ISERROR(SEARCH("Severe",H6)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M6:M15">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="Sustainable">
+    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="Sustainable">
       <formula>NOT(ISERROR(SEARCH("Sustainable",M6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="Moderate">
+    <cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="Moderate">
       <formula>NOT(ISERROR(SEARCH("Moderate",M6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="Critical">
+    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="Critical">
       <formula>NOT(ISERROR(SEARCH("Critical",M6)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="Severe">
+    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="Severe">
       <formula>NOT(ISERROR(SEARCH("Severe",M6)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -39155,69 +39952,69 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13" ht="24" customHeight="1">
-      <c r="B1" s="341" t="s">
+      <c r="B1" s="378" t="s">
         <v>185</v>
       </c>
-      <c r="C1" s="341"/>
-      <c r="D1" s="341"/>
-      <c r="E1" s="341"/>
-      <c r="F1" s="341"/>
-      <c r="G1" s="341"/>
-      <c r="H1" s="341"/>
-      <c r="I1" s="341"/>
-      <c r="J1" s="341"/>
+      <c r="C1" s="378"/>
+      <c r="D1" s="378"/>
+      <c r="E1" s="378"/>
+      <c r="F1" s="378"/>
+      <c r="G1" s="378"/>
+      <c r="H1" s="378"/>
+      <c r="I1" s="378"/>
+      <c r="J1" s="378"/>
     </row>
     <row r="2" spans="2:13" ht="24" customHeight="1">
-      <c r="B2" s="341"/>
-      <c r="C2" s="341"/>
-      <c r="D2" s="341"/>
-      <c r="E2" s="341"/>
-      <c r="F2" s="341"/>
-      <c r="G2" s="341"/>
-      <c r="H2" s="341"/>
-      <c r="I2" s="341"/>
-      <c r="J2" s="341"/>
+      <c r="B2" s="378"/>
+      <c r="C2" s="378"/>
+      <c r="D2" s="378"/>
+      <c r="E2" s="378"/>
+      <c r="F2" s="378"/>
+      <c r="G2" s="378"/>
+      <c r="H2" s="378"/>
+      <c r="I2" s="378"/>
+      <c r="J2" s="378"/>
     </row>
     <row r="3" spans="2:13" ht="24" customHeight="1" thickBot="1">
-      <c r="B3" s="342"/>
-      <c r="C3" s="341"/>
-      <c r="D3" s="341"/>
-      <c r="E3" s="341"/>
-      <c r="F3" s="341"/>
-      <c r="G3" s="341"/>
-      <c r="H3" s="341"/>
-      <c r="I3" s="341"/>
-      <c r="J3" s="343"/>
+      <c r="B3" s="379"/>
+      <c r="C3" s="378"/>
+      <c r="D3" s="378"/>
+      <c r="E3" s="378"/>
+      <c r="F3" s="378"/>
+      <c r="G3" s="378"/>
+      <c r="H3" s="378"/>
+      <c r="I3" s="378"/>
+      <c r="J3" s="380"/>
     </row>
     <row r="4" spans="2:13" ht="24" customHeight="1" thickBot="1">
       <c r="B4" s="161"/>
       <c r="C4" s="162" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="356" t="s">
+      <c r="D4" s="393" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="357"/>
+      <c r="E4" s="394"/>
       <c r="F4" s="163"/>
       <c r="G4" s="162" t="s">
         <v>186</v>
       </c>
-      <c r="H4" s="356" t="s">
+      <c r="H4" s="393" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="357"/>
+      <c r="I4" s="394"/>
       <c r="J4" s="164"/>
     </row>
     <row r="5" spans="2:13" ht="24" customHeight="1" thickBot="1">
-      <c r="B5" s="344"/>
-      <c r="C5" s="345"/>
-      <c r="D5" s="345"/>
-      <c r="E5" s="345"/>
-      <c r="F5" s="345"/>
-      <c r="G5" s="345"/>
-      <c r="H5" s="345"/>
-      <c r="I5" s="345"/>
-      <c r="J5" s="346"/>
+      <c r="B5" s="381"/>
+      <c r="C5" s="382"/>
+      <c r="D5" s="382"/>
+      <c r="E5" s="382"/>
+      <c r="F5" s="382"/>
+      <c r="G5" s="382"/>
+      <c r="H5" s="382"/>
+      <c r="I5" s="382"/>
+      <c r="J5" s="383"/>
     </row>
     <row r="6" spans="2:13" ht="45.75" customHeight="1">
       <c r="B6" s="165" t="s">
@@ -39616,50 +40413,50 @@
     </row>
     <row r="23" spans="2:10" ht="15.75" thickBot="1"/>
     <row r="24" spans="2:10" ht="16.5" thickBot="1">
-      <c r="B24" s="353" t="s">
+      <c r="B24" s="390" t="s">
         <v>264</v>
       </c>
-      <c r="C24" s="354"/>
-      <c r="D24" s="354"/>
-      <c r="E24" s="354"/>
-      <c r="F24" s="355"/>
+      <c r="C24" s="391"/>
+      <c r="D24" s="391"/>
+      <c r="E24" s="391"/>
+      <c r="F24" s="392"/>
     </row>
     <row r="25" spans="2:10" ht="30" customHeight="1">
-      <c r="B25" s="347" t="s">
+      <c r="B25" s="384" t="s">
         <v>265</v>
       </c>
-      <c r="C25" s="348"/>
-      <c r="D25" s="348"/>
-      <c r="E25" s="348"/>
-      <c r="F25" s="349"/>
+      <c r="C25" s="385"/>
+      <c r="D25" s="385"/>
+      <c r="E25" s="385"/>
+      <c r="F25" s="386"/>
     </row>
     <row r="26" spans="2:10" ht="30" customHeight="1">
-      <c r="B26" s="347"/>
-      <c r="C26" s="348"/>
-      <c r="D26" s="348"/>
-      <c r="E26" s="348"/>
-      <c r="F26" s="349"/>
+      <c r="B26" s="384"/>
+      <c r="C26" s="385"/>
+      <c r="D26" s="385"/>
+      <c r="E26" s="385"/>
+      <c r="F26" s="386"/>
     </row>
     <row r="27" spans="2:10" ht="30" customHeight="1">
-      <c r="B27" s="347"/>
-      <c r="C27" s="348"/>
-      <c r="D27" s="348"/>
-      <c r="E27" s="348"/>
-      <c r="F27" s="349"/>
+      <c r="B27" s="384"/>
+      <c r="C27" s="385"/>
+      <c r="D27" s="385"/>
+      <c r="E27" s="385"/>
+      <c r="F27" s="386"/>
     </row>
     <row r="28" spans="2:10" ht="30" customHeight="1">
-      <c r="B28" s="347"/>
-      <c r="C28" s="348"/>
-      <c r="D28" s="348"/>
-      <c r="E28" s="348"/>
-      <c r="F28" s="349"/>
+      <c r="B28" s="384"/>
+      <c r="C28" s="385"/>
+      <c r="D28" s="385"/>
+      <c r="E28" s="385"/>
+      <c r="F28" s="386"/>
     </row>
     <row r="29" spans="2:10" ht="30" customHeight="1" thickBot="1">
-      <c r="B29" s="350"/>
-      <c r="C29" s="351"/>
-      <c r="D29" s="351"/>
-      <c r="E29" s="351"/>
-      <c r="F29" s="352"/>
+      <c r="B29" s="387"/>
+      <c r="C29" s="388"/>
+      <c r="D29" s="388"/>
+      <c r="E29" s="388"/>
+      <c r="F29" s="389"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -39698,23 +40495,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="23.25" customHeight="1">
-      <c r="A1" s="341" t="s">
+      <c r="A1" s="378" t="s">
         <v>266</v>
       </c>
-      <c r="B1" s="341"/>
-      <c r="C1" s="341"/>
-      <c r="D1" s="341"/>
-      <c r="E1" s="341"/>
-      <c r="F1" s="341"/>
-      <c r="G1" s="341"/>
-      <c r="H1" s="341"/>
-      <c r="I1" s="341"/>
-      <c r="J1" s="341"/>
-      <c r="K1" s="341"/>
-      <c r="L1" s="341"/>
-      <c r="M1" s="341"/>
-      <c r="N1" s="341"/>
-      <c r="O1" s="341"/>
+      <c r="B1" s="378"/>
+      <c r="C1" s="378"/>
+      <c r="D1" s="378"/>
+      <c r="E1" s="378"/>
+      <c r="F1" s="378"/>
+      <c r="G1" s="378"/>
+      <c r="H1" s="378"/>
+      <c r="I1" s="378"/>
+      <c r="J1" s="378"/>
+      <c r="K1" s="378"/>
+      <c r="L1" s="378"/>
+      <c r="M1" s="378"/>
+      <c r="N1" s="378"/>
+      <c r="O1" s="378"/>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="160"/>
@@ -39750,10 +40547,10 @@
       <c r="J3" s="185" t="s">
         <v>268</v>
       </c>
-      <c r="K3" s="367" t="s">
+      <c r="K3" s="404" t="s">
         <v>15</v>
       </c>
-      <c r="L3" s="367"/>
+      <c r="L3" s="404"/>
       <c r="M3" s="160"/>
       <c r="N3" s="160"/>
       <c r="O3" s="160"/>
@@ -40153,78 +40950,78 @@
     </row>
     <row r="26" spans="2:9" ht="15.75" thickBot="1"/>
     <row r="27" spans="2:9" ht="20.25" customHeight="1" thickBot="1">
-      <c r="B27" s="358" t="s">
+      <c r="B27" s="395" t="s">
         <v>275</v>
       </c>
-      <c r="C27" s="359"/>
-      <c r="D27" s="359"/>
-      <c r="E27" s="359"/>
-      <c r="F27" s="359"/>
-      <c r="G27" s="359"/>
-      <c r="H27" s="359"/>
-      <c r="I27" s="360"/>
+      <c r="C27" s="396"/>
+      <c r="D27" s="396"/>
+      <c r="E27" s="396"/>
+      <c r="F27" s="396"/>
+      <c r="G27" s="396"/>
+      <c r="H27" s="396"/>
+      <c r="I27" s="397"/>
     </row>
     <row r="28" spans="2:9" ht="20.25" customHeight="1">
-      <c r="B28" s="361" t="s">
+      <c r="B28" s="398" t="s">
         <v>276</v>
       </c>
-      <c r="C28" s="362"/>
-      <c r="D28" s="362"/>
-      <c r="E28" s="362"/>
-      <c r="F28" s="362"/>
-      <c r="G28" s="362"/>
-      <c r="H28" s="362"/>
-      <c r="I28" s="363"/>
+      <c r="C28" s="399"/>
+      <c r="D28" s="399"/>
+      <c r="E28" s="399"/>
+      <c r="F28" s="399"/>
+      <c r="G28" s="399"/>
+      <c r="H28" s="399"/>
+      <c r="I28" s="400"/>
     </row>
     <row r="29" spans="2:9" ht="20.25" customHeight="1">
-      <c r="B29" s="361"/>
-      <c r="C29" s="362"/>
-      <c r="D29" s="362"/>
-      <c r="E29" s="362"/>
-      <c r="F29" s="362"/>
-      <c r="G29" s="362"/>
-      <c r="H29" s="362"/>
-      <c r="I29" s="363"/>
+      <c r="B29" s="398"/>
+      <c r="C29" s="399"/>
+      <c r="D29" s="399"/>
+      <c r="E29" s="399"/>
+      <c r="F29" s="399"/>
+      <c r="G29" s="399"/>
+      <c r="H29" s="399"/>
+      <c r="I29" s="400"/>
     </row>
     <row r="30" spans="2:9" ht="20.25" customHeight="1">
-      <c r="B30" s="361"/>
-      <c r="C30" s="362"/>
-      <c r="D30" s="362"/>
-      <c r="E30" s="362"/>
-      <c r="F30" s="362"/>
-      <c r="G30" s="362"/>
-      <c r="H30" s="362"/>
-      <c r="I30" s="363"/>
+      <c r="B30" s="398"/>
+      <c r="C30" s="399"/>
+      <c r="D30" s="399"/>
+      <c r="E30" s="399"/>
+      <c r="F30" s="399"/>
+      <c r="G30" s="399"/>
+      <c r="H30" s="399"/>
+      <c r="I30" s="400"/>
     </row>
     <row r="31" spans="2:9" ht="20.25" customHeight="1">
-      <c r="B31" s="361"/>
-      <c r="C31" s="362"/>
-      <c r="D31" s="362"/>
-      <c r="E31" s="362"/>
-      <c r="F31" s="362"/>
-      <c r="G31" s="362"/>
-      <c r="H31" s="362"/>
-      <c r="I31" s="363"/>
+      <c r="B31" s="398"/>
+      <c r="C31" s="399"/>
+      <c r="D31" s="399"/>
+      <c r="E31" s="399"/>
+      <c r="F31" s="399"/>
+      <c r="G31" s="399"/>
+      <c r="H31" s="399"/>
+      <c r="I31" s="400"/>
     </row>
     <row r="32" spans="2:9" ht="20.25" customHeight="1">
-      <c r="B32" s="361"/>
-      <c r="C32" s="362"/>
-      <c r="D32" s="362"/>
-      <c r="E32" s="362"/>
-      <c r="F32" s="362"/>
-      <c r="G32" s="362"/>
-      <c r="H32" s="362"/>
-      <c r="I32" s="363"/>
+      <c r="B32" s="398"/>
+      <c r="C32" s="399"/>
+      <c r="D32" s="399"/>
+      <c r="E32" s="399"/>
+      <c r="F32" s="399"/>
+      <c r="G32" s="399"/>
+      <c r="H32" s="399"/>
+      <c r="I32" s="400"/>
     </row>
     <row r="33" spans="2:9" ht="66" customHeight="1" thickBot="1">
-      <c r="B33" s="364"/>
-      <c r="C33" s="365"/>
-      <c r="D33" s="365"/>
-      <c r="E33" s="365"/>
-      <c r="F33" s="365"/>
-      <c r="G33" s="365"/>
-      <c r="H33" s="365"/>
-      <c r="I33" s="366"/>
+      <c r="B33" s="401"/>
+      <c r="C33" s="402"/>
+      <c r="D33" s="402"/>
+      <c r="E33" s="402"/>
+      <c r="F33" s="402"/>
+      <c r="G33" s="402"/>
+      <c r="H33" s="402"/>
+      <c r="I33" s="403"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -40270,28 +41067,28 @@
       <c r="I1"/>
     </row>
     <row r="2" spans="2:9" ht="30" customHeight="1" thickBot="1">
-      <c r="B2" s="368" t="s">
+      <c r="B2" s="408" t="s">
         <v>333</v>
       </c>
-      <c r="C2" s="369"/>
-      <c r="D2" s="369"/>
-      <c r="E2" s="369"/>
-      <c r="F2" s="369"/>
-      <c r="G2" s="369"/>
-      <c r="H2" s="369"/>
-      <c r="I2" s="370"/>
+      <c r="C2" s="409"/>
+      <c r="D2" s="409"/>
+      <c r="E2" s="409"/>
+      <c r="F2" s="409"/>
+      <c r="G2" s="409"/>
+      <c r="H2" s="409"/>
+      <c r="I2" s="410"/>
     </row>
     <row r="3" spans="2:9">
-      <c r="B3" s="371" t="s">
+      <c r="B3" s="411" t="s">
         <v>334</v>
       </c>
-      <c r="C3" s="372"/>
-      <c r="D3" s="372"/>
-      <c r="E3" s="372"/>
-      <c r="F3" s="372"/>
-      <c r="G3" s="372"/>
-      <c r="H3" s="372"/>
-      <c r="I3" s="373"/>
+      <c r="C3" s="412"/>
+      <c r="D3" s="412"/>
+      <c r="E3" s="412"/>
+      <c r="F3" s="412"/>
+      <c r="G3" s="412"/>
+      <c r="H3" s="412"/>
+      <c r="I3" s="413"/>
     </row>
     <row r="4" spans="2:9" ht="15.75" thickBot="1">
       <c r="B4" s="229"/>
@@ -40593,17 +41390,17 @@
       <c r="I16" s="203"/>
     </row>
     <row r="17" spans="2:9">
-      <c r="B17" s="374" t="s">
+      <c r="B17" s="414" t="s">
         <v>342</v>
       </c>
-      <c r="C17" s="375"/>
-      <c r="D17" s="376"/>
-      <c r="F17" s="377" t="s">
+      <c r="C17" s="415"/>
+      <c r="D17" s="416"/>
+      <c r="F17" s="417" t="s">
         <v>358</v>
       </c>
-      <c r="G17" s="378"/>
-      <c r="H17" s="378"/>
-      <c r="I17" s="379"/>
+      <c r="G17" s="418"/>
+      <c r="H17" s="418"/>
+      <c r="I17" s="419"/>
     </row>
     <row r="18" spans="2:9">
       <c r="B18" s="204" t="s">
@@ -40734,28 +41531,28 @@
       <c r="I24" s="230"/>
     </row>
     <row r="25" spans="2:9" ht="16.5" thickBot="1">
-      <c r="B25" s="380" t="s">
+      <c r="B25" s="420" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="381"/>
-      <c r="D25" s="381"/>
-      <c r="E25" s="381"/>
-      <c r="F25" s="381"/>
-      <c r="G25" s="381"/>
-      <c r="H25" s="381"/>
-      <c r="I25" s="382"/>
+      <c r="C25" s="421"/>
+      <c r="D25" s="421"/>
+      <c r="E25" s="421"/>
+      <c r="F25" s="421"/>
+      <c r="G25" s="421"/>
+      <c r="H25" s="421"/>
+      <c r="I25" s="422"/>
     </row>
     <row r="26" spans="2:9" ht="151.5" customHeight="1" thickBot="1">
-      <c r="B26" s="383" t="s">
+      <c r="B26" s="405" t="s">
         <v>369</v>
       </c>
-      <c r="C26" s="384"/>
-      <c r="D26" s="384"/>
-      <c r="E26" s="384"/>
-      <c r="F26" s="384"/>
-      <c r="G26" s="384"/>
-      <c r="H26" s="384"/>
-      <c r="I26" s="385"/>
+      <c r="C26" s="406"/>
+      <c r="D26" s="406"/>
+      <c r="E26" s="406"/>
+      <c r="F26" s="406"/>
+      <c r="G26" s="406"/>
+      <c r="H26" s="406"/>
+      <c r="I26" s="407"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/pm_dashboards/Project Management Charts.xlsx
+++ b/pm_dashboards/Project Management Charts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\excel_tutorial\pm_dashboards\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77CCFD15-676D-410B-9A6B-E874C4309FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C094C46-A645-41FE-A434-52D1B8C9098F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="513" firstSheet="6" activeTab="9" xr2:uid="{6ACA091F-59E3-41E7-B925-EA720AB063CF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="513" firstSheet="7" activeTab="10" xr2:uid="{6ACA091F-59E3-41E7-B925-EA720AB063CF}"/>
   </bookViews>
   <sheets>
     <sheet name="PMP" sheetId="11" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <sheet name="Pareto Principle" sheetId="10" r:id="rId8"/>
     <sheet name="Heatmap" sheetId="12" r:id="rId9"/>
     <sheet name="Nominal Group Technique" sheetId="15" r:id="rId10"/>
+    <sheet name="Root Cause Analysis" sheetId="16" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -165,7 +166,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="790" uniqueCount="454">
   <si>
     <t>Project Start Date:</t>
   </si>
@@ -1483,6 +1484,151 @@
       <t>Multi Voting</t>
     </r>
   </si>
+  <si>
+    <t>Root Cause Analysis</t>
+  </si>
+  <si>
+    <t>Project or Product Name:</t>
+  </si>
+  <si>
+    <t>Authored By:</t>
+  </si>
+  <si>
+    <t>People</t>
+  </si>
+  <si>
+    <t>Information</t>
+  </si>
+  <si>
+    <t>Process</t>
+  </si>
+  <si>
+    <t>Systems</t>
+  </si>
+  <si>
+    <t>Problem or Opportunity</t>
+  </si>
+  <si>
+    <t>Root Cause(s)</t>
+  </si>
+  <si>
+    <t>Number of Causes:</t>
+  </si>
+  <si>
+    <t>Nominal Group Technique (NGT) - Tutorial</t>
+  </si>
+  <si>
+    <t>What is the Nominal Group Technique?</t>
+  </si>
+  <si>
+    <t>A structured decision-making method that enables groups to prioritize ideas through individual voting, reducing bias and ensuring equal participation.</t>
+  </si>
+  <si>
+    <t>How to Use This Template:</t>
+  </si>
+  <si>
+    <t>Step 1: Generate Ideas - Team silently brainstorms and lists ideas in the 'Brainstormed Ideas List' column.
+Step 2: Discuss Ideas - Each idea is clarified and discussed (no criticism allowed).
+Step 3: Allocate Points - Each member distributes their allocated points (default: 10) across ideas they support.
+Step 4: Calculate Totals - The 'Total' column automatically sums all votes for each idea.
+Step 5: Rank Results - Use the 'Rank' column to identify top priorities. Lower rank = higher priority.</t>
+  </si>
+  <si>
+    <t>Root Cause Analysis (RCA) - Tutorial</t>
+  </si>
+  <si>
+    <t>What is Root Cause Analysis?</t>
+  </si>
+  <si>
+    <t>Root Cause Analysis is a systematic problem-solving method used to identify the underlying causes of problems or incidents. Instead of treating symptoms, RCA helps teams find and address the true source of issues to prevent recurrence.</t>
+  </si>
+  <si>
+    <t>Common RCA Techniques:</t>
+  </si>
+  <si>
+    <t>• 5 Whys: Ask 'Why?' repeatedly (typically 5 times) to drill down from the symptom to the root cause.</t>
+  </si>
+  <si>
+    <t>• Fishbone Diagram (Ishikawa): Categorize potential causes into groups (People, Process, Equipment, Materials, Environment, Management).</t>
+  </si>
+  <si>
+    <t>• Fault Tree Analysis: Use a top-down approach with logical diagrams to trace failure paths.</t>
+  </si>
+  <si>
+    <t>Benefits:</t>
+  </si>
+  <si>
+    <t>Prevents recurring issues, improves processes, reduces costs, enhances quality, and promotes a culture of continuous improvement.</t>
+  </si>
+  <si>
+    <t>💡 Tip: Document all findings and corrective actions. Review periodically to ensure solutions remain effective.</t>
+  </si>
+  <si>
+    <t>Key resource unavailability</t>
+  </si>
+  <si>
+    <t>User adoption resistance</t>
+  </si>
+  <si>
+    <t>Unclear legacy data formats</t>
+  </si>
+  <si>
+    <t>Incomplete requirements</t>
+  </si>
+  <si>
+    <t>Missing data mapping specs</t>
+  </si>
+  <si>
+    <t>Vendor dependency info gaps</t>
+  </si>
+  <si>
+    <t>Corrupt data records</t>
+  </si>
+  <si>
+    <t>Lack of change control</t>
+  </si>
+  <si>
+    <t>Insufficient validation checkpoints</t>
+  </si>
+  <si>
+    <t>Incompatible legacy systems</t>
+  </si>
+  <si>
+    <t>Integration complexity</t>
+  </si>
+  <si>
+    <t>Data Migration Failure - Incompatible legacy data formats &amp; corrupt records</t>
+  </si>
+  <si>
+    <t>Integration Complexity - Outdated APIs &amp; poor vendor documentation</t>
+  </si>
+  <si>
+    <t>Sarah Johnson, Project Manager</t>
+  </si>
+  <si>
+    <t>Database Design &amp; Development Blocked - Critical Path Delay</t>
+  </si>
+  <si>
+    <t>Poor vendor documentation</t>
+  </si>
+  <si>
+    <t>Staff turnover risk</t>
+  </si>
+  <si>
+    <t>Inadequate training</t>
+  </si>
+  <si>
+    <t>Competing priorities</t>
+  </si>
+  <si>
+    <t>Knowledge gaps</t>
+  </si>
+  <si>
+    <t>Team burnout</t>
+  </si>
+  <si>
+    <t>Communication gaps</t>
+  </si>
 </sst>
 </file>
 
@@ -1494,7 +1640,7 @@
     <numFmt numFmtId="166" formatCode="yyyy"/>
     <numFmt numFmtId="167" formatCode="dd\ mmm\ yy"/>
   </numFmts>
-  <fonts count="78">
+  <fonts count="80">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2044,8 +2190,22 @@
       <name val="Aptos Serif"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1" tint="0.499984740745262"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="54">
+  <fills count="58">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2364,8 +2524,32 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF9F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EAF8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="152">
+  <borders count="155">
     <border>
       <left/>
       <right/>
@@ -4326,12 +4510,51 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="dotted">
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="dotted">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom style="dotted">
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="dotted">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="450">
+  <cellXfs count="500">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
@@ -5046,45 +5269,75 @@
     </xf>
     <xf numFmtId="0" fontId="55" fillId="18" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="55" fillId="18" borderId="131" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="67" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="55" fillId="53" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="55" fillId="51" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="56" fillId="51" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="7"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="18" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="56" fillId="51" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="51" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="51" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="25" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="52" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="52" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="18" borderId="151" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="18" borderId="149" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="18" borderId="150" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="18" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="16"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="18" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="55" fillId="51" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="2" borderId="148" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="74" fillId="51" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="51" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="18" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="55" fillId="51" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="55" fillId="51" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="18" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="55" fillId="18" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="73" fillId="18" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="55" fillId="18" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="73" fillId="18" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="76" fillId="25" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="73" fillId="18" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="76" fillId="25" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="18" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="76" fillId="25" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="18" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="71" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="71" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="72" fillId="18" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="72" fillId="18" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="72" fillId="18" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="135" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -5109,28 +5362,43 @@
     <xf numFmtId="0" fontId="38" fillId="21" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="70" fillId="18" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="70" fillId="18" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="71" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="71" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="71" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="72" fillId="18" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="72" fillId="18" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="72" fillId="18" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="55" fillId="18" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="18" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="18" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="18" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="18" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="55" fillId="2" borderId="148" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5184,46 +5452,29 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="28" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="28" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="57" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="18" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="28" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="28" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="28" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
@@ -5279,6 +5530,53 @@
     <xf numFmtId="0" fontId="5" fillId="28" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" textRotation="90"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="18" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="57" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="45" fillId="18" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="18" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="45" fillId="18" borderId="104" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -5287,44 +5585,6 @@
     </xf>
     <xf numFmtId="0" fontId="45" fillId="18" borderId="93" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="29" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="29" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="29" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="36" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="27" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="27" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="18" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="18" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="52" fillId="22" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
@@ -5367,6 +5627,38 @@
     </xf>
     <xf numFmtId="0" fontId="53" fillId="24" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="29" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="29" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="29" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="36" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="27" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="27" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5491,79 +5783,134 @@
     <xf numFmtId="0" fontId="63" fillId="3" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="131" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="74" fillId="51" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="53" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="55" fillId="51" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="51" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="56" fillId="51" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" indent="7"/>
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="18" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="26" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="51" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="51" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="18" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="78" fillId="54" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="18" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="78" fillId="55" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="51" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="78" fillId="25" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="72" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="105" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="54" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="56" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="93" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="18" borderId="152" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="18" borderId="153" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="153" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="154" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="78" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="84" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="63" fillId="57" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="63" fillId="57" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="63" fillId="57" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="71" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="84" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="72" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="73" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="57" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="51" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="48" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="51" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
+    <xf numFmtId="0" fontId="32" fillId="57" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="51" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="51" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="62" fillId="48" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="25" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="25" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="32" fillId="57" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="25" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="25" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="62" fillId="48" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="52" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="18" borderId="104" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="77" fillId="52" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="105" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="18" borderId="151" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="93" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="18" borderId="149" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="104" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="18" borderId="150" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="105" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="18" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="16"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="18" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5571,16 +5918,16 @@
   </cellStyles>
   <dxfs count="28">
     <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFF5D5D"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -5927,15 +6274,15 @@
   </tableStyles>
   <colors>
     <mruColors>
+      <color rgb="FFFFFF9F"/>
+      <color rgb="FFA0E8AA"/>
+      <color rgb="FF9FBFFF"/>
+      <color rgb="FF163D64"/>
       <color rgb="FFFF5D5D"/>
-      <color rgb="FFA0E8AA"/>
       <color rgb="FF5E9DDC"/>
       <color rgb="FF3B88D5"/>
       <color rgb="FF205A94"/>
-      <color rgb="FF9FBFFF"/>
       <color rgb="FF85DFFF"/>
-      <color rgb="FF163D64"/>
-      <color rgb="FFFFFF9F"/>
       <color rgb="FF0D3514"/>
     </mruColors>
   </colors>
@@ -6065,7 +6412,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{DA0660E6-EC0C-49CE-99A6-F6BE3B21BEDF}" type="CELLRANGE">
+                    <a:fld id="{7CCA2253-A3B2-4CD6-889B-F3C2275BD927}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6098,7 +6445,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{63A9569A-564A-4B44-9A8E-96F448807024}" type="CELLRANGE">
+                    <a:fld id="{1D69DF29-8850-41F7-BFE3-FEBBE15B00DC}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6132,7 +6479,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{E4F1BB72-A833-4920-BB6F-CFC27D7838C4}" type="CELLRANGE">
+                    <a:fld id="{D03B2395-2CC8-444C-B017-FA4B03051F52}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6166,7 +6513,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{C59BDC6A-710E-4FC6-9332-1C030920EBD2}" type="CELLRANGE">
+                    <a:fld id="{18CFE0AB-86B4-4FF8-80EF-A9B1A9966F75}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6200,7 +6547,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7BAF19CE-9B91-494B-BC61-4EFEC1A269E3}" type="CELLRANGE">
+                    <a:fld id="{58C3C96C-93DE-440A-83C8-8E8EF11FE420}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6234,7 +6581,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0C340198-E7AE-481C-9042-F91BEC5D4BF4}" type="CELLRANGE">
+                    <a:fld id="{2A844BC1-E554-4E97-A639-5A5B9F0D4073}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6268,7 +6615,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{147FEB83-D47C-42D2-ABB9-B4847CABD015}" type="CELLRANGE">
+                    <a:fld id="{D10D568F-EB66-4B8B-89A0-00A09703C13D}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6302,7 +6649,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{ADB3E8EC-F276-4F3C-A95E-1AD68CBD02CF}" type="CELLRANGE">
+                    <a:fld id="{11415630-45C5-40D7-8F44-C213C5BC5A49}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6336,7 +6683,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{85DD4A33-2AF0-4066-B8E1-E474FCD5BF9D}" type="CELLRANGE">
+                    <a:fld id="{83CCCC2B-B32E-4E29-89F0-DC432359D591}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6370,7 +6717,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2157F310-6946-4776-9FAD-148F5489557B}" type="CELLRANGE">
+                    <a:fld id="{0E8A72E7-6E16-40CE-A80C-1D0D864A5927}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6404,7 +6751,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{55ADDAF0-8732-40B9-8112-85CD13F65E76}" type="CELLRANGE">
+                    <a:fld id="{AE66CDB0-33AD-4DA5-9461-C6BB44439D1C}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6438,7 +6785,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{17961558-11C8-4550-ADF1-123025DAAFA9}" type="CELLRANGE">
+                    <a:fld id="{6C4AA860-CCA2-4EA6-8A9A-CC39C74B115F}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6472,7 +6819,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{A6F4F703-541A-49CB-ABE8-55E747BCF9B3}" type="CELLRANGE">
+                    <a:fld id="{B9FCBC71-B83E-4356-9C0E-9FDC1E783A9A}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6506,7 +6853,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{236656AF-A6DE-405B-BC73-7370C561BD76}" type="CELLRANGE">
+                    <a:fld id="{44A84384-9213-4627-9E54-48705A43DD11}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -9089,6 +9436,210 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>314323</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>419099</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>171448</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="Isosceles Triangle 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DE2B595C-7678-4673-9E1C-416766805A9D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="523875" y="4076698"/>
+          <a:ext cx="971549" cy="1057275"/>
+        </a:xfrm>
+        <a:prstGeom prst="triangle">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 495"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>1566863</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>309567</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>414338</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>9528</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="Isosceles Triangle 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4412F344-58B7-B08C-A484-9A4A957A078A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="10732295" y="3421860"/>
+          <a:ext cx="2243136" cy="1028700"/>
+        </a:xfrm>
+        <a:prstGeom prst="triangle">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>419099</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>285748</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="Isosceles Triangle 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22DFF22E-6E38-4E48-959B-CE3C36468F51}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="523875" y="2019300"/>
+          <a:ext cx="971549" cy="2028823"/>
+        </a:xfrm>
+        <a:prstGeom prst="triangle">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 495"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-IN" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <person displayName="Vishvambruth Javagal" id="{A0845E40-F282-4CD2-AE9E-CF4D74007C33}" userId="S::Vishvambruth_Javagal@epam.com::a128490f-6659-4979-95ef-373d5d3ade91" providerId="AD"/>
@@ -9487,17 +10038,17 @@
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1">
       <c r="A1" s="233"/>
-      <c r="B1" s="287" t="s">
+      <c r="B1" s="295" t="s">
         <v>332</v>
       </c>
-      <c r="C1" s="287"/>
-      <c r="D1" s="287"/>
-      <c r="E1" s="287"/>
-      <c r="F1" s="287"/>
-      <c r="G1" s="288"/>
+      <c r="C1" s="295"/>
+      <c r="D1" s="295"/>
+      <c r="E1" s="295"/>
+      <c r="F1" s="295"/>
+      <c r="G1" s="296"/>
     </row>
     <row r="2" spans="1:7" ht="30" customHeight="1">
-      <c r="A2" s="285" t="s">
+      <c r="A2" s="293" t="s">
         <v>331</v>
       </c>
       <c r="B2" s="235" t="s">
@@ -9520,7 +10071,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="28.5">
-      <c r="A3" s="285"/>
+      <c r="A3" s="293"/>
       <c r="B3" s="240" t="s">
         <v>292</v>
       </c>
@@ -9541,7 +10092,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="42.75">
-      <c r="A4" s="285"/>
+      <c r="A4" s="293"/>
       <c r="B4" s="240" t="s">
         <v>298</v>
       </c>
@@ -9556,7 +10107,7 @@
       <c r="G4" s="245"/>
     </row>
     <row r="5" spans="1:7" ht="71.25">
-      <c r="A5" s="285"/>
+      <c r="A5" s="293"/>
       <c r="B5" s="240" t="s">
         <v>301</v>
       </c>
@@ -9571,7 +10122,7 @@
       <c r="G5" s="243"/>
     </row>
     <row r="6" spans="1:7" ht="42.75">
-      <c r="A6" s="285"/>
+      <c r="A6" s="293"/>
       <c r="B6" s="240" t="s">
         <v>304</v>
       </c>
@@ -9586,7 +10137,7 @@
       <c r="G6" s="245"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="285"/>
+      <c r="A7" s="293"/>
       <c r="B7" s="240" t="s">
         <v>307</v>
       </c>
@@ -9603,7 +10154,7 @@
       <c r="G7" s="243"/>
     </row>
     <row r="8" spans="1:7" ht="42.75">
-      <c r="A8" s="285"/>
+      <c r="A8" s="293"/>
       <c r="B8" s="240" t="s">
         <v>311</v>
       </c>
@@ -9618,7 +10169,7 @@
       <c r="G8" s="245"/>
     </row>
     <row r="9" spans="1:7" ht="28.5">
-      <c r="A9" s="285"/>
+      <c r="A9" s="293"/>
       <c r="B9" s="240" t="s">
         <v>314</v>
       </c>
@@ -9635,7 +10186,7 @@
       <c r="G9" s="243"/>
     </row>
     <row r="10" spans="1:7" ht="85.5">
-      <c r="A10" s="285"/>
+      <c r="A10" s="293"/>
       <c r="B10" s="240" t="s">
         <v>318</v>
       </c>
@@ -9652,7 +10203,7 @@
       <c r="G10" s="245"/>
     </row>
     <row r="11" spans="1:7" ht="28.5">
-      <c r="A11" s="285"/>
+      <c r="A11" s="293"/>
       <c r="B11" s="240" t="s">
         <v>322</v>
       </c>
@@ -9669,7 +10220,7 @@
       <c r="G11" s="243"/>
     </row>
     <row r="12" spans="1:7" ht="17.25" thickBot="1">
-      <c r="A12" s="286"/>
+      <c r="A12" s="294"/>
       <c r="B12" s="241" t="s">
         <v>326</v>
       </c>
@@ -9699,507 +10250,616 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A1336A8-0BDF-47A9-8475-C5035F8DF71A}">
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="2.7109375" style="423" customWidth="1"/>
-    <col min="2" max="2" width="35.85546875" style="423" bestFit="1" customWidth="1"/>
-    <col min="3" max="10" width="10.7109375" style="423" customWidth="1"/>
-    <col min="11" max="16384" width="9.140625" style="423"/>
+    <col min="1" max="1" width="2.7109375" style="84" customWidth="1"/>
+    <col min="2" max="2" width="35.85546875" style="84" bestFit="1" customWidth="1"/>
+    <col min="3" max="10" width="10.7109375" style="84" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="84"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="26.25">
-      <c r="A1" s="424" t="s">
+      <c r="A1" s="284" t="s">
         <v>406</v>
       </c>
-      <c r="B1" s="424"/>
-      <c r="C1" s="424"/>
-      <c r="D1" s="424"/>
-      <c r="E1" s="424"/>
-      <c r="F1" s="424"/>
-      <c r="G1" s="424"/>
-      <c r="H1" s="424"/>
-      <c r="I1" s="424"/>
-      <c r="J1" s="424"/>
-      <c r="K1" s="424"/>
-      <c r="L1" s="425"/>
+      <c r="B1" s="284"/>
+      <c r="C1" s="284"/>
+      <c r="D1" s="284"/>
+      <c r="E1" s="284"/>
+      <c r="F1" s="284"/>
+      <c r="G1" s="284"/>
+      <c r="H1" s="284"/>
+      <c r="I1" s="284"/>
+      <c r="J1" s="284"/>
+      <c r="K1" s="284"/>
+      <c r="L1" s="268"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A2" s="426"/>
-      <c r="B2" s="426"/>
-      <c r="C2" s="426"/>
-      <c r="D2" s="426"/>
-      <c r="E2" s="426"/>
-      <c r="F2" s="426"/>
-      <c r="G2" s="426"/>
-      <c r="H2" s="426"/>
-      <c r="I2" s="426"/>
-      <c r="J2" s="426"/>
-      <c r="K2" s="426"/>
-      <c r="L2" s="425"/>
+      <c r="A2" s="283"/>
+      <c r="B2" s="283"/>
+      <c r="C2" s="283"/>
+      <c r="D2" s="283"/>
+      <c r="E2" s="283"/>
+      <c r="F2" s="283"/>
+      <c r="G2" s="283"/>
+      <c r="H2" s="283"/>
+      <c r="I2" s="283"/>
+      <c r="J2" s="283"/>
+      <c r="K2" s="283"/>
+      <c r="L2" s="268"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A3" s="427"/>
-      <c r="B3" s="428" t="s">
+      <c r="A3" s="269"/>
+      <c r="B3" s="270" t="s">
         <v>386</v>
       </c>
-      <c r="C3" s="429">
+      <c r="C3" s="271">
         <v>10</v>
       </c>
-      <c r="D3" s="430" t="s">
+      <c r="D3" s="272" t="s">
         <v>389</v>
       </c>
-      <c r="E3" s="427"/>
-      <c r="F3" s="427"/>
-      <c r="G3" s="426"/>
-      <c r="H3" s="426"/>
-      <c r="I3" s="426"/>
-      <c r="J3" s="426"/>
-      <c r="K3" s="426"/>
-      <c r="L3" s="425"/>
+      <c r="E3" s="269"/>
+      <c r="F3" s="269"/>
+      <c r="G3" s="283"/>
+      <c r="H3" s="283"/>
+      <c r="I3" s="283"/>
+      <c r="J3" s="283"/>
+      <c r="K3" s="283"/>
+      <c r="L3" s="268"/>
     </row>
     <row r="4" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A4" s="426"/>
-      <c r="B4" s="426"/>
-      <c r="C4" s="426"/>
-      <c r="D4" s="426"/>
-      <c r="E4" s="426"/>
-      <c r="F4" s="426"/>
-      <c r="G4" s="426"/>
-      <c r="H4" s="426"/>
-      <c r="I4" s="426"/>
-      <c r="J4" s="426"/>
-      <c r="K4" s="426"/>
-      <c r="L4" s="425"/>
+      <c r="A4" s="283"/>
+      <c r="B4" s="283"/>
+      <c r="C4" s="283"/>
+      <c r="D4" s="283"/>
+      <c r="E4" s="283"/>
+      <c r="F4" s="283"/>
+      <c r="G4" s="283"/>
+      <c r="H4" s="283"/>
+      <c r="I4" s="283"/>
+      <c r="J4" s="283"/>
+      <c r="K4" s="283"/>
+      <c r="L4" s="268"/>
     </row>
     <row r="5" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A5" s="427"/>
-      <c r="B5" s="431" t="s">
+      <c r="A5" s="269"/>
+      <c r="B5" s="273" t="s">
         <v>387</v>
       </c>
-      <c r="C5" s="432"/>
-      <c r="D5" s="433"/>
-      <c r="E5" s="434"/>
-      <c r="F5" s="435"/>
-      <c r="G5" s="435"/>
-      <c r="H5" s="435"/>
-      <c r="I5" s="435"/>
-      <c r="J5" s="435"/>
-      <c r="K5" s="435"/>
-      <c r="L5" s="425"/>
+      <c r="C5" s="288"/>
+      <c r="D5" s="289"/>
+      <c r="E5" s="285"/>
+      <c r="F5" s="283"/>
+      <c r="G5" s="283"/>
+      <c r="H5" s="283"/>
+      <c r="I5" s="283"/>
+      <c r="J5" s="283"/>
+      <c r="K5" s="283"/>
+      <c r="L5" s="268"/>
     </row>
     <row r="6" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A6" s="426"/>
-      <c r="B6" s="426"/>
-      <c r="C6" s="426"/>
-      <c r="D6" s="426"/>
-      <c r="E6" s="426"/>
-      <c r="F6" s="426"/>
-      <c r="G6" s="426"/>
-      <c r="H6" s="426"/>
-      <c r="I6" s="426"/>
-      <c r="J6" s="426"/>
-      <c r="K6" s="426"/>
-      <c r="L6" s="425"/>
+      <c r="A6" s="283"/>
+      <c r="B6" s="283"/>
+      <c r="C6" s="283"/>
+      <c r="D6" s="283"/>
+      <c r="E6" s="283"/>
+      <c r="F6" s="283"/>
+      <c r="G6" s="283"/>
+      <c r="H6" s="283"/>
+      <c r="I6" s="283"/>
+      <c r="J6" s="283"/>
+      <c r="K6" s="283"/>
+      <c r="L6" s="268"/>
     </row>
     <row r="7" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A7" s="427"/>
-      <c r="B7" s="436" t="s">
+      <c r="A7" s="269"/>
+      <c r="B7" s="274" t="s">
         <v>388</v>
       </c>
-      <c r="C7" s="429"/>
-      <c r="D7" s="437"/>
-      <c r="E7" s="438"/>
-      <c r="F7" s="438"/>
-      <c r="G7" s="438"/>
-      <c r="H7" s="438"/>
-      <c r="I7" s="438"/>
-      <c r="J7" s="438"/>
-      <c r="K7" s="438"/>
-      <c r="L7" s="425"/>
+      <c r="C7" s="271"/>
+      <c r="D7" s="286"/>
+      <c r="E7" s="287"/>
+      <c r="F7" s="287"/>
+      <c r="G7" s="287"/>
+      <c r="H7" s="287"/>
+      <c r="I7" s="287"/>
+      <c r="J7" s="287"/>
+      <c r="K7" s="287"/>
+      <c r="L7" s="268"/>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="426"/>
-      <c r="B8" s="426"/>
-      <c r="C8" s="426"/>
-      <c r="D8" s="426"/>
-      <c r="E8" s="426"/>
-      <c r="F8" s="426"/>
-      <c r="G8" s="426"/>
-      <c r="H8" s="426"/>
-      <c r="I8" s="426"/>
-      <c r="J8" s="426"/>
-      <c r="K8" s="426"/>
-      <c r="L8" s="425"/>
+      <c r="A8" s="283"/>
+      <c r="B8" s="283"/>
+      <c r="C8" s="283"/>
+      <c r="D8" s="283"/>
+      <c r="E8" s="283"/>
+      <c r="F8" s="283"/>
+      <c r="G8" s="283"/>
+      <c r="H8" s="283"/>
+      <c r="I8" s="283"/>
+      <c r="J8" s="283"/>
+      <c r="K8" s="283"/>
+      <c r="L8" s="268"/>
     </row>
     <row r="9" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A9" s="425"/>
-      <c r="B9" s="425"/>
-      <c r="C9" s="425"/>
-      <c r="D9" s="425"/>
-      <c r="E9" s="425"/>
-      <c r="F9" s="425"/>
-      <c r="G9" s="425"/>
-      <c r="H9" s="425"/>
-      <c r="I9" s="425"/>
-      <c r="J9" s="425"/>
-      <c r="K9" s="425"/>
-      <c r="L9" s="425"/>
+      <c r="A9" s="268"/>
+      <c r="B9" s="268"/>
+      <c r="C9" s="268"/>
+      <c r="D9" s="268"/>
+      <c r="E9" s="268"/>
+      <c r="F9" s="268"/>
+      <c r="G9" s="268"/>
+      <c r="H9" s="268"/>
+      <c r="I9" s="268"/>
+      <c r="J9" s="268"/>
+      <c r="K9" s="268"/>
+      <c r="L9" s="268"/>
     </row>
     <row r="10" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A10" s="425"/>
-      <c r="B10" s="425"/>
-      <c r="C10" s="439" t="s">
+      <c r="A10" s="268"/>
+      <c r="B10" s="268"/>
+      <c r="C10" s="290" t="s">
         <v>390</v>
       </c>
-      <c r="D10" s="440"/>
-      <c r="E10" s="440"/>
-      <c r="F10" s="440"/>
-      <c r="G10" s="440"/>
-      <c r="H10" s="440"/>
-      <c r="I10" s="441"/>
-      <c r="J10" s="425"/>
-      <c r="K10" s="425"/>
-      <c r="L10" s="425"/>
+      <c r="D10" s="291"/>
+      <c r="E10" s="291"/>
+      <c r="F10" s="291"/>
+      <c r="G10" s="291"/>
+      <c r="H10" s="291"/>
+      <c r="I10" s="292"/>
+      <c r="J10" s="268"/>
+      <c r="K10" s="268"/>
+      <c r="L10" s="268"/>
     </row>
     <row r="11" spans="1:12" ht="28.5" customHeight="1" thickBot="1">
-      <c r="A11" s="425"/>
-      <c r="B11" s="442" t="s">
+      <c r="A11" s="268"/>
+      <c r="B11" s="275" t="s">
         <v>391</v>
       </c>
-      <c r="C11" s="443" t="s">
+      <c r="C11" s="276" t="s">
         <v>392</v>
       </c>
-      <c r="D11" s="443" t="s">
+      <c r="D11" s="276" t="s">
         <v>393</v>
       </c>
-      <c r="E11" s="443" t="s">
+      <c r="E11" s="276" t="s">
         <v>394</v>
       </c>
-      <c r="F11" s="443" t="s">
+      <c r="F11" s="276" t="s">
         <v>395</v>
       </c>
-      <c r="G11" s="443" t="s">
+      <c r="G11" s="276" t="s">
         <v>396</v>
       </c>
-      <c r="H11" s="443" t="s">
+      <c r="H11" s="276" t="s">
         <v>397</v>
       </c>
-      <c r="I11" s="443" t="s">
+      <c r="I11" s="276" t="s">
         <v>398</v>
       </c>
-      <c r="J11" s="444" t="s">
+      <c r="J11" s="277" t="s">
         <v>399</v>
       </c>
-      <c r="K11" s="444" t="s">
+      <c r="K11" s="277" t="s">
         <v>405</v>
       </c>
-      <c r="L11" s="425"/>
+      <c r="L11" s="268"/>
     </row>
     <row r="12" spans="1:12" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="425"/>
-      <c r="B12" s="445" t="s">
+      <c r="A12" s="268"/>
+      <c r="B12" s="278" t="s">
         <v>400</v>
       </c>
-      <c r="C12" s="445">
+      <c r="C12" s="278">
         <v>2</v>
       </c>
-      <c r="D12" s="445">
+      <c r="D12" s="278">
         <v>3</v>
       </c>
-      <c r="E12" s="445">
+      <c r="E12" s="278">
         <v>1</v>
       </c>
-      <c r="F12" s="445"/>
-      <c r="G12" s="445"/>
-      <c r="H12" s="445"/>
-      <c r="I12" s="445"/>
-      <c r="J12" s="445">
+      <c r="F12" s="278"/>
+      <c r="G12" s="278"/>
+      <c r="H12" s="278"/>
+      <c r="I12" s="278"/>
+      <c r="J12" s="278">
         <f>SUM(C12:I12)</f>
         <v>6</v>
       </c>
-      <c r="K12" s="445">
+      <c r="K12" s="278">
         <f>IF(OR(J12=0,J12=""),"",RANK(J12,J$12:J$20,0))</f>
         <v>5</v>
       </c>
-      <c r="L12" s="425"/>
+      <c r="L12" s="268"/>
     </row>
     <row r="13" spans="1:12" ht="20.100000000000001" customHeight="1">
-      <c r="A13" s="425"/>
-      <c r="B13" s="446" t="s">
+      <c r="A13" s="268"/>
+      <c r="B13" s="279" t="s">
         <v>401</v>
       </c>
-      <c r="C13" s="446">
+      <c r="C13" s="279">
         <v>3</v>
       </c>
-      <c r="D13" s="446">
+      <c r="D13" s="279">
         <v>4</v>
       </c>
-      <c r="E13" s="446">
+      <c r="E13" s="279">
         <v>3</v>
       </c>
-      <c r="F13" s="446"/>
-      <c r="G13" s="446"/>
-      <c r="H13" s="446"/>
-      <c r="I13" s="446"/>
-      <c r="J13" s="446">
+      <c r="F13" s="279"/>
+      <c r="G13" s="279"/>
+      <c r="H13" s="279"/>
+      <c r="I13" s="279"/>
+      <c r="J13" s="279">
         <f t="shared" ref="J13:J20" si="0">SUM(C13:I13)</f>
         <v>10</v>
       </c>
-      <c r="K13" s="446">
+      <c r="K13" s="279">
         <f t="shared" ref="K13:K20" si="1">IF(OR(J13=0,J13=""),"",RANK(J13,J$12:J$20,0))</f>
         <v>4</v>
       </c>
-      <c r="L13" s="425"/>
+      <c r="L13" s="268"/>
     </row>
     <row r="14" spans="1:12" ht="20.100000000000001" customHeight="1">
-      <c r="A14" s="425"/>
-      <c r="B14" s="446" t="s">
+      <c r="A14" s="268"/>
+      <c r="B14" s="279" t="s">
         <v>402</v>
       </c>
-      <c r="C14" s="446">
+      <c r="C14" s="279">
         <v>4</v>
       </c>
-      <c r="D14" s="446">
+      <c r="D14" s="279">
         <v>5</v>
       </c>
-      <c r="E14" s="446">
+      <c r="E14" s="279">
         <v>3</v>
       </c>
-      <c r="F14" s="446"/>
-      <c r="G14" s="446"/>
-      <c r="H14" s="446"/>
-      <c r="I14" s="446"/>
-      <c r="J14" s="446">
+      <c r="F14" s="279"/>
+      <c r="G14" s="279"/>
+      <c r="H14" s="279"/>
+      <c r="I14" s="279"/>
+      <c r="J14" s="279">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="K14" s="446">
+      <c r="K14" s="279">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="L14" s="425"/>
+      <c r="L14" s="268"/>
     </row>
     <row r="15" spans="1:12" ht="20.100000000000001" customHeight="1">
-      <c r="A15" s="425"/>
-      <c r="B15" s="446" t="s">
+      <c r="A15" s="268"/>
+      <c r="B15" s="279" t="s">
         <v>403</v>
       </c>
-      <c r="C15" s="446">
+      <c r="C15" s="279">
         <v>5</v>
       </c>
-      <c r="D15" s="446">
+      <c r="D15" s="279">
         <v>6</v>
       </c>
-      <c r="E15" s="446">
+      <c r="E15" s="279">
         <v>1</v>
       </c>
-      <c r="F15" s="446"/>
-      <c r="G15" s="446"/>
-      <c r="H15" s="446"/>
-      <c r="I15" s="446"/>
-      <c r="J15" s="446">
+      <c r="F15" s="279"/>
+      <c r="G15" s="279"/>
+      <c r="H15" s="279"/>
+      <c r="I15" s="279"/>
+      <c r="J15" s="279">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="K15" s="446">
+      <c r="K15" s="279">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="L15" s="425"/>
+      <c r="L15" s="268"/>
     </row>
     <row r="16" spans="1:12" ht="20.100000000000001" customHeight="1">
-      <c r="A16" s="425"/>
-      <c r="B16" s="446" t="s">
+      <c r="A16" s="268"/>
+      <c r="B16" s="279" t="s">
         <v>404</v>
       </c>
-      <c r="C16" s="446">
+      <c r="C16" s="279">
         <v>6</v>
       </c>
-      <c r="D16" s="446">
+      <c r="D16" s="279">
         <v>7</v>
       </c>
-      <c r="E16" s="446">
+      <c r="E16" s="279">
         <v>2</v>
       </c>
-      <c r="F16" s="446"/>
-      <c r="G16" s="446"/>
-      <c r="H16" s="446"/>
-      <c r="I16" s="446"/>
-      <c r="J16" s="446">
+      <c r="F16" s="279"/>
+      <c r="G16" s="279"/>
+      <c r="H16" s="279"/>
+      <c r="I16" s="279"/>
+      <c r="J16" s="279">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="K16" s="446">
+      <c r="K16" s="279">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="L16" s="425"/>
+      <c r="L16" s="268"/>
     </row>
     <row r="17" spans="1:12" ht="20.100000000000001" customHeight="1">
-      <c r="A17" s="425"/>
-      <c r="B17" s="446"/>
-      <c r="C17" s="446"/>
-      <c r="D17" s="446"/>
-      <c r="E17" s="446"/>
-      <c r="F17" s="446"/>
-      <c r="G17" s="446"/>
-      <c r="H17" s="446"/>
-      <c r="I17" s="446"/>
-      <c r="J17" s="446">
+      <c r="A17" s="268"/>
+      <c r="B17" s="279"/>
+      <c r="C17" s="279"/>
+      <c r="D17" s="279"/>
+      <c r="E17" s="279"/>
+      <c r="F17" s="279"/>
+      <c r="G17" s="279"/>
+      <c r="H17" s="279"/>
+      <c r="I17" s="279"/>
+      <c r="J17" s="279">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K17" s="446" t="str">
+      <c r="K17" s="279" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="L17" s="425"/>
+      <c r="L17" s="268"/>
     </row>
     <row r="18" spans="1:12" ht="20.100000000000001" customHeight="1">
-      <c r="A18" s="425"/>
-      <c r="B18" s="446"/>
-      <c r="C18" s="446"/>
-      <c r="D18" s="446"/>
-      <c r="E18" s="446"/>
-      <c r="F18" s="446"/>
-      <c r="G18" s="446"/>
-      <c r="H18" s="446"/>
-      <c r="I18" s="446"/>
-      <c r="J18" s="446">
+      <c r="A18" s="268"/>
+      <c r="B18" s="279"/>
+      <c r="C18" s="279"/>
+      <c r="D18" s="279"/>
+      <c r="E18" s="279"/>
+      <c r="F18" s="279"/>
+      <c r="G18" s="279"/>
+      <c r="H18" s="279"/>
+      <c r="I18" s="279"/>
+      <c r="J18" s="279">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K18" s="446" t="str">
+      <c r="K18" s="279" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="L18" s="425"/>
+      <c r="L18" s="268"/>
     </row>
     <row r="19" spans="1:12" ht="20.100000000000001" customHeight="1">
-      <c r="A19" s="425"/>
-      <c r="B19" s="446"/>
-      <c r="C19" s="446"/>
-      <c r="D19" s="446"/>
-      <c r="E19" s="446"/>
-      <c r="F19" s="446"/>
-      <c r="G19" s="446"/>
-      <c r="H19" s="446"/>
-      <c r="I19" s="446"/>
-      <c r="J19" s="446">
+      <c r="A19" s="268"/>
+      <c r="B19" s="279"/>
+      <c r="C19" s="279"/>
+      <c r="D19" s="279"/>
+      <c r="E19" s="279"/>
+      <c r="F19" s="279"/>
+      <c r="G19" s="279"/>
+      <c r="H19" s="279"/>
+      <c r="I19" s="279"/>
+      <c r="J19" s="279">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K19" s="446" t="str">
+      <c r="K19" s="279" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="L19" s="425"/>
+      <c r="L19" s="268"/>
     </row>
     <row r="20" spans="1:12" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A20" s="425"/>
-      <c r="B20" s="447"/>
-      <c r="C20" s="447"/>
-      <c r="D20" s="447"/>
-      <c r="E20" s="447"/>
-      <c r="F20" s="447"/>
-      <c r="G20" s="447"/>
-      <c r="H20" s="447"/>
-      <c r="I20" s="447"/>
-      <c r="J20" s="447">
+      <c r="A20" s="268"/>
+      <c r="B20" s="280"/>
+      <c r="C20" s="280"/>
+      <c r="D20" s="280"/>
+      <c r="E20" s="280"/>
+      <c r="F20" s="280"/>
+      <c r="G20" s="280"/>
+      <c r="H20" s="280"/>
+      <c r="I20" s="280"/>
+      <c r="J20" s="280">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="K20" s="447" t="str">
+      <c r="K20" s="280" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="L20" s="425"/>
+      <c r="L20" s="268"/>
     </row>
     <row r="21" spans="1:12" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A21" s="425"/>
-      <c r="B21" s="448" t="s">
+      <c r="A21" s="268"/>
+      <c r="B21" s="281" t="s">
         <v>399</v>
       </c>
-      <c r="C21" s="429">
+      <c r="C21" s="271">
         <f>SUM(C12:C20)</f>
         <v>20</v>
       </c>
-      <c r="D21" s="429">
+      <c r="D21" s="271">
         <f t="shared" ref="D21:J21" si="2">SUM(D12:D20)</f>
         <v>25</v>
       </c>
-      <c r="E21" s="429">
+      <c r="E21" s="271">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="F21" s="429">
+      <c r="F21" s="271">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="G21" s="429">
+      <c r="G21" s="271">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H21" s="429">
+      <c r="H21" s="271">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="I21" s="429">
+      <c r="I21" s="271">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J21" s="429">
+      <c r="J21" s="271">
         <f t="shared" si="2"/>
         <v>55</v>
       </c>
-      <c r="K21" s="449"/>
-      <c r="L21" s="425"/>
+      <c r="K21" s="282"/>
+      <c r="L21" s="268"/>
     </row>
     <row r="22" spans="1:12">
-      <c r="A22" s="425"/>
-      <c r="B22" s="425"/>
-      <c r="C22" s="425"/>
-      <c r="D22" s="425"/>
-      <c r="E22" s="425"/>
-      <c r="F22" s="425"/>
-      <c r="G22" s="425"/>
-      <c r="H22" s="425"/>
-      <c r="I22" s="425"/>
-      <c r="J22" s="425"/>
-      <c r="K22" s="425"/>
-      <c r="L22" s="425"/>
+      <c r="A22" s="268"/>
+      <c r="B22" s="268"/>
+      <c r="C22" s="268"/>
+      <c r="D22" s="268"/>
+      <c r="E22" s="268"/>
+      <c r="F22" s="268"/>
+      <c r="G22" s="268"/>
+      <c r="H22" s="268"/>
+      <c r="I22" s="268"/>
+      <c r="J22" s="268"/>
+      <c r="K22" s="268"/>
+      <c r="L22" s="268"/>
     </row>
     <row r="23" spans="1:12">
-      <c r="A23" s="425"/>
-      <c r="B23" s="425"/>
-      <c r="C23" s="425"/>
-      <c r="D23" s="425"/>
-      <c r="E23" s="425"/>
-      <c r="F23" s="425"/>
-      <c r="G23" s="425"/>
-      <c r="H23" s="425"/>
-      <c r="I23" s="425"/>
-      <c r="J23" s="425"/>
-      <c r="K23" s="425"/>
-      <c r="L23" s="425"/>
+      <c r="A23" s="268"/>
+      <c r="B23" s="268"/>
+      <c r="C23" s="268"/>
+      <c r="D23" s="268"/>
+      <c r="E23" s="268"/>
+      <c r="F23" s="268"/>
+      <c r="G23" s="268"/>
+      <c r="H23" s="268"/>
+      <c r="I23" s="268"/>
+      <c r="J23" s="268"/>
+      <c r="K23" s="268"/>
+      <c r="L23" s="268"/>
     </row>
     <row r="24" spans="1:12">
-      <c r="A24" s="425"/>
-      <c r="B24" s="425"/>
-      <c r="C24" s="425"/>
-      <c r="D24" s="425"/>
-      <c r="E24" s="425"/>
-      <c r="F24" s="425"/>
-      <c r="G24" s="425"/>
-      <c r="H24" s="425"/>
-      <c r="I24" s="425"/>
-      <c r="J24" s="425"/>
-      <c r="K24" s="425"/>
-      <c r="L24" s="425"/>
+      <c r="A24" s="268"/>
+      <c r="B24" s="268"/>
+      <c r="C24" s="268"/>
+      <c r="D24" s="268"/>
+      <c r="E24" s="268"/>
+      <c r="F24" s="268"/>
+      <c r="G24" s="268"/>
+      <c r="H24" s="268"/>
+      <c r="I24" s="268"/>
+      <c r="J24" s="268"/>
+      <c r="K24" s="268"/>
+      <c r="L24" s="268"/>
+    </row>
+    <row r="25" spans="1:12" ht="15.75" thickBot="1"/>
+    <row r="26" spans="1:12" ht="18.75">
+      <c r="B26" s="472" t="s">
+        <v>417</v>
+      </c>
+      <c r="C26" s="473"/>
+      <c r="D26" s="473"/>
+      <c r="E26" s="473"/>
+      <c r="F26" s="473"/>
+      <c r="G26" s="473"/>
+      <c r="H26" s="473"/>
+      <c r="I26" s="473"/>
+      <c r="J26" s="473"/>
+      <c r="K26" s="473"/>
+      <c r="L26" s="474"/>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="B27" s="229"/>
+      <c r="C27" s="457"/>
+      <c r="D27" s="457"/>
+      <c r="E27" s="457"/>
+      <c r="F27" s="457"/>
+      <c r="G27" s="457"/>
+      <c r="H27" s="457"/>
+      <c r="I27" s="457"/>
+      <c r="J27" s="457"/>
+      <c r="K27" s="457"/>
+      <c r="L27" s="230"/>
+    </row>
+    <row r="28" spans="1:12" ht="15.75">
+      <c r="B28" s="475" t="s">
+        <v>418</v>
+      </c>
+      <c r="C28" s="469"/>
+      <c r="D28" s="469"/>
+      <c r="E28" s="469"/>
+      <c r="F28" s="469"/>
+      <c r="G28" s="469"/>
+      <c r="H28" s="469"/>
+      <c r="I28" s="469"/>
+      <c r="J28" s="469"/>
+      <c r="K28" s="469"/>
+      <c r="L28" s="476"/>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="B29" s="477" t="s">
+        <v>419</v>
+      </c>
+      <c r="C29" s="470"/>
+      <c r="D29" s="470"/>
+      <c r="E29" s="470"/>
+      <c r="F29" s="470"/>
+      <c r="G29" s="470"/>
+      <c r="H29" s="470"/>
+      <c r="I29" s="470"/>
+      <c r="J29" s="470"/>
+      <c r="K29" s="470"/>
+      <c r="L29" s="478"/>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="B30" s="229"/>
+      <c r="C30" s="457"/>
+      <c r="D30" s="457"/>
+      <c r="E30" s="457"/>
+      <c r="F30" s="457"/>
+      <c r="G30" s="457"/>
+      <c r="H30" s="457"/>
+      <c r="I30" s="457"/>
+      <c r="J30" s="457"/>
+      <c r="K30" s="457"/>
+      <c r="L30" s="230"/>
+    </row>
+    <row r="31" spans="1:12" ht="15.75">
+      <c r="B31" s="475" t="s">
+        <v>420</v>
+      </c>
+      <c r="C31" s="469"/>
+      <c r="D31" s="469"/>
+      <c r="E31" s="469"/>
+      <c r="F31" s="469"/>
+      <c r="G31" s="469"/>
+      <c r="H31" s="469"/>
+      <c r="I31" s="469"/>
+      <c r="J31" s="469"/>
+      <c r="K31" s="469"/>
+      <c r="L31" s="476"/>
+    </row>
+    <row r="32" spans="1:12" ht="84.75" customHeight="1" thickBot="1">
+      <c r="B32" s="479" t="s">
+        <v>421</v>
+      </c>
+      <c r="C32" s="480"/>
+      <c r="D32" s="480"/>
+      <c r="E32" s="480"/>
+      <c r="F32" s="480"/>
+      <c r="G32" s="480"/>
+      <c r="H32" s="480"/>
+      <c r="I32" s="480"/>
+      <c r="J32" s="480"/>
+      <c r="K32" s="480"/>
+      <c r="L32" s="481"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="15">
+    <mergeCell ref="B31:L31"/>
+    <mergeCell ref="B32:L32"/>
+    <mergeCell ref="C10:I10"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="B26:L26"/>
+    <mergeCell ref="B28:L28"/>
+    <mergeCell ref="B29:L29"/>
     <mergeCell ref="A8:K8"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="G3:K3"/>
@@ -10208,22 +10868,18 @@
     <mergeCell ref="A6:K6"/>
     <mergeCell ref="D7:K7"/>
     <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C10:I10"/>
-    <mergeCell ref="A2:K2"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="C21:J21">
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="greaterThan">
-      <formula>$C$3</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="C21:J21">
     <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>0</formula>
     </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="greaterThan">
+      <formula>$C$3</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J12:J20">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -10241,6 +10897,434 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D17A7DF5-5736-4C22-9485-DAC8ED51D209}">
+  <dimension ref="A1:K32"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="4.85546875" style="84" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" style="84" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" style="84" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" style="84" customWidth="1"/>
+    <col min="5" max="5" width="28.7109375" style="84" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" style="84" customWidth="1"/>
+    <col min="7" max="7" width="23.5703125" style="84" customWidth="1"/>
+    <col min="8" max="8" width="11.28515625" style="84" customWidth="1"/>
+    <col min="9" max="9" width="23.5703125" style="84" customWidth="1"/>
+    <col min="10" max="10" width="3.42578125" style="84" customWidth="1"/>
+    <col min="11" max="11" width="23.5703125" style="84" customWidth="1"/>
+    <col min="12" max="16384" width="9.140625" style="84"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="39.75" customHeight="1">
+      <c r="A1" s="448" t="s">
+        <v>407</v>
+      </c>
+      <c r="B1" s="448"/>
+      <c r="C1" s="448"/>
+      <c r="D1" s="448"/>
+      <c r="E1" s="448"/>
+      <c r="F1" s="448"/>
+      <c r="G1" s="448"/>
+      <c r="H1" s="448"/>
+      <c r="I1" s="448"/>
+      <c r="J1" s="448"/>
+      <c r="K1" s="448"/>
+    </row>
+    <row r="2" spans="1:11" ht="21.75" customHeight="1">
+      <c r="A2" s="160"/>
+      <c r="B2" s="160"/>
+      <c r="C2" s="160"/>
+      <c r="D2" s="450" t="s">
+        <v>408</v>
+      </c>
+      <c r="E2" s="449" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="449"/>
+      <c r="G2" s="450" t="s">
+        <v>409</v>
+      </c>
+      <c r="H2" s="449" t="s">
+        <v>445</v>
+      </c>
+      <c r="I2" s="449"/>
+      <c r="J2" s="160"/>
+      <c r="K2" s="160"/>
+    </row>
+    <row r="3" spans="1:11" ht="21.75" customHeight="1">
+      <c r="A3" s="160"/>
+      <c r="B3" s="160"/>
+      <c r="C3" s="160"/>
+      <c r="D3" s="160"/>
+      <c r="E3" s="160"/>
+      <c r="F3" s="160"/>
+      <c r="G3" s="160"/>
+      <c r="H3" s="160"/>
+      <c r="I3" s="160"/>
+      <c r="J3" s="160"/>
+      <c r="K3" s="160"/>
+    </row>
+    <row r="4" spans="1:11" ht="15.75" thickBot="1"/>
+    <row r="5" spans="1:11" ht="24" customHeight="1" thickBot="1">
+      <c r="C5" s="452" t="s">
+        <v>410</v>
+      </c>
+      <c r="E5" s="453" t="s">
+        <v>411</v>
+      </c>
+      <c r="G5" s="454" t="s">
+        <v>412</v>
+      </c>
+      <c r="I5" s="455" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="24.75" customHeight="1">
+      <c r="C6" s="463" t="s">
+        <v>432</v>
+      </c>
+      <c r="D6" s="467">
+        <f>IF(E6="","",1)</f>
+        <v>1</v>
+      </c>
+      <c r="E6" s="463" t="s">
+        <v>434</v>
+      </c>
+      <c r="G6" s="463" t="s">
+        <v>439</v>
+      </c>
+      <c r="I6" s="463" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="24.75" customHeight="1">
+      <c r="C7" s="464" t="s">
+        <v>448</v>
+      </c>
+      <c r="D7" s="467">
+        <f>IF(E7="","",MAX(D$6:D6)+1)</f>
+        <v>2</v>
+      </c>
+      <c r="E7" s="464" t="s">
+        <v>447</v>
+      </c>
+      <c r="G7" s="464" t="s">
+        <v>440</v>
+      </c>
+      <c r="I7" s="464" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="24.75" customHeight="1">
+      <c r="C8" s="464" t="s">
+        <v>433</v>
+      </c>
+      <c r="D8" s="467">
+        <f>IF(E8="","",MAX(D$6:D7)+1)</f>
+        <v>3</v>
+      </c>
+      <c r="E8" s="464" t="s">
+        <v>435</v>
+      </c>
+      <c r="G8" s="464"/>
+      <c r="I8" s="465"/>
+    </row>
+    <row r="9" spans="1:11" ht="24.75" customHeight="1" thickBot="1">
+      <c r="C9" s="464" t="s">
+        <v>449</v>
+      </c>
+      <c r="D9" s="467">
+        <f>IF(E9="","",MAX(D$6:D8)+1)</f>
+        <v>4</v>
+      </c>
+      <c r="E9" s="464" t="s">
+        <v>436</v>
+      </c>
+      <c r="G9" s="464"/>
+      <c r="I9" s="465"/>
+    </row>
+    <row r="10" spans="1:11" ht="24.75" customHeight="1">
+      <c r="C10" s="464" t="s">
+        <v>450</v>
+      </c>
+      <c r="D10" s="467">
+        <f>IF(E10="","",MAX(D$6:D9)+1)</f>
+        <v>5</v>
+      </c>
+      <c r="E10" s="464" t="s">
+        <v>437</v>
+      </c>
+      <c r="G10" s="464"/>
+      <c r="I10" s="465"/>
+      <c r="K10" s="495" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="24.75" customHeight="1">
+      <c r="C11" s="464" t="s">
+        <v>451</v>
+      </c>
+      <c r="D11" s="467">
+        <f>IF(E11="","",MAX(D$6:D10)+1)</f>
+        <v>6</v>
+      </c>
+      <c r="E11" s="464" t="s">
+        <v>438</v>
+      </c>
+      <c r="G11" s="464"/>
+      <c r="I11" s="465"/>
+      <c r="K11" s="496"/>
+    </row>
+    <row r="12" spans="1:11" ht="24.75" customHeight="1" thickBot="1">
+      <c r="C12" s="464" t="s">
+        <v>452</v>
+      </c>
+      <c r="D12" s="84" t="str">
+        <f>IF(E12="","",MAX(D$6:D11)+1)</f>
+        <v/>
+      </c>
+      <c r="E12" s="465"/>
+      <c r="G12" s="465"/>
+      <c r="I12" s="465"/>
+      <c r="K12" s="497"/>
+    </row>
+    <row r="13" spans="1:11" ht="24.75" customHeight="1" thickBot="1">
+      <c r="C13" s="464" t="s">
+        <v>453</v>
+      </c>
+      <c r="D13" s="468" t="str">
+        <f>IF(E13="","",MAX(D$6:D12)+1)</f>
+        <v/>
+      </c>
+      <c r="E13" s="466"/>
+      <c r="F13" s="456"/>
+      <c r="G13" s="466"/>
+      <c r="H13" s="456"/>
+      <c r="I13" s="466"/>
+      <c r="J13" s="456"/>
+      <c r="K13" s="459" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="24.75" customHeight="1" thickBot="1">
+      <c r="C14" s="451">
+        <f>COUNTA(C6:C13)</f>
+        <v>8</v>
+      </c>
+      <c r="E14" s="451">
+        <f>COUNTA(E6:E13)</f>
+        <v>6</v>
+      </c>
+      <c r="G14" s="451">
+        <f>COUNTA(G6:G13)</f>
+        <v>2</v>
+      </c>
+      <c r="I14" s="451">
+        <f>COUNTA(I6:I13)</f>
+        <v>2</v>
+      </c>
+      <c r="K14" s="460" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="60">
+      <c r="K15" s="498" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="45">
+      <c r="K16" s="499" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11">
+      <c r="K17" s="458"/>
+    </row>
+    <row r="18" spans="2:11" ht="15.75" thickBot="1">
+      <c r="K18" s="461"/>
+    </row>
+    <row r="20" spans="2:11" ht="30">
+      <c r="B20" s="462" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" ht="15.75" thickBot="1"/>
+    <row r="22" spans="2:11" ht="18.75">
+      <c r="B22" s="485" t="s">
+        <v>422</v>
+      </c>
+      <c r="C22" s="483"/>
+      <c r="D22" s="483"/>
+      <c r="E22" s="483"/>
+      <c r="F22" s="483"/>
+      <c r="G22" s="483"/>
+      <c r="H22" s="483"/>
+      <c r="I22" s="483"/>
+      <c r="J22" s="483"/>
+      <c r="K22" s="490"/>
+    </row>
+    <row r="23" spans="2:11">
+      <c r="B23" s="486" t="s">
+        <v>423</v>
+      </c>
+      <c r="C23" s="482"/>
+      <c r="D23" s="482"/>
+      <c r="E23" s="482"/>
+      <c r="F23" s="482"/>
+      <c r="G23" s="482"/>
+      <c r="H23" s="482"/>
+      <c r="I23" s="482"/>
+      <c r="J23" s="482"/>
+      <c r="K23" s="491"/>
+    </row>
+    <row r="24" spans="2:11">
+      <c r="B24" s="487" t="s">
+        <v>424</v>
+      </c>
+      <c r="C24" s="471"/>
+      <c r="D24" s="471"/>
+      <c r="E24" s="471"/>
+      <c r="F24" s="471"/>
+      <c r="G24" s="471"/>
+      <c r="H24" s="471"/>
+      <c r="I24" s="471"/>
+      <c r="J24" s="471"/>
+      <c r="K24" s="492"/>
+    </row>
+    <row r="25" spans="2:11">
+      <c r="B25" s="487"/>
+      <c r="C25" s="471"/>
+      <c r="D25" s="471"/>
+      <c r="E25" s="471"/>
+      <c r="F25" s="471"/>
+      <c r="G25" s="471"/>
+      <c r="H25" s="471"/>
+      <c r="I25" s="471"/>
+      <c r="J25" s="471"/>
+      <c r="K25" s="492"/>
+    </row>
+    <row r="26" spans="2:11">
+      <c r="B26" s="486" t="s">
+        <v>425</v>
+      </c>
+      <c r="C26" s="482"/>
+      <c r="D26" s="482"/>
+      <c r="E26" s="482"/>
+      <c r="F26" s="482"/>
+      <c r="G26" s="482"/>
+      <c r="H26" s="482"/>
+      <c r="I26" s="482"/>
+      <c r="J26" s="482"/>
+      <c r="K26" s="491"/>
+    </row>
+    <row r="27" spans="2:11">
+      <c r="B27" s="488" t="s">
+        <v>426</v>
+      </c>
+      <c r="C27" s="470"/>
+      <c r="D27" s="470"/>
+      <c r="E27" s="470"/>
+      <c r="F27" s="470"/>
+      <c r="G27" s="470"/>
+      <c r="H27" s="470"/>
+      <c r="I27" s="470"/>
+      <c r="J27" s="470"/>
+      <c r="K27" s="493"/>
+    </row>
+    <row r="28" spans="2:11">
+      <c r="B28" s="488" t="s">
+        <v>427</v>
+      </c>
+      <c r="C28" s="470"/>
+      <c r="D28" s="470"/>
+      <c r="E28" s="470"/>
+      <c r="F28" s="470"/>
+      <c r="G28" s="470"/>
+      <c r="H28" s="470"/>
+      <c r="I28" s="470"/>
+      <c r="J28" s="470"/>
+      <c r="K28" s="493"/>
+    </row>
+    <row r="29" spans="2:11">
+      <c r="B29" s="488" t="s">
+        <v>428</v>
+      </c>
+      <c r="C29" s="470"/>
+      <c r="D29" s="470"/>
+      <c r="E29" s="470"/>
+      <c r="F29" s="470"/>
+      <c r="G29" s="470"/>
+      <c r="H29" s="470"/>
+      <c r="I29" s="470"/>
+      <c r="J29" s="470"/>
+      <c r="K29" s="493"/>
+    </row>
+    <row r="30" spans="2:11">
+      <c r="B30" s="486" t="s">
+        <v>429</v>
+      </c>
+      <c r="C30" s="482"/>
+      <c r="D30" s="482"/>
+      <c r="E30" s="482"/>
+      <c r="F30" s="482"/>
+      <c r="G30" s="482"/>
+      <c r="H30" s="482"/>
+      <c r="I30" s="482"/>
+      <c r="J30" s="482"/>
+      <c r="K30" s="491"/>
+    </row>
+    <row r="31" spans="2:11">
+      <c r="B31" s="488" t="s">
+        <v>430</v>
+      </c>
+      <c r="C31" s="470"/>
+      <c r="D31" s="470"/>
+      <c r="E31" s="470"/>
+      <c r="F31" s="470"/>
+      <c r="G31" s="470"/>
+      <c r="H31" s="470"/>
+      <c r="I31" s="470"/>
+      <c r="J31" s="470"/>
+      <c r="K31" s="493"/>
+    </row>
+    <row r="32" spans="2:11" ht="15.75" thickBot="1">
+      <c r="B32" s="489" t="s">
+        <v>431</v>
+      </c>
+      <c r="C32" s="484"/>
+      <c r="D32" s="484"/>
+      <c r="E32" s="484"/>
+      <c r="F32" s="484"/>
+      <c r="G32" s="484"/>
+      <c r="H32" s="484"/>
+      <c r="I32" s="484"/>
+      <c r="J32" s="484"/>
+      <c r="K32" s="494"/>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="B30:K30"/>
+    <mergeCell ref="B31:K31"/>
+    <mergeCell ref="B32:K32"/>
+    <mergeCell ref="B23:K23"/>
+    <mergeCell ref="B24:K25"/>
+    <mergeCell ref="B26:K26"/>
+    <mergeCell ref="B27:K27"/>
+    <mergeCell ref="B28:K28"/>
+    <mergeCell ref="B29:K29"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="K10:K12"/>
+    <mergeCell ref="B22:K22"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1DEED6C-4F0E-4895-BD77-03C3FD341752}">
   <dimension ref="B1:C19"/>
@@ -10254,10 +11338,10 @@
   <sheetData>
     <row r="1" spans="2:3" ht="15.75" thickBot="1"/>
     <row r="2" spans="2:3" ht="36.75" customHeight="1" thickBot="1">
-      <c r="B2" s="291" t="s">
+      <c r="B2" s="299" t="s">
         <v>80</v>
       </c>
-      <c r="C2" s="292"/>
+      <c r="C2" s="300"/>
     </row>
     <row r="3" spans="2:3" ht="17.25" thickBot="1">
       <c r="B3" s="104" t="s">
@@ -10312,10 +11396,10 @@
       <c r="C9" s="102"/>
     </row>
     <row r="10" spans="2:3" ht="30.75" customHeight="1">
-      <c r="B10" s="289" t="s">
+      <c r="B10" s="297" t="s">
         <v>89</v>
       </c>
-      <c r="C10" s="290"/>
+      <c r="C10" s="298"/>
     </row>
     <row r="11" spans="2:3" ht="30.75" customHeight="1">
       <c r="B11" s="107" t="s">
@@ -10414,110 +11498,110 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="20.100000000000001" customHeight="1">
-      <c r="A1" s="269"/>
-      <c r="B1" s="269"/>
-      <c r="C1" s="269"/>
-      <c r="D1" s="269"/>
-      <c r="E1" s="269"/>
-      <c r="F1" s="269"/>
-      <c r="G1" s="269"/>
-      <c r="H1" s="269"/>
-      <c r="I1" s="269"/>
-      <c r="J1" s="269"/>
-      <c r="K1" s="269"/>
-      <c r="L1" s="269"/>
-      <c r="M1" s="269"/>
-      <c r="N1" s="269"/>
-      <c r="O1" s="269"/>
-      <c r="P1" s="269"/>
-      <c r="Q1" s="269"/>
-      <c r="R1" s="269"/>
+      <c r="A1" s="316"/>
+      <c r="B1" s="316"/>
+      <c r="C1" s="316"/>
+      <c r="D1" s="316"/>
+      <c r="E1" s="316"/>
+      <c r="F1" s="316"/>
+      <c r="G1" s="316"/>
+      <c r="H1" s="316"/>
+      <c r="I1" s="316"/>
+      <c r="J1" s="316"/>
+      <c r="K1" s="316"/>
+      <c r="L1" s="316"/>
+      <c r="M1" s="316"/>
+      <c r="N1" s="316"/>
+      <c r="O1" s="316"/>
+      <c r="P1" s="316"/>
+      <c r="Q1" s="316"/>
+      <c r="R1" s="316"/>
     </row>
     <row r="2" spans="1:18" ht="36.75" customHeight="1">
-      <c r="A2" s="268" t="s">
+      <c r="A2" s="315" t="s">
         <v>371</v>
       </c>
-      <c r="B2" s="268"/>
-      <c r="C2" s="268"/>
-      <c r="D2" s="269"/>
-      <c r="E2" s="269"/>
-      <c r="F2" s="269"/>
-      <c r="G2" s="269"/>
-      <c r="H2" s="269"/>
-      <c r="I2" s="269"/>
-      <c r="J2" s="269"/>
-      <c r="K2" s="269"/>
-      <c r="L2" s="269"/>
-      <c r="M2" s="269"/>
-      <c r="N2" s="269"/>
-      <c r="O2" s="269"/>
-      <c r="P2" s="269"/>
-      <c r="Q2" s="269"/>
-      <c r="R2" s="269"/>
+      <c r="B2" s="315"/>
+      <c r="C2" s="315"/>
+      <c r="D2" s="316"/>
+      <c r="E2" s="316"/>
+      <c r="F2" s="316"/>
+      <c r="G2" s="316"/>
+      <c r="H2" s="316"/>
+      <c r="I2" s="316"/>
+      <c r="J2" s="316"/>
+      <c r="K2" s="316"/>
+      <c r="L2" s="316"/>
+      <c r="M2" s="316"/>
+      <c r="N2" s="316"/>
+      <c r="O2" s="316"/>
+      <c r="P2" s="316"/>
+      <c r="Q2" s="316"/>
+      <c r="R2" s="316"/>
     </row>
     <row r="3" spans="1:18" ht="20.100000000000001" customHeight="1">
       <c r="A3" s="251"/>
       <c r="B3" s="251"/>
       <c r="C3" s="251"/>
-      <c r="D3" s="269"/>
-      <c r="E3" s="269"/>
-      <c r="F3" s="269"/>
-      <c r="G3" s="269"/>
-      <c r="H3" s="269"/>
-      <c r="I3" s="269"/>
-      <c r="J3" s="269"/>
-      <c r="K3" s="269"/>
-      <c r="L3" s="269"/>
-      <c r="M3" s="269"/>
-      <c r="N3" s="269"/>
-      <c r="O3" s="269"/>
-      <c r="P3" s="269"/>
-      <c r="Q3" s="269"/>
-      <c r="R3" s="269"/>
+      <c r="D3" s="316"/>
+      <c r="E3" s="316"/>
+      <c r="F3" s="316"/>
+      <c r="G3" s="316"/>
+      <c r="H3" s="316"/>
+      <c r="I3" s="316"/>
+      <c r="J3" s="316"/>
+      <c r="K3" s="316"/>
+      <c r="L3" s="316"/>
+      <c r="M3" s="316"/>
+      <c r="N3" s="316"/>
+      <c r="O3" s="316"/>
+      <c r="P3" s="316"/>
+      <c r="Q3" s="316"/>
+      <c r="R3" s="316"/>
     </row>
     <row r="4" spans="1:18" ht="20.100000000000001" customHeight="1">
-      <c r="A4" s="269"/>
-      <c r="B4" s="269"/>
+      <c r="A4" s="316"/>
+      <c r="B4" s="316"/>
       <c r="C4" s="249" t="s">
         <v>370</v>
       </c>
       <c r="D4" s="248" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="269"/>
-      <c r="F4" s="269"/>
-      <c r="G4" s="269"/>
-      <c r="H4" s="269"/>
-      <c r="I4" s="269"/>
-      <c r="J4" s="269"/>
-      <c r="K4" s="269"/>
-      <c r="L4" s="269"/>
-      <c r="M4" s="269"/>
-      <c r="N4" s="269"/>
-      <c r="O4" s="269"/>
-      <c r="P4" s="269"/>
-      <c r="Q4" s="269"/>
-      <c r="R4" s="269"/>
+      <c r="E4" s="316"/>
+      <c r="F4" s="316"/>
+      <c r="G4" s="316"/>
+      <c r="H4" s="316"/>
+      <c r="I4" s="316"/>
+      <c r="J4" s="316"/>
+      <c r="K4" s="316"/>
+      <c r="L4" s="316"/>
+      <c r="M4" s="316"/>
+      <c r="N4" s="316"/>
+      <c r="O4" s="316"/>
+      <c r="P4" s="316"/>
+      <c r="Q4" s="316"/>
+      <c r="R4" s="316"/>
     </row>
     <row r="5" spans="1:18" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A5" s="270"/>
-      <c r="B5" s="270"/>
+      <c r="A5" s="317"/>
+      <c r="B5" s="317"/>
       <c r="C5" s="252"/>
       <c r="D5" s="252"/>
-      <c r="E5" s="270"/>
-      <c r="F5" s="270"/>
-      <c r="G5" s="270"/>
-      <c r="H5" s="270"/>
-      <c r="I5" s="270"/>
-      <c r="J5" s="270"/>
-      <c r="K5" s="270"/>
-      <c r="L5" s="270"/>
-      <c r="M5" s="270"/>
-      <c r="N5" s="270"/>
-      <c r="O5" s="270"/>
-      <c r="P5" s="270"/>
-      <c r="Q5" s="270"/>
-      <c r="R5" s="270"/>
+      <c r="E5" s="317"/>
+      <c r="F5" s="317"/>
+      <c r="G5" s="317"/>
+      <c r="H5" s="317"/>
+      <c r="I5" s="317"/>
+      <c r="J5" s="317"/>
+      <c r="K5" s="317"/>
+      <c r="L5" s="317"/>
+      <c r="M5" s="317"/>
+      <c r="N5" s="317"/>
+      <c r="O5" s="317"/>
+      <c r="P5" s="317"/>
+      <c r="Q5" s="317"/>
+      <c r="R5" s="317"/>
     </row>
     <row r="6" spans="1:18" ht="24.95" customHeight="1">
       <c r="B6" s="253" t="s">
@@ -10790,10 +11874,10 @@
     </row>
     <row r="22" spans="1:6" ht="15.75" thickBot="1"/>
     <row r="23" spans="1:6" ht="15.75" thickBot="1">
-      <c r="B23" s="277" t="s">
+      <c r="B23" s="301" t="s">
         <v>375</v>
       </c>
-      <c r="C23" s="278"/>
+      <c r="C23" s="302"/>
       <c r="D23" s="266">
         <v>5</v>
       </c>
@@ -10803,113 +11887,113 @@
     </row>
     <row r="25" spans="1:6" ht="15.75" thickBot="1"/>
     <row r="26" spans="1:6" ht="17.100000000000001" customHeight="1" thickBot="1">
-      <c r="A26" s="279" t="s">
+      <c r="A26" s="303" t="s">
         <v>377</v>
       </c>
-      <c r="B26" s="280"/>
-      <c r="C26" s="280"/>
-      <c r="D26" s="280"/>
-      <c r="E26" s="280"/>
-      <c r="F26" s="281"/>
+      <c r="B26" s="304"/>
+      <c r="C26" s="304"/>
+      <c r="D26" s="304"/>
+      <c r="E26" s="304"/>
+      <c r="F26" s="305"/>
     </row>
     <row r="27" spans="1:6" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A27" s="282" t="s">
+      <c r="A27" s="306" t="s">
         <v>378</v>
       </c>
-      <c r="B27" s="283"/>
-      <c r="C27" s="283"/>
-      <c r="D27" s="283"/>
-      <c r="E27" s="283"/>
-      <c r="F27" s="284"/>
+      <c r="B27" s="307"/>
+      <c r="C27" s="307"/>
+      <c r="D27" s="307"/>
+      <c r="E27" s="307"/>
+      <c r="F27" s="308"/>
     </row>
     <row r="28" spans="1:6" ht="30" customHeight="1" thickBot="1">
-      <c r="A28" s="271" t="s">
+      <c r="A28" s="309" t="s">
         <v>379</v>
       </c>
-      <c r="B28" s="272"/>
-      <c r="C28" s="272"/>
-      <c r="D28" s="272"/>
-      <c r="E28" s="272"/>
-      <c r="F28" s="273"/>
+      <c r="B28" s="310"/>
+      <c r="C28" s="310"/>
+      <c r="D28" s="310"/>
+      <c r="E28" s="310"/>
+      <c r="F28" s="311"/>
     </row>
     <row r="29" spans="1:6" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A29" s="282" t="s">
+      <c r="A29" s="306" t="s">
         <v>380</v>
       </c>
-      <c r="B29" s="283"/>
-      <c r="C29" s="283"/>
-      <c r="D29" s="283"/>
-      <c r="E29" s="283"/>
-      <c r="F29" s="284"/>
+      <c r="B29" s="307"/>
+      <c r="C29" s="307"/>
+      <c r="D29" s="307"/>
+      <c r="E29" s="307"/>
+      <c r="F29" s="308"/>
     </row>
     <row r="30" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A30" s="271" t="s">
+      <c r="A30" s="309" t="s">
         <v>381</v>
       </c>
-      <c r="B30" s="272"/>
-      <c r="C30" s="272"/>
-      <c r="D30" s="272"/>
-      <c r="E30" s="272"/>
-      <c r="F30" s="273"/>
+      <c r="B30" s="310"/>
+      <c r="C30" s="310"/>
+      <c r="D30" s="310"/>
+      <c r="E30" s="310"/>
+      <c r="F30" s="311"/>
     </row>
     <row r="31" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A31" s="271" t="s">
+      <c r="A31" s="309" t="s">
         <v>382</v>
       </c>
-      <c r="B31" s="272"/>
-      <c r="C31" s="272"/>
-      <c r="D31" s="272"/>
-      <c r="E31" s="272"/>
-      <c r="F31" s="273"/>
+      <c r="B31" s="310"/>
+      <c r="C31" s="310"/>
+      <c r="D31" s="310"/>
+      <c r="E31" s="310"/>
+      <c r="F31" s="311"/>
     </row>
     <row r="32" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A32" s="271" t="s">
+      <c r="A32" s="309" t="s">
         <v>383</v>
       </c>
-      <c r="B32" s="272"/>
-      <c r="C32" s="272"/>
-      <c r="D32" s="272"/>
-      <c r="E32" s="272"/>
-      <c r="F32" s="273"/>
+      <c r="B32" s="310"/>
+      <c r="C32" s="310"/>
+      <c r="D32" s="310"/>
+      <c r="E32" s="310"/>
+      <c r="F32" s="311"/>
     </row>
     <row r="33" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A33" s="271" t="s">
+      <c r="A33" s="309" t="s">
         <v>384</v>
       </c>
-      <c r="B33" s="272"/>
-      <c r="C33" s="272"/>
-      <c r="D33" s="272"/>
-      <c r="E33" s="272"/>
-      <c r="F33" s="273"/>
+      <c r="B33" s="310"/>
+      <c r="C33" s="310"/>
+      <c r="D33" s="310"/>
+      <c r="E33" s="310"/>
+      <c r="F33" s="311"/>
     </row>
     <row r="34" spans="1:6" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A34" s="274" t="s">
+      <c r="A34" s="312" t="s">
         <v>385</v>
       </c>
-      <c r="B34" s="275"/>
-      <c r="C34" s="275"/>
-      <c r="D34" s="275"/>
-      <c r="E34" s="275"/>
-      <c r="F34" s="276"/>
+      <c r="B34" s="313"/>
+      <c r="C34" s="313"/>
+      <c r="D34" s="313"/>
+      <c r="E34" s="313"/>
+      <c r="F34" s="314"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="A34:F34"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="D2:R2"/>
     <mergeCell ref="D3:R3"/>
     <mergeCell ref="A4:B5"/>
     <mergeCell ref="E4:R5"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A29:F29"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10934,16 +12018,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:44" ht="40.5">
-      <c r="B1" s="310" t="s">
+      <c r="B1" s="327" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="310"/>
-      <c r="D1" s="310"/>
-      <c r="E1" s="310"/>
-      <c r="F1" s="310"/>
-      <c r="G1" s="310"/>
-      <c r="H1" s="310"/>
-      <c r="I1" s="310"/>
+      <c r="C1" s="327"/>
+      <c r="D1" s="327"/>
+      <c r="E1" s="327"/>
+      <c r="F1" s="327"/>
+      <c r="G1" s="327"/>
+      <c r="H1" s="327"/>
+      <c r="I1" s="327"/>
       <c r="J1" s="31"/>
       <c r="K1" s="31"/>
       <c r="L1" s="31"/>
@@ -10981,16 +12065,16 @@
       <c r="AR1" s="31"/>
     </row>
     <row r="2" spans="2:44" ht="17.25" thickBot="1">
-      <c r="B2" s="311" t="s">
+      <c r="B2" s="328" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="311"/>
-      <c r="D2" s="311"/>
-      <c r="E2" s="311"/>
-      <c r="F2" s="311"/>
-      <c r="G2" s="311"/>
-      <c r="H2" s="311"/>
-      <c r="I2" s="311"/>
+      <c r="C2" s="328"/>
+      <c r="D2" s="328"/>
+      <c r="E2" s="328"/>
+      <c r="F2" s="328"/>
+      <c r="G2" s="328"/>
+      <c r="H2" s="328"/>
+      <c r="I2" s="328"/>
       <c r="J2" s="32"/>
       <c r="K2" s="32"/>
       <c r="L2" s="32"/>
@@ -11028,55 +12112,55 @@
       <c r="AR2" s="32"/>
     </row>
     <row r="3" spans="2:44" ht="18.75">
-      <c r="B3" s="312"/>
-      <c r="C3" s="313"/>
-      <c r="D3" s="313"/>
-      <c r="E3" s="313"/>
-      <c r="F3" s="313"/>
-      <c r="G3" s="313"/>
-      <c r="H3" s="313"/>
-      <c r="I3" s="313"/>
-      <c r="J3" s="293">
+      <c r="B3" s="329"/>
+      <c r="C3" s="330"/>
+      <c r="D3" s="330"/>
+      <c r="E3" s="330"/>
+      <c r="F3" s="330"/>
+      <c r="G3" s="330"/>
+      <c r="H3" s="330"/>
+      <c r="I3" s="330"/>
+      <c r="J3" s="335">
         <f ca="1">K5</f>
         <v>46181</v>
       </c>
-      <c r="K3" s="293"/>
-      <c r="L3" s="293"/>
-      <c r="M3" s="293"/>
-      <c r="N3" s="294"/>
-      <c r="O3" s="294"/>
-      <c r="P3" s="294"/>
-      <c r="Q3" s="294"/>
-      <c r="R3" s="294"/>
-      <c r="S3" s="294"/>
-      <c r="T3" s="294"/>
-      <c r="U3" s="294"/>
-      <c r="V3" s="294"/>
-      <c r="W3" s="294"/>
-      <c r="X3" s="294"/>
-      <c r="Y3" s="294"/>
-      <c r="Z3" s="294"/>
-      <c r="AA3" s="294"/>
-      <c r="AB3" s="294"/>
-      <c r="AC3" s="294"/>
-      <c r="AD3" s="294"/>
-      <c r="AE3" s="294"/>
-      <c r="AF3" s="294"/>
-      <c r="AG3" s="294"/>
-      <c r="AH3" s="294"/>
-      <c r="AI3" s="294"/>
-      <c r="AJ3" s="294"/>
-      <c r="AK3" s="294"/>
-      <c r="AL3" s="294"/>
-      <c r="AM3" s="294"/>
-      <c r="AN3" s="294"/>
-      <c r="AO3" s="294"/>
-      <c r="AP3" s="294"/>
-      <c r="AQ3" s="294"/>
-      <c r="AR3" s="294"/>
+      <c r="K3" s="335"/>
+      <c r="L3" s="335"/>
+      <c r="M3" s="335"/>
+      <c r="N3" s="336"/>
+      <c r="O3" s="336"/>
+      <c r="P3" s="336"/>
+      <c r="Q3" s="336"/>
+      <c r="R3" s="336"/>
+      <c r="S3" s="336"/>
+      <c r="T3" s="336"/>
+      <c r="U3" s="336"/>
+      <c r="V3" s="336"/>
+      <c r="W3" s="336"/>
+      <c r="X3" s="336"/>
+      <c r="Y3" s="336"/>
+      <c r="Z3" s="336"/>
+      <c r="AA3" s="336"/>
+      <c r="AB3" s="336"/>
+      <c r="AC3" s="336"/>
+      <c r="AD3" s="336"/>
+      <c r="AE3" s="336"/>
+      <c r="AF3" s="336"/>
+      <c r="AG3" s="336"/>
+      <c r="AH3" s="336"/>
+      <c r="AI3" s="336"/>
+      <c r="AJ3" s="336"/>
+      <c r="AK3" s="336"/>
+      <c r="AL3" s="336"/>
+      <c r="AM3" s="336"/>
+      <c r="AN3" s="336"/>
+      <c r="AO3" s="336"/>
+      <c r="AP3" s="336"/>
+      <c r="AQ3" s="336"/>
+      <c r="AR3" s="336"/>
     </row>
     <row r="4" spans="2:44" ht="15.75" thickBot="1">
-      <c r="B4" s="314"/>
+      <c r="B4" s="331"/>
       <c r="C4" s="78" t="s">
         <v>0</v>
       </c>
@@ -11084,82 +12168,82 @@
         <f ca="1">IF(MONTH(TODAY()-WEEKDAY(TODAY(),2)+1)&lt;MONTH(TODAY()),(TODAY()-28-DAY(TODAY())+7)-WEEKDAY((TODAY()-DAY(TODAY())+7),2)+1,(TODAY()-DAY(TODAY())+7)-WEEKDAY((TODAY()-DAY(TODAY())+7),2)+1)</f>
         <v>46174</v>
       </c>
-      <c r="E4" s="316"/>
-      <c r="F4" s="316"/>
-      <c r="G4" s="316"/>
-      <c r="H4" s="316"/>
-      <c r="I4" s="317"/>
-      <c r="J4" s="295">
+      <c r="E4" s="333"/>
+      <c r="F4" s="333"/>
+      <c r="G4" s="333"/>
+      <c r="H4" s="333"/>
+      <c r="I4" s="334"/>
+      <c r="J4" s="337">
         <f ca="1">K5</f>
         <v>46181</v>
       </c>
-      <c r="K4" s="295"/>
-      <c r="L4" s="295"/>
-      <c r="M4" s="295"/>
-      <c r="N4" s="300">
+      <c r="K4" s="337"/>
+      <c r="L4" s="337"/>
+      <c r="M4" s="337"/>
+      <c r="N4" s="342">
         <f ca="1">O5</f>
         <v>46209</v>
       </c>
-      <c r="O4" s="295"/>
-      <c r="P4" s="295"/>
-      <c r="Q4" s="295"/>
-      <c r="R4" s="295"/>
-      <c r="S4" s="295">
+      <c r="O4" s="337"/>
+      <c r="P4" s="337"/>
+      <c r="Q4" s="337"/>
+      <c r="R4" s="337"/>
+      <c r="S4" s="337">
         <f ca="1">T5</f>
         <v>46244</v>
       </c>
-      <c r="T4" s="295"/>
-      <c r="U4" s="295"/>
-      <c r="V4" s="295"/>
-      <c r="W4" s="295">
+      <c r="T4" s="337"/>
+      <c r="U4" s="337"/>
+      <c r="V4" s="337"/>
+      <c r="W4" s="337">
         <f ca="1">X5</f>
         <v>46272</v>
       </c>
-      <c r="X4" s="295"/>
-      <c r="Y4" s="295"/>
-      <c r="Z4" s="295"/>
-      <c r="AA4" s="295"/>
-      <c r="AB4" s="295">
+      <c r="X4" s="337"/>
+      <c r="Y4" s="337"/>
+      <c r="Z4" s="337"/>
+      <c r="AA4" s="337"/>
+      <c r="AB4" s="337">
         <f ca="1">AC5</f>
         <v>46307</v>
       </c>
-      <c r="AC4" s="295"/>
-      <c r="AD4" s="295"/>
-      <c r="AE4" s="295"/>
-      <c r="AF4" s="295">
+      <c r="AC4" s="337"/>
+      <c r="AD4" s="337"/>
+      <c r="AE4" s="337"/>
+      <c r="AF4" s="337">
         <f ca="1">AG5</f>
         <v>46335</v>
       </c>
-      <c r="AG4" s="295"/>
-      <c r="AH4" s="295"/>
-      <c r="AI4" s="295"/>
-      <c r="AJ4" s="295">
+      <c r="AG4" s="337"/>
+      <c r="AH4" s="337"/>
+      <c r="AI4" s="337"/>
+      <c r="AJ4" s="337">
         <f ca="1">AK5</f>
         <v>46363</v>
       </c>
-      <c r="AK4" s="295"/>
-      <c r="AL4" s="295"/>
-      <c r="AM4" s="295"/>
-      <c r="AN4" s="295"/>
-      <c r="AO4" s="295">
+      <c r="AK4" s="337"/>
+      <c r="AL4" s="337"/>
+      <c r="AM4" s="337"/>
+      <c r="AN4" s="337"/>
+      <c r="AO4" s="337">
         <f ca="1">AP5</f>
         <v>46398</v>
       </c>
-      <c r="AP4" s="295"/>
-      <c r="AQ4" s="295"/>
-      <c r="AR4" s="296"/>
+      <c r="AP4" s="337"/>
+      <c r="AQ4" s="337"/>
+      <c r="AR4" s="338"/>
     </row>
     <row r="5" spans="2:44" ht="33" thickBot="1">
-      <c r="B5" s="315"/>
+      <c r="B5" s="332"/>
       <c r="C5" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="297" t="s">
+      <c r="D5" s="339" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="298"/>
-      <c r="F5" s="298"/>
-      <c r="G5" s="299"/>
+      <c r="E5" s="340"/>
+      <c r="F5" s="340"/>
+      <c r="G5" s="341"/>
       <c r="H5" s="81"/>
       <c r="I5" s="79" t="s">
         <v>2</v>
@@ -13083,78 +14167,71 @@
     </row>
     <row r="24" spans="2:9" ht="15.75" thickBot="1"/>
     <row r="25" spans="2:9" ht="24.95" customHeight="1">
-      <c r="B25" s="301" t="s">
+      <c r="B25" s="318" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="302"/>
-      <c r="D25" s="302"/>
-      <c r="E25" s="302"/>
-      <c r="F25" s="302"/>
-      <c r="G25" s="302"/>
-      <c r="H25" s="302"/>
-      <c r="I25" s="303"/>
+      <c r="C25" s="319"/>
+      <c r="D25" s="319"/>
+      <c r="E25" s="319"/>
+      <c r="F25" s="319"/>
+      <c r="G25" s="319"/>
+      <c r="H25" s="319"/>
+      <c r="I25" s="320"/>
     </row>
     <row r="26" spans="2:9" ht="90" customHeight="1">
-      <c r="B26" s="304" t="s">
+      <c r="B26" s="321" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="305"/>
-      <c r="D26" s="305"/>
-      <c r="E26" s="305"/>
-      <c r="F26" s="305"/>
-      <c r="G26" s="305"/>
-      <c r="H26" s="305"/>
-      <c r="I26" s="306"/>
+      <c r="C26" s="322"/>
+      <c r="D26" s="322"/>
+      <c r="E26" s="322"/>
+      <c r="F26" s="322"/>
+      <c r="G26" s="322"/>
+      <c r="H26" s="322"/>
+      <c r="I26" s="323"/>
     </row>
     <row r="27" spans="2:9">
-      <c r="B27" s="304"/>
-      <c r="C27" s="305"/>
-      <c r="D27" s="305"/>
-      <c r="E27" s="305"/>
-      <c r="F27" s="305"/>
-      <c r="G27" s="305"/>
-      <c r="H27" s="305"/>
-      <c r="I27" s="306"/>
+      <c r="B27" s="321"/>
+      <c r="C27" s="322"/>
+      <c r="D27" s="322"/>
+      <c r="E27" s="322"/>
+      <c r="F27" s="322"/>
+      <c r="G27" s="322"/>
+      <c r="H27" s="322"/>
+      <c r="I27" s="323"/>
     </row>
     <row r="28" spans="2:9">
-      <c r="B28" s="304"/>
-      <c r="C28" s="305"/>
-      <c r="D28" s="305"/>
-      <c r="E28" s="305"/>
-      <c r="F28" s="305"/>
-      <c r="G28" s="305"/>
-      <c r="H28" s="305"/>
-      <c r="I28" s="306"/>
+      <c r="B28" s="321"/>
+      <c r="C28" s="322"/>
+      <c r="D28" s="322"/>
+      <c r="E28" s="322"/>
+      <c r="F28" s="322"/>
+      <c r="G28" s="322"/>
+      <c r="H28" s="322"/>
+      <c r="I28" s="323"/>
     </row>
     <row r="29" spans="2:9">
-      <c r="B29" s="304"/>
-      <c r="C29" s="305"/>
-      <c r="D29" s="305"/>
-      <c r="E29" s="305"/>
-      <c r="F29" s="305"/>
-      <c r="G29" s="305"/>
-      <c r="H29" s="305"/>
-      <c r="I29" s="306"/>
+      <c r="B29" s="321"/>
+      <c r="C29" s="322"/>
+      <c r="D29" s="322"/>
+      <c r="E29" s="322"/>
+      <c r="F29" s="322"/>
+      <c r="G29" s="322"/>
+      <c r="H29" s="322"/>
+      <c r="I29" s="323"/>
     </row>
     <row r="30" spans="2:9" ht="15.75" thickBot="1">
-      <c r="B30" s="307"/>
-      <c r="C30" s="308"/>
-      <c r="D30" s="308"/>
-      <c r="E30" s="308"/>
-      <c r="F30" s="308"/>
-      <c r="G30" s="308"/>
-      <c r="H30" s="308"/>
-      <c r="I30" s="309"/>
+      <c r="B30" s="324"/>
+      <c r="C30" s="325"/>
+      <c r="D30" s="325"/>
+      <c r="E30" s="325"/>
+      <c r="F30" s="325"/>
+      <c r="G30" s="325"/>
+      <c r="H30" s="325"/>
+      <c r="I30" s="326"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B25:I25"/>
-    <mergeCell ref="B26:I30"/>
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="E4:I4"/>
     <mergeCell ref="J3:AR3"/>
     <mergeCell ref="AF4:AI4"/>
     <mergeCell ref="AJ4:AN4"/>
@@ -13165,6 +14242,13 @@
     <mergeCell ref="S4:V4"/>
     <mergeCell ref="W4:AA4"/>
     <mergeCell ref="AB4:AE4"/>
+    <mergeCell ref="B25:I25"/>
+    <mergeCell ref="B26:I30"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="E4:I4"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H7:H16">
@@ -13207,150 +14291,150 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" ht="29.25" thickBot="1">
-      <c r="B2" s="336" t="s">
+      <c r="B2" s="344" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="337"/>
-      <c r="D2" s="337"/>
-      <c r="E2" s="337"/>
-      <c r="F2" s="337"/>
-      <c r="G2" s="337"/>
-      <c r="H2" s="337"/>
-      <c r="I2" s="337"/>
-      <c r="J2" s="337"/>
-      <c r="K2" s="337"/>
-      <c r="L2" s="337"/>
-      <c r="M2" s="337"/>
-      <c r="N2" s="337"/>
-      <c r="O2" s="337"/>
-      <c r="P2" s="338"/>
+      <c r="C2" s="345"/>
+      <c r="D2" s="345"/>
+      <c r="E2" s="345"/>
+      <c r="F2" s="345"/>
+      <c r="G2" s="345"/>
+      <c r="H2" s="345"/>
+      <c r="I2" s="345"/>
+      <c r="J2" s="345"/>
+      <c r="K2" s="345"/>
+      <c r="L2" s="345"/>
+      <c r="M2" s="345"/>
+      <c r="N2" s="345"/>
+      <c r="O2" s="345"/>
+      <c r="P2" s="346"/>
     </row>
     <row r="3" spans="2:16">
-      <c r="B3" s="339"/>
-      <c r="C3" s="340"/>
+      <c r="B3" s="347"/>
+      <c r="C3" s="348"/>
       <c r="D3" s="99" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="332" t="s">
+      <c r="E3" s="366" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="332"/>
-      <c r="G3" s="332"/>
-      <c r="H3" s="332"/>
-      <c r="I3" s="341" t="s">
+      <c r="F3" s="366"/>
+      <c r="G3" s="366"/>
+      <c r="H3" s="366"/>
+      <c r="I3" s="349" t="s">
         <v>46</v>
       </c>
-      <c r="J3" s="341"/>
-      <c r="K3" s="342" t="s">
+      <c r="J3" s="349"/>
+      <c r="K3" s="350" t="s">
         <v>17</v>
       </c>
-      <c r="L3" s="342"/>
-      <c r="M3" s="342"/>
-      <c r="N3" s="340"/>
-      <c r="O3" s="340"/>
-      <c r="P3" s="343"/>
+      <c r="L3" s="350"/>
+      <c r="M3" s="350"/>
+      <c r="N3" s="348"/>
+      <c r="O3" s="348"/>
+      <c r="P3" s="351"/>
     </row>
     <row r="4" spans="2:16" ht="15.75" thickBot="1">
-      <c r="B4" s="344"/>
-      <c r="C4" s="345"/>
-      <c r="D4" s="345"/>
-      <c r="E4" s="345"/>
-      <c r="F4" s="345"/>
-      <c r="G4" s="345"/>
-      <c r="H4" s="345"/>
-      <c r="I4" s="345"/>
-      <c r="J4" s="345"/>
-      <c r="K4" s="345"/>
-      <c r="L4" s="345"/>
-      <c r="M4" s="345"/>
-      <c r="N4" s="345"/>
-      <c r="O4" s="345"/>
-      <c r="P4" s="346"/>
+      <c r="B4" s="352"/>
+      <c r="C4" s="353"/>
+      <c r="D4" s="353"/>
+      <c r="E4" s="353"/>
+      <c r="F4" s="353"/>
+      <c r="G4" s="353"/>
+      <c r="H4" s="353"/>
+      <c r="I4" s="353"/>
+      <c r="J4" s="353"/>
+      <c r="K4" s="353"/>
+      <c r="L4" s="353"/>
+      <c r="M4" s="353"/>
+      <c r="N4" s="353"/>
+      <c r="O4" s="353"/>
+      <c r="P4" s="354"/>
     </row>
     <row r="5" spans="2:16" ht="15.75" thickBot="1">
-      <c r="B5" s="347" t="s">
+      <c r="B5" s="355" t="s">
         <v>79</v>
       </c>
-      <c r="C5" s="348"/>
-      <c r="D5" s="348"/>
-      <c r="E5" s="348"/>
-      <c r="F5" s="348"/>
-      <c r="G5" s="348"/>
-      <c r="H5" s="348"/>
-      <c r="I5" s="348"/>
-      <c r="J5" s="348"/>
-      <c r="K5" s="348"/>
-      <c r="L5" s="348"/>
-      <c r="M5" s="348"/>
-      <c r="N5" s="348"/>
-      <c r="O5" s="348"/>
-      <c r="P5" s="349"/>
+      <c r="C5" s="356"/>
+      <c r="D5" s="356"/>
+      <c r="E5" s="356"/>
+      <c r="F5" s="356"/>
+      <c r="G5" s="356"/>
+      <c r="H5" s="356"/>
+      <c r="I5" s="356"/>
+      <c r="J5" s="356"/>
+      <c r="K5" s="356"/>
+      <c r="L5" s="356"/>
+      <c r="M5" s="356"/>
+      <c r="N5" s="356"/>
+      <c r="O5" s="356"/>
+      <c r="P5" s="357"/>
     </row>
     <row r="6" spans="2:16" ht="129.75" customHeight="1" thickBot="1">
-      <c r="B6" s="350" t="s">
+      <c r="B6" s="358" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="351"/>
-      <c r="D6" s="352"/>
-      <c r="E6" s="331" t="s">
+      <c r="C6" s="359"/>
+      <c r="D6" s="360"/>
+      <c r="E6" s="361" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="331" t="s">
+      <c r="F6" s="361" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="331" t="s">
+      <c r="G6" s="361" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="331" t="s">
+      <c r="H6" s="361" t="s">
         <v>22</v>
       </c>
-      <c r="I6" s="331" t="s">
+      <c r="I6" s="361" t="s">
         <v>24</v>
       </c>
-      <c r="J6" s="331" t="s">
+      <c r="J6" s="361" t="s">
         <v>26</v>
       </c>
-      <c r="K6" s="331" t="s">
+      <c r="K6" s="361" t="s">
         <v>28</v>
       </c>
-      <c r="L6" s="331" t="s">
+      <c r="L6" s="361" t="s">
         <v>30</v>
       </c>
-      <c r="M6" s="331" t="s">
+      <c r="M6" s="361" t="s">
         <v>32</v>
       </c>
-      <c r="N6" s="335" t="s">
+      <c r="N6" s="343" t="s">
         <v>34</v>
       </c>
-      <c r="O6" s="335"/>
-      <c r="P6" s="335"/>
+      <c r="O6" s="343"/>
+      <c r="P6" s="343"/>
     </row>
     <row r="7" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B7" s="333" t="s">
+      <c r="B7" s="364" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="334"/>
+      <c r="C7" s="365"/>
       <c r="D7" s="114" t="s">
         <v>48</v>
       </c>
-      <c r="E7" s="331"/>
-      <c r="F7" s="331"/>
-      <c r="G7" s="331"/>
-      <c r="H7" s="331"/>
-      <c r="I7" s="331"/>
-      <c r="J7" s="331"/>
-      <c r="K7" s="331"/>
-      <c r="L7" s="331"/>
-      <c r="M7" s="331"/>
-      <c r="N7" s="335"/>
-      <c r="O7" s="335"/>
-      <c r="P7" s="335"/>
+      <c r="E7" s="361"/>
+      <c r="F7" s="361"/>
+      <c r="G7" s="361"/>
+      <c r="H7" s="361"/>
+      <c r="I7" s="361"/>
+      <c r="J7" s="361"/>
+      <c r="K7" s="361"/>
+      <c r="L7" s="361"/>
+      <c r="M7" s="361"/>
+      <c r="N7" s="343"/>
+      <c r="O7" s="343"/>
+      <c r="P7" s="343"/>
     </row>
     <row r="8" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B8" s="318" t="s">
+      <c r="B8" s="362" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="319"/>
+      <c r="C8" s="363"/>
       <c r="D8" s="100" t="s">
         <v>62</v>
       </c>
@@ -13388,10 +14472,10 @@
       <c r="P8" s="90"/>
     </row>
     <row r="9" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B9" s="318" t="s">
+      <c r="B9" s="362" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="319"/>
+      <c r="C9" s="363"/>
       <c r="D9" s="100" t="s">
         <v>50</v>
       </c>
@@ -13429,10 +14513,10 @@
       <c r="P9" s="94"/>
     </row>
     <row r="10" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B10" s="318" t="s">
+      <c r="B10" s="362" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="319"/>
+      <c r="C10" s="363"/>
       <c r="D10" s="100" t="s">
         <v>63</v>
       </c>
@@ -13470,10 +14554,10 @@
       <c r="P10" s="94"/>
     </row>
     <row r="11" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B11" s="318" t="s">
+      <c r="B11" s="362" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="319"/>
+      <c r="C11" s="363"/>
       <c r="D11" s="100" t="s">
         <v>64</v>
       </c>
@@ -13511,10 +14595,10 @@
       <c r="P11" s="94"/>
     </row>
     <row r="12" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B12" s="318" t="s">
+      <c r="B12" s="362" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="319"/>
+      <c r="C12" s="363"/>
       <c r="D12" s="100" t="s">
         <v>65</v>
       </c>
@@ -13552,10 +14636,10 @@
       <c r="P12" s="94"/>
     </row>
     <row r="13" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B13" s="318" t="s">
+      <c r="B13" s="362" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="319"/>
+      <c r="C13" s="363"/>
       <c r="D13" s="100" t="s">
         <v>66</v>
       </c>
@@ -13593,10 +14677,10 @@
       <c r="P13" s="94"/>
     </row>
     <row r="14" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B14" s="318" t="s">
+      <c r="B14" s="362" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="319"/>
+      <c r="C14" s="363"/>
       <c r="D14" s="100" t="s">
         <v>67</v>
       </c>
@@ -13634,10 +14718,10 @@
       <c r="P14" s="94"/>
     </row>
     <row r="15" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B15" s="318" t="s">
+      <c r="B15" s="362" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="319"/>
+      <c r="C15" s="363"/>
       <c r="D15" s="100" t="s">
         <v>68</v>
       </c>
@@ -13675,10 +14759,10 @@
       <c r="P15" s="94"/>
     </row>
     <row r="16" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B16" s="318" t="s">
+      <c r="B16" s="362" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="319"/>
+      <c r="C16" s="363"/>
       <c r="D16" s="100" t="s">
         <v>69</v>
       </c>
@@ -13716,10 +14800,10 @@
       <c r="P16" s="94"/>
     </row>
     <row r="17" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B17" s="318" t="s">
+      <c r="B17" s="362" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="319"/>
+      <c r="C17" s="363"/>
       <c r="D17" s="100" t="s">
         <v>70</v>
       </c>
@@ -13757,10 +14841,10 @@
       <c r="P17" s="94"/>
     </row>
     <row r="18" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B18" s="318" t="s">
+      <c r="B18" s="362" t="s">
         <v>71</v>
       </c>
-      <c r="C18" s="319"/>
+      <c r="C18" s="363"/>
       <c r="D18" s="100" t="s">
         <v>72</v>
       </c>
@@ -13798,10 +14882,10 @@
       <c r="P18" s="94"/>
     </row>
     <row r="19" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B19" s="318" t="s">
+      <c r="B19" s="362" t="s">
         <v>74</v>
       </c>
-      <c r="C19" s="319"/>
+      <c r="C19" s="363"/>
       <c r="D19" s="100" t="s">
         <v>77</v>
       </c>
@@ -13839,10 +14923,10 @@
       <c r="P19" s="94"/>
     </row>
     <row r="20" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B20" s="318" t="s">
+      <c r="B20" s="362" t="s">
         <v>75</v>
       </c>
-      <c r="C20" s="319"/>
+      <c r="C20" s="363"/>
       <c r="D20" s="100" t="s">
         <v>78</v>
       </c>
@@ -13880,10 +14964,10 @@
       <c r="P20" s="94"/>
     </row>
     <row r="21" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B21" s="318" t="s">
+      <c r="B21" s="362" t="s">
         <v>73</v>
       </c>
-      <c r="C21" s="319"/>
+      <c r="C21" s="363"/>
       <c r="D21" s="101" t="s">
         <v>76</v>
       </c>
@@ -13954,137 +15038,137 @@
       </c>
     </row>
     <row r="28" spans="2:16">
-      <c r="B28" s="323" t="s">
+      <c r="B28" s="375" t="s">
         <v>55</v>
       </c>
-      <c r="C28" s="324"/>
-      <c r="D28" s="324"/>
-      <c r="E28" s="324"/>
-      <c r="F28" s="324"/>
-      <c r="G28" s="324"/>
-      <c r="H28" s="324"/>
-      <c r="I28" s="324"/>
-      <c r="J28" s="324"/>
-      <c r="K28" s="324"/>
-      <c r="L28" s="324"/>
-      <c r="M28" s="324"/>
-      <c r="N28" s="324"/>
-      <c r="O28" s="324"/>
-      <c r="P28" s="325"/>
+      <c r="C28" s="376"/>
+      <c r="D28" s="376"/>
+      <c r="E28" s="376"/>
+      <c r="F28" s="376"/>
+      <c r="G28" s="376"/>
+      <c r="H28" s="376"/>
+      <c r="I28" s="376"/>
+      <c r="J28" s="376"/>
+      <c r="K28" s="376"/>
+      <c r="L28" s="376"/>
+      <c r="M28" s="376"/>
+      <c r="N28" s="376"/>
+      <c r="O28" s="376"/>
+      <c r="P28" s="377"/>
     </row>
     <row r="29" spans="2:16" ht="15" customHeight="1">
-      <c r="B29" s="320" t="s">
+      <c r="B29" s="367" t="s">
         <v>56</v>
       </c>
-      <c r="C29" s="321"/>
-      <c r="D29" s="321"/>
-      <c r="E29" s="321"/>
-      <c r="F29" s="321"/>
-      <c r="G29" s="321"/>
-      <c r="H29" s="321"/>
-      <c r="I29" s="321"/>
-      <c r="J29" s="321"/>
-      <c r="K29" s="321"/>
-      <c r="L29" s="321"/>
-      <c r="M29" s="321"/>
-      <c r="N29" s="321"/>
-      <c r="O29" s="321"/>
-      <c r="P29" s="322"/>
+      <c r="C29" s="368"/>
+      <c r="D29" s="368"/>
+      <c r="E29" s="368"/>
+      <c r="F29" s="368"/>
+      <c r="G29" s="368"/>
+      <c r="H29" s="368"/>
+      <c r="I29" s="368"/>
+      <c r="J29" s="368"/>
+      <c r="K29" s="368"/>
+      <c r="L29" s="368"/>
+      <c r="M29" s="368"/>
+      <c r="N29" s="368"/>
+      <c r="O29" s="368"/>
+      <c r="P29" s="369"/>
     </row>
     <row r="30" spans="2:16" ht="15" customHeight="1">
-      <c r="B30" s="320" t="s">
+      <c r="B30" s="367" t="s">
         <v>57</v>
       </c>
-      <c r="C30" s="321"/>
-      <c r="D30" s="321"/>
-      <c r="E30" s="321"/>
-      <c r="F30" s="321"/>
-      <c r="G30" s="321"/>
-      <c r="H30" s="321"/>
-      <c r="I30" s="321"/>
-      <c r="J30" s="321"/>
-      <c r="K30" s="321"/>
-      <c r="L30" s="321"/>
-      <c r="M30" s="321"/>
-      <c r="N30" s="321"/>
-      <c r="O30" s="321"/>
-      <c r="P30" s="322"/>
+      <c r="C30" s="368"/>
+      <c r="D30" s="368"/>
+      <c r="E30" s="368"/>
+      <c r="F30" s="368"/>
+      <c r="G30" s="368"/>
+      <c r="H30" s="368"/>
+      <c r="I30" s="368"/>
+      <c r="J30" s="368"/>
+      <c r="K30" s="368"/>
+      <c r="L30" s="368"/>
+      <c r="M30" s="368"/>
+      <c r="N30" s="368"/>
+      <c r="O30" s="368"/>
+      <c r="P30" s="369"/>
     </row>
     <row r="31" spans="2:16" ht="15" customHeight="1">
-      <c r="B31" s="320" t="s">
+      <c r="B31" s="367" t="s">
         <v>58</v>
       </c>
-      <c r="C31" s="321"/>
-      <c r="D31" s="321"/>
-      <c r="E31" s="321"/>
-      <c r="F31" s="321"/>
-      <c r="G31" s="321"/>
-      <c r="H31" s="321"/>
-      <c r="I31" s="321"/>
-      <c r="J31" s="321"/>
-      <c r="K31" s="321"/>
-      <c r="L31" s="321"/>
-      <c r="M31" s="321"/>
-      <c r="N31" s="321"/>
-      <c r="O31" s="321"/>
-      <c r="P31" s="322"/>
+      <c r="C31" s="368"/>
+      <c r="D31" s="368"/>
+      <c r="E31" s="368"/>
+      <c r="F31" s="368"/>
+      <c r="G31" s="368"/>
+      <c r="H31" s="368"/>
+      <c r="I31" s="368"/>
+      <c r="J31" s="368"/>
+      <c r="K31" s="368"/>
+      <c r="L31" s="368"/>
+      <c r="M31" s="368"/>
+      <c r="N31" s="368"/>
+      <c r="O31" s="368"/>
+      <c r="P31" s="369"/>
     </row>
     <row r="32" spans="2:16" ht="20.100000000000001" customHeight="1">
-      <c r="B32" s="320" t="s">
+      <c r="B32" s="367" t="s">
         <v>59</v>
       </c>
-      <c r="C32" s="326"/>
-      <c r="D32" s="326"/>
-      <c r="E32" s="326"/>
-      <c r="F32" s="326"/>
-      <c r="G32" s="326"/>
-      <c r="H32" s="326"/>
-      <c r="I32" s="326"/>
-      <c r="J32" s="326"/>
-      <c r="K32" s="326"/>
-      <c r="L32" s="326"/>
-      <c r="M32" s="326"/>
-      <c r="N32" s="326"/>
-      <c r="O32" s="326"/>
-      <c r="P32" s="327"/>
+      <c r="C32" s="370"/>
+      <c r="D32" s="370"/>
+      <c r="E32" s="370"/>
+      <c r="F32" s="370"/>
+      <c r="G32" s="370"/>
+      <c r="H32" s="370"/>
+      <c r="I32" s="370"/>
+      <c r="J32" s="370"/>
+      <c r="K32" s="370"/>
+      <c r="L32" s="370"/>
+      <c r="M32" s="370"/>
+      <c r="N32" s="370"/>
+      <c r="O32" s="370"/>
+      <c r="P32" s="371"/>
     </row>
     <row r="33" spans="1:16" ht="20.100000000000001" customHeight="1">
-      <c r="B33" s="320" t="s">
+      <c r="B33" s="367" t="s">
         <v>60</v>
       </c>
-      <c r="C33" s="326"/>
-      <c r="D33" s="326"/>
-      <c r="E33" s="326"/>
-      <c r="F33" s="326"/>
-      <c r="G33" s="326"/>
-      <c r="H33" s="326"/>
-      <c r="I33" s="326"/>
-      <c r="J33" s="326"/>
-      <c r="K33" s="326"/>
-      <c r="L33" s="326"/>
-      <c r="M33" s="326"/>
-      <c r="N33" s="326"/>
-      <c r="O33" s="326"/>
-      <c r="P33" s="327"/>
+      <c r="C33" s="370"/>
+      <c r="D33" s="370"/>
+      <c r="E33" s="370"/>
+      <c r="F33" s="370"/>
+      <c r="G33" s="370"/>
+      <c r="H33" s="370"/>
+      <c r="I33" s="370"/>
+      <c r="J33" s="370"/>
+      <c r="K33" s="370"/>
+      <c r="L33" s="370"/>
+      <c r="M33" s="370"/>
+      <c r="N33" s="370"/>
+      <c r="O33" s="370"/>
+      <c r="P33" s="371"/>
     </row>
     <row r="34" spans="1:16" ht="20.100000000000001" customHeight="1">
-      <c r="B34" s="328" t="s">
+      <c r="B34" s="372" t="s">
         <v>61</v>
       </c>
-      <c r="C34" s="329"/>
-      <c r="D34" s="329"/>
-      <c r="E34" s="329"/>
-      <c r="F34" s="329"/>
-      <c r="G34" s="329"/>
-      <c r="H34" s="329"/>
-      <c r="I34" s="329"/>
-      <c r="J34" s="329"/>
-      <c r="K34" s="329"/>
-      <c r="L34" s="329"/>
-      <c r="M34" s="329"/>
-      <c r="N34" s="329"/>
-      <c r="O34" s="329"/>
-      <c r="P34" s="330"/>
+      <c r="C34" s="373"/>
+      <c r="D34" s="373"/>
+      <c r="E34" s="373"/>
+      <c r="F34" s="373"/>
+      <c r="G34" s="373"/>
+      <c r="H34" s="373"/>
+      <c r="I34" s="373"/>
+      <c r="J34" s="373"/>
+      <c r="K34" s="373"/>
+      <c r="L34" s="373"/>
+      <c r="M34" s="373"/>
+      <c r="N34" s="373"/>
+      <c r="O34" s="373"/>
+      <c r="P34" s="374"/>
     </row>
     <row r="35" spans="1:16" ht="20.100000000000001" customHeight="1"/>
     <row r="39" spans="1:16" ht="15" customHeight="1"/>
@@ -14098,6 +15182,33 @@
     </row>
   </sheetData>
   <mergeCells count="43">
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B29:P29"/>
+    <mergeCell ref="B28:P28"/>
+    <mergeCell ref="B30:P30"/>
+    <mergeCell ref="B31:P31"/>
+    <mergeCell ref="B32:P32"/>
+    <mergeCell ref="B33:P33"/>
+    <mergeCell ref="B34:P34"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="M6:M7"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
     <mergeCell ref="N6:N7"/>
     <mergeCell ref="O6:O7"/>
     <mergeCell ref="P6:P7"/>
@@ -14114,33 +15225,6 @@
     <mergeCell ref="G6:G7"/>
     <mergeCell ref="H6:H7"/>
     <mergeCell ref="I6:I7"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="M6:M7"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="E3:H3"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="L6:L7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="B31:P31"/>
-    <mergeCell ref="B32:P32"/>
-    <mergeCell ref="B33:P33"/>
-    <mergeCell ref="B34:P34"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B29:P29"/>
-    <mergeCell ref="B28:P28"/>
-    <mergeCell ref="B30:P30"/>
   </mergeCells>
   <conditionalFormatting sqref="E8:N21 B23:B26">
     <cfRule type="containsText" dxfId="14" priority="1" operator="containsText" text="I">
@@ -14192,20 +15276,20 @@
   <sheetData>
     <row r="1" spans="1:25" ht="33" customHeight="1" thickBot="1">
       <c r="A1" s="115"/>
-      <c r="B1" s="356" t="s">
+      <c r="B1" s="395" t="s">
         <v>111</v>
       </c>
-      <c r="C1" s="357"/>
-      <c r="D1" s="357"/>
-      <c r="E1" s="357"/>
-      <c r="F1" s="357"/>
-      <c r="G1" s="357"/>
-      <c r="H1" s="357"/>
-      <c r="I1" s="357"/>
-      <c r="J1" s="357"/>
-      <c r="K1" s="357"/>
-      <c r="L1" s="357"/>
-      <c r="M1" s="358"/>
+      <c r="C1" s="396"/>
+      <c r="D1" s="396"/>
+      <c r="E1" s="396"/>
+      <c r="F1" s="396"/>
+      <c r="G1" s="396"/>
+      <c r="H1" s="396"/>
+      <c r="I1" s="396"/>
+      <c r="J1" s="396"/>
+      <c r="K1" s="396"/>
+      <c r="L1" s="396"/>
+      <c r="M1" s="397"/>
       <c r="N1" s="115"/>
       <c r="O1" s="115"/>
       <c r="P1" s="115"/>
@@ -14229,16 +15313,16 @@
       <c r="E2" s="130" t="s">
         <v>112</v>
       </c>
-      <c r="F2" s="359"/>
-      <c r="G2" s="359"/>
-      <c r="H2" s="359"/>
+      <c r="F2" s="398"/>
+      <c r="G2" s="398"/>
+      <c r="H2" s="398"/>
       <c r="I2" s="132" t="s">
         <v>113</v>
       </c>
-      <c r="J2" s="360">
+      <c r="J2" s="399">
         <v>46173</v>
       </c>
-      <c r="K2" s="360"/>
+      <c r="K2" s="399"/>
       <c r="L2" s="133"/>
       <c r="M2" s="117"/>
       <c r="N2" s="115"/>
@@ -14299,18 +15383,18 @@
       <c r="C4" s="133"/>
       <c r="D4" s="133"/>
       <c r="E4" s="133"/>
-      <c r="F4" s="361" t="s">
+      <c r="F4" s="400" t="s">
         <v>118</v>
       </c>
-      <c r="G4" s="361"/>
-      <c r="H4" s="361"/>
+      <c r="G4" s="400"/>
+      <c r="H4" s="400"/>
       <c r="I4" s="133"/>
       <c r="J4" s="133"/>
-      <c r="K4" s="362" t="s">
+      <c r="K4" s="401" t="s">
         <v>137</v>
       </c>
-      <c r="L4" s="362"/>
-      <c r="M4" s="363"/>
+      <c r="L4" s="401"/>
+      <c r="M4" s="402"/>
       <c r="N4" s="115"/>
       <c r="O4" s="115"/>
       <c r="P4" s="115"/>
@@ -14367,10 +15451,10 @@
         <v>126</v>
       </c>
       <c r="N5" s="115"/>
-      <c r="O5" s="364" t="s">
+      <c r="O5" s="378" t="s">
         <v>131</v>
       </c>
-      <c r="P5" s="365"/>
+      <c r="P5" s="379"/>
       <c r="Q5" s="139" t="str">
         <f>Y$7</f>
         <v>Very Low</v>
@@ -14441,7 +15525,7 @@
         <v>Severe</v>
       </c>
       <c r="N6" s="115"/>
-      <c r="O6" s="353" t="s">
+      <c r="O6" s="380" t="s">
         <v>121</v>
       </c>
       <c r="P6" s="140" t="str">
@@ -14513,7 +15597,7 @@
         <v>Moderate</v>
       </c>
       <c r="N7" s="115"/>
-      <c r="O7" s="354"/>
+      <c r="O7" s="381"/>
       <c r="P7" s="140" t="str">
         <f>X$4</f>
         <v>High</v>
@@ -14583,7 +15667,7 @@
         <v>Moderate</v>
       </c>
       <c r="N8" s="115"/>
-      <c r="O8" s="354"/>
+      <c r="O8" s="381"/>
       <c r="P8" s="140" t="str">
         <f>X$5</f>
         <v>Medium</v>
@@ -14649,7 +15733,7 @@
         <v>Moderate</v>
       </c>
       <c r="N9" s="115"/>
-      <c r="O9" s="354"/>
+      <c r="O9" s="381"/>
       <c r="P9" s="140" t="str">
         <f>X$6</f>
         <v>Low</v>
@@ -14715,7 +15799,7 @@
         <v>Moderate</v>
       </c>
       <c r="N10" s="115"/>
-      <c r="O10" s="355"/>
+      <c r="O10" s="382"/>
       <c r="P10" s="151" t="str">
         <f>X$7</f>
         <v>Very Low</v>
@@ -14836,10 +15920,10 @@
         <v>Moderate</v>
       </c>
       <c r="N12" s="115"/>
-      <c r="O12" s="364" t="s">
+      <c r="O12" s="378" t="s">
         <v>131</v>
       </c>
-      <c r="P12" s="365"/>
+      <c r="P12" s="379"/>
       <c r="Q12" s="139" t="str">
         <f>Y$7</f>
         <v>Very Low</v>
@@ -14906,7 +15990,7 @@
         <v>Sustainable</v>
       </c>
       <c r="N13" s="115"/>
-      <c r="O13" s="353" t="s">
+      <c r="O13" s="380" t="s">
         <v>121</v>
       </c>
       <c r="P13" s="140" t="str">
@@ -14979,7 +16063,7 @@
         <v>Moderate</v>
       </c>
       <c r="N14" s="115"/>
-      <c r="O14" s="354"/>
+      <c r="O14" s="381"/>
       <c r="P14" s="140" t="str">
         <f>X$4</f>
         <v>High</v>
@@ -15050,7 +16134,7 @@
         <v>Severe</v>
       </c>
       <c r="N15" s="115"/>
-      <c r="O15" s="354"/>
+      <c r="O15" s="381"/>
       <c r="P15" s="140" t="str">
         <f>X$5</f>
         <v>Medium</v>
@@ -15093,7 +16177,7 @@
       <c r="K16" s="115"/>
       <c r="L16" s="115"/>
       <c r="N16" s="115"/>
-      <c r="O16" s="354"/>
+      <c r="O16" s="381"/>
       <c r="P16" s="140" t="str">
         <f>X$6</f>
         <v>Low</v>
@@ -15125,22 +16209,22 @@
     </row>
     <row r="17" spans="1:25" ht="42" customHeight="1" thickBot="1">
       <c r="A17" s="115"/>
-      <c r="B17" s="366" t="s">
+      <c r="B17" s="383" t="s">
         <v>141</v>
       </c>
-      <c r="C17" s="367"/>
-      <c r="D17" s="367"/>
-      <c r="E17" s="367"/>
-      <c r="F17" s="367"/>
-      <c r="G17" s="367"/>
-      <c r="H17" s="368"/>
-      <c r="I17" s="367"/>
-      <c r="J17" s="367"/>
-      <c r="K17" s="367"/>
-      <c r="L17" s="367"/>
-      <c r="M17" s="369"/>
+      <c r="C17" s="384"/>
+      <c r="D17" s="384"/>
+      <c r="E17" s="384"/>
+      <c r="F17" s="384"/>
+      <c r="G17" s="384"/>
+      <c r="H17" s="385"/>
+      <c r="I17" s="384"/>
+      <c r="J17" s="384"/>
+      <c r="K17" s="384"/>
+      <c r="L17" s="384"/>
+      <c r="M17" s="386"/>
       <c r="N17" s="115"/>
-      <c r="O17" s="355"/>
+      <c r="O17" s="382"/>
       <c r="P17" s="151" t="str">
         <f>X$7</f>
         <v>Very Low</v>
@@ -15172,20 +16256,20 @@
     </row>
     <row r="18" spans="1:25">
       <c r="A18" s="115"/>
-      <c r="B18" s="370" t="s">
+      <c r="B18" s="387" t="s">
         <v>142</v>
       </c>
-      <c r="C18" s="371"/>
-      <c r="D18" s="371"/>
-      <c r="E18" s="371"/>
-      <c r="F18" s="371"/>
-      <c r="G18" s="371"/>
-      <c r="H18" s="372"/>
-      <c r="I18" s="371"/>
-      <c r="J18" s="371"/>
-      <c r="K18" s="371"/>
-      <c r="L18" s="371"/>
-      <c r="M18" s="373"/>
+      <c r="C18" s="388"/>
+      <c r="D18" s="388"/>
+      <c r="E18" s="388"/>
+      <c r="F18" s="388"/>
+      <c r="G18" s="388"/>
+      <c r="H18" s="389"/>
+      <c r="I18" s="388"/>
+      <c r="J18" s="388"/>
+      <c r="K18" s="388"/>
+      <c r="L18" s="388"/>
+      <c r="M18" s="390"/>
       <c r="N18" s="115"/>
       <c r="O18" s="115"/>
       <c r="P18" s="115"/>
@@ -15201,20 +16285,20 @@
     </row>
     <row r="19" spans="1:25" ht="19.5" thickBot="1">
       <c r="A19" s="115"/>
-      <c r="B19" s="370" t="s">
+      <c r="B19" s="387" t="s">
         <v>143</v>
       </c>
-      <c r="C19" s="371"/>
-      <c r="D19" s="371"/>
-      <c r="E19" s="371"/>
-      <c r="F19" s="371"/>
-      <c r="G19" s="371"/>
-      <c r="H19" s="372"/>
-      <c r="I19" s="371"/>
-      <c r="J19" s="371"/>
-      <c r="K19" s="371"/>
-      <c r="L19" s="371"/>
-      <c r="M19" s="373"/>
+      <c r="C19" s="388"/>
+      <c r="D19" s="388"/>
+      <c r="E19" s="388"/>
+      <c r="F19" s="388"/>
+      <c r="G19" s="388"/>
+      <c r="H19" s="389"/>
+      <c r="I19" s="388"/>
+      <c r="J19" s="388"/>
+      <c r="K19" s="388"/>
+      <c r="L19" s="388"/>
+      <c r="M19" s="390"/>
       <c r="N19" s="115"/>
       <c r="O19" s="138" t="s">
         <v>139</v>
@@ -15232,25 +16316,25 @@
     </row>
     <row r="20" spans="1:25" ht="42" customHeight="1" thickBot="1">
       <c r="A20" s="115"/>
-      <c r="B20" s="370" t="s">
+      <c r="B20" s="387" t="s">
         <v>144</v>
       </c>
-      <c r="C20" s="371"/>
-      <c r="D20" s="371"/>
-      <c r="E20" s="371"/>
-      <c r="F20" s="371"/>
-      <c r="G20" s="371"/>
-      <c r="H20" s="372"/>
-      <c r="I20" s="371"/>
-      <c r="J20" s="371"/>
-      <c r="K20" s="371"/>
-      <c r="L20" s="371"/>
-      <c r="M20" s="373"/>
+      <c r="C20" s="388"/>
+      <c r="D20" s="388"/>
+      <c r="E20" s="388"/>
+      <c r="F20" s="388"/>
+      <c r="G20" s="388"/>
+      <c r="H20" s="389"/>
+      <c r="I20" s="388"/>
+      <c r="J20" s="388"/>
+      <c r="K20" s="388"/>
+      <c r="L20" s="388"/>
+      <c r="M20" s="390"/>
       <c r="N20" s="115"/>
-      <c r="O20" s="364" t="s">
+      <c r="O20" s="378" t="s">
         <v>131</v>
       </c>
-      <c r="P20" s="365"/>
+      <c r="P20" s="379"/>
       <c r="Q20" s="139" t="str">
         <f>Y$7</f>
         <v>Very Low</v>
@@ -15278,22 +16362,22 @@
     </row>
     <row r="21" spans="1:25" ht="42" customHeight="1" thickBot="1">
       <c r="A21" s="115"/>
-      <c r="B21" s="370" t="s">
+      <c r="B21" s="387" t="s">
         <v>145</v>
       </c>
-      <c r="C21" s="371"/>
-      <c r="D21" s="371"/>
-      <c r="E21" s="371"/>
-      <c r="F21" s="371"/>
-      <c r="G21" s="371"/>
-      <c r="H21" s="372"/>
-      <c r="I21" s="371"/>
-      <c r="J21" s="371"/>
-      <c r="K21" s="371"/>
-      <c r="L21" s="371"/>
-      <c r="M21" s="373"/>
+      <c r="C21" s="388"/>
+      <c r="D21" s="388"/>
+      <c r="E21" s="388"/>
+      <c r="F21" s="388"/>
+      <c r="G21" s="388"/>
+      <c r="H21" s="389"/>
+      <c r="I21" s="388"/>
+      <c r="J21" s="388"/>
+      <c r="K21" s="388"/>
+      <c r="L21" s="388"/>
+      <c r="M21" s="390"/>
       <c r="N21" s="115"/>
-      <c r="O21" s="353" t="s">
+      <c r="O21" s="380" t="s">
         <v>121</v>
       </c>
       <c r="P21" s="140" t="str">
@@ -15327,22 +16411,22 @@
     </row>
     <row r="22" spans="1:25" ht="42" customHeight="1" thickBot="1">
       <c r="A22" s="115"/>
-      <c r="B22" s="374" t="s">
+      <c r="B22" s="391" t="s">
         <v>146</v>
       </c>
-      <c r="C22" s="375"/>
-      <c r="D22" s="375"/>
-      <c r="E22" s="375"/>
-      <c r="F22" s="375"/>
-      <c r="G22" s="375"/>
-      <c r="H22" s="376"/>
-      <c r="I22" s="375"/>
-      <c r="J22" s="375"/>
-      <c r="K22" s="375"/>
-      <c r="L22" s="375"/>
-      <c r="M22" s="377"/>
+      <c r="C22" s="392"/>
+      <c r="D22" s="392"/>
+      <c r="E22" s="392"/>
+      <c r="F22" s="392"/>
+      <c r="G22" s="392"/>
+      <c r="H22" s="393"/>
+      <c r="I22" s="392"/>
+      <c r="J22" s="392"/>
+      <c r="K22" s="392"/>
+      <c r="L22" s="392"/>
+      <c r="M22" s="394"/>
       <c r="N22" s="115"/>
-      <c r="O22" s="354"/>
+      <c r="O22" s="381"/>
       <c r="P22" s="140" t="str">
         <f>X$4</f>
         <v>High</v>
@@ -15385,7 +16469,7 @@
       <c r="K23" s="115"/>
       <c r="L23" s="115"/>
       <c r="N23" s="115"/>
-      <c r="O23" s="354"/>
+      <c r="O23" s="381"/>
       <c r="P23" s="140" t="str">
         <f>X$5</f>
         <v>Medium</v>
@@ -15428,7 +16512,7 @@
       <c r="K24" s="115"/>
       <c r="L24" s="115"/>
       <c r="N24" s="115"/>
-      <c r="O24" s="354"/>
+      <c r="O24" s="381"/>
       <c r="P24" s="140" t="str">
         <f>X$6</f>
         <v>Low</v>
@@ -15471,7 +16555,7 @@
       <c r="K25" s="115"/>
       <c r="L25" s="115"/>
       <c r="N25" s="115"/>
-      <c r="O25" s="355"/>
+      <c r="O25" s="382"/>
       <c r="P25" s="151" t="str">
         <f>X$7</f>
         <v>Very Low</v>
@@ -39878,6 +40962,13 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="O6:O10"/>
+    <mergeCell ref="B1:M1"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="O5:P5"/>
     <mergeCell ref="O12:P12"/>
     <mergeCell ref="O13:O17"/>
     <mergeCell ref="O20:P20"/>
@@ -39888,13 +40979,6 @@
     <mergeCell ref="B20:M20"/>
     <mergeCell ref="B21:M21"/>
     <mergeCell ref="B22:M22"/>
-    <mergeCell ref="O6:O10"/>
-    <mergeCell ref="B1:M1"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="O5:P5"/>
   </mergeCells>
   <conditionalFormatting sqref="H6:H15">
     <cfRule type="containsText" dxfId="10" priority="13" operator="containsText" text="Sustainable">
@@ -39952,69 +41036,69 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13" ht="24" customHeight="1">
-      <c r="B1" s="378" t="s">
+      <c r="B1" s="403" t="s">
         <v>185</v>
       </c>
-      <c r="C1" s="378"/>
-      <c r="D1" s="378"/>
-      <c r="E1" s="378"/>
-      <c r="F1" s="378"/>
-      <c r="G1" s="378"/>
-      <c r="H1" s="378"/>
-      <c r="I1" s="378"/>
-      <c r="J1" s="378"/>
+      <c r="C1" s="403"/>
+      <c r="D1" s="403"/>
+      <c r="E1" s="403"/>
+      <c r="F1" s="403"/>
+      <c r="G1" s="403"/>
+      <c r="H1" s="403"/>
+      <c r="I1" s="403"/>
+      <c r="J1" s="403"/>
     </row>
     <row r="2" spans="2:13" ht="24" customHeight="1">
-      <c r="B2" s="378"/>
-      <c r="C2" s="378"/>
-      <c r="D2" s="378"/>
-      <c r="E2" s="378"/>
-      <c r="F2" s="378"/>
-      <c r="G2" s="378"/>
-      <c r="H2" s="378"/>
-      <c r="I2" s="378"/>
-      <c r="J2" s="378"/>
+      <c r="B2" s="403"/>
+      <c r="C2" s="403"/>
+      <c r="D2" s="403"/>
+      <c r="E2" s="403"/>
+      <c r="F2" s="403"/>
+      <c r="G2" s="403"/>
+      <c r="H2" s="403"/>
+      <c r="I2" s="403"/>
+      <c r="J2" s="403"/>
     </row>
     <row r="3" spans="2:13" ht="24" customHeight="1" thickBot="1">
-      <c r="B3" s="379"/>
-      <c r="C3" s="378"/>
-      <c r="D3" s="378"/>
-      <c r="E3" s="378"/>
-      <c r="F3" s="378"/>
-      <c r="G3" s="378"/>
-      <c r="H3" s="378"/>
-      <c r="I3" s="378"/>
-      <c r="J3" s="380"/>
+      <c r="B3" s="404"/>
+      <c r="C3" s="403"/>
+      <c r="D3" s="403"/>
+      <c r="E3" s="403"/>
+      <c r="F3" s="403"/>
+      <c r="G3" s="403"/>
+      <c r="H3" s="403"/>
+      <c r="I3" s="403"/>
+      <c r="J3" s="405"/>
     </row>
     <row r="4" spans="2:13" ht="24" customHeight="1" thickBot="1">
       <c r="B4" s="161"/>
       <c r="C4" s="162" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="393" t="s">
+      <c r="D4" s="418" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="394"/>
+      <c r="E4" s="419"/>
       <c r="F4" s="163"/>
       <c r="G4" s="162" t="s">
         <v>186</v>
       </c>
-      <c r="H4" s="393" t="s">
+      <c r="H4" s="418" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="394"/>
+      <c r="I4" s="419"/>
       <c r="J4" s="164"/>
     </row>
     <row r="5" spans="2:13" ht="24" customHeight="1" thickBot="1">
-      <c r="B5" s="381"/>
-      <c r="C5" s="382"/>
-      <c r="D5" s="382"/>
-      <c r="E5" s="382"/>
-      <c r="F5" s="382"/>
-      <c r="G5" s="382"/>
-      <c r="H5" s="382"/>
-      <c r="I5" s="382"/>
-      <c r="J5" s="383"/>
+      <c r="B5" s="406"/>
+      <c r="C5" s="407"/>
+      <c r="D5" s="407"/>
+      <c r="E5" s="407"/>
+      <c r="F5" s="407"/>
+      <c r="G5" s="407"/>
+      <c r="H5" s="407"/>
+      <c r="I5" s="407"/>
+      <c r="J5" s="408"/>
     </row>
     <row r="6" spans="2:13" ht="45.75" customHeight="1">
       <c r="B6" s="165" t="s">
@@ -40413,50 +41497,50 @@
     </row>
     <row r="23" spans="2:10" ht="15.75" thickBot="1"/>
     <row r="24" spans="2:10" ht="16.5" thickBot="1">
-      <c r="B24" s="390" t="s">
+      <c r="B24" s="415" t="s">
         <v>264</v>
       </c>
-      <c r="C24" s="391"/>
-      <c r="D24" s="391"/>
-      <c r="E24" s="391"/>
-      <c r="F24" s="392"/>
+      <c r="C24" s="416"/>
+      <c r="D24" s="416"/>
+      <c r="E24" s="416"/>
+      <c r="F24" s="417"/>
     </row>
     <row r="25" spans="2:10" ht="30" customHeight="1">
-      <c r="B25" s="384" t="s">
+      <c r="B25" s="409" t="s">
         <v>265</v>
       </c>
-      <c r="C25" s="385"/>
-      <c r="D25" s="385"/>
-      <c r="E25" s="385"/>
-      <c r="F25" s="386"/>
+      <c r="C25" s="410"/>
+      <c r="D25" s="410"/>
+      <c r="E25" s="410"/>
+      <c r="F25" s="411"/>
     </row>
     <row r="26" spans="2:10" ht="30" customHeight="1">
-      <c r="B26" s="384"/>
-      <c r="C26" s="385"/>
-      <c r="D26" s="385"/>
-      <c r="E26" s="385"/>
-      <c r="F26" s="386"/>
+      <c r="B26" s="409"/>
+      <c r="C26" s="410"/>
+      <c r="D26" s="410"/>
+      <c r="E26" s="410"/>
+      <c r="F26" s="411"/>
     </row>
     <row r="27" spans="2:10" ht="30" customHeight="1">
-      <c r="B27" s="384"/>
-      <c r="C27" s="385"/>
-      <c r="D27" s="385"/>
-      <c r="E27" s="385"/>
-      <c r="F27" s="386"/>
+      <c r="B27" s="409"/>
+      <c r="C27" s="410"/>
+      <c r="D27" s="410"/>
+      <c r="E27" s="410"/>
+      <c r="F27" s="411"/>
     </row>
     <row r="28" spans="2:10" ht="30" customHeight="1">
-      <c r="B28" s="384"/>
-      <c r="C28" s="385"/>
-      <c r="D28" s="385"/>
-      <c r="E28" s="385"/>
-      <c r="F28" s="386"/>
+      <c r="B28" s="409"/>
+      <c r="C28" s="410"/>
+      <c r="D28" s="410"/>
+      <c r="E28" s="410"/>
+      <c r="F28" s="411"/>
     </row>
     <row r="29" spans="2:10" ht="30" customHeight="1" thickBot="1">
-      <c r="B29" s="387"/>
-      <c r="C29" s="388"/>
-      <c r="D29" s="388"/>
-      <c r="E29" s="388"/>
-      <c r="F29" s="389"/>
+      <c r="B29" s="412"/>
+      <c r="C29" s="413"/>
+      <c r="D29" s="413"/>
+      <c r="E29" s="413"/>
+      <c r="F29" s="414"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -40495,23 +41579,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="23.25" customHeight="1">
-      <c r="A1" s="378" t="s">
+      <c r="A1" s="403" t="s">
         <v>266</v>
       </c>
-      <c r="B1" s="378"/>
-      <c r="C1" s="378"/>
-      <c r="D1" s="378"/>
-      <c r="E1" s="378"/>
-      <c r="F1" s="378"/>
-      <c r="G1" s="378"/>
-      <c r="H1" s="378"/>
-      <c r="I1" s="378"/>
-      <c r="J1" s="378"/>
-      <c r="K1" s="378"/>
-      <c r="L1" s="378"/>
-      <c r="M1" s="378"/>
-      <c r="N1" s="378"/>
-      <c r="O1" s="378"/>
+      <c r="B1" s="403"/>
+      <c r="C1" s="403"/>
+      <c r="D1" s="403"/>
+      <c r="E1" s="403"/>
+      <c r="F1" s="403"/>
+      <c r="G1" s="403"/>
+      <c r="H1" s="403"/>
+      <c r="I1" s="403"/>
+      <c r="J1" s="403"/>
+      <c r="K1" s="403"/>
+      <c r="L1" s="403"/>
+      <c r="M1" s="403"/>
+      <c r="N1" s="403"/>
+      <c r="O1" s="403"/>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="160"/>
@@ -40547,10 +41631,10 @@
       <c r="J3" s="185" t="s">
         <v>268</v>
       </c>
-      <c r="K3" s="404" t="s">
+      <c r="K3" s="429" t="s">
         <v>15</v>
       </c>
-      <c r="L3" s="404"/>
+      <c r="L3" s="429"/>
       <c r="M3" s="160"/>
       <c r="N3" s="160"/>
       <c r="O3" s="160"/>
@@ -40950,78 +42034,78 @@
     </row>
     <row r="26" spans="2:9" ht="15.75" thickBot="1"/>
     <row r="27" spans="2:9" ht="20.25" customHeight="1" thickBot="1">
-      <c r="B27" s="395" t="s">
+      <c r="B27" s="420" t="s">
         <v>275</v>
       </c>
-      <c r="C27" s="396"/>
-      <c r="D27" s="396"/>
-      <c r="E27" s="396"/>
-      <c r="F27" s="396"/>
-      <c r="G27" s="396"/>
-      <c r="H27" s="396"/>
-      <c r="I27" s="397"/>
+      <c r="C27" s="421"/>
+      <c r="D27" s="421"/>
+      <c r="E27" s="421"/>
+      <c r="F27" s="421"/>
+      <c r="G27" s="421"/>
+      <c r="H27" s="421"/>
+      <c r="I27" s="422"/>
     </row>
     <row r="28" spans="2:9" ht="20.25" customHeight="1">
-      <c r="B28" s="398" t="s">
+      <c r="B28" s="423" t="s">
         <v>276</v>
       </c>
-      <c r="C28" s="399"/>
-      <c r="D28" s="399"/>
-      <c r="E28" s="399"/>
-      <c r="F28" s="399"/>
-      <c r="G28" s="399"/>
-      <c r="H28" s="399"/>
-      <c r="I28" s="400"/>
+      <c r="C28" s="424"/>
+      <c r="D28" s="424"/>
+      <c r="E28" s="424"/>
+      <c r="F28" s="424"/>
+      <c r="G28" s="424"/>
+      <c r="H28" s="424"/>
+      <c r="I28" s="425"/>
     </row>
     <row r="29" spans="2:9" ht="20.25" customHeight="1">
-      <c r="B29" s="398"/>
-      <c r="C29" s="399"/>
-      <c r="D29" s="399"/>
-      <c r="E29" s="399"/>
-      <c r="F29" s="399"/>
-      <c r="G29" s="399"/>
-      <c r="H29" s="399"/>
-      <c r="I29" s="400"/>
+      <c r="B29" s="423"/>
+      <c r="C29" s="424"/>
+      <c r="D29" s="424"/>
+      <c r="E29" s="424"/>
+      <c r="F29" s="424"/>
+      <c r="G29" s="424"/>
+      <c r="H29" s="424"/>
+      <c r="I29" s="425"/>
     </row>
     <row r="30" spans="2:9" ht="20.25" customHeight="1">
-      <c r="B30" s="398"/>
-      <c r="C30" s="399"/>
-      <c r="D30" s="399"/>
-      <c r="E30" s="399"/>
-      <c r="F30" s="399"/>
-      <c r="G30" s="399"/>
-      <c r="H30" s="399"/>
-      <c r="I30" s="400"/>
+      <c r="B30" s="423"/>
+      <c r="C30" s="424"/>
+      <c r="D30" s="424"/>
+      <c r="E30" s="424"/>
+      <c r="F30" s="424"/>
+      <c r="G30" s="424"/>
+      <c r="H30" s="424"/>
+      <c r="I30" s="425"/>
     </row>
     <row r="31" spans="2:9" ht="20.25" customHeight="1">
-      <c r="B31" s="398"/>
-      <c r="C31" s="399"/>
-      <c r="D31" s="399"/>
-      <c r="E31" s="399"/>
-      <c r="F31" s="399"/>
-      <c r="G31" s="399"/>
-      <c r="H31" s="399"/>
-      <c r="I31" s="400"/>
+      <c r="B31" s="423"/>
+      <c r="C31" s="424"/>
+      <c r="D31" s="424"/>
+      <c r="E31" s="424"/>
+      <c r="F31" s="424"/>
+      <c r="G31" s="424"/>
+      <c r="H31" s="424"/>
+      <c r="I31" s="425"/>
     </row>
     <row r="32" spans="2:9" ht="20.25" customHeight="1">
-      <c r="B32" s="398"/>
-      <c r="C32" s="399"/>
-      <c r="D32" s="399"/>
-      <c r="E32" s="399"/>
-      <c r="F32" s="399"/>
-      <c r="G32" s="399"/>
-      <c r="H32" s="399"/>
-      <c r="I32" s="400"/>
+      <c r="B32" s="423"/>
+      <c r="C32" s="424"/>
+      <c r="D32" s="424"/>
+      <c r="E32" s="424"/>
+      <c r="F32" s="424"/>
+      <c r="G32" s="424"/>
+      <c r="H32" s="424"/>
+      <c r="I32" s="425"/>
     </row>
     <row r="33" spans="2:9" ht="66" customHeight="1" thickBot="1">
-      <c r="B33" s="401"/>
-      <c r="C33" s="402"/>
-      <c r="D33" s="402"/>
-      <c r="E33" s="402"/>
-      <c r="F33" s="402"/>
-      <c r="G33" s="402"/>
-      <c r="H33" s="402"/>
-      <c r="I33" s="403"/>
+      <c r="B33" s="426"/>
+      <c r="C33" s="427"/>
+      <c r="D33" s="427"/>
+      <c r="E33" s="427"/>
+      <c r="F33" s="427"/>
+      <c r="G33" s="427"/>
+      <c r="H33" s="427"/>
+      <c r="I33" s="428"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -41067,28 +42151,28 @@
       <c r="I1"/>
     </row>
     <row r="2" spans="2:9" ht="30" customHeight="1" thickBot="1">
-      <c r="B2" s="408" t="s">
+      <c r="B2" s="433" t="s">
         <v>333</v>
       </c>
-      <c r="C2" s="409"/>
-      <c r="D2" s="409"/>
-      <c r="E2" s="409"/>
-      <c r="F2" s="409"/>
-      <c r="G2" s="409"/>
-      <c r="H2" s="409"/>
-      <c r="I2" s="410"/>
+      <c r="C2" s="434"/>
+      <c r="D2" s="434"/>
+      <c r="E2" s="434"/>
+      <c r="F2" s="434"/>
+      <c r="G2" s="434"/>
+      <c r="H2" s="434"/>
+      <c r="I2" s="435"/>
     </row>
     <row r="3" spans="2:9">
-      <c r="B3" s="411" t="s">
+      <c r="B3" s="436" t="s">
         <v>334</v>
       </c>
-      <c r="C3" s="412"/>
-      <c r="D3" s="412"/>
-      <c r="E3" s="412"/>
-      <c r="F3" s="412"/>
-      <c r="G3" s="412"/>
-      <c r="H3" s="412"/>
-      <c r="I3" s="413"/>
+      <c r="C3" s="437"/>
+      <c r="D3" s="437"/>
+      <c r="E3" s="437"/>
+      <c r="F3" s="437"/>
+      <c r="G3" s="437"/>
+      <c r="H3" s="437"/>
+      <c r="I3" s="438"/>
     </row>
     <row r="4" spans="2:9" ht="15.75" thickBot="1">
       <c r="B4" s="229"/>
@@ -41390,17 +42474,17 @@
       <c r="I16" s="203"/>
     </row>
     <row r="17" spans="2:9">
-      <c r="B17" s="414" t="s">
+      <c r="B17" s="439" t="s">
         <v>342</v>
       </c>
-      <c r="C17" s="415"/>
-      <c r="D17" s="416"/>
-      <c r="F17" s="417" t="s">
+      <c r="C17" s="440"/>
+      <c r="D17" s="441"/>
+      <c r="F17" s="442" t="s">
         <v>358</v>
       </c>
-      <c r="G17" s="418"/>
-      <c r="H17" s="418"/>
-      <c r="I17" s="419"/>
+      <c r="G17" s="443"/>
+      <c r="H17" s="443"/>
+      <c r="I17" s="444"/>
     </row>
     <row r="18" spans="2:9">
       <c r="B18" s="204" t="s">
@@ -41531,28 +42615,28 @@
       <c r="I24" s="230"/>
     </row>
     <row r="25" spans="2:9" ht="16.5" thickBot="1">
-      <c r="B25" s="420" t="s">
+      <c r="B25" s="445" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="421"/>
-      <c r="D25" s="421"/>
-      <c r="E25" s="421"/>
-      <c r="F25" s="421"/>
-      <c r="G25" s="421"/>
-      <c r="H25" s="421"/>
-      <c r="I25" s="422"/>
+      <c r="C25" s="446"/>
+      <c r="D25" s="446"/>
+      <c r="E25" s="446"/>
+      <c r="F25" s="446"/>
+      <c r="G25" s="446"/>
+      <c r="H25" s="446"/>
+      <c r="I25" s="447"/>
     </row>
     <row r="26" spans="2:9" ht="151.5" customHeight="1" thickBot="1">
-      <c r="B26" s="405" t="s">
+      <c r="B26" s="430" t="s">
         <v>369</v>
       </c>
-      <c r="C26" s="406"/>
-      <c r="D26" s="406"/>
-      <c r="E26" s="406"/>
-      <c r="F26" s="406"/>
-      <c r="G26" s="406"/>
-      <c r="H26" s="406"/>
-      <c r="I26" s="407"/>
+      <c r="C26" s="431"/>
+      <c r="D26" s="431"/>
+      <c r="E26" s="431"/>
+      <c r="F26" s="431"/>
+      <c r="G26" s="431"/>
+      <c r="H26" s="431"/>
+      <c r="I26" s="432"/>
     </row>
   </sheetData>
   <mergeCells count="6">

--- a/pm_dashboards/Project Management Charts.xlsx
+++ b/pm_dashboards/Project Management Charts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\excel_tutorial\pm_dashboards\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C094C46-A645-41FE-A434-52D1B8C9098F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB660496-FAA7-40B6-96FA-ED8036CA90C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="513" firstSheet="7" activeTab="10" xr2:uid="{6ACA091F-59E3-41E7-B925-EA720AB063CF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="513" firstSheet="7" activeTab="11" xr2:uid="{6ACA091F-59E3-41E7-B925-EA720AB063CF}"/>
   </bookViews>
   <sheets>
     <sheet name="PMP" sheetId="11" r:id="rId1"/>
@@ -24,6 +24,7 @@
     <sheet name="Heatmap" sheetId="12" r:id="rId9"/>
     <sheet name="Nominal Group Technique" sheetId="15" r:id="rId10"/>
     <sheet name="Root Cause Analysis" sheetId="16" r:id="rId11"/>
+    <sheet name="Sheet1" sheetId="17" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -4554,7 +4555,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="500">
+  <cellXfs count="499">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
@@ -5308,35 +5309,111 @@
       <alignment horizontal="left" indent="16"/>
     </xf>
     <xf numFmtId="0" fontId="55" fillId="18" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="55" fillId="51" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="74" fillId="51" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="26" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="51" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="78" fillId="54" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="55" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="25" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="72" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="105" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="54" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="56" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="93" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="18" borderId="152" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="18" borderId="153" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="153" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="154" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="78" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="84" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="104" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="105" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="57" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="57" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="32" fillId="57" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="48" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="48" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="48" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="51" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="62" fillId="18" borderId="104" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="51" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="105" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="18" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="93" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="18" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="25" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="76" fillId="25" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="76" fillId="25" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="135" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
@@ -5362,18 +5439,15 @@
     <xf numFmtId="0" fontId="38" fillId="21" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="18" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="67" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="18" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="55" fillId="2" borderId="148" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="71" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="71" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="71" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="72" fillId="18" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="72" fillId="18" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="72" fillId="18" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="55" fillId="18" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -5392,13 +5466,40 @@
     <xf numFmtId="0" fontId="73" fillId="18" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="67" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="70" fillId="18" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="2" borderId="148" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="70" fillId="18" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="71" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="71" fillId="2" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="72" fillId="18" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="72" fillId="18" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="72" fillId="18" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5452,29 +5553,46 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="57" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="18" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="28" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
@@ -5530,53 +5648,6 @@
     <xf numFmtId="0" fontId="5" fillId="28" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="28" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="28" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="28" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="28" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="18" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="57" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="57" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="56" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="55" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="58" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="66" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="45" fillId="18" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="18" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="45" fillId="18" borderId="104" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -5585,6 +5656,44 @@
     </xf>
     <xf numFmtId="0" fontId="45" fillId="18" borderId="93" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="29" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="29" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="29" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="36" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="27" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="27" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="18" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="18" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="52" fillId="22" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
@@ -5627,38 +5736,6 @@
     </xf>
     <xf numFmtId="0" fontId="53" fillId="24" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="29" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="29" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="29" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="36" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="27" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="27" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5783,77 +5860,9 @@
     <xf numFmtId="0" fontId="63" fillId="3" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="61" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="131" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="42" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="26" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="54" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="55" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="25" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="72" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="105" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="54" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="56" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="93" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="79" fillId="18" borderId="152" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="79" fillId="18" borderId="153" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="153" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="154" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="78" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="84" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="63" fillId="57" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="63" fillId="57" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="63" fillId="57" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="63" fillId="57" borderId="71" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="71" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="84" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -5863,53 +5872,44 @@
     <xf numFmtId="0" fontId="0" fillId="18" borderId="73" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="57" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="76" fillId="25" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="25" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="25" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="51" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="48" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="71" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="51" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="51" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="57" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="55" fillId="51" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="55" fillId="51" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="48" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="55" fillId="18" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="57" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="48" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="18" borderId="104" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="105" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="93" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="104" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="105" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="55" fillId="18" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -6412,7 +6412,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{7CCA2253-A3B2-4CD6-889B-F3C2275BD927}" type="CELLRANGE">
+                    <a:fld id="{DAE97482-4CE3-49D7-B49A-09129CF7B058}" type="CELLRANGE">
                       <a:rPr lang="en-US"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6445,7 +6445,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{1D69DF29-8850-41F7-BFE3-FEBBE15B00DC}" type="CELLRANGE">
+                    <a:fld id="{F27C8748-244D-4B4B-86D6-4E1099231FAA}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6479,7 +6479,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D03B2395-2CC8-444C-B017-FA4B03051F52}" type="CELLRANGE">
+                    <a:fld id="{DFF9D3B7-A63B-4254-A0B0-32C7B6CBC629}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6513,7 +6513,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{18CFE0AB-86B4-4FF8-80EF-A9B1A9966F75}" type="CELLRANGE">
+                    <a:fld id="{0EC2F968-0EA4-49C8-A433-430E7CADB102}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6547,7 +6547,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{58C3C96C-93DE-440A-83C8-8E8EF11FE420}" type="CELLRANGE">
+                    <a:fld id="{0B06BC33-9063-43F0-A8D0-99B37F13AA90}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6581,7 +6581,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{2A844BC1-E554-4E97-A639-5A5B9F0D4073}" type="CELLRANGE">
+                    <a:fld id="{7A818CA5-BC58-4DE5-9667-B25EEA5AADC4}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6615,7 +6615,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{D10D568F-EB66-4B8B-89A0-00A09703C13D}" type="CELLRANGE">
+                    <a:fld id="{E34D62D3-784D-4348-A9D9-A6408A9A0DFC}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6649,7 +6649,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{11415630-45C5-40D7-8F44-C213C5BC5A49}" type="CELLRANGE">
+                    <a:fld id="{0E080FBA-FFD1-4A78-9667-5F8838F02890}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6683,7 +6683,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{83CCCC2B-B32E-4E29-89F0-DC432359D591}" type="CELLRANGE">
+                    <a:fld id="{9577931E-7CF0-446C-BE6D-EB0EE08783F8}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6717,7 +6717,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{0E8A72E7-6E16-40CE-A80C-1D0D864A5927}" type="CELLRANGE">
+                    <a:fld id="{E01E8F9C-B87D-4C36-AE10-744901D872D3}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6751,7 +6751,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{AE66CDB0-33AD-4DA5-9461-C6BB44439D1C}" type="CELLRANGE">
+                    <a:fld id="{89E1B20F-B922-4167-9F3E-BD94893932B0}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6785,7 +6785,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{6C4AA860-CCA2-4EA6-8A9A-CC39C74B115F}" type="CELLRANGE">
+                    <a:fld id="{EF313984-83F2-4509-8C19-8F32C8D7C8BB}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6819,7 +6819,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{B9FCBC71-B83E-4356-9C0E-9FDC1E783A9A}" type="CELLRANGE">
+                    <a:fld id="{7DE1B8DC-976E-4571-A006-3C018E2E34D0}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -6853,7 +6853,7 @@
                   <a:bodyPr/>
                   <a:lstStyle/>
                   <a:p>
-                    <a:fld id="{44A84384-9213-4627-9E54-48705A43DD11}" type="CELLRANGE">
+                    <a:fld id="{F826E7BF-E2EA-4542-9982-3D22B6226C29}" type="CELLRANGE">
                       <a:rPr lang="en-IN"/>
                       <a:pPr/>
                       <a:t>[CELLRANGE]</a:t>
@@ -10038,17 +10038,17 @@
   <sheetData>
     <row r="1" spans="1:7" ht="30" customHeight="1">
       <c r="A1" s="233"/>
-      <c r="B1" s="295" t="s">
+      <c r="B1" s="325" t="s">
         <v>332</v>
       </c>
-      <c r="C1" s="295"/>
-      <c r="D1" s="295"/>
-      <c r="E1" s="295"/>
-      <c r="F1" s="295"/>
-      <c r="G1" s="296"/>
+      <c r="C1" s="325"/>
+      <c r="D1" s="325"/>
+      <c r="E1" s="325"/>
+      <c r="F1" s="325"/>
+      <c r="G1" s="326"/>
     </row>
     <row r="2" spans="1:7" ht="30" customHeight="1">
-      <c r="A2" s="293" t="s">
+      <c r="A2" s="323" t="s">
         <v>331</v>
       </c>
       <c r="B2" s="235" t="s">
@@ -10071,7 +10071,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="28.5">
-      <c r="A3" s="293"/>
+      <c r="A3" s="323"/>
       <c r="B3" s="240" t="s">
         <v>292</v>
       </c>
@@ -10092,7 +10092,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="42.75">
-      <c r="A4" s="293"/>
+      <c r="A4" s="323"/>
       <c r="B4" s="240" t="s">
         <v>298</v>
       </c>
@@ -10107,7 +10107,7 @@
       <c r="G4" s="245"/>
     </row>
     <row r="5" spans="1:7" ht="71.25">
-      <c r="A5" s="293"/>
+      <c r="A5" s="323"/>
       <c r="B5" s="240" t="s">
         <v>301</v>
       </c>
@@ -10122,7 +10122,7 @@
       <c r="G5" s="243"/>
     </row>
     <row r="6" spans="1:7" ht="42.75">
-      <c r="A6" s="293"/>
+      <c r="A6" s="323"/>
       <c r="B6" s="240" t="s">
         <v>304</v>
       </c>
@@ -10137,7 +10137,7 @@
       <c r="G6" s="245"/>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="293"/>
+      <c r="A7" s="323"/>
       <c r="B7" s="240" t="s">
         <v>307</v>
       </c>
@@ -10154,7 +10154,7 @@
       <c r="G7" s="243"/>
     </row>
     <row r="8" spans="1:7" ht="42.75">
-      <c r="A8" s="293"/>
+      <c r="A8" s="323"/>
       <c r="B8" s="240" t="s">
         <v>311</v>
       </c>
@@ -10169,7 +10169,7 @@
       <c r="G8" s="245"/>
     </row>
     <row r="9" spans="1:7" ht="28.5">
-      <c r="A9" s="293"/>
+      <c r="A9" s="323"/>
       <c r="B9" s="240" t="s">
         <v>314</v>
       </c>
@@ -10186,7 +10186,7 @@
       <c r="G9" s="243"/>
     </row>
     <row r="10" spans="1:7" ht="85.5">
-      <c r="A10" s="293"/>
+      <c r="A10" s="323"/>
       <c r="B10" s="240" t="s">
         <v>318</v>
       </c>
@@ -10203,7 +10203,7 @@
       <c r="G10" s="245"/>
     </row>
     <row r="11" spans="1:7" ht="28.5">
-      <c r="A11" s="293"/>
+      <c r="A11" s="323"/>
       <c r="B11" s="240" t="s">
         <v>322</v>
       </c>
@@ -10220,7 +10220,7 @@
       <c r="G11" s="243"/>
     </row>
     <row r="12" spans="1:7" ht="17.25" thickBot="1">
-      <c r="A12" s="294"/>
+      <c r="A12" s="324"/>
       <c r="B12" s="241" t="s">
         <v>326</v>
       </c>
@@ -10260,33 +10260,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="26.25">
-      <c r="A1" s="284" t="s">
+      <c r="A1" s="493" t="s">
         <v>406</v>
       </c>
-      <c r="B1" s="284"/>
-      <c r="C1" s="284"/>
-      <c r="D1" s="284"/>
-      <c r="E1" s="284"/>
-      <c r="F1" s="284"/>
-      <c r="G1" s="284"/>
-      <c r="H1" s="284"/>
-      <c r="I1" s="284"/>
-      <c r="J1" s="284"/>
-      <c r="K1" s="284"/>
+      <c r="B1" s="493"/>
+      <c r="C1" s="493"/>
+      <c r="D1" s="493"/>
+      <c r="E1" s="493"/>
+      <c r="F1" s="493"/>
+      <c r="G1" s="493"/>
+      <c r="H1" s="493"/>
+      <c r="I1" s="493"/>
+      <c r="J1" s="493"/>
+      <c r="K1" s="493"/>
       <c r="L1" s="268"/>
     </row>
     <row r="2" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A2" s="283"/>
-      <c r="B2" s="283"/>
-      <c r="C2" s="283"/>
-      <c r="D2" s="283"/>
-      <c r="E2" s="283"/>
-      <c r="F2" s="283"/>
-      <c r="G2" s="283"/>
-      <c r="H2" s="283"/>
-      <c r="I2" s="283"/>
-      <c r="J2" s="283"/>
-      <c r="K2" s="283"/>
+      <c r="A2" s="487"/>
+      <c r="B2" s="487"/>
+      <c r="C2" s="487"/>
+      <c r="D2" s="487"/>
+      <c r="E2" s="487"/>
+      <c r="F2" s="487"/>
+      <c r="G2" s="487"/>
+      <c r="H2" s="487"/>
+      <c r="I2" s="487"/>
+      <c r="J2" s="487"/>
+      <c r="K2" s="487"/>
       <c r="L2" s="268"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" thickBot="1">
@@ -10302,25 +10302,25 @@
       </c>
       <c r="E3" s="269"/>
       <c r="F3" s="269"/>
-      <c r="G3" s="283"/>
-      <c r="H3" s="283"/>
-      <c r="I3" s="283"/>
-      <c r="J3" s="283"/>
-      <c r="K3" s="283"/>
+      <c r="G3" s="487"/>
+      <c r="H3" s="487"/>
+      <c r="I3" s="487"/>
+      <c r="J3" s="487"/>
+      <c r="K3" s="487"/>
       <c r="L3" s="268"/>
     </row>
     <row r="4" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A4" s="283"/>
-      <c r="B4" s="283"/>
-      <c r="C4" s="283"/>
-      <c r="D4" s="283"/>
-      <c r="E4" s="283"/>
-      <c r="F4" s="283"/>
-      <c r="G4" s="283"/>
-      <c r="H4" s="283"/>
-      <c r="I4" s="283"/>
-      <c r="J4" s="283"/>
-      <c r="K4" s="283"/>
+      <c r="A4" s="487"/>
+      <c r="B4" s="487"/>
+      <c r="C4" s="487"/>
+      <c r="D4" s="487"/>
+      <c r="E4" s="487"/>
+      <c r="F4" s="487"/>
+      <c r="G4" s="487"/>
+      <c r="H4" s="487"/>
+      <c r="I4" s="487"/>
+      <c r="J4" s="487"/>
+      <c r="K4" s="487"/>
       <c r="L4" s="268"/>
     </row>
     <row r="5" spans="1:12" ht="15.75" thickBot="1">
@@ -10328,29 +10328,29 @@
       <c r="B5" s="273" t="s">
         <v>387</v>
       </c>
-      <c r="C5" s="288"/>
-      <c r="D5" s="289"/>
-      <c r="E5" s="285"/>
-      <c r="F5" s="283"/>
-      <c r="G5" s="283"/>
-      <c r="H5" s="283"/>
-      <c r="I5" s="283"/>
-      <c r="J5" s="283"/>
-      <c r="K5" s="283"/>
+      <c r="C5" s="497"/>
+      <c r="D5" s="498"/>
+      <c r="E5" s="494"/>
+      <c r="F5" s="487"/>
+      <c r="G5" s="487"/>
+      <c r="H5" s="487"/>
+      <c r="I5" s="487"/>
+      <c r="J5" s="487"/>
+      <c r="K5" s="487"/>
       <c r="L5" s="268"/>
     </row>
     <row r="6" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A6" s="283"/>
-      <c r="B6" s="283"/>
-      <c r="C6" s="283"/>
-      <c r="D6" s="283"/>
-      <c r="E6" s="283"/>
-      <c r="F6" s="283"/>
-      <c r="G6" s="283"/>
-      <c r="H6" s="283"/>
-      <c r="I6" s="283"/>
-      <c r="J6" s="283"/>
-      <c r="K6" s="283"/>
+      <c r="A6" s="487"/>
+      <c r="B6" s="487"/>
+      <c r="C6" s="487"/>
+      <c r="D6" s="487"/>
+      <c r="E6" s="487"/>
+      <c r="F6" s="487"/>
+      <c r="G6" s="487"/>
+      <c r="H6" s="487"/>
+      <c r="I6" s="487"/>
+      <c r="J6" s="487"/>
+      <c r="K6" s="487"/>
       <c r="L6" s="268"/>
     </row>
     <row r="7" spans="1:12" ht="15.75" thickBot="1">
@@ -10359,28 +10359,28 @@
         <v>388</v>
       </c>
       <c r="C7" s="271"/>
-      <c r="D7" s="286"/>
-      <c r="E7" s="287"/>
-      <c r="F7" s="287"/>
-      <c r="G7" s="287"/>
-      <c r="H7" s="287"/>
-      <c r="I7" s="287"/>
-      <c r="J7" s="287"/>
-      <c r="K7" s="287"/>
+      <c r="D7" s="495"/>
+      <c r="E7" s="496"/>
+      <c r="F7" s="496"/>
+      <c r="G7" s="496"/>
+      <c r="H7" s="496"/>
+      <c r="I7" s="496"/>
+      <c r="J7" s="496"/>
+      <c r="K7" s="496"/>
       <c r="L7" s="268"/>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="283"/>
-      <c r="B8" s="283"/>
-      <c r="C8" s="283"/>
-      <c r="D8" s="283"/>
-      <c r="E8" s="283"/>
-      <c r="F8" s="283"/>
-      <c r="G8" s="283"/>
-      <c r="H8" s="283"/>
-      <c r="I8" s="283"/>
-      <c r="J8" s="283"/>
-      <c r="K8" s="283"/>
+      <c r="A8" s="487"/>
+      <c r="B8" s="487"/>
+      <c r="C8" s="487"/>
+      <c r="D8" s="487"/>
+      <c r="E8" s="487"/>
+      <c r="F8" s="487"/>
+      <c r="G8" s="487"/>
+      <c r="H8" s="487"/>
+      <c r="I8" s="487"/>
+      <c r="J8" s="487"/>
+      <c r="K8" s="487"/>
       <c r="L8" s="268"/>
     </row>
     <row r="9" spans="1:12" ht="15.75" thickBot="1">
@@ -10400,15 +10400,15 @@
     <row r="10" spans="1:12" ht="15.75" thickBot="1">
       <c r="A10" s="268"/>
       <c r="B10" s="268"/>
-      <c r="C10" s="290" t="s">
+      <c r="C10" s="484" t="s">
         <v>390</v>
       </c>
-      <c r="D10" s="291"/>
-      <c r="E10" s="291"/>
-      <c r="F10" s="291"/>
-      <c r="G10" s="291"/>
-      <c r="H10" s="291"/>
-      <c r="I10" s="292"/>
+      <c r="D10" s="485"/>
+      <c r="E10" s="485"/>
+      <c r="F10" s="485"/>
+      <c r="G10" s="485"/>
+      <c r="H10" s="485"/>
+      <c r="I10" s="486"/>
       <c r="J10" s="268"/>
       <c r="K10" s="268"/>
       <c r="L10" s="268"/>
@@ -10751,108 +10751,96 @@
     </row>
     <row r="25" spans="1:12" ht="15.75" thickBot="1"/>
     <row r="26" spans="1:12" ht="18.75">
-      <c r="B26" s="472" t="s">
+      <c r="B26" s="488" t="s">
         <v>417</v>
       </c>
-      <c r="C26" s="473"/>
-      <c r="D26" s="473"/>
-      <c r="E26" s="473"/>
-      <c r="F26" s="473"/>
-      <c r="G26" s="473"/>
-      <c r="H26" s="473"/>
-      <c r="I26" s="473"/>
-      <c r="J26" s="473"/>
-      <c r="K26" s="473"/>
-      <c r="L26" s="474"/>
+      <c r="C26" s="489"/>
+      <c r="D26" s="489"/>
+      <c r="E26" s="489"/>
+      <c r="F26" s="489"/>
+      <c r="G26" s="489"/>
+      <c r="H26" s="489"/>
+      <c r="I26" s="489"/>
+      <c r="J26" s="489"/>
+      <c r="K26" s="489"/>
+      <c r="L26" s="490"/>
     </row>
     <row r="27" spans="1:12">
       <c r="B27" s="229"/>
-      <c r="C27" s="457"/>
-      <c r="D27" s="457"/>
-      <c r="E27" s="457"/>
-      <c r="F27" s="457"/>
-      <c r="G27" s="457"/>
-      <c r="H27" s="457"/>
-      <c r="I27" s="457"/>
-      <c r="J27" s="457"/>
-      <c r="K27" s="457"/>
       <c r="L27" s="230"/>
     </row>
     <row r="28" spans="1:12" ht="15.75">
-      <c r="B28" s="475" t="s">
+      <c r="B28" s="478" t="s">
         <v>418</v>
       </c>
-      <c r="C28" s="469"/>
-      <c r="D28" s="469"/>
-      <c r="E28" s="469"/>
-      <c r="F28" s="469"/>
-      <c r="G28" s="469"/>
-      <c r="H28" s="469"/>
-      <c r="I28" s="469"/>
-      <c r="J28" s="469"/>
-      <c r="K28" s="469"/>
-      <c r="L28" s="476"/>
+      <c r="C28" s="479"/>
+      <c r="D28" s="479"/>
+      <c r="E28" s="479"/>
+      <c r="F28" s="479"/>
+      <c r="G28" s="479"/>
+      <c r="H28" s="479"/>
+      <c r="I28" s="479"/>
+      <c r="J28" s="479"/>
+      <c r="K28" s="479"/>
+      <c r="L28" s="480"/>
     </row>
     <row r="29" spans="1:12">
-      <c r="B29" s="477" t="s">
+      <c r="B29" s="491" t="s">
         <v>419</v>
       </c>
-      <c r="C29" s="470"/>
-      <c r="D29" s="470"/>
-      <c r="E29" s="470"/>
-      <c r="F29" s="470"/>
-      <c r="G29" s="470"/>
-      <c r="H29" s="470"/>
-      <c r="I29" s="470"/>
-      <c r="J29" s="470"/>
-      <c r="K29" s="470"/>
-      <c r="L29" s="478"/>
+      <c r="C29" s="307"/>
+      <c r="D29" s="307"/>
+      <c r="E29" s="307"/>
+      <c r="F29" s="307"/>
+      <c r="G29" s="307"/>
+      <c r="H29" s="307"/>
+      <c r="I29" s="307"/>
+      <c r="J29" s="307"/>
+      <c r="K29" s="307"/>
+      <c r="L29" s="492"/>
     </row>
     <row r="30" spans="1:12">
       <c r="B30" s="229"/>
-      <c r="C30" s="457"/>
-      <c r="D30" s="457"/>
-      <c r="E30" s="457"/>
-      <c r="F30" s="457"/>
-      <c r="G30" s="457"/>
-      <c r="H30" s="457"/>
-      <c r="I30" s="457"/>
-      <c r="J30" s="457"/>
-      <c r="K30" s="457"/>
       <c r="L30" s="230"/>
     </row>
     <row r="31" spans="1:12" ht="15.75">
-      <c r="B31" s="475" t="s">
+      <c r="B31" s="478" t="s">
         <v>420</v>
       </c>
-      <c r="C31" s="469"/>
-      <c r="D31" s="469"/>
-      <c r="E31" s="469"/>
-      <c r="F31" s="469"/>
-      <c r="G31" s="469"/>
-      <c r="H31" s="469"/>
-      <c r="I31" s="469"/>
-      <c r="J31" s="469"/>
-      <c r="K31" s="469"/>
-      <c r="L31" s="476"/>
+      <c r="C31" s="479"/>
+      <c r="D31" s="479"/>
+      <c r="E31" s="479"/>
+      <c r="F31" s="479"/>
+      <c r="G31" s="479"/>
+      <c r="H31" s="479"/>
+      <c r="I31" s="479"/>
+      <c r="J31" s="479"/>
+      <c r="K31" s="479"/>
+      <c r="L31" s="480"/>
     </row>
     <row r="32" spans="1:12" ht="84.75" customHeight="1" thickBot="1">
-      <c r="B32" s="479" t="s">
+      <c r="B32" s="481" t="s">
         <v>421</v>
       </c>
-      <c r="C32" s="480"/>
-      <c r="D32" s="480"/>
-      <c r="E32" s="480"/>
-      <c r="F32" s="480"/>
-      <c r="G32" s="480"/>
-      <c r="H32" s="480"/>
-      <c r="I32" s="480"/>
-      <c r="J32" s="480"/>
-      <c r="K32" s="480"/>
-      <c r="L32" s="481"/>
+      <c r="C32" s="482"/>
+      <c r="D32" s="482"/>
+      <c r="E32" s="482"/>
+      <c r="F32" s="482"/>
+      <c r="G32" s="482"/>
+      <c r="H32" s="482"/>
+      <c r="I32" s="482"/>
+      <c r="J32" s="482"/>
+      <c r="K32" s="482"/>
+      <c r="L32" s="483"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="G3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="E5:K5"/>
+    <mergeCell ref="A6:K6"/>
+    <mergeCell ref="C5:D5"/>
     <mergeCell ref="B31:L31"/>
     <mergeCell ref="B32:L32"/>
     <mergeCell ref="C10:I10"/>
@@ -10861,13 +10849,7 @@
     <mergeCell ref="B28:L28"/>
     <mergeCell ref="B29:L29"/>
     <mergeCell ref="A8:K8"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="G3:K3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="E5:K5"/>
-    <mergeCell ref="A6:K6"/>
     <mergeCell ref="D7:K7"/>
-    <mergeCell ref="C5:D5"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="C21:J21">
@@ -10917,38 +10899,38 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="39.75" customHeight="1">
-      <c r="A1" s="448" t="s">
+      <c r="A1" s="315" t="s">
         <v>407</v>
       </c>
-      <c r="B1" s="448"/>
-      <c r="C1" s="448"/>
-      <c r="D1" s="448"/>
-      <c r="E1" s="448"/>
-      <c r="F1" s="448"/>
-      <c r="G1" s="448"/>
-      <c r="H1" s="448"/>
-      <c r="I1" s="448"/>
-      <c r="J1" s="448"/>
-      <c r="K1" s="448"/>
+      <c r="B1" s="315"/>
+      <c r="C1" s="315"/>
+      <c r="D1" s="315"/>
+      <c r="E1" s="315"/>
+      <c r="F1" s="315"/>
+      <c r="G1" s="315"/>
+      <c r="H1" s="315"/>
+      <c r="I1" s="315"/>
+      <c r="J1" s="315"/>
+      <c r="K1" s="315"/>
     </row>
     <row r="2" spans="1:11" ht="21.75" customHeight="1">
       <c r="A2" s="160"/>
       <c r="B2" s="160"/>
       <c r="C2" s="160"/>
-      <c r="D2" s="450" t="s">
+      <c r="D2" s="284" t="s">
         <v>408</v>
       </c>
-      <c r="E2" s="449" t="s">
+      <c r="E2" s="316" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="449"/>
-      <c r="G2" s="450" t="s">
+      <c r="F2" s="316"/>
+      <c r="G2" s="284" t="s">
         <v>409</v>
       </c>
-      <c r="H2" s="449" t="s">
+      <c r="H2" s="316" t="s">
         <v>445</v>
       </c>
-      <c r="I2" s="449"/>
+      <c r="I2" s="316"/>
       <c r="J2" s="160"/>
       <c r="K2" s="160"/>
     </row>
@@ -10967,343 +10949,348 @@
     </row>
     <row r="4" spans="1:11" ht="15.75" thickBot="1"/>
     <row r="5" spans="1:11" ht="24" customHeight="1" thickBot="1">
-      <c r="C5" s="452" t="s">
+      <c r="C5" s="285" t="s">
         <v>410</v>
       </c>
-      <c r="E5" s="453" t="s">
+      <c r="E5" s="286" t="s">
         <v>411</v>
       </c>
-      <c r="G5" s="454" t="s">
+      <c r="G5" s="287" t="s">
         <v>412</v>
       </c>
-      <c r="I5" s="455" t="s">
+      <c r="I5" s="288" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="24.75" customHeight="1">
-      <c r="C6" s="463" t="s">
+      <c r="C6" s="295" t="s">
         <v>432</v>
       </c>
-      <c r="D6" s="467">
+      <c r="D6" s="299">
         <f>IF(E6="","",1)</f>
         <v>1</v>
       </c>
-      <c r="E6" s="463" t="s">
+      <c r="E6" s="295" t="s">
         <v>434</v>
       </c>
-      <c r="G6" s="463" t="s">
+      <c r="G6" s="295" t="s">
         <v>439</v>
       </c>
-      <c r="I6" s="463" t="s">
+      <c r="I6" s="295" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="24.75" customHeight="1">
-      <c r="C7" s="464" t="s">
+      <c r="C7" s="296" t="s">
         <v>448</v>
       </c>
-      <c r="D7" s="467">
+      <c r="D7" s="299">
         <f>IF(E7="","",MAX(D$6:D6)+1)</f>
         <v>2</v>
       </c>
-      <c r="E7" s="464" t="s">
+      <c r="E7" s="296" t="s">
         <v>447</v>
       </c>
-      <c r="G7" s="464" t="s">
+      <c r="G7" s="296" t="s">
         <v>440</v>
       </c>
-      <c r="I7" s="464" t="s">
+      <c r="I7" s="296" t="s">
         <v>442</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="24.75" customHeight="1">
-      <c r="C8" s="464" t="s">
+      <c r="C8" s="296" t="s">
         <v>433</v>
       </c>
-      <c r="D8" s="467">
+      <c r="D8" s="299">
         <f>IF(E8="","",MAX(D$6:D7)+1)</f>
         <v>3</v>
       </c>
-      <c r="E8" s="464" t="s">
+      <c r="E8" s="296" t="s">
         <v>435</v>
       </c>
-      <c r="G8" s="464"/>
-      <c r="I8" s="465"/>
+      <c r="G8" s="296"/>
+      <c r="I8" s="297"/>
     </row>
     <row r="9" spans="1:11" ht="24.75" customHeight="1" thickBot="1">
-      <c r="C9" s="464" t="s">
+      <c r="C9" s="296" t="s">
         <v>449</v>
       </c>
-      <c r="D9" s="467">
+      <c r="D9" s="299">
         <f>IF(E9="","",MAX(D$6:D8)+1)</f>
         <v>4</v>
       </c>
-      <c r="E9" s="464" t="s">
+      <c r="E9" s="296" t="s">
         <v>436</v>
       </c>
-      <c r="G9" s="464"/>
-      <c r="I9" s="465"/>
+      <c r="G9" s="296"/>
+      <c r="I9" s="297"/>
     </row>
     <row r="10" spans="1:11" ht="24.75" customHeight="1">
-      <c r="C10" s="464" t="s">
+      <c r="C10" s="296" t="s">
         <v>450</v>
       </c>
-      <c r="D10" s="467">
+      <c r="D10" s="299">
         <f>IF(E10="","",MAX(D$6:D9)+1)</f>
         <v>5</v>
       </c>
-      <c r="E10" s="464" t="s">
+      <c r="E10" s="296" t="s">
         <v>437</v>
       </c>
-      <c r="G10" s="464"/>
-      <c r="I10" s="465"/>
-      <c r="K10" s="495" t="s">
+      <c r="G10" s="296"/>
+      <c r="I10" s="297"/>
+      <c r="K10" s="317" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="24.75" customHeight="1">
-      <c r="C11" s="464" t="s">
+      <c r="C11" s="296" t="s">
         <v>451</v>
       </c>
-      <c r="D11" s="467">
+      <c r="D11" s="299">
         <f>IF(E11="","",MAX(D$6:D10)+1)</f>
         <v>6</v>
       </c>
-      <c r="E11" s="464" t="s">
+      <c r="E11" s="296" t="s">
         <v>438</v>
       </c>
-      <c r="G11" s="464"/>
-      <c r="I11" s="465"/>
-      <c r="K11" s="496"/>
+      <c r="G11" s="296"/>
+      <c r="I11" s="297"/>
+      <c r="K11" s="318"/>
     </row>
     <row r="12" spans="1:11" ht="24.75" customHeight="1" thickBot="1">
-      <c r="C12" s="464" t="s">
+      <c r="C12" s="296" t="s">
         <v>452</v>
       </c>
       <c r="D12" s="84" t="str">
         <f>IF(E12="","",MAX(D$6:D11)+1)</f>
         <v/>
       </c>
-      <c r="E12" s="465"/>
-      <c r="G12" s="465"/>
-      <c r="I12" s="465"/>
-      <c r="K12" s="497"/>
+      <c r="E12" s="297"/>
+      <c r="G12" s="297"/>
+      <c r="I12" s="297"/>
+      <c r="K12" s="319"/>
     </row>
     <row r="13" spans="1:11" ht="24.75" customHeight="1" thickBot="1">
-      <c r="C13" s="464" t="s">
+      <c r="C13" s="296" t="s">
         <v>453</v>
       </c>
-      <c r="D13" s="468" t="str">
+      <c r="D13" s="300" t="str">
         <f>IF(E13="","",MAX(D$6:D12)+1)</f>
         <v/>
       </c>
-      <c r="E13" s="466"/>
-      <c r="F13" s="456"/>
-      <c r="G13" s="466"/>
-      <c r="H13" s="456"/>
-      <c r="I13" s="466"/>
-      <c r="J13" s="456"/>
-      <c r="K13" s="459" t="s">
+      <c r="E13" s="298"/>
+      <c r="F13" s="289"/>
+      <c r="G13" s="298"/>
+      <c r="H13" s="289"/>
+      <c r="I13" s="298"/>
+      <c r="J13" s="289"/>
+      <c r="K13" s="291" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="24.75" customHeight="1" thickBot="1">
-      <c r="C14" s="451">
+      <c r="C14" s="283">
         <f>COUNTA(C6:C13)</f>
         <v>8</v>
       </c>
-      <c r="E14" s="451">
+      <c r="E14" s="283">
         <f>COUNTA(E6:E13)</f>
         <v>6</v>
       </c>
-      <c r="G14" s="451">
+      <c r="G14" s="283">
         <f>COUNTA(G6:G13)</f>
         <v>2</v>
       </c>
-      <c r="I14" s="451">
+      <c r="I14" s="283">
         <f>COUNTA(I6:I13)</f>
         <v>2</v>
       </c>
-      <c r="K14" s="460" t="s">
+      <c r="K14" s="292" t="s">
         <v>415</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="60">
-      <c r="K15" s="498" t="s">
+      <c r="K15" s="301" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="45">
-      <c r="K16" s="499" t="s">
+      <c r="K16" s="302" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="17" spans="2:11">
-      <c r="K17" s="458"/>
+      <c r="K17" s="290"/>
     </row>
     <row r="18" spans="2:11" ht="15.75" thickBot="1">
-      <c r="K18" s="461"/>
+      <c r="K18" s="293"/>
     </row>
     <row r="20" spans="2:11" ht="30">
-      <c r="B20" s="462" t="s">
+      <c r="B20" s="294" t="s">
         <v>416</v>
       </c>
     </row>
     <row r="21" spans="2:11" ht="15.75" thickBot="1"/>
     <row r="22" spans="2:11" ht="18.75">
-      <c r="B22" s="485" t="s">
+      <c r="B22" s="320" t="s">
         <v>422</v>
       </c>
-      <c r="C22" s="483"/>
-      <c r="D22" s="483"/>
-      <c r="E22" s="483"/>
-      <c r="F22" s="483"/>
-      <c r="G22" s="483"/>
-      <c r="H22" s="483"/>
-      <c r="I22" s="483"/>
-      <c r="J22" s="483"/>
-      <c r="K22" s="490"/>
+      <c r="C22" s="321"/>
+      <c r="D22" s="321"/>
+      <c r="E22" s="321"/>
+      <c r="F22" s="321"/>
+      <c r="G22" s="321"/>
+      <c r="H22" s="321"/>
+      <c r="I22" s="321"/>
+      <c r="J22" s="321"/>
+      <c r="K22" s="322"/>
     </row>
     <row r="23" spans="2:11">
-      <c r="B23" s="486" t="s">
+      <c r="B23" s="303" t="s">
         <v>423</v>
       </c>
-      <c r="C23" s="482"/>
-      <c r="D23" s="482"/>
-      <c r="E23" s="482"/>
-      <c r="F23" s="482"/>
-      <c r="G23" s="482"/>
-      <c r="H23" s="482"/>
-      <c r="I23" s="482"/>
-      <c r="J23" s="482"/>
-      <c r="K23" s="491"/>
+      <c r="C23" s="304"/>
+      <c r="D23" s="304"/>
+      <c r="E23" s="304"/>
+      <c r="F23" s="304"/>
+      <c r="G23" s="304"/>
+      <c r="H23" s="304"/>
+      <c r="I23" s="304"/>
+      <c r="J23" s="304"/>
+      <c r="K23" s="305"/>
     </row>
     <row r="24" spans="2:11">
-      <c r="B24" s="487" t="s">
+      <c r="B24" s="312" t="s">
         <v>424</v>
       </c>
-      <c r="C24" s="471"/>
-      <c r="D24" s="471"/>
-      <c r="E24" s="471"/>
-      <c r="F24" s="471"/>
-      <c r="G24" s="471"/>
-      <c r="H24" s="471"/>
-      <c r="I24" s="471"/>
-      <c r="J24" s="471"/>
-      <c r="K24" s="492"/>
+      <c r="C24" s="313"/>
+      <c r="D24" s="313"/>
+      <c r="E24" s="313"/>
+      <c r="F24" s="313"/>
+      <c r="G24" s="313"/>
+      <c r="H24" s="313"/>
+      <c r="I24" s="313"/>
+      <c r="J24" s="313"/>
+      <c r="K24" s="314"/>
     </row>
     <row r="25" spans="2:11">
-      <c r="B25" s="487"/>
-      <c r="C25" s="471"/>
-      <c r="D25" s="471"/>
-      <c r="E25" s="471"/>
-      <c r="F25" s="471"/>
-      <c r="G25" s="471"/>
-      <c r="H25" s="471"/>
-      <c r="I25" s="471"/>
-      <c r="J25" s="471"/>
-      <c r="K25" s="492"/>
+      <c r="B25" s="312"/>
+      <c r="C25" s="313"/>
+      <c r="D25" s="313"/>
+      <c r="E25" s="313"/>
+      <c r="F25" s="313"/>
+      <c r="G25" s="313"/>
+      <c r="H25" s="313"/>
+      <c r="I25" s="313"/>
+      <c r="J25" s="313"/>
+      <c r="K25" s="314"/>
     </row>
     <row r="26" spans="2:11">
-      <c r="B26" s="486" t="s">
+      <c r="B26" s="303" t="s">
         <v>425</v>
       </c>
-      <c r="C26" s="482"/>
-      <c r="D26" s="482"/>
-      <c r="E26" s="482"/>
-      <c r="F26" s="482"/>
-      <c r="G26" s="482"/>
-      <c r="H26" s="482"/>
-      <c r="I26" s="482"/>
-      <c r="J26" s="482"/>
-      <c r="K26" s="491"/>
+      <c r="C26" s="304"/>
+      <c r="D26" s="304"/>
+      <c r="E26" s="304"/>
+      <c r="F26" s="304"/>
+      <c r="G26" s="304"/>
+      <c r="H26" s="304"/>
+      <c r="I26" s="304"/>
+      <c r="J26" s="304"/>
+      <c r="K26" s="305"/>
     </row>
     <row r="27" spans="2:11">
-      <c r="B27" s="488" t="s">
+      <c r="B27" s="306" t="s">
         <v>426</v>
       </c>
-      <c r="C27" s="470"/>
-      <c r="D27" s="470"/>
-      <c r="E27" s="470"/>
-      <c r="F27" s="470"/>
-      <c r="G27" s="470"/>
-      <c r="H27" s="470"/>
-      <c r="I27" s="470"/>
-      <c r="J27" s="470"/>
-      <c r="K27" s="493"/>
+      <c r="C27" s="307"/>
+      <c r="D27" s="307"/>
+      <c r="E27" s="307"/>
+      <c r="F27" s="307"/>
+      <c r="G27" s="307"/>
+      <c r="H27" s="307"/>
+      <c r="I27" s="307"/>
+      <c r="J27" s="307"/>
+      <c r="K27" s="308"/>
     </row>
     <row r="28" spans="2:11">
-      <c r="B28" s="488" t="s">
+      <c r="B28" s="306" t="s">
         <v>427</v>
       </c>
-      <c r="C28" s="470"/>
-      <c r="D28" s="470"/>
-      <c r="E28" s="470"/>
-      <c r="F28" s="470"/>
-      <c r="G28" s="470"/>
-      <c r="H28" s="470"/>
-      <c r="I28" s="470"/>
-      <c r="J28" s="470"/>
-      <c r="K28" s="493"/>
+      <c r="C28" s="307"/>
+      <c r="D28" s="307"/>
+      <c r="E28" s="307"/>
+      <c r="F28" s="307"/>
+      <c r="G28" s="307"/>
+      <c r="H28" s="307"/>
+      <c r="I28" s="307"/>
+      <c r="J28" s="307"/>
+      <c r="K28" s="308"/>
     </row>
     <row r="29" spans="2:11">
-      <c r="B29" s="488" t="s">
+      <c r="B29" s="306" t="s">
         <v>428</v>
       </c>
-      <c r="C29" s="470"/>
-      <c r="D29" s="470"/>
-      <c r="E29" s="470"/>
-      <c r="F29" s="470"/>
-      <c r="G29" s="470"/>
-      <c r="H29" s="470"/>
-      <c r="I29" s="470"/>
-      <c r="J29" s="470"/>
-      <c r="K29" s="493"/>
+      <c r="C29" s="307"/>
+      <c r="D29" s="307"/>
+      <c r="E29" s="307"/>
+      <c r="F29" s="307"/>
+      <c r="G29" s="307"/>
+      <c r="H29" s="307"/>
+      <c r="I29" s="307"/>
+      <c r="J29" s="307"/>
+      <c r="K29" s="308"/>
     </row>
     <row r="30" spans="2:11">
-      <c r="B30" s="486" t="s">
+      <c r="B30" s="303" t="s">
         <v>429</v>
       </c>
-      <c r="C30" s="482"/>
-      <c r="D30" s="482"/>
-      <c r="E30" s="482"/>
-      <c r="F30" s="482"/>
-      <c r="G30" s="482"/>
-      <c r="H30" s="482"/>
-      <c r="I30" s="482"/>
-      <c r="J30" s="482"/>
-      <c r="K30" s="491"/>
+      <c r="C30" s="304"/>
+      <c r="D30" s="304"/>
+      <c r="E30" s="304"/>
+      <c r="F30" s="304"/>
+      <c r="G30" s="304"/>
+      <c r="H30" s="304"/>
+      <c r="I30" s="304"/>
+      <c r="J30" s="304"/>
+      <c r="K30" s="305"/>
     </row>
     <row r="31" spans="2:11">
-      <c r="B31" s="488" t="s">
+      <c r="B31" s="306" t="s">
         <v>430</v>
       </c>
-      <c r="C31" s="470"/>
-      <c r="D31" s="470"/>
-      <c r="E31" s="470"/>
-      <c r="F31" s="470"/>
-      <c r="G31" s="470"/>
-      <c r="H31" s="470"/>
-      <c r="I31" s="470"/>
-      <c r="J31" s="470"/>
-      <c r="K31" s="493"/>
+      <c r="C31" s="307"/>
+      <c r="D31" s="307"/>
+      <c r="E31" s="307"/>
+      <c r="F31" s="307"/>
+      <c r="G31" s="307"/>
+      <c r="H31" s="307"/>
+      <c r="I31" s="307"/>
+      <c r="J31" s="307"/>
+      <c r="K31" s="308"/>
     </row>
     <row r="32" spans="2:11" ht="15.75" thickBot="1">
-      <c r="B32" s="489" t="s">
+      <c r="B32" s="309" t="s">
         <v>431</v>
       </c>
-      <c r="C32" s="484"/>
-      <c r="D32" s="484"/>
-      <c r="E32" s="484"/>
-      <c r="F32" s="484"/>
-      <c r="G32" s="484"/>
-      <c r="H32" s="484"/>
-      <c r="I32" s="484"/>
-      <c r="J32" s="484"/>
-      <c r="K32" s="494"/>
+      <c r="C32" s="310"/>
+      <c r="D32" s="310"/>
+      <c r="E32" s="310"/>
+      <c r="F32" s="310"/>
+      <c r="G32" s="310"/>
+      <c r="H32" s="310"/>
+      <c r="I32" s="310"/>
+      <c r="J32" s="310"/>
+      <c r="K32" s="311"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="K10:K12"/>
+    <mergeCell ref="B22:K22"/>
     <mergeCell ref="B30:K30"/>
     <mergeCell ref="B31:K31"/>
     <mergeCell ref="B32:K32"/>
@@ -11313,15 +11300,19 @@
     <mergeCell ref="B27:K27"/>
     <mergeCell ref="B28:K28"/>
     <mergeCell ref="B29:K29"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="K10:K12"/>
-    <mergeCell ref="B22:K22"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD59E254-9A27-4EFE-8B7C-B3AEB9069A3C}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -11338,10 +11329,10 @@
   <sheetData>
     <row r="1" spans="2:3" ht="15.75" thickBot="1"/>
     <row r="2" spans="2:3" ht="36.75" customHeight="1" thickBot="1">
-      <c r="B2" s="299" t="s">
+      <c r="B2" s="329" t="s">
         <v>80</v>
       </c>
-      <c r="C2" s="300"/>
+      <c r="C2" s="330"/>
     </row>
     <row r="3" spans="2:3" ht="17.25" thickBot="1">
       <c r="B3" s="104" t="s">
@@ -11396,10 +11387,10 @@
       <c r="C9" s="102"/>
     </row>
     <row r="10" spans="2:3" ht="30.75" customHeight="1">
-      <c r="B10" s="297" t="s">
+      <c r="B10" s="327" t="s">
         <v>89</v>
       </c>
-      <c r="C10" s="298"/>
+      <c r="C10" s="328"/>
     </row>
     <row r="11" spans="2:3" ht="30.75" customHeight="1">
       <c r="B11" s="107" t="s">
@@ -11498,110 +11489,110 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="20.100000000000001" customHeight="1">
-      <c r="A1" s="316"/>
-      <c r="B1" s="316"/>
-      <c r="C1" s="316"/>
-      <c r="D1" s="316"/>
-      <c r="E1" s="316"/>
-      <c r="F1" s="316"/>
-      <c r="G1" s="316"/>
-      <c r="H1" s="316"/>
-      <c r="I1" s="316"/>
-      <c r="J1" s="316"/>
-      <c r="K1" s="316"/>
-      <c r="L1" s="316"/>
-      <c r="M1" s="316"/>
-      <c r="N1" s="316"/>
-      <c r="O1" s="316"/>
-      <c r="P1" s="316"/>
-      <c r="Q1" s="316"/>
-      <c r="R1" s="316"/>
+      <c r="A1" s="332"/>
+      <c r="B1" s="332"/>
+      <c r="C1" s="332"/>
+      <c r="D1" s="332"/>
+      <c r="E1" s="332"/>
+      <c r="F1" s="332"/>
+      <c r="G1" s="332"/>
+      <c r="H1" s="332"/>
+      <c r="I1" s="332"/>
+      <c r="J1" s="332"/>
+      <c r="K1" s="332"/>
+      <c r="L1" s="332"/>
+      <c r="M1" s="332"/>
+      <c r="N1" s="332"/>
+      <c r="O1" s="332"/>
+      <c r="P1" s="332"/>
+      <c r="Q1" s="332"/>
+      <c r="R1" s="332"/>
     </row>
     <row r="2" spans="1:18" ht="36.75" customHeight="1">
-      <c r="A2" s="315" t="s">
+      <c r="A2" s="331" t="s">
         <v>371</v>
       </c>
-      <c r="B2" s="315"/>
-      <c r="C2" s="315"/>
-      <c r="D2" s="316"/>
-      <c r="E2" s="316"/>
-      <c r="F2" s="316"/>
-      <c r="G2" s="316"/>
-      <c r="H2" s="316"/>
-      <c r="I2" s="316"/>
-      <c r="J2" s="316"/>
-      <c r="K2" s="316"/>
-      <c r="L2" s="316"/>
-      <c r="M2" s="316"/>
-      <c r="N2" s="316"/>
-      <c r="O2" s="316"/>
-      <c r="P2" s="316"/>
-      <c r="Q2" s="316"/>
-      <c r="R2" s="316"/>
+      <c r="B2" s="331"/>
+      <c r="C2" s="331"/>
+      <c r="D2" s="332"/>
+      <c r="E2" s="332"/>
+      <c r="F2" s="332"/>
+      <c r="G2" s="332"/>
+      <c r="H2" s="332"/>
+      <c r="I2" s="332"/>
+      <c r="J2" s="332"/>
+      <c r="K2" s="332"/>
+      <c r="L2" s="332"/>
+      <c r="M2" s="332"/>
+      <c r="N2" s="332"/>
+      <c r="O2" s="332"/>
+      <c r="P2" s="332"/>
+      <c r="Q2" s="332"/>
+      <c r="R2" s="332"/>
     </row>
     <row r="3" spans="1:18" ht="20.100000000000001" customHeight="1">
       <c r="A3" s="251"/>
       <c r="B3" s="251"/>
       <c r="C3" s="251"/>
-      <c r="D3" s="316"/>
-      <c r="E3" s="316"/>
-      <c r="F3" s="316"/>
-      <c r="G3" s="316"/>
-      <c r="H3" s="316"/>
-      <c r="I3" s="316"/>
-      <c r="J3" s="316"/>
-      <c r="K3" s="316"/>
-      <c r="L3" s="316"/>
-      <c r="M3" s="316"/>
-      <c r="N3" s="316"/>
-      <c r="O3" s="316"/>
-      <c r="P3" s="316"/>
-      <c r="Q3" s="316"/>
-      <c r="R3" s="316"/>
+      <c r="D3" s="332"/>
+      <c r="E3" s="332"/>
+      <c r="F3" s="332"/>
+      <c r="G3" s="332"/>
+      <c r="H3" s="332"/>
+      <c r="I3" s="332"/>
+      <c r="J3" s="332"/>
+      <c r="K3" s="332"/>
+      <c r="L3" s="332"/>
+      <c r="M3" s="332"/>
+      <c r="N3" s="332"/>
+      <c r="O3" s="332"/>
+      <c r="P3" s="332"/>
+      <c r="Q3" s="332"/>
+      <c r="R3" s="332"/>
     </row>
     <row r="4" spans="1:18" ht="20.100000000000001" customHeight="1">
-      <c r="A4" s="316"/>
-      <c r="B4" s="316"/>
+      <c r="A4" s="332"/>
+      <c r="B4" s="332"/>
       <c r="C4" s="249" t="s">
         <v>370</v>
       </c>
       <c r="D4" s="248" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="316"/>
-      <c r="F4" s="316"/>
-      <c r="G4" s="316"/>
-      <c r="H4" s="316"/>
-      <c r="I4" s="316"/>
-      <c r="J4" s="316"/>
-      <c r="K4" s="316"/>
-      <c r="L4" s="316"/>
-      <c r="M4" s="316"/>
-      <c r="N4" s="316"/>
-      <c r="O4" s="316"/>
-      <c r="P4" s="316"/>
-      <c r="Q4" s="316"/>
-      <c r="R4" s="316"/>
+      <c r="E4" s="332"/>
+      <c r="F4" s="332"/>
+      <c r="G4" s="332"/>
+      <c r="H4" s="332"/>
+      <c r="I4" s="332"/>
+      <c r="J4" s="332"/>
+      <c r="K4" s="332"/>
+      <c r="L4" s="332"/>
+      <c r="M4" s="332"/>
+      <c r="N4" s="332"/>
+      <c r="O4" s="332"/>
+      <c r="P4" s="332"/>
+      <c r="Q4" s="332"/>
+      <c r="R4" s="332"/>
     </row>
     <row r="5" spans="1:18" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A5" s="317"/>
-      <c r="B5" s="317"/>
+      <c r="A5" s="333"/>
+      <c r="B5" s="333"/>
       <c r="C5" s="252"/>
       <c r="D5" s="252"/>
-      <c r="E5" s="317"/>
-      <c r="F5" s="317"/>
-      <c r="G5" s="317"/>
-      <c r="H5" s="317"/>
-      <c r="I5" s="317"/>
-      <c r="J5" s="317"/>
-      <c r="K5" s="317"/>
-      <c r="L5" s="317"/>
-      <c r="M5" s="317"/>
-      <c r="N5" s="317"/>
-      <c r="O5" s="317"/>
-      <c r="P5" s="317"/>
-      <c r="Q5" s="317"/>
-      <c r="R5" s="317"/>
+      <c r="E5" s="333"/>
+      <c r="F5" s="333"/>
+      <c r="G5" s="333"/>
+      <c r="H5" s="333"/>
+      <c r="I5" s="333"/>
+      <c r="J5" s="333"/>
+      <c r="K5" s="333"/>
+      <c r="L5" s="333"/>
+      <c r="M5" s="333"/>
+      <c r="N5" s="333"/>
+      <c r="O5" s="333"/>
+      <c r="P5" s="333"/>
+      <c r="Q5" s="333"/>
+      <c r="R5" s="333"/>
     </row>
     <row r="6" spans="1:18" ht="24.95" customHeight="1">
       <c r="B6" s="253" t="s">
@@ -11874,10 +11865,10 @@
     </row>
     <row r="22" spans="1:6" ht="15.75" thickBot="1"/>
     <row r="23" spans="1:6" ht="15.75" thickBot="1">
-      <c r="B23" s="301" t="s">
+      <c r="B23" s="340" t="s">
         <v>375</v>
       </c>
-      <c r="C23" s="302"/>
+      <c r="C23" s="341"/>
       <c r="D23" s="266">
         <v>5</v>
       </c>
@@ -11887,113 +11878,113 @@
     </row>
     <row r="25" spans="1:6" ht="15.75" thickBot="1"/>
     <row r="26" spans="1:6" ht="17.100000000000001" customHeight="1" thickBot="1">
-      <c r="A26" s="303" t="s">
+      <c r="A26" s="342" t="s">
         <v>377</v>
       </c>
-      <c r="B26" s="304"/>
-      <c r="C26" s="304"/>
-      <c r="D26" s="304"/>
-      <c r="E26" s="304"/>
-      <c r="F26" s="305"/>
+      <c r="B26" s="343"/>
+      <c r="C26" s="343"/>
+      <c r="D26" s="343"/>
+      <c r="E26" s="343"/>
+      <c r="F26" s="344"/>
     </row>
     <row r="27" spans="1:6" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A27" s="306" t="s">
+      <c r="A27" s="345" t="s">
         <v>378</v>
       </c>
-      <c r="B27" s="307"/>
-      <c r="C27" s="307"/>
-      <c r="D27" s="307"/>
-      <c r="E27" s="307"/>
-      <c r="F27" s="308"/>
+      <c r="B27" s="346"/>
+      <c r="C27" s="346"/>
+      <c r="D27" s="346"/>
+      <c r="E27" s="346"/>
+      <c r="F27" s="347"/>
     </row>
     <row r="28" spans="1:6" ht="30" customHeight="1" thickBot="1">
-      <c r="A28" s="309" t="s">
+      <c r="A28" s="334" t="s">
         <v>379</v>
       </c>
-      <c r="B28" s="310"/>
-      <c r="C28" s="310"/>
-      <c r="D28" s="310"/>
-      <c r="E28" s="310"/>
-      <c r="F28" s="311"/>
+      <c r="B28" s="335"/>
+      <c r="C28" s="335"/>
+      <c r="D28" s="335"/>
+      <c r="E28" s="335"/>
+      <c r="F28" s="336"/>
     </row>
     <row r="29" spans="1:6" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A29" s="306" t="s">
+      <c r="A29" s="345" t="s">
         <v>380</v>
       </c>
-      <c r="B29" s="307"/>
-      <c r="C29" s="307"/>
-      <c r="D29" s="307"/>
-      <c r="E29" s="307"/>
-      <c r="F29" s="308"/>
+      <c r="B29" s="346"/>
+      <c r="C29" s="346"/>
+      <c r="D29" s="346"/>
+      <c r="E29" s="346"/>
+      <c r="F29" s="347"/>
     </row>
     <row r="30" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A30" s="309" t="s">
+      <c r="A30" s="334" t="s">
         <v>381</v>
       </c>
-      <c r="B30" s="310"/>
-      <c r="C30" s="310"/>
-      <c r="D30" s="310"/>
-      <c r="E30" s="310"/>
-      <c r="F30" s="311"/>
+      <c r="B30" s="335"/>
+      <c r="C30" s="335"/>
+      <c r="D30" s="335"/>
+      <c r="E30" s="335"/>
+      <c r="F30" s="336"/>
     </row>
     <row r="31" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A31" s="309" t="s">
+      <c r="A31" s="334" t="s">
         <v>382</v>
       </c>
-      <c r="B31" s="310"/>
-      <c r="C31" s="310"/>
-      <c r="D31" s="310"/>
-      <c r="E31" s="310"/>
-      <c r="F31" s="311"/>
+      <c r="B31" s="335"/>
+      <c r="C31" s="335"/>
+      <c r="D31" s="335"/>
+      <c r="E31" s="335"/>
+      <c r="F31" s="336"/>
     </row>
     <row r="32" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A32" s="309" t="s">
+      <c r="A32" s="334" t="s">
         <v>383</v>
       </c>
-      <c r="B32" s="310"/>
-      <c r="C32" s="310"/>
-      <c r="D32" s="310"/>
-      <c r="E32" s="310"/>
-      <c r="F32" s="311"/>
+      <c r="B32" s="335"/>
+      <c r="C32" s="335"/>
+      <c r="D32" s="335"/>
+      <c r="E32" s="335"/>
+      <c r="F32" s="336"/>
     </row>
     <row r="33" spans="1:6" ht="14.25" customHeight="1">
-      <c r="A33" s="309" t="s">
+      <c r="A33" s="334" t="s">
         <v>384</v>
       </c>
-      <c r="B33" s="310"/>
-      <c r="C33" s="310"/>
-      <c r="D33" s="310"/>
-      <c r="E33" s="310"/>
-      <c r="F33" s="311"/>
+      <c r="B33" s="335"/>
+      <c r="C33" s="335"/>
+      <c r="D33" s="335"/>
+      <c r="E33" s="335"/>
+      <c r="F33" s="336"/>
     </row>
     <row r="34" spans="1:6" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A34" s="312" t="s">
+      <c r="A34" s="337" t="s">
         <v>385</v>
       </c>
-      <c r="B34" s="313"/>
-      <c r="C34" s="313"/>
-      <c r="D34" s="313"/>
-      <c r="E34" s="313"/>
-      <c r="F34" s="314"/>
+      <c r="B34" s="338"/>
+      <c r="C34" s="338"/>
+      <c r="D34" s="338"/>
+      <c r="E34" s="338"/>
+      <c r="F34" s="339"/>
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A34:F34"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="D2:R2"/>
     <mergeCell ref="D3:R3"/>
     <mergeCell ref="A4:B5"/>
     <mergeCell ref="E4:R5"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A32:F32"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A29:F29"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12018,16 +12009,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:44" ht="40.5">
-      <c r="B1" s="327" t="s">
+      <c r="B1" s="365" t="s">
         <v>36</v>
       </c>
-      <c r="C1" s="327"/>
-      <c r="D1" s="327"/>
-      <c r="E1" s="327"/>
-      <c r="F1" s="327"/>
-      <c r="G1" s="327"/>
-      <c r="H1" s="327"/>
-      <c r="I1" s="327"/>
+      <c r="C1" s="365"/>
+      <c r="D1" s="365"/>
+      <c r="E1" s="365"/>
+      <c r="F1" s="365"/>
+      <c r="G1" s="365"/>
+      <c r="H1" s="365"/>
+      <c r="I1" s="365"/>
       <c r="J1" s="31"/>
       <c r="K1" s="31"/>
       <c r="L1" s="31"/>
@@ -12065,16 +12056,16 @@
       <c r="AR1" s="31"/>
     </row>
     <row r="2" spans="2:44" ht="17.25" thickBot="1">
-      <c r="B2" s="328" t="s">
+      <c r="B2" s="366" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="328"/>
-      <c r="D2" s="328"/>
-      <c r="E2" s="328"/>
-      <c r="F2" s="328"/>
-      <c r="G2" s="328"/>
-      <c r="H2" s="328"/>
-      <c r="I2" s="328"/>
+      <c r="C2" s="366"/>
+      <c r="D2" s="366"/>
+      <c r="E2" s="366"/>
+      <c r="F2" s="366"/>
+      <c r="G2" s="366"/>
+      <c r="H2" s="366"/>
+      <c r="I2" s="366"/>
       <c r="J2" s="32"/>
       <c r="K2" s="32"/>
       <c r="L2" s="32"/>
@@ -12112,55 +12103,55 @@
       <c r="AR2" s="32"/>
     </row>
     <row r="3" spans="2:44" ht="18.75">
-      <c r="B3" s="329"/>
-      <c r="C3" s="330"/>
-      <c r="D3" s="330"/>
-      <c r="E3" s="330"/>
-      <c r="F3" s="330"/>
-      <c r="G3" s="330"/>
-      <c r="H3" s="330"/>
-      <c r="I3" s="330"/>
-      <c r="J3" s="335">
+      <c r="B3" s="367"/>
+      <c r="C3" s="368"/>
+      <c r="D3" s="368"/>
+      <c r="E3" s="368"/>
+      <c r="F3" s="368"/>
+      <c r="G3" s="368"/>
+      <c r="H3" s="368"/>
+      <c r="I3" s="368"/>
+      <c r="J3" s="348">
         <f ca="1">K5</f>
         <v>46181</v>
       </c>
-      <c r="K3" s="335"/>
-      <c r="L3" s="335"/>
-      <c r="M3" s="335"/>
-      <c r="N3" s="336"/>
-      <c r="O3" s="336"/>
-      <c r="P3" s="336"/>
-      <c r="Q3" s="336"/>
-      <c r="R3" s="336"/>
-      <c r="S3" s="336"/>
-      <c r="T3" s="336"/>
-      <c r="U3" s="336"/>
-      <c r="V3" s="336"/>
-      <c r="W3" s="336"/>
-      <c r="X3" s="336"/>
-      <c r="Y3" s="336"/>
-      <c r="Z3" s="336"/>
-      <c r="AA3" s="336"/>
-      <c r="AB3" s="336"/>
-      <c r="AC3" s="336"/>
-      <c r="AD3" s="336"/>
-      <c r="AE3" s="336"/>
-      <c r="AF3" s="336"/>
-      <c r="AG3" s="336"/>
-      <c r="AH3" s="336"/>
-      <c r="AI3" s="336"/>
-      <c r="AJ3" s="336"/>
-      <c r="AK3" s="336"/>
-      <c r="AL3" s="336"/>
-      <c r="AM3" s="336"/>
-      <c r="AN3" s="336"/>
-      <c r="AO3" s="336"/>
-      <c r="AP3" s="336"/>
-      <c r="AQ3" s="336"/>
-      <c r="AR3" s="336"/>
+      <c r="K3" s="348"/>
+      <c r="L3" s="348"/>
+      <c r="M3" s="348"/>
+      <c r="N3" s="349"/>
+      <c r="O3" s="349"/>
+      <c r="P3" s="349"/>
+      <c r="Q3" s="349"/>
+      <c r="R3" s="349"/>
+      <c r="S3" s="349"/>
+      <c r="T3" s="349"/>
+      <c r="U3" s="349"/>
+      <c r="V3" s="349"/>
+      <c r="W3" s="349"/>
+      <c r="X3" s="349"/>
+      <c r="Y3" s="349"/>
+      <c r="Z3" s="349"/>
+      <c r="AA3" s="349"/>
+      <c r="AB3" s="349"/>
+      <c r="AC3" s="349"/>
+      <c r="AD3" s="349"/>
+      <c r="AE3" s="349"/>
+      <c r="AF3" s="349"/>
+      <c r="AG3" s="349"/>
+      <c r="AH3" s="349"/>
+      <c r="AI3" s="349"/>
+      <c r="AJ3" s="349"/>
+      <c r="AK3" s="349"/>
+      <c r="AL3" s="349"/>
+      <c r="AM3" s="349"/>
+      <c r="AN3" s="349"/>
+      <c r="AO3" s="349"/>
+      <c r="AP3" s="349"/>
+      <c r="AQ3" s="349"/>
+      <c r="AR3" s="349"/>
     </row>
     <row r="4" spans="2:44" ht="15.75" thickBot="1">
-      <c r="B4" s="331"/>
+      <c r="B4" s="369"/>
       <c r="C4" s="78" t="s">
         <v>0</v>
       </c>
@@ -12168,82 +12159,82 @@
         <f ca="1">IF(MONTH(TODAY()-WEEKDAY(TODAY(),2)+1)&lt;MONTH(TODAY()),(TODAY()-28-DAY(TODAY())+7)-WEEKDAY((TODAY()-DAY(TODAY())+7),2)+1,(TODAY()-DAY(TODAY())+7)-WEEKDAY((TODAY()-DAY(TODAY())+7),2)+1)</f>
         <v>46174</v>
       </c>
-      <c r="E4" s="333"/>
-      <c r="F4" s="333"/>
-      <c r="G4" s="333"/>
-      <c r="H4" s="333"/>
-      <c r="I4" s="334"/>
-      <c r="J4" s="337">
+      <c r="E4" s="371"/>
+      <c r="F4" s="371"/>
+      <c r="G4" s="371"/>
+      <c r="H4" s="371"/>
+      <c r="I4" s="372"/>
+      <c r="J4" s="350">
         <f ca="1">K5</f>
         <v>46181</v>
       </c>
-      <c r="K4" s="337"/>
-      <c r="L4" s="337"/>
-      <c r="M4" s="337"/>
-      <c r="N4" s="342">
+      <c r="K4" s="350"/>
+      <c r="L4" s="350"/>
+      <c r="M4" s="350"/>
+      <c r="N4" s="355">
         <f ca="1">O5</f>
         <v>46209</v>
       </c>
-      <c r="O4" s="337"/>
-      <c r="P4" s="337"/>
-      <c r="Q4" s="337"/>
-      <c r="R4" s="337"/>
-      <c r="S4" s="337">
+      <c r="O4" s="350"/>
+      <c r="P4" s="350"/>
+      <c r="Q4" s="350"/>
+      <c r="R4" s="350"/>
+      <c r="S4" s="350">
         <f ca="1">T5</f>
         <v>46244</v>
       </c>
-      <c r="T4" s="337"/>
-      <c r="U4" s="337"/>
-      <c r="V4" s="337"/>
-      <c r="W4" s="337">
+      <c r="T4" s="350"/>
+      <c r="U4" s="350"/>
+      <c r="V4" s="350"/>
+      <c r="W4" s="350">
         <f ca="1">X5</f>
         <v>46272</v>
       </c>
-      <c r="X4" s="337"/>
-      <c r="Y4" s="337"/>
-      <c r="Z4" s="337"/>
-      <c r="AA4" s="337"/>
-      <c r="AB4" s="337">
+      <c r="X4" s="350"/>
+      <c r="Y4" s="350"/>
+      <c r="Z4" s="350"/>
+      <c r="AA4" s="350"/>
+      <c r="AB4" s="350">
         <f ca="1">AC5</f>
         <v>46307</v>
       </c>
-      <c r="AC4" s="337"/>
-      <c r="AD4" s="337"/>
-      <c r="AE4" s="337"/>
-      <c r="AF4" s="337">
+      <c r="AC4" s="350"/>
+      <c r="AD4" s="350"/>
+      <c r="AE4" s="350"/>
+      <c r="AF4" s="350">
         <f ca="1">AG5</f>
         <v>46335</v>
       </c>
-      <c r="AG4" s="337"/>
-      <c r="AH4" s="337"/>
-      <c r="AI4" s="337"/>
-      <c r="AJ4" s="337">
+      <c r="AG4" s="350"/>
+      <c r="AH4" s="350"/>
+      <c r="AI4" s="350"/>
+      <c r="AJ4" s="350">
         <f ca="1">AK5</f>
         <v>46363</v>
       </c>
-      <c r="AK4" s="337"/>
-      <c r="AL4" s="337"/>
-      <c r="AM4" s="337"/>
-      <c r="AN4" s="337"/>
-      <c r="AO4" s="337">
+      <c r="AK4" s="350"/>
+      <c r="AL4" s="350"/>
+      <c r="AM4" s="350"/>
+      <c r="AN4" s="350"/>
+      <c r="AO4" s="350">
         <f ca="1">AP5</f>
         <v>46398</v>
       </c>
-      <c r="AP4" s="337"/>
-      <c r="AQ4" s="337"/>
-      <c r="AR4" s="338"/>
+      <c r="AP4" s="350"/>
+      <c r="AQ4" s="350"/>
+      <c r="AR4" s="351"/>
     </row>
     <row r="5" spans="2:44" ht="33" thickBot="1">
-      <c r="B5" s="332"/>
+      <c r="B5" s="370"/>
       <c r="C5" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="339" t="s">
+      <c r="D5" s="352" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="340"/>
-      <c r="F5" s="340"/>
-      <c r="G5" s="341"/>
+      <c r="E5" s="353"/>
+      <c r="F5" s="353"/>
+      <c r="G5" s="354"/>
       <c r="H5" s="81"/>
       <c r="I5" s="79" t="s">
         <v>2</v>
@@ -14167,71 +14158,78 @@
     </row>
     <row r="24" spans="2:9" ht="15.75" thickBot="1"/>
     <row r="25" spans="2:9" ht="24.95" customHeight="1">
-      <c r="B25" s="318" t="s">
+      <c r="B25" s="356" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="319"/>
-      <c r="D25" s="319"/>
-      <c r="E25" s="319"/>
-      <c r="F25" s="319"/>
-      <c r="G25" s="319"/>
-      <c r="H25" s="319"/>
-      <c r="I25" s="320"/>
+      <c r="C25" s="357"/>
+      <c r="D25" s="357"/>
+      <c r="E25" s="357"/>
+      <c r="F25" s="357"/>
+      <c r="G25" s="357"/>
+      <c r="H25" s="357"/>
+      <c r="I25" s="358"/>
     </row>
     <row r="26" spans="2:9" ht="90" customHeight="1">
-      <c r="B26" s="321" t="s">
+      <c r="B26" s="359" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="322"/>
-      <c r="D26" s="322"/>
-      <c r="E26" s="322"/>
-      <c r="F26" s="322"/>
-      <c r="G26" s="322"/>
-      <c r="H26" s="322"/>
-      <c r="I26" s="323"/>
+      <c r="C26" s="360"/>
+      <c r="D26" s="360"/>
+      <c r="E26" s="360"/>
+      <c r="F26" s="360"/>
+      <c r="G26" s="360"/>
+      <c r="H26" s="360"/>
+      <c r="I26" s="361"/>
     </row>
     <row r="27" spans="2:9">
-      <c r="B27" s="321"/>
-      <c r="C27" s="322"/>
-      <c r="D27" s="322"/>
-      <c r="E27" s="322"/>
-      <c r="F27" s="322"/>
-      <c r="G27" s="322"/>
-      <c r="H27" s="322"/>
-      <c r="I27" s="323"/>
+      <c r="B27" s="359"/>
+      <c r="C27" s="360"/>
+      <c r="D27" s="360"/>
+      <c r="E27" s="360"/>
+      <c r="F27" s="360"/>
+      <c r="G27" s="360"/>
+      <c r="H27" s="360"/>
+      <c r="I27" s="361"/>
     </row>
     <row r="28" spans="2:9">
-      <c r="B28" s="321"/>
-      <c r="C28" s="322"/>
-      <c r="D28" s="322"/>
-      <c r="E28" s="322"/>
-      <c r="F28" s="322"/>
-      <c r="G28" s="322"/>
-      <c r="H28" s="322"/>
-      <c r="I28" s="323"/>
+      <c r="B28" s="359"/>
+      <c r="C28" s="360"/>
+      <c r="D28" s="360"/>
+      <c r="E28" s="360"/>
+      <c r="F28" s="360"/>
+      <c r="G28" s="360"/>
+      <c r="H28" s="360"/>
+      <c r="I28" s="361"/>
     </row>
     <row r="29" spans="2:9">
-      <c r="B29" s="321"/>
-      <c r="C29" s="322"/>
-      <c r="D29" s="322"/>
-      <c r="E29" s="322"/>
-      <c r="F29" s="322"/>
-      <c r="G29" s="322"/>
-      <c r="H29" s="322"/>
-      <c r="I29" s="323"/>
+      <c r="B29" s="359"/>
+      <c r="C29" s="360"/>
+      <c r="D29" s="360"/>
+      <c r="E29" s="360"/>
+      <c r="F29" s="360"/>
+      <c r="G29" s="360"/>
+      <c r="H29" s="360"/>
+      <c r="I29" s="361"/>
     </row>
     <row r="30" spans="2:9" ht="15.75" thickBot="1">
-      <c r="B30" s="324"/>
-      <c r="C30" s="325"/>
-      <c r="D30" s="325"/>
-      <c r="E30" s="325"/>
-      <c r="F30" s="325"/>
-      <c r="G30" s="325"/>
-      <c r="H30" s="325"/>
-      <c r="I30" s="326"/>
+      <c r="B30" s="362"/>
+      <c r="C30" s="363"/>
+      <c r="D30" s="363"/>
+      <c r="E30" s="363"/>
+      <c r="F30" s="363"/>
+      <c r="G30" s="363"/>
+      <c r="H30" s="363"/>
+      <c r="I30" s="364"/>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B25:I25"/>
+    <mergeCell ref="B26:I30"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="E4:I4"/>
     <mergeCell ref="J3:AR3"/>
     <mergeCell ref="AF4:AI4"/>
     <mergeCell ref="AJ4:AN4"/>
@@ -14242,13 +14240,6 @@
     <mergeCell ref="S4:V4"/>
     <mergeCell ref="W4:AA4"/>
     <mergeCell ref="AB4:AE4"/>
-    <mergeCell ref="B25:I25"/>
-    <mergeCell ref="B26:I30"/>
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="E4:I4"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="H7:H16">
@@ -14291,150 +14282,150 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" ht="29.25" thickBot="1">
-      <c r="B2" s="344" t="s">
+      <c r="B2" s="391" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="345"/>
-      <c r="D2" s="345"/>
-      <c r="E2" s="345"/>
-      <c r="F2" s="345"/>
-      <c r="G2" s="345"/>
-      <c r="H2" s="345"/>
-      <c r="I2" s="345"/>
-      <c r="J2" s="345"/>
-      <c r="K2" s="345"/>
-      <c r="L2" s="345"/>
-      <c r="M2" s="345"/>
-      <c r="N2" s="345"/>
-      <c r="O2" s="345"/>
-      <c r="P2" s="346"/>
+      <c r="C2" s="392"/>
+      <c r="D2" s="392"/>
+      <c r="E2" s="392"/>
+      <c r="F2" s="392"/>
+      <c r="G2" s="392"/>
+      <c r="H2" s="392"/>
+      <c r="I2" s="392"/>
+      <c r="J2" s="392"/>
+      <c r="K2" s="392"/>
+      <c r="L2" s="392"/>
+      <c r="M2" s="392"/>
+      <c r="N2" s="392"/>
+      <c r="O2" s="392"/>
+      <c r="P2" s="393"/>
     </row>
     <row r="3" spans="2:16">
-      <c r="B3" s="347"/>
-      <c r="C3" s="348"/>
+      <c r="B3" s="394"/>
+      <c r="C3" s="395"/>
       <c r="D3" s="99" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="366" t="s">
+      <c r="E3" s="387" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="366"/>
-      <c r="G3" s="366"/>
-      <c r="H3" s="366"/>
-      <c r="I3" s="349" t="s">
+      <c r="F3" s="387"/>
+      <c r="G3" s="387"/>
+      <c r="H3" s="387"/>
+      <c r="I3" s="396" t="s">
         <v>46</v>
       </c>
-      <c r="J3" s="349"/>
-      <c r="K3" s="350" t="s">
+      <c r="J3" s="396"/>
+      <c r="K3" s="397" t="s">
         <v>17</v>
       </c>
-      <c r="L3" s="350"/>
-      <c r="M3" s="350"/>
-      <c r="N3" s="348"/>
-      <c r="O3" s="348"/>
-      <c r="P3" s="351"/>
+      <c r="L3" s="397"/>
+      <c r="M3" s="397"/>
+      <c r="N3" s="395"/>
+      <c r="O3" s="395"/>
+      <c r="P3" s="398"/>
     </row>
     <row r="4" spans="2:16" ht="15.75" thickBot="1">
-      <c r="B4" s="352"/>
-      <c r="C4" s="353"/>
-      <c r="D4" s="353"/>
-      <c r="E4" s="353"/>
-      <c r="F4" s="353"/>
-      <c r="G4" s="353"/>
-      <c r="H4" s="353"/>
-      <c r="I4" s="353"/>
-      <c r="J4" s="353"/>
-      <c r="K4" s="353"/>
-      <c r="L4" s="353"/>
-      <c r="M4" s="353"/>
-      <c r="N4" s="353"/>
-      <c r="O4" s="353"/>
-      <c r="P4" s="354"/>
+      <c r="B4" s="399"/>
+      <c r="C4" s="400"/>
+      <c r="D4" s="400"/>
+      <c r="E4" s="400"/>
+      <c r="F4" s="400"/>
+      <c r="G4" s="400"/>
+      <c r="H4" s="400"/>
+      <c r="I4" s="400"/>
+      <c r="J4" s="400"/>
+      <c r="K4" s="400"/>
+      <c r="L4" s="400"/>
+      <c r="M4" s="400"/>
+      <c r="N4" s="400"/>
+      <c r="O4" s="400"/>
+      <c r="P4" s="401"/>
     </row>
     <row r="5" spans="2:16" ht="15.75" thickBot="1">
-      <c r="B5" s="355" t="s">
+      <c r="B5" s="402" t="s">
         <v>79</v>
       </c>
-      <c r="C5" s="356"/>
-      <c r="D5" s="356"/>
-      <c r="E5" s="356"/>
-      <c r="F5" s="356"/>
-      <c r="G5" s="356"/>
-      <c r="H5" s="356"/>
-      <c r="I5" s="356"/>
-      <c r="J5" s="356"/>
-      <c r="K5" s="356"/>
-      <c r="L5" s="356"/>
-      <c r="M5" s="356"/>
-      <c r="N5" s="356"/>
-      <c r="O5" s="356"/>
-      <c r="P5" s="357"/>
+      <c r="C5" s="403"/>
+      <c r="D5" s="403"/>
+      <c r="E5" s="403"/>
+      <c r="F5" s="403"/>
+      <c r="G5" s="403"/>
+      <c r="H5" s="403"/>
+      <c r="I5" s="403"/>
+      <c r="J5" s="403"/>
+      <c r="K5" s="403"/>
+      <c r="L5" s="403"/>
+      <c r="M5" s="403"/>
+      <c r="N5" s="403"/>
+      <c r="O5" s="403"/>
+      <c r="P5" s="404"/>
     </row>
     <row r="6" spans="2:16" ht="129.75" customHeight="1" thickBot="1">
-      <c r="B6" s="358" t="s">
+      <c r="B6" s="405" t="s">
         <v>44</v>
       </c>
-      <c r="C6" s="359"/>
-      <c r="D6" s="360"/>
-      <c r="E6" s="361" t="s">
+      <c r="C6" s="406"/>
+      <c r="D6" s="407"/>
+      <c r="E6" s="386" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="361" t="s">
+      <c r="F6" s="386" t="s">
         <v>18</v>
       </c>
-      <c r="G6" s="361" t="s">
+      <c r="G6" s="386" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="361" t="s">
+      <c r="H6" s="386" t="s">
         <v>22</v>
       </c>
-      <c r="I6" s="361" t="s">
+      <c r="I6" s="386" t="s">
         <v>24</v>
       </c>
-      <c r="J6" s="361" t="s">
+      <c r="J6" s="386" t="s">
         <v>26</v>
       </c>
-      <c r="K6" s="361" t="s">
+      <c r="K6" s="386" t="s">
         <v>28</v>
       </c>
-      <c r="L6" s="361" t="s">
+      <c r="L6" s="386" t="s">
         <v>30</v>
       </c>
-      <c r="M6" s="361" t="s">
+      <c r="M6" s="386" t="s">
         <v>32</v>
       </c>
-      <c r="N6" s="343" t="s">
+      <c r="N6" s="390" t="s">
         <v>34</v>
       </c>
-      <c r="O6" s="343"/>
-      <c r="P6" s="343"/>
+      <c r="O6" s="390"/>
+      <c r="P6" s="390"/>
     </row>
     <row r="7" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B7" s="364" t="s">
+      <c r="B7" s="388" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="365"/>
+      <c r="C7" s="389"/>
       <c r="D7" s="114" t="s">
         <v>48</v>
       </c>
-      <c r="E7" s="361"/>
-      <c r="F7" s="361"/>
-      <c r="G7" s="361"/>
-      <c r="H7" s="361"/>
-      <c r="I7" s="361"/>
-      <c r="J7" s="361"/>
-      <c r="K7" s="361"/>
-      <c r="L7" s="361"/>
-      <c r="M7" s="361"/>
-      <c r="N7" s="343"/>
-      <c r="O7" s="343"/>
-      <c r="P7" s="343"/>
+      <c r="E7" s="386"/>
+      <c r="F7" s="386"/>
+      <c r="G7" s="386"/>
+      <c r="H7" s="386"/>
+      <c r="I7" s="386"/>
+      <c r="J7" s="386"/>
+      <c r="K7" s="386"/>
+      <c r="L7" s="386"/>
+      <c r="M7" s="386"/>
+      <c r="N7" s="390"/>
+      <c r="O7" s="390"/>
+      <c r="P7" s="390"/>
     </row>
     <row r="8" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B8" s="362" t="s">
+      <c r="B8" s="373" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="363"/>
+      <c r="C8" s="374"/>
       <c r="D8" s="100" t="s">
         <v>62</v>
       </c>
@@ -14472,10 +14463,10 @@
       <c r="P8" s="90"/>
     </row>
     <row r="9" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B9" s="362" t="s">
+      <c r="B9" s="373" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="363"/>
+      <c r="C9" s="374"/>
       <c r="D9" s="100" t="s">
         <v>50</v>
       </c>
@@ -14513,10 +14504,10 @@
       <c r="P9" s="94"/>
     </row>
     <row r="10" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B10" s="362" t="s">
+      <c r="B10" s="373" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="363"/>
+      <c r="C10" s="374"/>
       <c r="D10" s="100" t="s">
         <v>63</v>
       </c>
@@ -14554,10 +14545,10 @@
       <c r="P10" s="94"/>
     </row>
     <row r="11" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B11" s="362" t="s">
+      <c r="B11" s="373" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="363"/>
+      <c r="C11" s="374"/>
       <c r="D11" s="100" t="s">
         <v>64</v>
       </c>
@@ -14595,10 +14586,10 @@
       <c r="P11" s="94"/>
     </row>
     <row r="12" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B12" s="362" t="s">
+      <c r="B12" s="373" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="363"/>
+      <c r="C12" s="374"/>
       <c r="D12" s="100" t="s">
         <v>65</v>
       </c>
@@ -14636,10 +14627,10 @@
       <c r="P12" s="94"/>
     </row>
     <row r="13" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B13" s="362" t="s">
+      <c r="B13" s="373" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="363"/>
+      <c r="C13" s="374"/>
       <c r="D13" s="100" t="s">
         <v>66</v>
       </c>
@@ -14677,10 +14668,10 @@
       <c r="P13" s="94"/>
     </row>
     <row r="14" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B14" s="362" t="s">
+      <c r="B14" s="373" t="s">
         <v>29</v>
       </c>
-      <c r="C14" s="363"/>
+      <c r="C14" s="374"/>
       <c r="D14" s="100" t="s">
         <v>67</v>
       </c>
@@ -14718,10 +14709,10 @@
       <c r="P14" s="94"/>
     </row>
     <row r="15" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B15" s="362" t="s">
+      <c r="B15" s="373" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="363"/>
+      <c r="C15" s="374"/>
       <c r="D15" s="100" t="s">
         <v>68</v>
       </c>
@@ -14759,10 +14750,10 @@
       <c r="P15" s="94"/>
     </row>
     <row r="16" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B16" s="362" t="s">
+      <c r="B16" s="373" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="363"/>
+      <c r="C16" s="374"/>
       <c r="D16" s="100" t="s">
         <v>69</v>
       </c>
@@ -14800,10 +14791,10 @@
       <c r="P16" s="94"/>
     </row>
     <row r="17" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B17" s="362" t="s">
+      <c r="B17" s="373" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="363"/>
+      <c r="C17" s="374"/>
       <c r="D17" s="100" t="s">
         <v>70</v>
       </c>
@@ -14841,10 +14832,10 @@
       <c r="P17" s="94"/>
     </row>
     <row r="18" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B18" s="362" t="s">
+      <c r="B18" s="373" t="s">
         <v>71</v>
       </c>
-      <c r="C18" s="363"/>
+      <c r="C18" s="374"/>
       <c r="D18" s="100" t="s">
         <v>72</v>
       </c>
@@ -14882,10 +14873,10 @@
       <c r="P18" s="94"/>
     </row>
     <row r="19" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B19" s="362" t="s">
+      <c r="B19" s="373" t="s">
         <v>74</v>
       </c>
-      <c r="C19" s="363"/>
+      <c r="C19" s="374"/>
       <c r="D19" s="100" t="s">
         <v>77</v>
       </c>
@@ -14923,10 +14914,10 @@
       <c r="P19" s="94"/>
     </row>
     <row r="20" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B20" s="362" t="s">
+      <c r="B20" s="373" t="s">
         <v>75</v>
       </c>
-      <c r="C20" s="363"/>
+      <c r="C20" s="374"/>
       <c r="D20" s="100" t="s">
         <v>78</v>
       </c>
@@ -14964,10 +14955,10 @@
       <c r="P20" s="94"/>
     </row>
     <row r="21" spans="2:16" ht="35.1" customHeight="1" thickBot="1">
-      <c r="B21" s="362" t="s">
+      <c r="B21" s="373" t="s">
         <v>73</v>
       </c>
-      <c r="C21" s="363"/>
+      <c r="C21" s="374"/>
       <c r="D21" s="101" t="s">
         <v>76</v>
       </c>
@@ -15038,137 +15029,137 @@
       </c>
     </row>
     <row r="28" spans="2:16">
-      <c r="B28" s="375" t="s">
+      <c r="B28" s="378" t="s">
         <v>55</v>
       </c>
-      <c r="C28" s="376"/>
-      <c r="D28" s="376"/>
-      <c r="E28" s="376"/>
-      <c r="F28" s="376"/>
-      <c r="G28" s="376"/>
-      <c r="H28" s="376"/>
-      <c r="I28" s="376"/>
-      <c r="J28" s="376"/>
-      <c r="K28" s="376"/>
-      <c r="L28" s="376"/>
-      <c r="M28" s="376"/>
-      <c r="N28" s="376"/>
-      <c r="O28" s="376"/>
-      <c r="P28" s="377"/>
+      <c r="C28" s="379"/>
+      <c r="D28" s="379"/>
+      <c r="E28" s="379"/>
+      <c r="F28" s="379"/>
+      <c r="G28" s="379"/>
+      <c r="H28" s="379"/>
+      <c r="I28" s="379"/>
+      <c r="J28" s="379"/>
+      <c r="K28" s="379"/>
+      <c r="L28" s="379"/>
+      <c r="M28" s="379"/>
+      <c r="N28" s="379"/>
+      <c r="O28" s="379"/>
+      <c r="P28" s="380"/>
     </row>
     <row r="29" spans="2:16" ht="15" customHeight="1">
-      <c r="B29" s="367" t="s">
+      <c r="B29" s="375" t="s">
         <v>56</v>
       </c>
-      <c r="C29" s="368"/>
-      <c r="D29" s="368"/>
-      <c r="E29" s="368"/>
-      <c r="F29" s="368"/>
-      <c r="G29" s="368"/>
-      <c r="H29" s="368"/>
-      <c r="I29" s="368"/>
-      <c r="J29" s="368"/>
-      <c r="K29" s="368"/>
-      <c r="L29" s="368"/>
-      <c r="M29" s="368"/>
-      <c r="N29" s="368"/>
-      <c r="O29" s="368"/>
-      <c r="P29" s="369"/>
+      <c r="C29" s="376"/>
+      <c r="D29" s="376"/>
+      <c r="E29" s="376"/>
+      <c r="F29" s="376"/>
+      <c r="G29" s="376"/>
+      <c r="H29" s="376"/>
+      <c r="I29" s="376"/>
+      <c r="J29" s="376"/>
+      <c r="K29" s="376"/>
+      <c r="L29" s="376"/>
+      <c r="M29" s="376"/>
+      <c r="N29" s="376"/>
+      <c r="O29" s="376"/>
+      <c r="P29" s="377"/>
     </row>
     <row r="30" spans="2:16" ht="15" customHeight="1">
-      <c r="B30" s="367" t="s">
+      <c r="B30" s="375" t="s">
         <v>57</v>
       </c>
-      <c r="C30" s="368"/>
-      <c r="D30" s="368"/>
-      <c r="E30" s="368"/>
-      <c r="F30" s="368"/>
-      <c r="G30" s="368"/>
-      <c r="H30" s="368"/>
-      <c r="I30" s="368"/>
-      <c r="J30" s="368"/>
-      <c r="K30" s="368"/>
-      <c r="L30" s="368"/>
-      <c r="M30" s="368"/>
-      <c r="N30" s="368"/>
-      <c r="O30" s="368"/>
-      <c r="P30" s="369"/>
+      <c r="C30" s="376"/>
+      <c r="D30" s="376"/>
+      <c r="E30" s="376"/>
+      <c r="F30" s="376"/>
+      <c r="G30" s="376"/>
+      <c r="H30" s="376"/>
+      <c r="I30" s="376"/>
+      <c r="J30" s="376"/>
+      <c r="K30" s="376"/>
+      <c r="L30" s="376"/>
+      <c r="M30" s="376"/>
+      <c r="N30" s="376"/>
+      <c r="O30" s="376"/>
+      <c r="P30" s="377"/>
     </row>
     <row r="31" spans="2:16" ht="15" customHeight="1">
-      <c r="B31" s="367" t="s">
+      <c r="B31" s="375" t="s">
         <v>58</v>
       </c>
-      <c r="C31" s="368"/>
-      <c r="D31" s="368"/>
-      <c r="E31" s="368"/>
-      <c r="F31" s="368"/>
-      <c r="G31" s="368"/>
-      <c r="H31" s="368"/>
-      <c r="I31" s="368"/>
-      <c r="J31" s="368"/>
-      <c r="K31" s="368"/>
-      <c r="L31" s="368"/>
-      <c r="M31" s="368"/>
-      <c r="N31" s="368"/>
-      <c r="O31" s="368"/>
-      <c r="P31" s="369"/>
+      <c r="C31" s="376"/>
+      <c r="D31" s="376"/>
+      <c r="E31" s="376"/>
+      <c r="F31" s="376"/>
+      <c r="G31" s="376"/>
+      <c r="H31" s="376"/>
+      <c r="I31" s="376"/>
+      <c r="J31" s="376"/>
+      <c r="K31" s="376"/>
+      <c r="L31" s="376"/>
+      <c r="M31" s="376"/>
+      <c r="N31" s="376"/>
+      <c r="O31" s="376"/>
+      <c r="P31" s="377"/>
     </row>
     <row r="32" spans="2:16" ht="20.100000000000001" customHeight="1">
-      <c r="B32" s="367" t="s">
+      <c r="B32" s="375" t="s">
         <v>59</v>
       </c>
-      <c r="C32" s="370"/>
-      <c r="D32" s="370"/>
-      <c r="E32" s="370"/>
-      <c r="F32" s="370"/>
-      <c r="G32" s="370"/>
-      <c r="H32" s="370"/>
-      <c r="I32" s="370"/>
-      <c r="J32" s="370"/>
-      <c r="K32" s="370"/>
-      <c r="L32" s="370"/>
-      <c r="M32" s="370"/>
-      <c r="N32" s="370"/>
-      <c r="O32" s="370"/>
-      <c r="P32" s="371"/>
+      <c r="C32" s="381"/>
+      <c r="D32" s="381"/>
+      <c r="E32" s="381"/>
+      <c r="F32" s="381"/>
+      <c r="G32" s="381"/>
+      <c r="H32" s="381"/>
+      <c r="I32" s="381"/>
+      <c r="J32" s="381"/>
+      <c r="K32" s="381"/>
+      <c r="L32" s="381"/>
+      <c r="M32" s="381"/>
+      <c r="N32" s="381"/>
+      <c r="O32" s="381"/>
+      <c r="P32" s="382"/>
     </row>
     <row r="33" spans="1:16" ht="20.100000000000001" customHeight="1">
-      <c r="B33" s="367" t="s">
+      <c r="B33" s="375" t="s">
         <v>60</v>
       </c>
-      <c r="C33" s="370"/>
-      <c r="D33" s="370"/>
-      <c r="E33" s="370"/>
-      <c r="F33" s="370"/>
-      <c r="G33" s="370"/>
-      <c r="H33" s="370"/>
-      <c r="I33" s="370"/>
-      <c r="J33" s="370"/>
-      <c r="K33" s="370"/>
-      <c r="L33" s="370"/>
-      <c r="M33" s="370"/>
-      <c r="N33" s="370"/>
-      <c r="O33" s="370"/>
-      <c r="P33" s="371"/>
+      <c r="C33" s="381"/>
+      <c r="D33" s="381"/>
+      <c r="E33" s="381"/>
+      <c r="F33" s="381"/>
+      <c r="G33" s="381"/>
+      <c r="H33" s="381"/>
+      <c r="I33" s="381"/>
+      <c r="J33" s="381"/>
+      <c r="K33" s="381"/>
+      <c r="L33" s="381"/>
+      <c r="M33" s="381"/>
+      <c r="N33" s="381"/>
+      <c r="O33" s="381"/>
+      <c r="P33" s="382"/>
     </row>
     <row r="34" spans="1:16" ht="20.100000000000001" customHeight="1">
-      <c r="B34" s="372" t="s">
+      <c r="B34" s="383" t="s">
         <v>61</v>
       </c>
-      <c r="C34" s="373"/>
-      <c r="D34" s="373"/>
-      <c r="E34" s="373"/>
-      <c r="F34" s="373"/>
-      <c r="G34" s="373"/>
-      <c r="H34" s="373"/>
-      <c r="I34" s="373"/>
-      <c r="J34" s="373"/>
-      <c r="K34" s="373"/>
-      <c r="L34" s="373"/>
-      <c r="M34" s="373"/>
-      <c r="N34" s="373"/>
-      <c r="O34" s="373"/>
-      <c r="P34" s="374"/>
+      <c r="C34" s="384"/>
+      <c r="D34" s="384"/>
+      <c r="E34" s="384"/>
+      <c r="F34" s="384"/>
+      <c r="G34" s="384"/>
+      <c r="H34" s="384"/>
+      <c r="I34" s="384"/>
+      <c r="J34" s="384"/>
+      <c r="K34" s="384"/>
+      <c r="L34" s="384"/>
+      <c r="M34" s="384"/>
+      <c r="N34" s="384"/>
+      <c r="O34" s="384"/>
+      <c r="P34" s="385"/>
     </row>
     <row r="35" spans="1:16" ht="20.100000000000001" customHeight="1"/>
     <row r="39" spans="1:16" ht="15" customHeight="1"/>
@@ -15182,33 +15173,6 @@
     </row>
   </sheetData>
   <mergeCells count="43">
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B29:P29"/>
-    <mergeCell ref="B28:P28"/>
-    <mergeCell ref="B30:P30"/>
-    <mergeCell ref="B31:P31"/>
-    <mergeCell ref="B32:P32"/>
-    <mergeCell ref="B33:P33"/>
-    <mergeCell ref="B34:P34"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="M6:M7"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="E3:H3"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="L6:L7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
     <mergeCell ref="N6:N7"/>
     <mergeCell ref="O6:O7"/>
     <mergeCell ref="P6:P7"/>
@@ -15225,6 +15189,33 @@
     <mergeCell ref="G6:G7"/>
     <mergeCell ref="H6:H7"/>
     <mergeCell ref="I6:I7"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="M6:M7"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="B31:P31"/>
+    <mergeCell ref="B32:P32"/>
+    <mergeCell ref="B33:P33"/>
+    <mergeCell ref="B34:P34"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B29:P29"/>
+    <mergeCell ref="B28:P28"/>
+    <mergeCell ref="B30:P30"/>
   </mergeCells>
   <conditionalFormatting sqref="E8:N21 B23:B26">
     <cfRule type="containsText" dxfId="14" priority="1" operator="containsText" text="I">
@@ -15276,20 +15267,20 @@
   <sheetData>
     <row r="1" spans="1:25" ht="33" customHeight="1" thickBot="1">
       <c r="A1" s="115"/>
-      <c r="B1" s="395" t="s">
+      <c r="B1" s="411" t="s">
         <v>111</v>
       </c>
-      <c r="C1" s="396"/>
-      <c r="D1" s="396"/>
-      <c r="E1" s="396"/>
-      <c r="F1" s="396"/>
-      <c r="G1" s="396"/>
-      <c r="H1" s="396"/>
-      <c r="I1" s="396"/>
-      <c r="J1" s="396"/>
-      <c r="K1" s="396"/>
-      <c r="L1" s="396"/>
-      <c r="M1" s="397"/>
+      <c r="C1" s="412"/>
+      <c r="D1" s="412"/>
+      <c r="E1" s="412"/>
+      <c r="F1" s="412"/>
+      <c r="G1" s="412"/>
+      <c r="H1" s="412"/>
+      <c r="I1" s="412"/>
+      <c r="J1" s="412"/>
+      <c r="K1" s="412"/>
+      <c r="L1" s="412"/>
+      <c r="M1" s="413"/>
       <c r="N1" s="115"/>
       <c r="O1" s="115"/>
       <c r="P1" s="115"/>
@@ -15313,16 +15304,16 @@
       <c r="E2" s="130" t="s">
         <v>112</v>
       </c>
-      <c r="F2" s="398"/>
-      <c r="G2" s="398"/>
-      <c r="H2" s="398"/>
+      <c r="F2" s="414"/>
+      <c r="G2" s="414"/>
+      <c r="H2" s="414"/>
       <c r="I2" s="132" t="s">
         <v>113</v>
       </c>
-      <c r="J2" s="399">
+      <c r="J2" s="415">
         <v>46173</v>
       </c>
-      <c r="K2" s="399"/>
+      <c r="K2" s="415"/>
       <c r="L2" s="133"/>
       <c r="M2" s="117"/>
       <c r="N2" s="115"/>
@@ -15383,18 +15374,18 @@
       <c r="C4" s="133"/>
       <c r="D4" s="133"/>
       <c r="E4" s="133"/>
-      <c r="F4" s="400" t="s">
+      <c r="F4" s="416" t="s">
         <v>118</v>
       </c>
-      <c r="G4" s="400"/>
-      <c r="H4" s="400"/>
+      <c r="G4" s="416"/>
+      <c r="H4" s="416"/>
       <c r="I4" s="133"/>
       <c r="J4" s="133"/>
-      <c r="K4" s="401" t="s">
+      <c r="K4" s="417" t="s">
         <v>137</v>
       </c>
-      <c r="L4" s="401"/>
-      <c r="M4" s="402"/>
+      <c r="L4" s="417"/>
+      <c r="M4" s="418"/>
       <c r="N4" s="115"/>
       <c r="O4" s="115"/>
       <c r="P4" s="115"/>
@@ -15451,10 +15442,10 @@
         <v>126</v>
       </c>
       <c r="N5" s="115"/>
-      <c r="O5" s="378" t="s">
+      <c r="O5" s="419" t="s">
         <v>131</v>
       </c>
-      <c r="P5" s="379"/>
+      <c r="P5" s="420"/>
       <c r="Q5" s="139" t="str">
         <f>Y$7</f>
         <v>Very Low</v>
@@ -15525,7 +15516,7 @@
         <v>Severe</v>
       </c>
       <c r="N6" s="115"/>
-      <c r="O6" s="380" t="s">
+      <c r="O6" s="408" t="s">
         <v>121</v>
       </c>
       <c r="P6" s="140" t="str">
@@ -15597,7 +15588,7 @@
         <v>Moderate</v>
       </c>
       <c r="N7" s="115"/>
-      <c r="O7" s="381"/>
+      <c r="O7" s="409"/>
       <c r="P7" s="140" t="str">
         <f>X$4</f>
         <v>High</v>
@@ -15667,7 +15658,7 @@
         <v>Moderate</v>
       </c>
       <c r="N8" s="115"/>
-      <c r="O8" s="381"/>
+      <c r="O8" s="409"/>
       <c r="P8" s="140" t="str">
         <f>X$5</f>
         <v>Medium</v>
@@ -15733,7 +15724,7 @@
         <v>Moderate</v>
       </c>
       <c r="N9" s="115"/>
-      <c r="O9" s="381"/>
+      <c r="O9" s="409"/>
       <c r="P9" s="140" t="str">
         <f>X$6</f>
         <v>Low</v>
@@ -15799,7 +15790,7 @@
         <v>Moderate</v>
       </c>
       <c r="N10" s="115"/>
-      <c r="O10" s="382"/>
+      <c r="O10" s="410"/>
       <c r="P10" s="151" t="str">
         <f>X$7</f>
         <v>Very Low</v>
@@ -15920,10 +15911,10 @@
         <v>Moderate</v>
       </c>
       <c r="N12" s="115"/>
-      <c r="O12" s="378" t="s">
+      <c r="O12" s="419" t="s">
         <v>131</v>
       </c>
-      <c r="P12" s="379"/>
+      <c r="P12" s="420"/>
       <c r="Q12" s="139" t="str">
         <f>Y$7</f>
         <v>Very Low</v>
@@ -15990,7 +15981,7 @@
         <v>Sustainable</v>
       </c>
       <c r="N13" s="115"/>
-      <c r="O13" s="380" t="s">
+      <c r="O13" s="408" t="s">
         <v>121</v>
       </c>
       <c r="P13" s="140" t="str">
@@ -16063,7 +16054,7 @@
         <v>Moderate</v>
       </c>
       <c r="N14" s="115"/>
-      <c r="O14" s="381"/>
+      <c r="O14" s="409"/>
       <c r="P14" s="140" t="str">
         <f>X$4</f>
         <v>High</v>
@@ -16134,7 +16125,7 @@
         <v>Severe</v>
       </c>
       <c r="N15" s="115"/>
-      <c r="O15" s="381"/>
+      <c r="O15" s="409"/>
       <c r="P15" s="140" t="str">
         <f>X$5</f>
         <v>Medium</v>
@@ -16177,7 +16168,7 @@
       <c r="K16" s="115"/>
       <c r="L16" s="115"/>
       <c r="N16" s="115"/>
-      <c r="O16" s="381"/>
+      <c r="O16" s="409"/>
       <c r="P16" s="140" t="str">
         <f>X$6</f>
         <v>Low</v>
@@ -16209,22 +16200,22 @@
     </row>
     <row r="17" spans="1:25" ht="42" customHeight="1" thickBot="1">
       <c r="A17" s="115"/>
-      <c r="B17" s="383" t="s">
+      <c r="B17" s="421" t="s">
         <v>141</v>
       </c>
-      <c r="C17" s="384"/>
-      <c r="D17" s="384"/>
-      <c r="E17" s="384"/>
-      <c r="F17" s="384"/>
-      <c r="G17" s="384"/>
-      <c r="H17" s="385"/>
-      <c r="I17" s="384"/>
-      <c r="J17" s="384"/>
-      <c r="K17" s="384"/>
-      <c r="L17" s="384"/>
-      <c r="M17" s="386"/>
+      <c r="C17" s="422"/>
+      <c r="D17" s="422"/>
+      <c r="E17" s="422"/>
+      <c r="F17" s="422"/>
+      <c r="G17" s="422"/>
+      <c r="H17" s="423"/>
+      <c r="I17" s="422"/>
+      <c r="J17" s="422"/>
+      <c r="K17" s="422"/>
+      <c r="L17" s="422"/>
+      <c r="M17" s="424"/>
       <c r="N17" s="115"/>
-      <c r="O17" s="382"/>
+      <c r="O17" s="410"/>
       <c r="P17" s="151" t="str">
         <f>X$7</f>
         <v>Very Low</v>
@@ -16256,20 +16247,20 @@
     </row>
     <row r="18" spans="1:25">
       <c r="A18" s="115"/>
-      <c r="B18" s="387" t="s">
+      <c r="B18" s="425" t="s">
         <v>142</v>
       </c>
-      <c r="C18" s="388"/>
-      <c r="D18" s="388"/>
-      <c r="E18" s="388"/>
-      <c r="F18" s="388"/>
-      <c r="G18" s="388"/>
-      <c r="H18" s="389"/>
-      <c r="I18" s="388"/>
-      <c r="J18" s="388"/>
-      <c r="K18" s="388"/>
-      <c r="L18" s="388"/>
-      <c r="M18" s="390"/>
+      <c r="C18" s="426"/>
+      <c r="D18" s="426"/>
+      <c r="E18" s="426"/>
+      <c r="F18" s="426"/>
+      <c r="G18" s="426"/>
+      <c r="H18" s="427"/>
+      <c r="I18" s="426"/>
+      <c r="J18" s="426"/>
+      <c r="K18" s="426"/>
+      <c r="L18" s="426"/>
+      <c r="M18" s="428"/>
       <c r="N18" s="115"/>
       <c r="O18" s="115"/>
       <c r="P18" s="115"/>
@@ -16285,20 +16276,20 @@
     </row>
     <row r="19" spans="1:25" ht="19.5" thickBot="1">
       <c r="A19" s="115"/>
-      <c r="B19" s="387" t="s">
+      <c r="B19" s="425" t="s">
         <v>143</v>
       </c>
-      <c r="C19" s="388"/>
-      <c r="D19" s="388"/>
-      <c r="E19" s="388"/>
-      <c r="F19" s="388"/>
-      <c r="G19" s="388"/>
-      <c r="H19" s="389"/>
-      <c r="I19" s="388"/>
-      <c r="J19" s="388"/>
-      <c r="K19" s="388"/>
-      <c r="L19" s="388"/>
-      <c r="M19" s="390"/>
+      <c r="C19" s="426"/>
+      <c r="D19" s="426"/>
+      <c r="E19" s="426"/>
+      <c r="F19" s="426"/>
+      <c r="G19" s="426"/>
+      <c r="H19" s="427"/>
+      <c r="I19" s="426"/>
+      <c r="J19" s="426"/>
+      <c r="K19" s="426"/>
+      <c r="L19" s="426"/>
+      <c r="M19" s="428"/>
       <c r="N19" s="115"/>
       <c r="O19" s="138" t="s">
         <v>139</v>
@@ -16316,25 +16307,25 @@
     </row>
     <row r="20" spans="1:25" ht="42" customHeight="1" thickBot="1">
       <c r="A20" s="115"/>
-      <c r="B20" s="387" t="s">
+      <c r="B20" s="425" t="s">
         <v>144</v>
       </c>
-      <c r="C20" s="388"/>
-      <c r="D20" s="388"/>
-      <c r="E20" s="388"/>
-      <c r="F20" s="388"/>
-      <c r="G20" s="388"/>
-      <c r="H20" s="389"/>
-      <c r="I20" s="388"/>
-      <c r="J20" s="388"/>
-      <c r="K20" s="388"/>
-      <c r="L20" s="388"/>
-      <c r="M20" s="390"/>
+      <c r="C20" s="426"/>
+      <c r="D20" s="426"/>
+      <c r="E20" s="426"/>
+      <c r="F20" s="426"/>
+      <c r="G20" s="426"/>
+      <c r="H20" s="427"/>
+      <c r="I20" s="426"/>
+      <c r="J20" s="426"/>
+      <c r="K20" s="426"/>
+      <c r="L20" s="426"/>
+      <c r="M20" s="428"/>
       <c r="N20" s="115"/>
-      <c r="O20" s="378" t="s">
+      <c r="O20" s="419" t="s">
         <v>131</v>
       </c>
-      <c r="P20" s="379"/>
+      <c r="P20" s="420"/>
       <c r="Q20" s="139" t="str">
         <f>Y$7</f>
         <v>Very Low</v>
@@ -16362,22 +16353,22 @@
     </row>
     <row r="21" spans="1:25" ht="42" customHeight="1" thickBot="1">
       <c r="A21" s="115"/>
-      <c r="B21" s="387" t="s">
+      <c r="B21" s="425" t="s">
         <v>145</v>
       </c>
-      <c r="C21" s="388"/>
-      <c r="D21" s="388"/>
-      <c r="E21" s="388"/>
-      <c r="F21" s="388"/>
-      <c r="G21" s="388"/>
-      <c r="H21" s="389"/>
-      <c r="I21" s="388"/>
-      <c r="J21" s="388"/>
-      <c r="K21" s="388"/>
-      <c r="L21" s="388"/>
-      <c r="M21" s="390"/>
+      <c r="C21" s="426"/>
+      <c r="D21" s="426"/>
+      <c r="E21" s="426"/>
+      <c r="F21" s="426"/>
+      <c r="G21" s="426"/>
+      <c r="H21" s="427"/>
+      <c r="I21" s="426"/>
+      <c r="J21" s="426"/>
+      <c r="K21" s="426"/>
+      <c r="L21" s="426"/>
+      <c r="M21" s="428"/>
       <c r="N21" s="115"/>
-      <c r="O21" s="380" t="s">
+      <c r="O21" s="408" t="s">
         <v>121</v>
       </c>
       <c r="P21" s="140" t="str">
@@ -16411,22 +16402,22 @@
     </row>
     <row r="22" spans="1:25" ht="42" customHeight="1" thickBot="1">
       <c r="A22" s="115"/>
-      <c r="B22" s="391" t="s">
+      <c r="B22" s="429" t="s">
         <v>146</v>
       </c>
-      <c r="C22" s="392"/>
-      <c r="D22" s="392"/>
-      <c r="E22" s="392"/>
-      <c r="F22" s="392"/>
-      <c r="G22" s="392"/>
-      <c r="H22" s="393"/>
-      <c r="I22" s="392"/>
-      <c r="J22" s="392"/>
-      <c r="K22" s="392"/>
-      <c r="L22" s="392"/>
-      <c r="M22" s="394"/>
+      <c r="C22" s="430"/>
+      <c r="D22" s="430"/>
+      <c r="E22" s="430"/>
+      <c r="F22" s="430"/>
+      <c r="G22" s="430"/>
+      <c r="H22" s="431"/>
+      <c r="I22" s="430"/>
+      <c r="J22" s="430"/>
+      <c r="K22" s="430"/>
+      <c r="L22" s="430"/>
+      <c r="M22" s="432"/>
       <c r="N22" s="115"/>
-      <c r="O22" s="381"/>
+      <c r="O22" s="409"/>
       <c r="P22" s="140" t="str">
         <f>X$4</f>
         <v>High</v>
@@ -16469,7 +16460,7 @@
       <c r="K23" s="115"/>
       <c r="L23" s="115"/>
       <c r="N23" s="115"/>
-      <c r="O23" s="381"/>
+      <c r="O23" s="409"/>
       <c r="P23" s="140" t="str">
         <f>X$5</f>
         <v>Medium</v>
@@ -16512,7 +16503,7 @@
       <c r="K24" s="115"/>
       <c r="L24" s="115"/>
       <c r="N24" s="115"/>
-      <c r="O24" s="381"/>
+      <c r="O24" s="409"/>
       <c r="P24" s="140" t="str">
         <f>X$6</f>
         <v>Low</v>
@@ -16555,7 +16546,7 @@
       <c r="K25" s="115"/>
       <c r="L25" s="115"/>
       <c r="N25" s="115"/>
-      <c r="O25" s="382"/>
+      <c r="O25" s="410"/>
       <c r="P25" s="151" t="str">
         <f>X$7</f>
         <v>Very Low</v>
@@ -40962,13 +40953,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="O6:O10"/>
-    <mergeCell ref="B1:M1"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="O5:P5"/>
     <mergeCell ref="O12:P12"/>
     <mergeCell ref="O13:O17"/>
     <mergeCell ref="O20:P20"/>
@@ -40979,6 +40963,13 @@
     <mergeCell ref="B20:M20"/>
     <mergeCell ref="B21:M21"/>
     <mergeCell ref="B22:M22"/>
+    <mergeCell ref="O6:O10"/>
+    <mergeCell ref="B1:M1"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="O5:P5"/>
   </mergeCells>
   <conditionalFormatting sqref="H6:H15">
     <cfRule type="containsText" dxfId="10" priority="13" operator="containsText" text="Sustainable">
@@ -41036,69 +41027,69 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13" ht="24" customHeight="1">
-      <c r="B1" s="403" t="s">
+      <c r="B1" s="433" t="s">
         <v>185</v>
       </c>
-      <c r="C1" s="403"/>
-      <c r="D1" s="403"/>
-      <c r="E1" s="403"/>
-      <c r="F1" s="403"/>
-      <c r="G1" s="403"/>
-      <c r="H1" s="403"/>
-      <c r="I1" s="403"/>
-      <c r="J1" s="403"/>
+      <c r="C1" s="433"/>
+      <c r="D1" s="433"/>
+      <c r="E1" s="433"/>
+      <c r="F1" s="433"/>
+      <c r="G1" s="433"/>
+      <c r="H1" s="433"/>
+      <c r="I1" s="433"/>
+      <c r="J1" s="433"/>
     </row>
     <row r="2" spans="2:13" ht="24" customHeight="1">
-      <c r="B2" s="403"/>
-      <c r="C2" s="403"/>
-      <c r="D2" s="403"/>
-      <c r="E2" s="403"/>
-      <c r="F2" s="403"/>
-      <c r="G2" s="403"/>
-      <c r="H2" s="403"/>
-      <c r="I2" s="403"/>
-      <c r="J2" s="403"/>
+      <c r="B2" s="433"/>
+      <c r="C2" s="433"/>
+      <c r="D2" s="433"/>
+      <c r="E2" s="433"/>
+      <c r="F2" s="433"/>
+      <c r="G2" s="433"/>
+      <c r="H2" s="433"/>
+      <c r="I2" s="433"/>
+      <c r="J2" s="433"/>
     </row>
     <row r="3" spans="2:13" ht="24" customHeight="1" thickBot="1">
-      <c r="B3" s="404"/>
-      <c r="C3" s="403"/>
-      <c r="D3" s="403"/>
-      <c r="E3" s="403"/>
-      <c r="F3" s="403"/>
-      <c r="G3" s="403"/>
-      <c r="H3" s="403"/>
-      <c r="I3" s="403"/>
-      <c r="J3" s="405"/>
+      <c r="B3" s="434"/>
+      <c r="C3" s="433"/>
+      <c r="D3" s="433"/>
+      <c r="E3" s="433"/>
+      <c r="F3" s="433"/>
+      <c r="G3" s="433"/>
+      <c r="H3" s="433"/>
+      <c r="I3" s="433"/>
+      <c r="J3" s="435"/>
     </row>
     <row r="4" spans="2:13" ht="24" customHeight="1" thickBot="1">
       <c r="B4" s="161"/>
       <c r="C4" s="162" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="418" t="s">
+      <c r="D4" s="448" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="419"/>
+      <c r="E4" s="449"/>
       <c r="F4" s="163"/>
       <c r="G4" s="162" t="s">
         <v>186</v>
       </c>
-      <c r="H4" s="418" t="s">
+      <c r="H4" s="448" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="419"/>
+      <c r="I4" s="449"/>
       <c r="J4" s="164"/>
     </row>
     <row r="5" spans="2:13" ht="24" customHeight="1" thickBot="1">
-      <c r="B5" s="406"/>
-      <c r="C5" s="407"/>
-      <c r="D5" s="407"/>
-      <c r="E5" s="407"/>
-      <c r="F5" s="407"/>
-      <c r="G5" s="407"/>
-      <c r="H5" s="407"/>
-      <c r="I5" s="407"/>
-      <c r="J5" s="408"/>
+      <c r="B5" s="436"/>
+      <c r="C5" s="437"/>
+      <c r="D5" s="437"/>
+      <c r="E5" s="437"/>
+      <c r="F5" s="437"/>
+      <c r="G5" s="437"/>
+      <c r="H5" s="437"/>
+      <c r="I5" s="437"/>
+      <c r="J5" s="438"/>
     </row>
     <row r="6" spans="2:13" ht="45.75" customHeight="1">
       <c r="B6" s="165" t="s">
@@ -41497,50 +41488,50 @@
     </row>
     <row r="23" spans="2:10" ht="15.75" thickBot="1"/>
     <row r="24" spans="2:10" ht="16.5" thickBot="1">
-      <c r="B24" s="415" t="s">
+      <c r="B24" s="445" t="s">
         <v>264</v>
       </c>
-      <c r="C24" s="416"/>
-      <c r="D24" s="416"/>
-      <c r="E24" s="416"/>
-      <c r="F24" s="417"/>
+      <c r="C24" s="446"/>
+      <c r="D24" s="446"/>
+      <c r="E24" s="446"/>
+      <c r="F24" s="447"/>
     </row>
     <row r="25" spans="2:10" ht="30" customHeight="1">
-      <c r="B25" s="409" t="s">
+      <c r="B25" s="439" t="s">
         <v>265</v>
       </c>
-      <c r="C25" s="410"/>
-      <c r="D25" s="410"/>
-      <c r="E25" s="410"/>
-      <c r="F25" s="411"/>
+      <c r="C25" s="440"/>
+      <c r="D25" s="440"/>
+      <c r="E25" s="440"/>
+      <c r="F25" s="441"/>
     </row>
     <row r="26" spans="2:10" ht="30" customHeight="1">
-      <c r="B26" s="409"/>
-      <c r="C26" s="410"/>
-      <c r="D26" s="410"/>
-      <c r="E26" s="410"/>
-      <c r="F26" s="411"/>
+      <c r="B26" s="439"/>
+      <c r="C26" s="440"/>
+      <c r="D26" s="440"/>
+      <c r="E26" s="440"/>
+      <c r="F26" s="441"/>
     </row>
     <row r="27" spans="2:10" ht="30" customHeight="1">
-      <c r="B27" s="409"/>
-      <c r="C27" s="410"/>
-      <c r="D27" s="410"/>
-      <c r="E27" s="410"/>
-      <c r="F27" s="411"/>
+      <c r="B27" s="439"/>
+      <c r="C27" s="440"/>
+      <c r="D27" s="440"/>
+      <c r="E27" s="440"/>
+      <c r="F27" s="441"/>
     </row>
     <row r="28" spans="2:10" ht="30" customHeight="1">
-      <c r="B28" s="409"/>
-      <c r="C28" s="410"/>
-      <c r="D28" s="410"/>
-      <c r="E28" s="410"/>
-      <c r="F28" s="411"/>
+      <c r="B28" s="439"/>
+      <c r="C28" s="440"/>
+      <c r="D28" s="440"/>
+      <c r="E28" s="440"/>
+      <c r="F28" s="441"/>
     </row>
     <row r="29" spans="2:10" ht="30" customHeight="1" thickBot="1">
-      <c r="B29" s="412"/>
-      <c r="C29" s="413"/>
-      <c r="D29" s="413"/>
-      <c r="E29" s="413"/>
-      <c r="F29" s="414"/>
+      <c r="B29" s="442"/>
+      <c r="C29" s="443"/>
+      <c r="D29" s="443"/>
+      <c r="E29" s="443"/>
+      <c r="F29" s="444"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -41579,23 +41570,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="23.25" customHeight="1">
-      <c r="A1" s="403" t="s">
+      <c r="A1" s="433" t="s">
         <v>266</v>
       </c>
-      <c r="B1" s="403"/>
-      <c r="C1" s="403"/>
-      <c r="D1" s="403"/>
-      <c r="E1" s="403"/>
-      <c r="F1" s="403"/>
-      <c r="G1" s="403"/>
-      <c r="H1" s="403"/>
-      <c r="I1" s="403"/>
-      <c r="J1" s="403"/>
-      <c r="K1" s="403"/>
-      <c r="L1" s="403"/>
-      <c r="M1" s="403"/>
-      <c r="N1" s="403"/>
-      <c r="O1" s="403"/>
+      <c r="B1" s="433"/>
+      <c r="C1" s="433"/>
+      <c r="D1" s="433"/>
+      <c r="E1" s="433"/>
+      <c r="F1" s="433"/>
+      <c r="G1" s="433"/>
+      <c r="H1" s="433"/>
+      <c r="I1" s="433"/>
+      <c r="J1" s="433"/>
+      <c r="K1" s="433"/>
+      <c r="L1" s="433"/>
+      <c r="M1" s="433"/>
+      <c r="N1" s="433"/>
+      <c r="O1" s="433"/>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="160"/>
@@ -41631,10 +41622,10 @@
       <c r="J3" s="185" t="s">
         <v>268</v>
       </c>
-      <c r="K3" s="429" t="s">
+      <c r="K3" s="459" t="s">
         <v>15</v>
       </c>
-      <c r="L3" s="429"/>
+      <c r="L3" s="459"/>
       <c r="M3" s="160"/>
       <c r="N3" s="160"/>
       <c r="O3" s="160"/>
@@ -42034,78 +42025,78 @@
     </row>
     <row r="26" spans="2:9" ht="15.75" thickBot="1"/>
     <row r="27" spans="2:9" ht="20.25" customHeight="1" thickBot="1">
-      <c r="B27" s="420" t="s">
+      <c r="B27" s="450" t="s">
         <v>275</v>
       </c>
-      <c r="C27" s="421"/>
-      <c r="D27" s="421"/>
-      <c r="E27" s="421"/>
-      <c r="F27" s="421"/>
-      <c r="G27" s="421"/>
-      <c r="H27" s="421"/>
-      <c r="I27" s="422"/>
+      <c r="C27" s="451"/>
+      <c r="D27" s="451"/>
+      <c r="E27" s="451"/>
+      <c r="F27" s="451"/>
+      <c r="G27" s="451"/>
+      <c r="H27" s="451"/>
+      <c r="I27" s="452"/>
     </row>
     <row r="28" spans="2:9" ht="20.25" customHeight="1">
-      <c r="B28" s="423" t="s">
+      <c r="B28" s="453" t="s">
         <v>276</v>
       </c>
-      <c r="C28" s="424"/>
-      <c r="D28" s="424"/>
-      <c r="E28" s="424"/>
-      <c r="F28" s="424"/>
-      <c r="G28" s="424"/>
-      <c r="H28" s="424"/>
-      <c r="I28" s="425"/>
+      <c r="C28" s="454"/>
+      <c r="D28" s="454"/>
+      <c r="E28" s="454"/>
+      <c r="F28" s="454"/>
+      <c r="G28" s="454"/>
+      <c r="H28" s="454"/>
+      <c r="I28" s="455"/>
     </row>
     <row r="29" spans="2:9" ht="20.25" customHeight="1">
-      <c r="B29" s="423"/>
-      <c r="C29" s="424"/>
-      <c r="D29" s="424"/>
-      <c r="E29" s="424"/>
-      <c r="F29" s="424"/>
-      <c r="G29" s="424"/>
-      <c r="H29" s="424"/>
-      <c r="I29" s="425"/>
+      <c r="B29" s="453"/>
+      <c r="C29" s="454"/>
+      <c r="D29" s="454"/>
+      <c r="E29" s="454"/>
+      <c r="F29" s="454"/>
+      <c r="G29" s="454"/>
+      <c r="H29" s="454"/>
+      <c r="I29" s="455"/>
     </row>
     <row r="30" spans="2:9" ht="20.25" customHeight="1">
-      <c r="B30" s="423"/>
-      <c r="C30" s="424"/>
-      <c r="D30" s="424"/>
-      <c r="E30" s="424"/>
-      <c r="F30" s="424"/>
-      <c r="G30" s="424"/>
-      <c r="H30" s="424"/>
-      <c r="I30" s="425"/>
+      <c r="B30" s="453"/>
+      <c r="C30" s="454"/>
+      <c r="D30" s="454"/>
+      <c r="E30" s="454"/>
+      <c r="F30" s="454"/>
+      <c r="G30" s="454"/>
+      <c r="H30" s="454"/>
+      <c r="I30" s="455"/>
     </row>
     <row r="31" spans="2:9" ht="20.25" customHeight="1">
-      <c r="B31" s="423"/>
-      <c r="C31" s="424"/>
-      <c r="D31" s="424"/>
-      <c r="E31" s="424"/>
-      <c r="F31" s="424"/>
-      <c r="G31" s="424"/>
-      <c r="H31" s="424"/>
-      <c r="I31" s="425"/>
+      <c r="B31" s="453"/>
+      <c r="C31" s="454"/>
+      <c r="D31" s="454"/>
+      <c r="E31" s="454"/>
+      <c r="F31" s="454"/>
+      <c r="G31" s="454"/>
+      <c r="H31" s="454"/>
+      <c r="I31" s="455"/>
     </row>
     <row r="32" spans="2:9" ht="20.25" customHeight="1">
-      <c r="B32" s="423"/>
-      <c r="C32" s="424"/>
-      <c r="D32" s="424"/>
-      <c r="E32" s="424"/>
-      <c r="F32" s="424"/>
-      <c r="G32" s="424"/>
-      <c r="H32" s="424"/>
-      <c r="I32" s="425"/>
+      <c r="B32" s="453"/>
+      <c r="C32" s="454"/>
+      <c r="D32" s="454"/>
+      <c r="E32" s="454"/>
+      <c r="F32" s="454"/>
+      <c r="G32" s="454"/>
+      <c r="H32" s="454"/>
+      <c r="I32" s="455"/>
     </row>
     <row r="33" spans="2:9" ht="66" customHeight="1" thickBot="1">
-      <c r="B33" s="426"/>
-      <c r="C33" s="427"/>
-      <c r="D33" s="427"/>
-      <c r="E33" s="427"/>
-      <c r="F33" s="427"/>
-      <c r="G33" s="427"/>
-      <c r="H33" s="427"/>
-      <c r="I33" s="428"/>
+      <c r="B33" s="456"/>
+      <c r="C33" s="457"/>
+      <c r="D33" s="457"/>
+      <c r="E33" s="457"/>
+      <c r="F33" s="457"/>
+      <c r="G33" s="457"/>
+      <c r="H33" s="457"/>
+      <c r="I33" s="458"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -42151,28 +42142,28 @@
       <c r="I1"/>
     </row>
     <row r="2" spans="2:9" ht="30" customHeight="1" thickBot="1">
-      <c r="B2" s="433" t="s">
+      <c r="B2" s="463" t="s">
         <v>333</v>
       </c>
-      <c r="C2" s="434"/>
-      <c r="D2" s="434"/>
-      <c r="E2" s="434"/>
-      <c r="F2" s="434"/>
-      <c r="G2" s="434"/>
-      <c r="H2" s="434"/>
-      <c r="I2" s="435"/>
+      <c r="C2" s="464"/>
+      <c r="D2" s="464"/>
+      <c r="E2" s="464"/>
+      <c r="F2" s="464"/>
+      <c r="G2" s="464"/>
+      <c r="H2" s="464"/>
+      <c r="I2" s="465"/>
     </row>
     <row r="3" spans="2:9">
-      <c r="B3" s="436" t="s">
+      <c r="B3" s="466" t="s">
         <v>334</v>
       </c>
-      <c r="C3" s="437"/>
-      <c r="D3" s="437"/>
-      <c r="E3" s="437"/>
-      <c r="F3" s="437"/>
-      <c r="G3" s="437"/>
-      <c r="H3" s="437"/>
-      <c r="I3" s="438"/>
+      <c r="C3" s="467"/>
+      <c r="D3" s="467"/>
+      <c r="E3" s="467"/>
+      <c r="F3" s="467"/>
+      <c r="G3" s="467"/>
+      <c r="H3" s="467"/>
+      <c r="I3" s="468"/>
     </row>
     <row r="4" spans="2:9" ht="15.75" thickBot="1">
       <c r="B4" s="229"/>
@@ -42474,17 +42465,17 @@
       <c r="I16" s="203"/>
     </row>
     <row r="17" spans="2:9">
-      <c r="B17" s="439" t="s">
+      <c r="B17" s="469" t="s">
         <v>342</v>
       </c>
-      <c r="C17" s="440"/>
-      <c r="D17" s="441"/>
-      <c r="F17" s="442" t="s">
+      <c r="C17" s="470"/>
+      <c r="D17" s="471"/>
+      <c r="F17" s="472" t="s">
         <v>358</v>
       </c>
-      <c r="G17" s="443"/>
-      <c r="H17" s="443"/>
-      <c r="I17" s="444"/>
+      <c r="G17" s="473"/>
+      <c r="H17" s="473"/>
+      <c r="I17" s="474"/>
     </row>
     <row r="18" spans="2:9">
       <c r="B18" s="204" t="s">
@@ -42615,28 +42606,28 @@
       <c r="I24" s="230"/>
     </row>
     <row r="25" spans="2:9" ht="16.5" thickBot="1">
-      <c r="B25" s="445" t="s">
+      <c r="B25" s="475" t="s">
         <v>368</v>
       </c>
-      <c r="C25" s="446"/>
-      <c r="D25" s="446"/>
-      <c r="E25" s="446"/>
-      <c r="F25" s="446"/>
-      <c r="G25" s="446"/>
-      <c r="H25" s="446"/>
-      <c r="I25" s="447"/>
+      <c r="C25" s="476"/>
+      <c r="D25" s="476"/>
+      <c r="E25" s="476"/>
+      <c r="F25" s="476"/>
+      <c r="G25" s="476"/>
+      <c r="H25" s="476"/>
+      <c r="I25" s="477"/>
     </row>
     <row r="26" spans="2:9" ht="151.5" customHeight="1" thickBot="1">
-      <c r="B26" s="430" t="s">
+      <c r="B26" s="460" t="s">
         <v>369</v>
       </c>
-      <c r="C26" s="431"/>
-      <c r="D26" s="431"/>
-      <c r="E26" s="431"/>
-      <c r="F26" s="431"/>
-      <c r="G26" s="431"/>
-      <c r="H26" s="431"/>
-      <c r="I26" s="432"/>
+      <c r="C26" s="461"/>
+      <c r="D26" s="461"/>
+      <c r="E26" s="461"/>
+      <c r="F26" s="461"/>
+      <c r="G26" s="461"/>
+      <c r="H26" s="461"/>
+      <c r="I26" s="462"/>
     </row>
   </sheetData>
   <mergeCells count="6">
